--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P640"/>
+  <dimension ref="A1:P649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37059,16 +37059,16 @@
         <v>10.38768</v>
       </c>
       <c r="M632" t="n">
-        <v>0.02624371745869324</v>
+        <v>0.0262437174586932</v>
       </c>
       <c r="N632" t="n">
-        <v>0.02881581244168899</v>
+        <v>0.0288158124416889</v>
       </c>
       <c r="O632" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P632" t="n">
-        <v>-0.02093418660463669</v>
+        <v>-0.0209341866046366</v>
       </c>
     </row>
     <row r="633">
@@ -37117,16 +37117,16 @@
         <v>20.398724</v>
       </c>
       <c r="M633" t="n">
-        <v>0.007614360723073645</v>
+        <v>0.0076143607230736</v>
       </c>
       <c r="N633" t="n">
         <v>0.0300515180284037</v>
       </c>
       <c r="O633" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P633" t="n">
-        <v>-0.01969848101792198</v>
+        <v>-0.0196984810179219</v>
       </c>
     </row>
     <row r="634">
@@ -37175,16 +37175,16 @@
         <v>3.5706854</v>
       </c>
       <c r="M634" t="n">
-        <v>0.048368252979204</v>
+        <v>0.0483682529792039</v>
       </c>
       <c r="N634" t="n">
-        <v>0.04051674585248073</v>
+        <v>0.0405167458524807</v>
       </c>
       <c r="O634" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P634" t="n">
-        <v>-0.009233253193844951</v>
+        <v>-0.0092332531938449</v>
       </c>
     </row>
     <row r="635">
@@ -37233,16 +37233,16 @@
         <v>19.39314</v>
       </c>
       <c r="M635" t="n">
-        <v>0.02163043177988342</v>
+        <v>0.0216304317798834</v>
       </c>
       <c r="N635" t="n">
-        <v>0.05354819193900384</v>
+        <v>0.0535481919390038</v>
       </c>
       <c r="O635" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P635" t="n">
-        <v>0.003798192892678159</v>
+        <v>0.0037981928926781</v>
       </c>
     </row>
     <row r="636">
@@ -37291,16 +37291,16 @@
         <v>9.201266</v>
       </c>
       <c r="M636" t="n">
-        <v>0.05938291846772992</v>
+        <v>0.0593829184677299</v>
       </c>
       <c r="N636" t="n">
         <v>0.0443399314353853</v>
       </c>
       <c r="O636" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P636" t="n">
-        <v>-0.005410067610940379</v>
+        <v>-0.0054100676109403</v>
       </c>
     </row>
     <row r="637">
@@ -37349,16 +37349,16 @@
         <v>7.232781</v>
       </c>
       <c r="M637" t="n">
-        <v>0.04097032544789593</v>
+        <v>0.0409703254478959</v>
       </c>
       <c r="N637" t="n">
-        <v>0.05394759501874914</v>
+        <v>0.0539475950187491</v>
       </c>
       <c r="O637" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P637" t="n">
-        <v>0.004197595972423453</v>
+        <v>0.0041975959724234</v>
       </c>
     </row>
     <row r="638">
@@ -37410,13 +37410,13 @@
         <v>0.0362568851764421</v>
       </c>
       <c r="N638" t="n">
-        <v>0.04756164881060469</v>
+        <v>0.0475616488106046</v>
       </c>
       <c r="O638" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P638" t="n">
-        <v>-0.002188350235720997</v>
+        <v>-0.0021883502357209</v>
       </c>
     </row>
     <row r="639">
@@ -37465,16 +37465,16 @@
         <v>6.662887</v>
       </c>
       <c r="M639" t="n">
-        <v>0.04108527131782946</v>
+        <v>0.0410852713178294</v>
       </c>
       <c r="N639" t="n">
         <v>0.0493657622739018</v>
       </c>
       <c r="O639" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P639" t="n">
-        <v>-0.0003842367724238779</v>
+        <v>-0.0003842367724238</v>
       </c>
     </row>
     <row r="640">
@@ -37523,16 +37523,538 @@
         <v>17.39792</v>
       </c>
       <c r="M640" t="n">
-        <v>0.03619038893215448</v>
+        <v>0.0361903889321544</v>
       </c>
       <c r="N640" t="n">
-        <v>0.07131581840670667</v>
+        <v>0.0713158184067066</v>
       </c>
       <c r="O640" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.0497499990463256</v>
       </c>
       <c r="P640" t="n">
-        <v>0.02156581936038099</v>
+        <v>0.0215658193603809</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>333.08</v>
+      </c>
+      <c r="F641" t="n">
+        <v>4861029515264</v>
+      </c>
+      <c r="G641" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H641" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I641" t="n">
+        <v>38.2411</v>
+      </c>
+      <c r="J641" t="n">
+        <v>34.757923</v>
+      </c>
+      <c r="K641" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L641" t="n">
+        <v>10.413004</v>
+      </c>
+      <c r="M641" t="n">
+        <v>0.02614987390416717</v>
+      </c>
+      <c r="N641" t="n">
+        <v>0.028770415515792</v>
+      </c>
+      <c r="O641" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P641" t="n">
+        <v>-0.02083958414088525</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>493.41</v>
+      </c>
+      <c r="F642" t="n">
+        <v>805479514112</v>
+      </c>
+      <c r="G642" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H642" t="n">
+        <v>15.51049</v>
+      </c>
+      <c r="I642" t="n">
+        <v>125.869896</v>
+      </c>
+      <c r="J642" t="n">
+        <v>31.811373</v>
+      </c>
+      <c r="K642" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L642" t="n">
+        <v>19.500774</v>
+      </c>
+      <c r="M642" t="n">
+        <v>0.007944711294866338</v>
+      </c>
+      <c r="N642" t="n">
+        <v>0.03143529721732433</v>
+      </c>
+      <c r="O642" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P642" t="n">
+        <v>-0.01817470243935292</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>253.54</v>
+      </c>
+      <c r="F643" t="n">
+        <v>2734761705472</v>
+      </c>
+      <c r="G643" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H643" t="n">
+        <v>10.40389</v>
+      </c>
+      <c r="I643" t="n">
+        <v>20.397425</v>
+      </c>
+      <c r="J643" t="n">
+        <v>24.369732</v>
+      </c>
+      <c r="K643" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L643" t="n">
+        <v>3.5256312</v>
+      </c>
+      <c r="M643" t="n">
+        <v>0.0490257947463911</v>
+      </c>
+      <c r="N643" t="n">
+        <v>0.04103451131971287</v>
+      </c>
+      <c r="O643" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P643" t="n">
+        <v>-0.008575488336964379</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>344.72</v>
+      </c>
+      <c r="F644" t="n">
+        <v>1645565706240</v>
+      </c>
+      <c r="G644" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H644" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I644" t="n">
+        <v>44.025543</v>
+      </c>
+      <c r="J644" t="n">
+        <v>17.783823</v>
+      </c>
+      <c r="K644" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L644" t="n">
+        <v>18.467922</v>
+      </c>
+      <c r="M644" t="n">
+        <v>0.02271408679508006</v>
+      </c>
+      <c r="N644" t="n">
+        <v>0.05623088303550707</v>
+      </c>
+      <c r="O644" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P644" t="n">
+        <v>0.006620883378829823</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="F645" t="n">
+        <v>4228010737664</v>
+      </c>
+      <c r="G645" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H645" t="n">
+        <v>14.87383</v>
+      </c>
+      <c r="I645" t="n">
+        <v>17.34621</v>
+      </c>
+      <c r="J645" t="n">
+        <v>23.242836</v>
+      </c>
+      <c r="K645" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L645" t="n">
+        <v>9.482694</v>
+      </c>
+      <c r="M645" t="n">
+        <v>0.05764947499349166</v>
+      </c>
+      <c r="N645" t="n">
+        <v>0.04302400856208961</v>
+      </c>
+      <c r="O645" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P645" t="n">
+        <v>-0.006585991094587636</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>665.6</v>
+      </c>
+      <c r="F646" t="n">
+        <v>1695620005888</v>
+      </c>
+      <c r="G646" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H646" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I646" t="n">
+        <v>25.050808</v>
+      </c>
+      <c r="J646" t="n">
+        <v>19.039085</v>
+      </c>
+      <c r="K646" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L646" t="n">
+        <v>7.428882</v>
+      </c>
+      <c r="M646" t="n">
+        <v>0.03991887019230769</v>
+      </c>
+      <c r="N646" t="n">
+        <v>0.05252352764423077</v>
+      </c>
+      <c r="O646" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P646" t="n">
+        <v>0.002913527987553517</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>505.41</v>
+      </c>
+      <c r="F647" t="n">
+        <v>3752944992256</v>
+      </c>
+      <c r="G647" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H647" t="n">
+        <v>23.59268</v>
+      </c>
+      <c r="I647" t="n">
+        <v>28.17224</v>
+      </c>
+      <c r="J647" t="n">
+        <v>21.422323</v>
+      </c>
+      <c r="K647" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L647" t="n">
+        <v>11.309535</v>
+      </c>
+      <c r="M647" t="n">
+        <v>0.03549593399418294</v>
+      </c>
+      <c r="N647" t="n">
+        <v>0.04668027937713935</v>
+      </c>
+      <c r="O647" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P647" t="n">
+        <v>-0.002929720279537897</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="F648" t="n">
+        <v>334447640576</v>
+      </c>
+      <c r="G648" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H648" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I648" t="n">
+        <v>25.25786</v>
+      </c>
+      <c r="J648" t="n">
+        <v>21.02117</v>
+      </c>
+      <c r="K648" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L648" t="n">
+        <v>6.9142513</v>
+      </c>
+      <c r="M648" t="n">
+        <v>0.03959163346613546</v>
+      </c>
+      <c r="N648" t="n">
+        <v>0.0475710906374502</v>
+      </c>
+      <c r="O648" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P648" t="n">
+        <v>-0.002038909019227049</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:44:04</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>210.96</v>
+      </c>
+      <c r="F649" t="n">
+        <v>5094050889728</v>
+      </c>
+      <c r="G649" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H649" t="n">
+        <v>15.61489</v>
+      </c>
+      <c r="I649" t="n">
+        <v>26.703798</v>
+      </c>
+      <c r="J649" t="n">
+        <v>13.510182</v>
+      </c>
+      <c r="K649" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L649" t="n">
+        <v>16.813713</v>
+      </c>
+      <c r="M649" t="n">
+        <v>0.03744785741372772</v>
+      </c>
+      <c r="N649" t="n">
+        <v>0.0740182499051953</v>
+      </c>
+      <c r="O649" t="n">
+        <v>0.04960999965667725</v>
+      </c>
+      <c r="P649" t="n">
+        <v>0.02440825024851805</v>
       </c>
     </row>
   </sheetData>
@@ -37634,12 +38156,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -37653,51 +38175,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>335.45</v>
+        <v>345.71</v>
       </c>
       <c r="F2" t="n">
-        <v>4102531842048</v>
+        <v>4228010737664</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
         <v>14.87383</v>
       </c>
       <c r="I2" t="n">
-        <v>16.83986</v>
+        <v>17.34621</v>
       </c>
       <c r="J2" t="n">
-        <v>22.553036</v>
+        <v>23.242836</v>
       </c>
       <c r="K2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="L2" t="n">
-        <v>9.201266</v>
+        <v>9.482694</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05938291846772992</v>
+        <v>0.05764947499349166</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0443399314353853</v>
+        <v>0.04302400856208961</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005410067610940379</v>
+        <v>-0.006585991094587636</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -37711,51 +38233,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="F3" t="n">
-        <v>3680323239936</v>
+        <v>3752944992256</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
-        <v>23.57298</v>
+        <v>23.59268</v>
       </c>
       <c r="I3" t="n">
-        <v>27.580969</v>
+        <v>28.17224</v>
       </c>
       <c r="J3" t="n">
-        <v>21.025343</v>
+        <v>21.422323</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>11.090689</v>
+        <v>11.309535</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0362568851764421</v>
+        <v>0.03549593399418294</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04756164881060469</v>
+        <v>0.04668027937713935</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002188350235720997</v>
+        <v>-0.002929720279537897</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -37769,51 +38291,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>648.03</v>
+        <v>665.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1650860490752</v>
+        <v>1695620005888</v>
       </c>
       <c r="G4" t="n">
-        <v>26.55</v>
+        <v>26.57</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>24.407911</v>
+        <v>25.050808</v>
       </c>
       <c r="J4" t="n">
-        <v>18.536509</v>
+        <v>19.039085</v>
       </c>
       <c r="K4" t="n">
         <v>0.86</v>
       </c>
       <c r="L4" t="n">
-        <v>7.232781</v>
+        <v>7.428882</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04097032544789593</v>
+        <v>0.03991887019230769</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05394759501874914</v>
+        <v>0.05252352764423077</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004197595972423453</v>
+        <v>0.002913527987553517</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -37827,51 +38349,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256.78</v>
+        <v>253.54</v>
       </c>
       <c r="F5" t="n">
-        <v>2769709432832</v>
+        <v>2734761705472</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.40389</v>
       </c>
       <c r="I5" t="n">
-        <v>20.674719</v>
+        <v>20.397425</v>
       </c>
       <c r="J5" t="n">
-        <v>24.681154</v>
+        <v>24.369732</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5706854</v>
+        <v>3.5256312</v>
       </c>
       <c r="M5" t="n">
-        <v>0.048368252979204</v>
+        <v>0.0490257947463911</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04051674585248073</v>
+        <v>0.04103451131971287</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009233253193844951</v>
+        <v>-0.008575488336964379</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -37885,51 +38407,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>332.27</v>
+        <v>333.08</v>
       </c>
       <c r="F6" t="n">
-        <v>4849207869440</v>
+        <v>4861029515264</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.574630000000001</v>
+        <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.104355</v>
+        <v>38.2411</v>
       </c>
       <c r="J6" t="n">
-        <v>34.703167</v>
+        <v>34.757923</v>
       </c>
       <c r="K6" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="L6" t="n">
-        <v>10.38768</v>
+        <v>10.413004</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02624371745869324</v>
+        <v>0.02614987390416717</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02881581244168899</v>
+        <v>0.028770415515792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02093418660463669</v>
+        <v>-0.02083958414088525</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -37943,51 +38465,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>218.29</v>
+        <v>210.96</v>
       </c>
       <c r="F7" t="n">
-        <v>5271048421376</v>
+        <v>5094050889728</v>
       </c>
       <c r="G7" t="n">
         <v>7.9</v>
       </c>
       <c r="H7" t="n">
-        <v>15.56753</v>
+        <v>15.61489</v>
       </c>
       <c r="I7" t="n">
-        <v>27.631645</v>
+        <v>26.703798</v>
       </c>
       <c r="J7" t="n">
-        <v>14.022135</v>
+        <v>13.510182</v>
       </c>
       <c r="K7" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="L7" t="n">
-        <v>17.39792</v>
+        <v>16.813713</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03619038893215448</v>
+        <v>0.03744785741372772</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07131581840670667</v>
+        <v>0.0740182499051953</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02156581936038099</v>
+        <v>0.02440825024851805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38001,51 +38523,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>516.13</v>
+        <v>493.41</v>
       </c>
       <c r="F8" t="n">
-        <v>842569351168</v>
+        <v>805479514112</v>
       </c>
       <c r="G8" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="n">
         <v>15.51049</v>
       </c>
       <c r="I8" t="n">
-        <v>131.3308</v>
+        <v>125.869896</v>
       </c>
       <c r="J8" t="n">
-        <v>33.276188</v>
+        <v>31.811373</v>
       </c>
       <c r="K8" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>20.398724</v>
+        <v>19.500774</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007614360723073645</v>
+        <v>0.007944711294866338</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0300515180284037</v>
+        <v>0.03143529721732433</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01969848101792198</v>
+        <v>-0.01817470243935292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38059,10 +38581,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>361.99</v>
+        <v>344.72</v>
       </c>
       <c r="F9" t="n">
-        <v>1728006324224</v>
+        <v>1645565706240</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -38071,39 +38593,39 @@
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>46.231163</v>
+        <v>44.025543</v>
       </c>
       <c r="J9" t="n">
-        <v>18.674767</v>
+        <v>17.783823</v>
       </c>
       <c r="K9" t="n">
         <v>0.36</v>
       </c>
       <c r="L9" t="n">
-        <v>19.39314</v>
+        <v>18.467922</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02163043177988342</v>
+        <v>0.02271408679508006</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05354819193900384</v>
+        <v>0.05623088303550707</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003798192892678159</v>
+        <v>0.006620883378829823</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:28</t>
+          <t>2026-09-14 17:44:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38117,10 +38639,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77.40000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>322288943104</v>
+        <v>334447640576</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -38129,28 +38651,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>24.339622</v>
+        <v>25.25786</v>
       </c>
       <c r="J10" t="n">
-        <v>20.256954</v>
+        <v>21.02117</v>
       </c>
       <c r="K10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="L10" t="n">
-        <v>6.662887</v>
+        <v>6.9142513</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04108527131782946</v>
+        <v>0.03959163346613546</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0493657622739018</v>
+        <v>0.0475710906374502</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04974999904632568</v>
+        <v>0.04960999965667725</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0003842367724238779</v>
+        <v>-0.002038909019227049</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P649"/>
+  <dimension ref="A1:P658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37581,16 +37581,16 @@
         <v>10.413004</v>
       </c>
       <c r="M641" t="n">
-        <v>0.02614987390416717</v>
+        <v>0.0261498739041671</v>
       </c>
       <c r="N641" t="n">
         <v>0.028770415515792</v>
       </c>
       <c r="O641" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P641" t="n">
-        <v>-0.02083958414088525</v>
+        <v>-0.0208395841408852</v>
       </c>
     </row>
     <row r="642">
@@ -37639,16 +37639,16 @@
         <v>19.500774</v>
       </c>
       <c r="M642" t="n">
-        <v>0.007944711294866338</v>
+        <v>0.0079447112948663</v>
       </c>
       <c r="N642" t="n">
-        <v>0.03143529721732433</v>
+        <v>0.0314352972173243</v>
       </c>
       <c r="O642" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P642" t="n">
-        <v>-0.01817470243935292</v>
+        <v>-0.0181747024393529</v>
       </c>
     </row>
     <row r="643">
@@ -37700,13 +37700,13 @@
         <v>0.0490257947463911</v>
       </c>
       <c r="N643" t="n">
-        <v>0.04103451131971287</v>
+        <v>0.0410345113197128</v>
       </c>
       <c r="O643" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P643" t="n">
-        <v>-0.008575488336964379</v>
+        <v>-0.008575488336964299</v>
       </c>
     </row>
     <row r="644">
@@ -37755,16 +37755,16 @@
         <v>18.467922</v>
       </c>
       <c r="M644" t="n">
-        <v>0.02271408679508006</v>
+        <v>0.02271408679508</v>
       </c>
       <c r="N644" t="n">
-        <v>0.05623088303550707</v>
+        <v>0.056230883035507</v>
       </c>
       <c r="O644" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P644" t="n">
-        <v>0.006620883378829823</v>
+        <v>0.0066208833788298</v>
       </c>
     </row>
     <row r="645">
@@ -37813,16 +37813,16 @@
         <v>9.482694</v>
       </c>
       <c r="M645" t="n">
-        <v>0.05764947499349166</v>
+        <v>0.0576494749934916</v>
       </c>
       <c r="N645" t="n">
-        <v>0.04302400856208961</v>
+        <v>0.0430240085620896</v>
       </c>
       <c r="O645" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P645" t="n">
-        <v>-0.006585991094587636</v>
+        <v>-0.0065859910945876</v>
       </c>
     </row>
     <row r="646">
@@ -37871,16 +37871,16 @@
         <v>7.428882</v>
       </c>
       <c r="M646" t="n">
-        <v>0.03991887019230769</v>
+        <v>0.0399188701923076</v>
       </c>
       <c r="N646" t="n">
-        <v>0.05252352764423077</v>
+        <v>0.0525235276442307</v>
       </c>
       <c r="O646" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P646" t="n">
-        <v>0.002913527987553517</v>
+        <v>0.0029135279875535</v>
       </c>
     </row>
     <row r="647">
@@ -37929,16 +37929,16 @@
         <v>11.309535</v>
       </c>
       <c r="M647" t="n">
-        <v>0.03549593399418294</v>
+        <v>0.0354959339941829</v>
       </c>
       <c r="N647" t="n">
-        <v>0.04668027937713935</v>
+        <v>0.0466802793771393</v>
       </c>
       <c r="O647" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P647" t="n">
-        <v>-0.002929720279537897</v>
+        <v>-0.0029297202795378</v>
       </c>
     </row>
     <row r="648">
@@ -37987,16 +37987,16 @@
         <v>6.9142513</v>
       </c>
       <c r="M648" t="n">
-        <v>0.03959163346613546</v>
+        <v>0.0395916334661354</v>
       </c>
       <c r="N648" t="n">
         <v>0.0475710906374502</v>
       </c>
       <c r="O648" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P648" t="n">
-        <v>-0.002038909019227049</v>
+        <v>-0.002038909019227</v>
       </c>
     </row>
     <row r="649">
@@ -38045,16 +38045,538 @@
         <v>16.813713</v>
       </c>
       <c r="M649" t="n">
-        <v>0.03744785741372772</v>
+        <v>0.0374478574137277</v>
       </c>
       <c r="N649" t="n">
         <v>0.0740182499051953</v>
       </c>
       <c r="O649" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.0496099996566772</v>
       </c>
       <c r="P649" t="n">
-        <v>0.02440825024851805</v>
+        <v>0.024408250248518</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>331.34</v>
+      </c>
+      <c r="F650" t="n">
+        <v>4835635625984</v>
+      </c>
+      <c r="G650" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H650" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I650" t="n">
+        <v>37.95418</v>
+      </c>
+      <c r="J650" t="n">
+        <v>34.57635</v>
+      </c>
+      <c r="K650" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L650" t="n">
+        <v>10.358606</v>
+      </c>
+      <c r="M650" t="n">
+        <v>0.02634755839922738</v>
+      </c>
+      <c r="N650" t="n">
+        <v>0.02892150057342911</v>
+      </c>
+      <c r="O650" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P650" t="n">
+        <v>-0.02103849755736923</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="F651" t="n">
+        <v>823093886976</v>
+      </c>
+      <c r="G651" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H651" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I651" t="n">
+        <v>129.28206</v>
+      </c>
+      <c r="J651" t="n">
+        <v>32.38135</v>
+      </c>
+      <c r="K651" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L651" t="n">
+        <v>19.927221</v>
+      </c>
+      <c r="M651" t="n">
+        <v>0.007735025783419278</v>
+      </c>
+      <c r="N651" t="n">
+        <v>0.0308819714399048</v>
+      </c>
+      <c r="O651" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P651" t="n">
+        <v>-0.01907802669089354</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>248.42</v>
+      </c>
+      <c r="F652" t="n">
+        <v>2679535828992</v>
+      </c>
+      <c r="G652" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H652" t="n">
+        <v>10.40032</v>
+      </c>
+      <c r="I652" t="n">
+        <v>20.00161</v>
+      </c>
+      <c r="J652" t="n">
+        <v>23.885803</v>
+      </c>
+      <c r="K652" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L652" t="n">
+        <v>3.4544344</v>
+      </c>
+      <c r="M652" t="n">
+        <v>0.04999597455921424</v>
+      </c>
+      <c r="N652" t="n">
+        <v>0.04186587231301828</v>
+      </c>
+      <c r="O652" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P652" t="n">
+        <v>-0.00809412581778006</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="F653" t="n">
+        <v>1619549356032</v>
+      </c>
+      <c r="G653" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H653" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I653" t="n">
+        <v>43.329502</v>
+      </c>
+      <c r="J653" t="n">
+        <v>17.50266</v>
+      </c>
+      <c r="K653" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L653" t="n">
+        <v>18.175945</v>
+      </c>
+      <c r="M653" t="n">
+        <v>0.02307896365726413</v>
+      </c>
+      <c r="N653" t="n">
+        <v>0.05713417042473547</v>
+      </c>
+      <c r="O653" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P653" t="n">
+        <v>0.007174172293937124</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="F654" t="n">
+        <v>4175666610176</v>
+      </c>
+      <c r="G654" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="H654" t="n">
+        <v>14.85683</v>
+      </c>
+      <c r="I654" t="n">
+        <v>17.148668</v>
+      </c>
+      <c r="J654" t="n">
+        <v>22.98135</v>
+      </c>
+      <c r="K654" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L654" t="n">
+        <v>9.365295</v>
+      </c>
+      <c r="M654" t="n">
+        <v>0.05831356354157514</v>
+      </c>
+      <c r="N654" t="n">
+        <v>0.04351354596842691</v>
+      </c>
+      <c r="O654" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P654" t="n">
+        <v>-0.006446452162371434</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>670.24</v>
+      </c>
+      <c r="F655" t="n">
+        <v>1707440472064</v>
+      </c>
+      <c r="G655" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H655" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I655" t="n">
+        <v>25.23494</v>
+      </c>
+      <c r="J655" t="n">
+        <v>19.171812</v>
+      </c>
+      <c r="K655" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L655" t="n">
+        <v>7.48067</v>
+      </c>
+      <c r="M655" t="n">
+        <v>0.03962759608498448</v>
+      </c>
+      <c r="N655" t="n">
+        <v>0.05215991286703271</v>
+      </c>
+      <c r="O655" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P655" t="n">
+        <v>0.002199914736234362</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>497.12</v>
+      </c>
+      <c r="F656" t="n">
+        <v>3691387289600</v>
+      </c>
+      <c r="G656" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H656" t="n">
+        <v>23.59268</v>
+      </c>
+      <c r="I656" t="n">
+        <v>27.710144</v>
+      </c>
+      <c r="J656" t="n">
+        <v>21.070942</v>
+      </c>
+      <c r="K656" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L656" t="n">
+        <v>11.12403</v>
+      </c>
+      <c r="M656" t="n">
+        <v>0.03608786610878661</v>
+      </c>
+      <c r="N656" t="n">
+        <v>0.04745872224010299</v>
+      </c>
+      <c r="O656" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P656" t="n">
+        <v>-0.002501275890695348</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="F657" t="n">
+        <v>324370890752</v>
+      </c>
+      <c r="G657" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H657" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I657" t="n">
+        <v>24.496855</v>
+      </c>
+      <c r="J657" t="n">
+        <v>20.387814</v>
+      </c>
+      <c r="K657" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L657" t="n">
+        <v>6.7059283</v>
+      </c>
+      <c r="M657" t="n">
+        <v>0.04082156611039794</v>
+      </c>
+      <c r="N657" t="n">
+        <v>0.04904890885750963</v>
+      </c>
+      <c r="O657" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P657" t="n">
+        <v>-0.0009110892732887149</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:34:10</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>212.17</v>
+      </c>
+      <c r="F658" t="n">
+        <v>5123268935680</v>
+      </c>
+      <c r="G658" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H658" t="n">
+        <v>15.61489</v>
+      </c>
+      <c r="I658" t="n">
+        <v>26.82301</v>
+      </c>
+      <c r="J658" t="n">
+        <v>13.587671</v>
+      </c>
+      <c r="K658" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L658" t="n">
+        <v>16.910152</v>
+      </c>
+      <c r="M658" t="n">
+        <v>0.0372814252721874</v>
+      </c>
+      <c r="N658" t="n">
+        <v>0.07359612574822078</v>
+      </c>
+      <c r="O658" t="n">
+        <v>0.04995999813079834</v>
+      </c>
+      <c r="P658" t="n">
+        <v>0.02363612761742243</v>
       </c>
     </row>
   </sheetData>
@@ -38156,12 +38678,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -38175,51 +38697,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>345.71</v>
+        <v>341.43</v>
       </c>
       <c r="F2" t="n">
-        <v>4228010737664</v>
+        <v>4175666610176</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.91</v>
       </c>
       <c r="H2" t="n">
-        <v>14.87383</v>
+        <v>14.85683</v>
       </c>
       <c r="I2" t="n">
-        <v>17.34621</v>
+        <v>17.148668</v>
       </c>
       <c r="J2" t="n">
-        <v>23.242836</v>
+        <v>22.98135</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="L2" t="n">
-        <v>9.482694</v>
+        <v>9.365295</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05764947499349166</v>
+        <v>0.05831356354157514</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04302400856208961</v>
+        <v>0.04351354596842691</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006585991094587636</v>
+        <v>-0.006446452162371434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -38233,10 +38755,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="F3" t="n">
-        <v>3752944992256</v>
+        <v>3691387289600</v>
       </c>
       <c r="G3" t="n">
         <v>17.94</v>
@@ -38245,39 +38767,39 @@
         <v>23.59268</v>
       </c>
       <c r="I3" t="n">
-        <v>28.17224</v>
+        <v>27.710144</v>
       </c>
       <c r="J3" t="n">
-        <v>21.422323</v>
+        <v>21.070942</v>
       </c>
       <c r="K3" t="n">
         <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>11.309535</v>
+        <v>11.12403</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03549593399418294</v>
+        <v>0.03608786610878661</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04668027937713935</v>
+        <v>0.04745872224010299</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002929720279537897</v>
+        <v>-0.002501275890695348</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38291,51 +38813,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>665.6</v>
+        <v>670.24</v>
       </c>
       <c r="F4" t="n">
-        <v>1695620005888</v>
+        <v>1707440472064</v>
       </c>
       <c r="G4" t="n">
-        <v>26.57</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>25.050808</v>
+        <v>25.23494</v>
       </c>
       <c r="J4" t="n">
-        <v>19.039085</v>
+        <v>19.171812</v>
       </c>
       <c r="K4" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>7.428882</v>
+        <v>7.48067</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03991887019230769</v>
+        <v>0.03962759608498448</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05252352764423077</v>
+        <v>0.05215991286703271</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002913527987553517</v>
+        <v>0.002199914736234362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38349,51 +38871,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>253.54</v>
+        <v>248.42</v>
       </c>
       <c r="F5" t="n">
-        <v>2734761705472</v>
+        <v>2679535828992</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="H5" t="n">
-        <v>10.40389</v>
+        <v>10.40032</v>
       </c>
       <c r="I5" t="n">
-        <v>20.397425</v>
+        <v>20.00161</v>
       </c>
       <c r="J5" t="n">
-        <v>24.369732</v>
+        <v>23.885803</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5256312</v>
+        <v>3.4544344</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0490257947463911</v>
+        <v>0.04999597455921424</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04103451131971287</v>
+        <v>0.04186587231301828</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008575488336964379</v>
+        <v>-0.00809412581778006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38407,51 +38929,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.08</v>
+        <v>331.34</v>
       </c>
       <c r="F6" t="n">
-        <v>4861029515264</v>
+        <v>4835635625984</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
         <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.2411</v>
+        <v>37.95418</v>
       </c>
       <c r="J6" t="n">
-        <v>34.757923</v>
+        <v>34.57635</v>
       </c>
       <c r="K6" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.413004</v>
+        <v>10.358606</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02614987390416717</v>
+        <v>0.02634755839922738</v>
       </c>
       <c r="N6" t="n">
-        <v>0.028770415515792</v>
+        <v>0.02892150057342911</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02083958414088525</v>
+        <v>-0.02103849755736923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38465,51 +38987,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210.96</v>
+        <v>212.17</v>
       </c>
       <c r="F7" t="n">
-        <v>5094050889728</v>
+        <v>5123268935680</v>
       </c>
       <c r="G7" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.61489</v>
       </c>
       <c r="I7" t="n">
-        <v>26.703798</v>
+        <v>26.82301</v>
       </c>
       <c r="J7" t="n">
-        <v>13.510182</v>
+        <v>13.587671</v>
       </c>
       <c r="K7" t="n">
         <v>0.46</v>
       </c>
       <c r="L7" t="n">
-        <v>16.813713</v>
+        <v>16.910152</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03744785741372772</v>
+        <v>0.0372814252721874</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0740182499051953</v>
+        <v>0.07359612574822078</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02440825024851805</v>
+        <v>0.02363612761742243</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38523,51 +39045,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>493.41</v>
+        <v>504.2</v>
       </c>
       <c r="F8" t="n">
-        <v>805479514112</v>
+        <v>823093886976</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
-        <v>15.51049</v>
+        <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>125.869896</v>
+        <v>129.28206</v>
       </c>
       <c r="J8" t="n">
-        <v>31.811373</v>
+        <v>32.38135</v>
       </c>
       <c r="K8" t="n">
         <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>19.500774</v>
+        <v>19.927221</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007944711294866338</v>
+        <v>0.007735025783419278</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03143529721732433</v>
+        <v>0.0308819714399048</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01817470243935292</v>
+        <v>-0.01907802669089354</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38581,10 +39103,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>344.72</v>
+        <v>339.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1645565706240</v>
+        <v>1619549356032</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -38593,39 +39115,39 @@
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>44.025543</v>
+        <v>43.329502</v>
       </c>
       <c r="J9" t="n">
-        <v>17.783823</v>
+        <v>17.50266</v>
       </c>
       <c r="K9" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.467922</v>
+        <v>18.175945</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02271408679508006</v>
+        <v>0.02307896365726413</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05623088303550707</v>
+        <v>0.05713417042473547</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006620883378829823</v>
+        <v>0.007174172293937124</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14 17:44:04</t>
+          <t>2026-09-15 17:34:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38639,10 +39161,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.31999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>334447640576</v>
+        <v>324370890752</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -38651,28 +39173,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.25786</v>
+        <v>24.496855</v>
       </c>
       <c r="J10" t="n">
-        <v>21.02117</v>
+        <v>20.387814</v>
       </c>
       <c r="K10" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="L10" t="n">
-        <v>6.9142513</v>
+        <v>6.7059283</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03959163346613546</v>
+        <v>0.04082156611039794</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0475710906374502</v>
+        <v>0.04904890885750963</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04960999965667725</v>
+        <v>0.04995999813079834</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.002038909019227049</v>
+        <v>-0.0009110892732887149</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P658"/>
+  <dimension ref="A1:P667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38103,16 +38103,16 @@
         <v>10.358606</v>
       </c>
       <c r="M650" t="n">
-        <v>0.02634755839922738</v>
+        <v>0.0263475583992273</v>
       </c>
       <c r="N650" t="n">
-        <v>0.02892150057342911</v>
+        <v>0.0289215005734291</v>
       </c>
       <c r="O650" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P650" t="n">
-        <v>-0.02103849755736923</v>
+        <v>-0.0210384975573692</v>
       </c>
     </row>
     <row r="651">
@@ -38161,16 +38161,16 @@
         <v>19.927221</v>
       </c>
       <c r="M651" t="n">
-        <v>0.007735025783419278</v>
+        <v>0.0077350257834192</v>
       </c>
       <c r="N651" t="n">
         <v>0.0308819714399048</v>
       </c>
       <c r="O651" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P651" t="n">
-        <v>-0.01907802669089354</v>
+        <v>-0.0190780266908935</v>
       </c>
     </row>
     <row r="652">
@@ -38219,16 +38219,16 @@
         <v>3.4544344</v>
       </c>
       <c r="M652" t="n">
-        <v>0.04999597455921424</v>
+        <v>0.0499959745592142</v>
       </c>
       <c r="N652" t="n">
-        <v>0.04186587231301828</v>
+        <v>0.0418658723130182</v>
       </c>
       <c r="O652" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P652" t="n">
-        <v>-0.00809412581778006</v>
+        <v>-0.008094125817780001</v>
       </c>
     </row>
     <row r="653">
@@ -38277,16 +38277,16 @@
         <v>18.175945</v>
       </c>
       <c r="M653" t="n">
-        <v>0.02307896365726413</v>
+        <v>0.0230789636572641</v>
       </c>
       <c r="N653" t="n">
-        <v>0.05713417042473547</v>
+        <v>0.0571341704247354</v>
       </c>
       <c r="O653" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P653" t="n">
-        <v>0.007174172293937124</v>
+        <v>0.0071741722939371</v>
       </c>
     </row>
     <row r="654">
@@ -38335,16 +38335,16 @@
         <v>9.365295</v>
       </c>
       <c r="M654" t="n">
-        <v>0.05831356354157514</v>
+        <v>0.0583135635415751</v>
       </c>
       <c r="N654" t="n">
-        <v>0.04351354596842691</v>
+        <v>0.0435135459684269</v>
       </c>
       <c r="O654" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P654" t="n">
-        <v>-0.006446452162371434</v>
+        <v>-0.0064464521623714</v>
       </c>
     </row>
     <row r="655">
@@ -38393,16 +38393,16 @@
         <v>7.48067</v>
       </c>
       <c r="M655" t="n">
-        <v>0.03962759608498448</v>
+        <v>0.0396275960849844</v>
       </c>
       <c r="N655" t="n">
-        <v>0.05215991286703271</v>
+        <v>0.0521599128670327</v>
       </c>
       <c r="O655" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P655" t="n">
-        <v>0.002199914736234362</v>
+        <v>0.0021999147362343</v>
       </c>
     </row>
     <row r="656">
@@ -38451,16 +38451,16 @@
         <v>11.12403</v>
       </c>
       <c r="M656" t="n">
-        <v>0.03608786610878661</v>
+        <v>0.0360878661087866</v>
       </c>
       <c r="N656" t="n">
-        <v>0.04745872224010299</v>
+        <v>0.0474587222401029</v>
       </c>
       <c r="O656" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P656" t="n">
-        <v>-0.002501275890695348</v>
+        <v>-0.0025012758906953</v>
       </c>
     </row>
     <row r="657">
@@ -38509,16 +38509,16 @@
         <v>6.7059283</v>
       </c>
       <c r="M657" t="n">
-        <v>0.04082156611039794</v>
+        <v>0.0408215661103979</v>
       </c>
       <c r="N657" t="n">
-        <v>0.04904890885750963</v>
+        <v>0.0490489088575096</v>
       </c>
       <c r="O657" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P657" t="n">
-        <v>-0.0009110892732887149</v>
+        <v>-0.0009110892732887</v>
       </c>
     </row>
     <row r="658">
@@ -38570,13 +38570,535 @@
         <v>0.0372814252721874</v>
       </c>
       <c r="N658" t="n">
-        <v>0.07359612574822078</v>
+        <v>0.07359612574822071</v>
       </c>
       <c r="O658" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0499599981307983</v>
       </c>
       <c r="P658" t="n">
-        <v>0.02363612761742243</v>
+        <v>0.0236361276174224</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>332.41</v>
+      </c>
+      <c r="F659" t="n">
+        <v>4851251544064</v>
+      </c>
+      <c r="G659" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H659" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I659" t="n">
+        <v>38.033184</v>
+      </c>
+      <c r="J659" t="n">
+        <v>34.688007</v>
+      </c>
+      <c r="K659" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L659" t="n">
+        <v>10.392058</v>
+      </c>
+      <c r="M659" t="n">
+        <v>0.02629283114226407</v>
+      </c>
+      <c r="N659" t="n">
+        <v>0.02882840468096627</v>
+      </c>
+      <c r="O659" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P659" t="n">
+        <v>-0.02123159573865042</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="F660" t="n">
+        <v>836643454976</v>
+      </c>
+      <c r="G660" t="n">
+        <v>4</v>
+      </c>
+      <c r="H660" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I660" t="n">
+        <v>128.125</v>
+      </c>
+      <c r="J660" t="n">
+        <v>32.914406</v>
+      </c>
+      <c r="K660" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L660" t="n">
+        <v>20.255257</v>
+      </c>
+      <c r="M660" t="n">
+        <v>0.007804878048780488</v>
+      </c>
+      <c r="N660" t="n">
+        <v>0.03038183414634147</v>
+      </c>
+      <c r="O660" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P660" t="n">
+        <v>-0.01967816627327523</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>245.96</v>
+      </c>
+      <c r="F661" t="n">
+        <v>2653001613312</v>
+      </c>
+      <c r="G661" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H661" t="n">
+        <v>10.37503</v>
+      </c>
+      <c r="I661" t="n">
+        <v>19.803543</v>
+      </c>
+      <c r="J661" t="n">
+        <v>23.70692</v>
+      </c>
+      <c r="K661" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L661" t="n">
+        <v>3.4202268</v>
+      </c>
+      <c r="M661" t="n">
+        <v>0.05049601561229468</v>
+      </c>
+      <c r="N661" t="n">
+        <v>0.04218177752480078</v>
+      </c>
+      <c r="O661" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P661" t="n">
+        <v>-0.007878222894815913</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="F662" t="n">
+        <v>1620695187456</v>
+      </c>
+      <c r="G662" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H662" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I662" t="n">
+        <v>43.304848</v>
+      </c>
+      <c r="J662" t="n">
+        <v>17.515043</v>
+      </c>
+      <c r="K662" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L662" t="n">
+        <v>18.188805</v>
+      </c>
+      <c r="M662" t="n">
+        <v>0.0230921033253807</v>
+      </c>
+      <c r="N662" t="n">
+        <v>0.05709378221554594</v>
+      </c>
+      <c r="O662" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P662" t="n">
+        <v>0.007033781795929242</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="F663" t="n">
+        <v>4150350577664</v>
+      </c>
+      <c r="G663" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H663" t="n">
+        <v>14.85683</v>
+      </c>
+      <c r="I663" t="n">
+        <v>17.122099</v>
+      </c>
+      <c r="J663" t="n">
+        <v>22.842018</v>
+      </c>
+      <c r="K663" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L663" t="n">
+        <v>9.308515999999999</v>
+      </c>
+      <c r="M663" t="n">
+        <v>0.0584040546911834</v>
+      </c>
+      <c r="N663" t="n">
+        <v>0.04377896628948609</v>
+      </c>
+      <c r="O663" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P663" t="n">
+        <v>-0.006281034130130606</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>673.3099999999999</v>
+      </c>
+      <c r="F664" t="n">
+        <v>1715261407232</v>
+      </c>
+      <c r="G664" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="H664" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I664" t="n">
+        <v>25.25544</v>
+      </c>
+      <c r="J664" t="n">
+        <v>19.259626</v>
+      </c>
+      <c r="K664" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L664" t="n">
+        <v>7.5149355</v>
+      </c>
+      <c r="M664" t="n">
+        <v>0.03959543152485483</v>
+      </c>
+      <c r="N664" t="n">
+        <v>0.05192208640893497</v>
+      </c>
+      <c r="O664" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P664" t="n">
+        <v>0.001862085989318273</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>490.3</v>
+      </c>
+      <c r="F665" t="n">
+        <v>3640745000960</v>
+      </c>
+      <c r="G665" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H665" t="n">
+        <v>23.59268</v>
+      </c>
+      <c r="I665" t="n">
+        <v>27.314762</v>
+      </c>
+      <c r="J665" t="n">
+        <v>20.78187</v>
+      </c>
+      <c r="K665" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L665" t="n">
+        <v>10.971419</v>
+      </c>
+      <c r="M665" t="n">
+        <v>0.03661023862941056</v>
+      </c>
+      <c r="N665" t="n">
+        <v>0.04811886600040791</v>
+      </c>
+      <c r="O665" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P665" t="n">
+        <v>-0.001941134419208783</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>76.41</v>
+      </c>
+      <c r="F666" t="n">
+        <v>318166630400</v>
+      </c>
+      <c r="G666" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H666" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I666" t="n">
+        <v>24.490387</v>
+      </c>
+      <c r="J666" t="n">
+        <v>19.997854</v>
+      </c>
+      <c r="K666" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L666" t="n">
+        <v>6.577664</v>
+      </c>
+      <c r="M666" t="n">
+        <v>0.04083235178641539</v>
+      </c>
+      <c r="N666" t="n">
+        <v>0.05000536578981809</v>
+      </c>
+      <c r="O666" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P666" t="n">
+        <v>-5.463462979860695e-05</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:41:39</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>213.9</v>
+      </c>
+      <c r="F667" t="n">
+        <v>5165043154944</v>
+      </c>
+      <c r="G667" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="H667" t="n">
+        <v>15.61489</v>
+      </c>
+      <c r="I667" t="n">
+        <v>26.80451</v>
+      </c>
+      <c r="J667" t="n">
+        <v>13.698463</v>
+      </c>
+      <c r="K667" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L667" t="n">
+        <v>17.048035</v>
+      </c>
+      <c r="M667" t="n">
+        <v>0.03730715287517532</v>
+      </c>
+      <c r="N667" t="n">
+        <v>0.07300088826554466</v>
+      </c>
+      <c r="O667" t="n">
+        <v>0.0500600004196167</v>
+      </c>
+      <c r="P667" t="n">
+        <v>0.02294088784592796</v>
       </c>
     </row>
   </sheetData>
@@ -38678,12 +39200,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -38697,51 +39219,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>341.43</v>
+        <v>339.36</v>
       </c>
       <c r="F2" t="n">
-        <v>4175666610176</v>
+        <v>4150350577664</v>
       </c>
       <c r="G2" t="n">
-        <v>19.91</v>
+        <v>19.82</v>
       </c>
       <c r="H2" t="n">
         <v>14.85683</v>
       </c>
       <c r="I2" t="n">
-        <v>17.148668</v>
+        <v>17.122099</v>
       </c>
       <c r="J2" t="n">
-        <v>22.98135</v>
+        <v>22.842018</v>
       </c>
       <c r="K2" t="n">
         <v>1.24</v>
       </c>
       <c r="L2" t="n">
-        <v>9.365295</v>
+        <v>9.308515999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05831356354157514</v>
+        <v>0.0584040546911834</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04351354596842691</v>
+        <v>0.04377896628948609</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006446452162371434</v>
+        <v>-0.006281034130130606</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -38755,51 +39277,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="F3" t="n">
-        <v>3691387289600</v>
+        <v>3640745000960</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
         <v>23.59268</v>
       </c>
       <c r="I3" t="n">
-        <v>27.710144</v>
+        <v>27.314762</v>
       </c>
       <c r="J3" t="n">
-        <v>21.070942</v>
+        <v>20.78187</v>
       </c>
       <c r="K3" t="n">
         <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>11.12403</v>
+        <v>10.971419</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03608786610878661</v>
+        <v>0.03661023862941056</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04745872224010299</v>
+        <v>0.04811886600040791</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002501275890695348</v>
+        <v>-0.001941134419208783</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38813,51 +39335,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>670.24</v>
+        <v>673.3099999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1707440472064</v>
+        <v>1715261407232</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.66</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>25.23494</v>
+        <v>25.25544</v>
       </c>
       <c r="J4" t="n">
-        <v>19.171812</v>
+        <v>19.259626</v>
       </c>
       <c r="K4" t="n">
         <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>7.48067</v>
+        <v>7.5149355</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03962759608498448</v>
+        <v>0.03959543152485483</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05215991286703271</v>
+        <v>0.05192208640893497</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002199914736234362</v>
+        <v>0.001862085989318273</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38871,51 +39393,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248.42</v>
+        <v>245.96</v>
       </c>
       <c r="F5" t="n">
-        <v>2679535828992</v>
+        <v>2653001613312</v>
       </c>
       <c r="G5" t="n">
         <v>12.42</v>
       </c>
       <c r="H5" t="n">
-        <v>10.40032</v>
+        <v>10.37503</v>
       </c>
       <c r="I5" t="n">
-        <v>20.00161</v>
+        <v>19.803543</v>
       </c>
       <c r="J5" t="n">
-        <v>23.885803</v>
+        <v>23.70692</v>
       </c>
       <c r="K5" t="n">
         <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4544344</v>
+        <v>3.4202268</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04999597455921424</v>
+        <v>0.05049601561229468</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04186587231301828</v>
+        <v>0.04218177752480078</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00809412581778006</v>
+        <v>-0.007878222894815913</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38929,51 +39451,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>331.34</v>
+        <v>332.41</v>
       </c>
       <c r="F6" t="n">
-        <v>4835635625984</v>
+        <v>4851251544064</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
         <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>37.95418</v>
+        <v>38.033184</v>
       </c>
       <c r="J6" t="n">
-        <v>34.57635</v>
+        <v>34.688007</v>
       </c>
       <c r="K6" t="n">
         <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.358606</v>
+        <v>10.392058</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02634755839922738</v>
+        <v>0.02629283114226407</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02892150057342911</v>
+        <v>0.02882840468096627</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02103849755736923</v>
+        <v>-0.02123159573865042</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38987,51 +39509,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>212.17</v>
+        <v>213.9</v>
       </c>
       <c r="F7" t="n">
-        <v>5123268935680</v>
+        <v>5165043154944</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.98</v>
       </c>
       <c r="H7" t="n">
         <v>15.61489</v>
       </c>
       <c r="I7" t="n">
-        <v>26.82301</v>
+        <v>26.80451</v>
       </c>
       <c r="J7" t="n">
-        <v>13.587671</v>
+        <v>13.698463</v>
       </c>
       <c r="K7" t="n">
         <v>0.46</v>
       </c>
       <c r="L7" t="n">
-        <v>16.910152</v>
+        <v>17.048035</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0372814252721874</v>
+        <v>0.03730715287517532</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07359612574822078</v>
+        <v>0.07300088826554466</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02363612761742243</v>
+        <v>0.02294088784592796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -39045,51 +39567,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504.2</v>
+        <v>512.5</v>
       </c>
       <c r="F8" t="n">
-        <v>823093886976</v>
+        <v>836643454976</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>129.28206</v>
+        <v>128.125</v>
       </c>
       <c r="J8" t="n">
-        <v>32.38135</v>
+        <v>32.914406</v>
       </c>
       <c r="K8" t="n">
         <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>19.927221</v>
+        <v>20.255257</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007735025783419278</v>
+        <v>0.007804878048780488</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0308819714399048</v>
+        <v>0.03038183414634147</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01907802669089354</v>
+        <v>-0.01967816627327523</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -39103,51 +39625,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>339.27</v>
+        <v>339.51</v>
       </c>
       <c r="F9" t="n">
-        <v>1619549356032</v>
+        <v>1620695187456</v>
       </c>
       <c r="G9" t="n">
-        <v>7.83</v>
+        <v>7.84</v>
       </c>
       <c r="H9" t="n">
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>43.329502</v>
+        <v>43.304848</v>
       </c>
       <c r="J9" t="n">
-        <v>17.50266</v>
+        <v>17.515043</v>
       </c>
       <c r="K9" t="n">
         <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.175945</v>
+        <v>18.188805</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02307896365726413</v>
+        <v>0.0230921033253807</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05713417042473547</v>
+        <v>0.05709378221554594</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007174172293937124</v>
+        <v>0.007033781795929242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 17:34:10</t>
+          <t>2026-09-16 17:41:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -39161,40 +39683,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77.90000000000001</v>
+        <v>76.41</v>
       </c>
       <c r="F10" t="n">
-        <v>324370890752</v>
+        <v>318166630400</v>
       </c>
       <c r="G10" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="H10" t="n">
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>24.496855</v>
+        <v>24.490387</v>
       </c>
       <c r="J10" t="n">
-        <v>20.387814</v>
+        <v>19.997854</v>
       </c>
       <c r="K10" t="n">
         <v>1.48</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7059283</v>
+        <v>6.577664</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04082156611039794</v>
+        <v>0.04083235178641539</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04904890885750963</v>
+        <v>0.05000536578981809</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04995999813079834</v>
+        <v>0.0500600004196167</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0009110892732887149</v>
+        <v>-5.463462979860695e-05</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P667"/>
+  <dimension ref="A1:P676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38625,16 +38625,16 @@
         <v>10.392058</v>
       </c>
       <c r="M659" t="n">
-        <v>0.02629283114226407</v>
+        <v>0.026292831142264</v>
       </c>
       <c r="N659" t="n">
-        <v>0.02882840468096627</v>
+        <v>0.0288284046809662</v>
       </c>
       <c r="O659" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P659" t="n">
-        <v>-0.02123159573865042</v>
+        <v>-0.0212315957386504</v>
       </c>
     </row>
     <row r="660">
@@ -38683,16 +38683,16 @@
         <v>20.255257</v>
       </c>
       <c r="M660" t="n">
-        <v>0.007804878048780488</v>
+        <v>0.0078048780487804</v>
       </c>
       <c r="N660" t="n">
-        <v>0.03038183414634147</v>
+        <v>0.0303818341463414</v>
       </c>
       <c r="O660" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P660" t="n">
-        <v>-0.01967816627327523</v>
+        <v>-0.0196781662732752</v>
       </c>
     </row>
     <row r="661">
@@ -38741,16 +38741,16 @@
         <v>3.4202268</v>
       </c>
       <c r="M661" t="n">
-        <v>0.05049601561229468</v>
+        <v>0.0504960156122946</v>
       </c>
       <c r="N661" t="n">
-        <v>0.04218177752480078</v>
+        <v>0.0421817775248007</v>
       </c>
       <c r="O661" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P661" t="n">
-        <v>-0.007878222894815913</v>
+        <v>-0.007878222894815899</v>
       </c>
     </row>
     <row r="662">
@@ -38799,16 +38799,16 @@
         <v>18.188805</v>
       </c>
       <c r="M662" t="n">
-        <v>0.0230921033253807</v>
+        <v>0.0230921033253806</v>
       </c>
       <c r="N662" t="n">
-        <v>0.05709378221554594</v>
+        <v>0.0570937822155459</v>
       </c>
       <c r="O662" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P662" t="n">
-        <v>0.007033781795929242</v>
+        <v>0.0070337817959292</v>
       </c>
     </row>
     <row r="663">
@@ -38860,13 +38860,13 @@
         <v>0.0584040546911834</v>
       </c>
       <c r="N663" t="n">
-        <v>0.04377896628948609</v>
+        <v>0.043778966289486</v>
       </c>
       <c r="O663" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P663" t="n">
-        <v>-0.006281034130130606</v>
+        <v>-0.0062810341301306</v>
       </c>
     </row>
     <row r="664">
@@ -38915,16 +38915,16 @@
         <v>7.5149355</v>
       </c>
       <c r="M664" t="n">
-        <v>0.03959543152485483</v>
+        <v>0.0395954315248548</v>
       </c>
       <c r="N664" t="n">
-        <v>0.05192208640893497</v>
+        <v>0.0519220864089349</v>
       </c>
       <c r="O664" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P664" t="n">
-        <v>0.001862085989318273</v>
+        <v>0.0018620859893182</v>
       </c>
     </row>
     <row r="665">
@@ -38973,16 +38973,16 @@
         <v>10.971419</v>
       </c>
       <c r="M665" t="n">
-        <v>0.03661023862941056</v>
+        <v>0.0366102386294105</v>
       </c>
       <c r="N665" t="n">
-        <v>0.04811886600040791</v>
+        <v>0.0481188660004079</v>
       </c>
       <c r="O665" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P665" t="n">
-        <v>-0.001941134419208783</v>
+        <v>-0.0019411344192087</v>
       </c>
     </row>
     <row r="666">
@@ -39031,13 +39031,13 @@
         <v>6.577664</v>
       </c>
       <c r="M666" t="n">
-        <v>0.04083235178641539</v>
+        <v>0.0408323517864153</v>
       </c>
       <c r="N666" t="n">
-        <v>0.05000536578981809</v>
+        <v>0.050005365789818</v>
       </c>
       <c r="O666" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P666" t="n">
         <v>-5.463462979860695e-05</v>
@@ -39089,16 +39089,538 @@
         <v>17.048035</v>
       </c>
       <c r="M667" t="n">
-        <v>0.03730715287517532</v>
+        <v>0.0373071528751753</v>
       </c>
       <c r="N667" t="n">
-        <v>0.07300088826554466</v>
+        <v>0.0730008882655446</v>
       </c>
       <c r="O667" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.0500600004196166</v>
       </c>
       <c r="P667" t="n">
-        <v>0.02294088784592796</v>
+        <v>0.0229408878459279</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>337</v>
+      </c>
+      <c r="F668" t="n">
+        <v>4918238773248</v>
+      </c>
+      <c r="G668" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H668" t="n">
+        <v>9.5886</v>
+      </c>
+      <c r="I668" t="n">
+        <v>38.69116</v>
+      </c>
+      <c r="J668" t="n">
+        <v>35.1459</v>
+      </c>
+      <c r="K668" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L668" t="n">
+        <v>10.535554</v>
+      </c>
+      <c r="M668" t="n">
+        <v>0.02584569732937686</v>
+      </c>
+      <c r="N668" t="n">
+        <v>0.02845281899109792</v>
+      </c>
+      <c r="O668" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P668" t="n">
+        <v>-0.02101718127593089</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>545.09</v>
+      </c>
+      <c r="F669" t="n">
+        <v>889845841920</v>
+      </c>
+      <c r="G669" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H669" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I669" t="n">
+        <v>139.76666</v>
+      </c>
+      <c r="J669" t="n">
+        <v>35.007442</v>
+      </c>
+      <c r="K669" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L669" t="n">
+        <v>21.543295</v>
+      </c>
+      <c r="M669" t="n">
+        <v>0.007154781779155735</v>
+      </c>
+      <c r="N669" t="n">
+        <v>0.02856535617971344</v>
+      </c>
+      <c r="O669" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P669" t="n">
+        <v>-0.02090464408731537</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>251.19</v>
+      </c>
+      <c r="F670" t="n">
+        <v>2709413953536</v>
+      </c>
+      <c r="G670" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H670" t="n">
+        <v>10.37503</v>
+      </c>
+      <c r="I670" t="n">
+        <v>20.224638</v>
+      </c>
+      <c r="J670" t="n">
+        <v>24.211016</v>
+      </c>
+      <c r="K670" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L670" t="n">
+        <v>3.492953</v>
+      </c>
+      <c r="M670" t="n">
+        <v>0.04944464349695449</v>
+      </c>
+      <c r="N670" t="n">
+        <v>0.04130351526732753</v>
+      </c>
+      <c r="O670" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P670" t="n">
+        <v>-0.008166484999701282</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>347.3</v>
+      </c>
+      <c r="F671" t="n">
+        <v>1657881624576</v>
+      </c>
+      <c r="G671" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H671" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I671" t="n">
+        <v>44.298466</v>
+      </c>
+      <c r="J671" t="n">
+        <v>17.916922</v>
+      </c>
+      <c r="K671" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L671" t="n">
+        <v>18.606142</v>
+      </c>
+      <c r="M671" t="n">
+        <v>0.02257414339188022</v>
+      </c>
+      <c r="N671" t="n">
+        <v>0.05581315865246185</v>
+      </c>
+      <c r="O671" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P671" t="n">
+        <v>0.006343158385433041</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>343.68</v>
+      </c>
+      <c r="F672" t="n">
+        <v>4203184128000</v>
+      </c>
+      <c r="G672" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H672" t="n">
+        <v>14.85683</v>
+      </c>
+      <c r="I672" t="n">
+        <v>17.253012</v>
+      </c>
+      <c r="J672" t="n">
+        <v>23.132795</v>
+      </c>
+      <c r="K672" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L672" t="n">
+        <v>9.427012</v>
+      </c>
+      <c r="M672" t="n">
+        <v>0.0579608938547486</v>
+      </c>
+      <c r="N672" t="n">
+        <v>0.04322867202048417</v>
+      </c>
+      <c r="O672" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P672" t="n">
+        <v>-0.006241328246544636</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>682.3099999999999</v>
+      </c>
+      <c r="F673" t="n">
+        <v>1738188914688</v>
+      </c>
+      <c r="G673" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H673" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I673" t="n">
+        <v>25.718431</v>
+      </c>
+      <c r="J673" t="n">
+        <v>19.517067</v>
+      </c>
+      <c r="K673" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L673" t="n">
+        <v>7.6153855</v>
+      </c>
+      <c r="M673" t="n">
+        <v>0.0388826193372514</v>
+      </c>
+      <c r="N673" t="n">
+        <v>0.05123720889331829</v>
+      </c>
+      <c r="O673" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P673" t="n">
+        <v>0.001767208626289478</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>497.75</v>
+      </c>
+      <c r="F674" t="n">
+        <v>3696065511424</v>
+      </c>
+      <c r="G674" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H674" t="n">
+        <v>23.59268</v>
+      </c>
+      <c r="I674" t="n">
+        <v>27.74526</v>
+      </c>
+      <c r="J674" t="n">
+        <v>21.097645</v>
+      </c>
+      <c r="K674" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L674" t="n">
+        <v>11.138128</v>
+      </c>
+      <c r="M674" t="n">
+        <v>0.03604218985434456</v>
+      </c>
+      <c r="N674" t="n">
+        <v>0.04739865394274234</v>
+      </c>
+      <c r="O674" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P674" t="n">
+        <v>-0.002071346324286467</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>75.31</v>
+      </c>
+      <c r="F675" t="n">
+        <v>313586286592</v>
+      </c>
+      <c r="G675" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H675" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I675" t="n">
+        <v>23.682388</v>
+      </c>
+      <c r="J675" t="n">
+        <v>19.709965</v>
+      </c>
+      <c r="K675" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L675" t="n">
+        <v>6.482971</v>
+      </c>
+      <c r="M675" t="n">
+        <v>0.04222546806532997</v>
+      </c>
+      <c r="N675" t="n">
+        <v>0.05073575886336476</v>
+      </c>
+      <c r="O675" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P675" t="n">
+        <v>0.001265758596335952</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:30:21</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>219.34</v>
+      </c>
+      <c r="F676" t="n">
+        <v>5296402989056</v>
+      </c>
+      <c r="G676" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H676" t="n">
+        <v>15.61489</v>
+      </c>
+      <c r="I676" t="n">
+        <v>27.729456</v>
+      </c>
+      <c r="J676" t="n">
+        <v>14.046848</v>
+      </c>
+      <c r="K676" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L676" t="n">
+        <v>17.481607</v>
+      </c>
+      <c r="M676" t="n">
+        <v>0.03606273365551199</v>
+      </c>
+      <c r="N676" t="n">
+        <v>0.07119034375854838</v>
+      </c>
+      <c r="O676" t="n">
+        <v>0.04947000026702881</v>
+      </c>
+      <c r="P676" t="n">
+        <v>0.02172034349151957</v>
       </c>
     </row>
   </sheetData>
@@ -39200,12 +39722,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -39219,51 +39741,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>339.36</v>
+        <v>343.68</v>
       </c>
       <c r="F2" t="n">
-        <v>4150350577664</v>
+        <v>4203184128000</v>
       </c>
       <c r="G2" t="n">
-        <v>19.82</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
         <v>14.85683</v>
       </c>
       <c r="I2" t="n">
-        <v>17.122099</v>
+        <v>17.253012</v>
       </c>
       <c r="J2" t="n">
-        <v>22.842018</v>
+        <v>23.132795</v>
       </c>
       <c r="K2" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.308515999999999</v>
+        <v>9.427012</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0584040546911834</v>
+        <v>0.0579608938547486</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04377896628948609</v>
+        <v>0.04322867202048417</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006281034130130606</v>
+        <v>-0.006241328246544636</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -39277,51 +39799,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="F3" t="n">
-        <v>3640745000960</v>
+        <v>3696065511424</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
         <v>23.59268</v>
       </c>
       <c r="I3" t="n">
-        <v>27.314762</v>
+        <v>27.74526</v>
       </c>
       <c r="J3" t="n">
-        <v>20.78187</v>
+        <v>21.097645</v>
       </c>
       <c r="K3" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>10.971419</v>
+        <v>11.138128</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03661023862941056</v>
+        <v>0.03604218985434456</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04811886600040791</v>
+        <v>0.04739865394274234</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001941134419208783</v>
+        <v>-0.002071346324286467</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -39335,51 +39857,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>673.3099999999999</v>
+        <v>682.3099999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1715261407232</v>
+        <v>1738188914688</v>
       </c>
       <c r="G4" t="n">
-        <v>26.66</v>
+        <v>26.53</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>25.25544</v>
+        <v>25.718431</v>
       </c>
       <c r="J4" t="n">
-        <v>19.259626</v>
+        <v>19.517067</v>
       </c>
       <c r="K4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="L4" t="n">
-        <v>7.5149355</v>
+        <v>7.6153855</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03959543152485483</v>
+        <v>0.0388826193372514</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05192208640893497</v>
+        <v>0.05123720889331829</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001862085989318273</v>
+        <v>0.001767208626289478</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -39393,10 +39915,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245.96</v>
+        <v>251.19</v>
       </c>
       <c r="F5" t="n">
-        <v>2653001613312</v>
+        <v>2709413953536</v>
       </c>
       <c r="G5" t="n">
         <v>12.42</v>
@@ -39405,39 +39927,39 @@
         <v>10.37503</v>
       </c>
       <c r="I5" t="n">
-        <v>19.803543</v>
+        <v>20.224638</v>
       </c>
       <c r="J5" t="n">
-        <v>23.70692</v>
+        <v>24.211016</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4202268</v>
+        <v>3.492953</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05049601561229468</v>
+        <v>0.04944464349695449</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04218177752480078</v>
+        <v>0.04130351526732753</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007878222894815913</v>
+        <v>-0.008166484999701282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -39451,51 +39973,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>332.41</v>
+        <v>337</v>
       </c>
       <c r="F6" t="n">
-        <v>4851251544064</v>
+        <v>4918238773248</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.582850000000001</v>
+        <v>9.5886</v>
       </c>
       <c r="I6" t="n">
-        <v>38.033184</v>
+        <v>38.69116</v>
       </c>
       <c r="J6" t="n">
-        <v>34.688007</v>
+        <v>35.1459</v>
       </c>
       <c r="K6" t="n">
         <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.392058</v>
+        <v>10.535554</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02629283114226407</v>
+        <v>0.02584569732937686</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02882840468096627</v>
+        <v>0.02845281899109792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02123159573865042</v>
+        <v>-0.02101718127593089</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -39509,51 +40031,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>213.9</v>
+        <v>219.34</v>
       </c>
       <c r="F7" t="n">
-        <v>5165043154944</v>
+        <v>5296402989056</v>
       </c>
       <c r="G7" t="n">
-        <v>7.98</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.61489</v>
       </c>
       <c r="I7" t="n">
-        <v>26.80451</v>
+        <v>27.729456</v>
       </c>
       <c r="J7" t="n">
-        <v>13.698463</v>
+        <v>14.046848</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="L7" t="n">
-        <v>17.048035</v>
+        <v>17.481607</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03730715287517532</v>
+        <v>0.03606273365551199</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07300088826554466</v>
+        <v>0.07119034375854838</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02294088784592796</v>
+        <v>0.02172034349151957</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -39567,51 +40089,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>512.5</v>
+        <v>545.09</v>
       </c>
       <c r="F8" t="n">
-        <v>836643454976</v>
+        <v>889845841920</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
         <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>128.125</v>
+        <v>139.76666</v>
       </c>
       <c r="J8" t="n">
-        <v>32.914406</v>
+        <v>35.007442</v>
       </c>
       <c r="K8" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="L8" t="n">
-        <v>20.255257</v>
+        <v>21.543295</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007804878048780488</v>
+        <v>0.007154781779155735</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03038183414634147</v>
+        <v>0.02856535617971344</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01967816627327523</v>
+        <v>-0.02090464408731537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -39625,10 +40147,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>339.51</v>
+        <v>347.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1620695187456</v>
+        <v>1657881624576</v>
       </c>
       <c r="G9" t="n">
         <v>7.84</v>
@@ -39637,39 +40159,39 @@
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>43.304848</v>
+        <v>44.298466</v>
       </c>
       <c r="J9" t="n">
-        <v>17.515043</v>
+        <v>17.916922</v>
       </c>
       <c r="K9" t="n">
         <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.188805</v>
+        <v>18.606142</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0230921033253807</v>
+        <v>0.02257414339188022</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05709378221554594</v>
+        <v>0.05581315865246185</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007033781795929242</v>
+        <v>0.006343158385433041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-16 17:41:39</t>
+          <t>2026-09-17 17:30:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -39683,40 +40205,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76.41</v>
+        <v>75.31</v>
       </c>
       <c r="F10" t="n">
-        <v>318166630400</v>
+        <v>313586286592</v>
       </c>
       <c r="G10" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="H10" t="n">
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>24.490387</v>
+        <v>23.682388</v>
       </c>
       <c r="J10" t="n">
-        <v>19.997854</v>
+        <v>19.709965</v>
       </c>
       <c r="K10" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="L10" t="n">
-        <v>6.577664</v>
+        <v>6.482971</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04083235178641539</v>
+        <v>0.04222546806532997</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05000536578981809</v>
+        <v>0.05073575886336476</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0500600004196167</v>
+        <v>0.04947000026702881</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.463462979860695e-05</v>
+        <v>0.001265758596335952</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P676"/>
+  <dimension ref="A1:P685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39147,16 +39147,16 @@
         <v>10.535554</v>
       </c>
       <c r="M668" t="n">
-        <v>0.02584569732937686</v>
+        <v>0.0258456973293768</v>
       </c>
       <c r="N668" t="n">
-        <v>0.02845281899109792</v>
+        <v>0.0284528189910979</v>
       </c>
       <c r="O668" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P668" t="n">
-        <v>-0.02101718127593089</v>
+        <v>-0.0210171812759308</v>
       </c>
     </row>
     <row r="669">
@@ -39205,16 +39205,16 @@
         <v>21.543295</v>
       </c>
       <c r="M669" t="n">
-        <v>0.007154781779155735</v>
+        <v>0.0071547817791557</v>
       </c>
       <c r="N669" t="n">
-        <v>0.02856535617971344</v>
+        <v>0.0285653561797134</v>
       </c>
       <c r="O669" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P669" t="n">
-        <v>-0.02090464408731537</v>
+        <v>-0.0209046440873153</v>
       </c>
     </row>
     <row r="670">
@@ -39263,16 +39263,16 @@
         <v>3.492953</v>
       </c>
       <c r="M670" t="n">
-        <v>0.04944464349695449</v>
+        <v>0.0494446434969544</v>
       </c>
       <c r="N670" t="n">
-        <v>0.04130351526732753</v>
+        <v>0.0413035152673275</v>
       </c>
       <c r="O670" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P670" t="n">
-        <v>-0.008166484999701282</v>
+        <v>-0.0081664849997012</v>
       </c>
     </row>
     <row r="671">
@@ -39321,16 +39321,16 @@
         <v>18.606142</v>
       </c>
       <c r="M671" t="n">
-        <v>0.02257414339188022</v>
+        <v>0.0225741433918802</v>
       </c>
       <c r="N671" t="n">
-        <v>0.05581315865246185</v>
+        <v>0.0558131586524618</v>
       </c>
       <c r="O671" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P671" t="n">
-        <v>0.006343158385433041</v>
+        <v>0.006343158385433</v>
       </c>
     </row>
     <row r="672">
@@ -39382,13 +39382,13 @@
         <v>0.0579608938547486</v>
       </c>
       <c r="N672" t="n">
-        <v>0.04322867202048417</v>
+        <v>0.0432286720204841</v>
       </c>
       <c r="O672" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P672" t="n">
-        <v>-0.006241328246544636</v>
+        <v>-0.0062413282465446</v>
       </c>
     </row>
     <row r="673">
@@ -39440,13 +39440,13 @@
         <v>0.0388826193372514</v>
       </c>
       <c r="N673" t="n">
-        <v>0.05123720889331829</v>
+        <v>0.0512372088933182</v>
       </c>
       <c r="O673" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P673" t="n">
-        <v>0.001767208626289478</v>
+        <v>0.0017672086262894</v>
       </c>
     </row>
     <row r="674">
@@ -39495,16 +39495,16 @@
         <v>11.138128</v>
       </c>
       <c r="M674" t="n">
-        <v>0.03604218985434456</v>
+        <v>0.0360421898543445</v>
       </c>
       <c r="N674" t="n">
-        <v>0.04739865394274234</v>
+        <v>0.0473986539427423</v>
       </c>
       <c r="O674" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P674" t="n">
-        <v>-0.002071346324286467</v>
+        <v>-0.0020713463242864</v>
       </c>
     </row>
     <row r="675">
@@ -39553,16 +39553,16 @@
         <v>6.482971</v>
       </c>
       <c r="M675" t="n">
-        <v>0.04222546806532997</v>
+        <v>0.0422254680653299</v>
       </c>
       <c r="N675" t="n">
-        <v>0.05073575886336476</v>
+        <v>0.0507357588633647</v>
       </c>
       <c r="O675" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P675" t="n">
-        <v>0.001265758596335952</v>
+        <v>0.0012657585963359</v>
       </c>
     </row>
     <row r="676">
@@ -39611,16 +39611,538 @@
         <v>17.481607</v>
       </c>
       <c r="M676" t="n">
-        <v>0.03606273365551199</v>
+        <v>0.0360627336555119</v>
       </c>
       <c r="N676" t="n">
-        <v>0.07119034375854838</v>
+        <v>0.0711903437585483</v>
       </c>
       <c r="O676" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.0494700002670288</v>
       </c>
       <c r="P676" t="n">
-        <v>0.02172034349151957</v>
+        <v>0.0217203434915195</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>336.13</v>
+      </c>
+      <c r="F677" t="n">
+        <v>4905541566464</v>
+      </c>
+      <c r="G677" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H677" t="n">
+        <v>9.5886</v>
+      </c>
+      <c r="I677" t="n">
+        <v>38.502865</v>
+      </c>
+      <c r="J677" t="n">
+        <v>35.05517</v>
+      </c>
+      <c r="K677" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L677" t="n">
+        <v>10.508355</v>
+      </c>
+      <c r="M677" t="n">
+        <v>0.02597209413024723</v>
+      </c>
+      <c r="N677" t="n">
+        <v>0.02852646297563443</v>
+      </c>
+      <c r="O677" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P677" t="n">
+        <v>-0.02145353847395054</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>559.8200000000001</v>
+      </c>
+      <c r="F678" t="n">
+        <v>913892179968</v>
+      </c>
+      <c r="G678" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H678" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I678" t="n">
+        <v>142.81122</v>
+      </c>
+      <c r="J678" t="n">
+        <v>35.95345</v>
+      </c>
+      <c r="K678" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L678" t="n">
+        <v>22.12546</v>
+      </c>
+      <c r="M678" t="n">
+        <v>0.007002250723446821</v>
+      </c>
+      <c r="N678" t="n">
+        <v>0.02781374370333321</v>
+      </c>
+      <c r="O678" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P678" t="n">
+        <v>-0.02216625774625175</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>253.71</v>
+      </c>
+      <c r="F679" t="n">
+        <v>2736595664896</v>
+      </c>
+      <c r="G679" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H679" t="n">
+        <v>10.37503</v>
+      </c>
+      <c r="I679" t="n">
+        <v>20.411102</v>
+      </c>
+      <c r="J679" t="n">
+        <v>24.453907</v>
+      </c>
+      <c r="K679" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L679" t="n">
+        <v>3.5279956</v>
+      </c>
+      <c r="M679" t="n">
+        <v>0.04899294470064246</v>
+      </c>
+      <c r="N679" t="n">
+        <v>0.04089326396279216</v>
+      </c>
+      <c r="O679" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P679" t="n">
+        <v>-0.009086737486792798</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>357.61</v>
+      </c>
+      <c r="F680" t="n">
+        <v>1707097718784</v>
+      </c>
+      <c r="G680" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H680" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I680" t="n">
+        <v>45.555412</v>
+      </c>
+      <c r="J680" t="n">
+        <v>18.448807</v>
+      </c>
+      <c r="K680" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L680" t="n">
+        <v>19.158485</v>
+      </c>
+      <c r="M680" t="n">
+        <v>0.0219512877156679</v>
+      </c>
+      <c r="N680" t="n">
+        <v>0.05420404910377227</v>
+      </c>
+      <c r="O680" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P680" t="n">
+        <v>0.004224047654187303</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="F681" t="n">
+        <v>4212111966208</v>
+      </c>
+      <c r="G681" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H681" t="n">
+        <v>14.84399</v>
+      </c>
+      <c r="I681" t="n">
+        <v>17.280983</v>
+      </c>
+      <c r="J681" t="n">
+        <v>23.201982</v>
+      </c>
+      <c r="K681" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L681" t="n">
+        <v>9.447036000000001</v>
+      </c>
+      <c r="M681" t="n">
+        <v>0.05786707703028367</v>
+      </c>
+      <c r="N681" t="n">
+        <v>0.04309976481519119</v>
+      </c>
+      <c r="O681" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P681" t="n">
+        <v>-0.006880236634393772</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>665.75</v>
+      </c>
+      <c r="F682" t="n">
+        <v>1696002211840</v>
+      </c>
+      <c r="G682" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H682" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I682" t="n">
+        <v>25.084776</v>
+      </c>
+      <c r="J682" t="n">
+        <v>19.043377</v>
+      </c>
+      <c r="K682" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L682" t="n">
+        <v>7.430557</v>
+      </c>
+      <c r="M682" t="n">
+        <v>0.03986481411941419</v>
+      </c>
+      <c r="N682" t="n">
+        <v>0.05251169357867067</v>
+      </c>
+      <c r="O682" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P682" t="n">
+        <v>0.002531692129085709</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>493.78</v>
+      </c>
+      <c r="F683" t="n">
+        <v>3666585845760</v>
+      </c>
+      <c r="G683" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H683" t="n">
+        <v>23.59268</v>
+      </c>
+      <c r="I683" t="n">
+        <v>27.47802</v>
+      </c>
+      <c r="J683" t="n">
+        <v>20.929373</v>
+      </c>
+      <c r="K683" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L683" t="n">
+        <v>11.049291</v>
+      </c>
+      <c r="M683" t="n">
+        <v>0.03639272550528575</v>
+      </c>
+      <c r="N683" t="n">
+        <v>0.04777973996516668</v>
+      </c>
+      <c r="O683" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P683" t="n">
+        <v>-0.002200261484418285</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="F684" t="n">
+        <v>298929225728</v>
+      </c>
+      <c r="G684" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H684" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I684" t="n">
+        <v>22.575472</v>
+      </c>
+      <c r="J684" t="n">
+        <v>18.78872</v>
+      </c>
+      <c r="K684" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L684" t="n">
+        <v>6.1799564</v>
+      </c>
+      <c r="M684" t="n">
+        <v>0.0442958629335562</v>
+      </c>
+      <c r="N684" t="n">
+        <v>0.05322342944699818</v>
+      </c>
+      <c r="O684" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P684" t="n">
+        <v>0.003243427997413222</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:26:06</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>222.27</v>
+      </c>
+      <c r="F685" t="n">
+        <v>5367153557504</v>
+      </c>
+      <c r="G685" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H685" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I685" t="n">
+        <v>28.064394</v>
+      </c>
+      <c r="J685" t="n">
+        <v>14.173006</v>
+      </c>
+      <c r="K685" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L685" t="n">
+        <v>17.715132</v>
+      </c>
+      <c r="M685" t="n">
+        <v>0.03563233904710487</v>
+      </c>
+      <c r="N685" t="n">
+        <v>0.07055666531695685</v>
+      </c>
+      <c r="O685" t="n">
+        <v>0.04998000144958496</v>
+      </c>
+      <c r="P685" t="n">
+        <v>0.02057666386737189</v>
       </c>
     </row>
   </sheetData>
@@ -39722,12 +40244,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -39741,51 +40263,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>343.68</v>
+        <v>344.41</v>
       </c>
       <c r="F2" t="n">
-        <v>4203184128000</v>
+        <v>4212111966208</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>14.85683</v>
+        <v>14.84399</v>
       </c>
       <c r="I2" t="n">
-        <v>17.253012</v>
+        <v>17.280983</v>
       </c>
       <c r="J2" t="n">
-        <v>23.132795</v>
+        <v>23.201982</v>
       </c>
       <c r="K2" t="n">
         <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.427012</v>
+        <v>9.447036000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0579608938547486</v>
+        <v>0.05786707703028367</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04322867202048417</v>
+        <v>0.04309976481519119</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006241328246544636</v>
+        <v>-0.006880236634393772</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -39799,51 +40321,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="F3" t="n">
-        <v>3696065511424</v>
+        <v>3666585845760</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
         <v>23.59268</v>
       </c>
       <c r="I3" t="n">
-        <v>27.74526</v>
+        <v>27.47802</v>
       </c>
       <c r="J3" t="n">
-        <v>21.097645</v>
+        <v>20.929373</v>
       </c>
       <c r="K3" t="n">
         <v>1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>11.138128</v>
+        <v>11.049291</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03604218985434456</v>
+        <v>0.03639272550528575</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04739865394274234</v>
+        <v>0.04777973996516668</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002071346324286467</v>
+        <v>-0.002200261484418285</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -39857,51 +40379,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>682.3099999999999</v>
+        <v>665.75</v>
       </c>
       <c r="F4" t="n">
-        <v>1738188914688</v>
+        <v>1696002211840</v>
       </c>
       <c r="G4" t="n">
-        <v>26.53</v>
+        <v>26.54</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>25.718431</v>
+        <v>25.084776</v>
       </c>
       <c r="J4" t="n">
-        <v>19.517067</v>
+        <v>19.043377</v>
       </c>
       <c r="K4" t="n">
         <v>0.89</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6153855</v>
+        <v>7.430557</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0388826193372514</v>
+        <v>0.03986481411941419</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05123720889331829</v>
+        <v>0.05251169357867067</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001767208626289478</v>
+        <v>0.002531692129085709</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -39915,51 +40437,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>251.19</v>
+        <v>253.71</v>
       </c>
       <c r="F5" t="n">
-        <v>2709413953536</v>
+        <v>2736595664896</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.37503</v>
       </c>
       <c r="I5" t="n">
-        <v>20.224638</v>
+        <v>20.411102</v>
       </c>
       <c r="J5" t="n">
-        <v>24.211016</v>
+        <v>24.453907</v>
       </c>
       <c r="K5" t="n">
         <v>1.44</v>
       </c>
       <c r="L5" t="n">
-        <v>3.492953</v>
+        <v>3.5279956</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04944464349695449</v>
+        <v>0.04899294470064246</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04130351526732753</v>
+        <v>0.04089326396279216</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008166484999701282</v>
+        <v>-0.009086737486792798</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -39973,51 +40495,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>337</v>
+        <v>336.13</v>
       </c>
       <c r="F6" t="n">
-        <v>4918238773248</v>
+        <v>4905541566464</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
         <v>9.5886</v>
       </c>
       <c r="I6" t="n">
-        <v>38.69116</v>
+        <v>38.502865</v>
       </c>
       <c r="J6" t="n">
-        <v>35.1459</v>
+        <v>35.05517</v>
       </c>
       <c r="K6" t="n">
         <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.535554</v>
+        <v>10.508355</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02584569732937686</v>
+        <v>0.02597209413024723</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02845281899109792</v>
+        <v>0.02852646297563443</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02101718127593089</v>
+        <v>-0.02145353847395054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -40031,51 +40553,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219.34</v>
+        <v>222.27</v>
       </c>
       <c r="F7" t="n">
-        <v>5296402989056</v>
+        <v>5367153557504</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="H7" t="n">
-        <v>15.61489</v>
+        <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>27.729456</v>
+        <v>28.064394</v>
       </c>
       <c r="J7" t="n">
-        <v>14.046848</v>
+        <v>14.173006</v>
       </c>
       <c r="K7" t="n">
         <v>0.45</v>
       </c>
       <c r="L7" t="n">
-        <v>17.481607</v>
+        <v>17.715132</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03606273365551199</v>
+        <v>0.03563233904710487</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07119034375854838</v>
+        <v>0.07055666531695685</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02172034349151957</v>
+        <v>0.02057666386737189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -40089,51 +40611,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>545.09</v>
+        <v>559.8200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>889845841920</v>
+        <v>913892179968</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="n">
         <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>139.76666</v>
+        <v>142.81122</v>
       </c>
       <c r="J8" t="n">
-        <v>35.007442</v>
+        <v>35.95345</v>
       </c>
       <c r="K8" t="n">
         <v>0.52</v>
       </c>
       <c r="L8" t="n">
-        <v>21.543295</v>
+        <v>22.12546</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007154781779155735</v>
+        <v>0.007002250723446821</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02856535617971344</v>
+        <v>0.02781374370333321</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02090464408731537</v>
+        <v>-0.02216625774625175</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -40147,51 +40669,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>347.3</v>
+        <v>357.61</v>
       </c>
       <c r="F9" t="n">
-        <v>1657881624576</v>
+        <v>1707097718784</v>
       </c>
       <c r="G9" t="n">
-        <v>7.84</v>
+        <v>7.85</v>
       </c>
       <c r="H9" t="n">
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>44.298466</v>
+        <v>45.555412</v>
       </c>
       <c r="J9" t="n">
-        <v>17.916922</v>
+        <v>18.448807</v>
       </c>
       <c r="K9" t="n">
         <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.606142</v>
+        <v>19.158485</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02257414339188022</v>
+        <v>0.0219512877156679</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05581315865246185</v>
+        <v>0.05420404910377227</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006343158385433041</v>
+        <v>0.004224047654187303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-17 17:30:21</t>
+          <t>2026-09-18 17:26:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -40205,10 +40727,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75.31</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>313586286592</v>
+        <v>298929225728</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -40217,28 +40739,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>23.682388</v>
+        <v>22.575472</v>
       </c>
       <c r="J10" t="n">
-        <v>19.709965</v>
+        <v>18.78872</v>
       </c>
       <c r="K10" t="n">
         <v>1.41</v>
       </c>
       <c r="L10" t="n">
-        <v>6.482971</v>
+        <v>6.1799564</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04222546806532997</v>
+        <v>0.0442958629335562</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05073575886336476</v>
+        <v>0.05322342944699818</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04998000144958496</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001265758596335952</v>
+        <v>0.003243427997413222</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P685"/>
+  <dimension ref="A1:P694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39669,16 +39669,16 @@
         <v>10.508355</v>
       </c>
       <c r="M677" t="n">
-        <v>0.02597209413024723</v>
+        <v>0.0259720941302472</v>
       </c>
       <c r="N677" t="n">
-        <v>0.02852646297563443</v>
+        <v>0.0285264629756344</v>
       </c>
       <c r="O677" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P677" t="n">
-        <v>-0.02145353847395054</v>
+        <v>-0.0214535384739505</v>
       </c>
     </row>
     <row r="678">
@@ -39727,16 +39727,16 @@
         <v>22.12546</v>
       </c>
       <c r="M678" t="n">
-        <v>0.007002250723446821</v>
+        <v>0.0070022507234468</v>
       </c>
       <c r="N678" t="n">
-        <v>0.02781374370333321</v>
+        <v>0.0278137437033332</v>
       </c>
       <c r="O678" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P678" t="n">
-        <v>-0.02216625774625175</v>
+        <v>-0.0221662577462517</v>
       </c>
     </row>
     <row r="679">
@@ -39785,16 +39785,16 @@
         <v>3.5279956</v>
       </c>
       <c r="M679" t="n">
-        <v>0.04899294470064246</v>
+        <v>0.0489929447006424</v>
       </c>
       <c r="N679" t="n">
-        <v>0.04089326396279216</v>
+        <v>0.0408932639627921</v>
       </c>
       <c r="O679" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P679" t="n">
-        <v>-0.009086737486792798</v>
+        <v>-0.009086737486792699</v>
       </c>
     </row>
     <row r="680">
@@ -39846,13 +39846,13 @@
         <v>0.0219512877156679</v>
       </c>
       <c r="N680" t="n">
-        <v>0.05420404910377227</v>
+        <v>0.0542040491037722</v>
       </c>
       <c r="O680" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P680" t="n">
-        <v>0.004224047654187303</v>
+        <v>0.0042240476541873</v>
       </c>
     </row>
     <row r="681">
@@ -39901,16 +39901,16 @@
         <v>9.447036000000001</v>
       </c>
       <c r="M681" t="n">
-        <v>0.05786707703028367</v>
+        <v>0.0578670770302836</v>
       </c>
       <c r="N681" t="n">
-        <v>0.04309976481519119</v>
+        <v>0.0430997648151911</v>
       </c>
       <c r="O681" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P681" t="n">
-        <v>-0.006880236634393772</v>
+        <v>-0.0068802366343937</v>
       </c>
     </row>
     <row r="682">
@@ -39959,16 +39959,16 @@
         <v>7.430557</v>
       </c>
       <c r="M682" t="n">
-        <v>0.03986481411941419</v>
+        <v>0.0398648141194141</v>
       </c>
       <c r="N682" t="n">
-        <v>0.05251169357867067</v>
+        <v>0.0525116935786706</v>
       </c>
       <c r="O682" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P682" t="n">
-        <v>0.002531692129085709</v>
+        <v>0.0025316921290857</v>
       </c>
     </row>
     <row r="683">
@@ -40017,16 +40017,16 @@
         <v>11.049291</v>
       </c>
       <c r="M683" t="n">
-        <v>0.03639272550528575</v>
+        <v>0.0363927255052857</v>
       </c>
       <c r="N683" t="n">
-        <v>0.04777973996516668</v>
+        <v>0.0477797399651666</v>
       </c>
       <c r="O683" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P683" t="n">
-        <v>-0.002200261484418285</v>
+        <v>-0.0022002614844182</v>
       </c>
     </row>
     <row r="684">
@@ -40078,13 +40078,13 @@
         <v>0.0442958629335562</v>
       </c>
       <c r="N684" t="n">
-        <v>0.05322342944699818</v>
+        <v>0.0532234294469981</v>
       </c>
       <c r="O684" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P684" t="n">
-        <v>0.003243427997413222</v>
+        <v>0.0032434279974132</v>
       </c>
     </row>
     <row r="685">
@@ -40133,16 +40133,538 @@
         <v>17.715132</v>
       </c>
       <c r="M685" t="n">
-        <v>0.03563233904710487</v>
+        <v>0.0356323390471048</v>
       </c>
       <c r="N685" t="n">
-        <v>0.07055666531695685</v>
+        <v>0.0705566653169568</v>
       </c>
       <c r="O685" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.0499800014495849</v>
       </c>
       <c r="P685" t="n">
-        <v>0.02057666386737189</v>
+        <v>0.0205766638673718</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>338.98</v>
+      </c>
+      <c r="F686" t="n">
+        <v>4947135430656</v>
+      </c>
+      <c r="G686" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H686" t="n">
+        <v>9.5886</v>
+      </c>
+      <c r="I686" t="n">
+        <v>38.918484</v>
+      </c>
+      <c r="J686" t="n">
+        <v>35.352398</v>
+      </c>
+      <c r="K686" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L686" t="n">
+        <v>10.597455</v>
+      </c>
+      <c r="M686" t="n">
+        <v>0.02569473125258127</v>
+      </c>
+      <c r="N686" t="n">
+        <v>0.02828662457962122</v>
+      </c>
+      <c r="O686" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P686" t="n">
+        <v>-0.02134337839584265</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>615.52</v>
+      </c>
+      <c r="F687" t="n">
+        <v>1004821020672</v>
+      </c>
+      <c r="G687" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H687" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I687" t="n">
+        <v>157.02042</v>
+      </c>
+      <c r="J687" t="n">
+        <v>39.53068</v>
+      </c>
+      <c r="K687" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L687" t="n">
+        <v>24.32686</v>
+      </c>
+      <c r="M687" t="n">
+        <v>0.006368598908240188</v>
+      </c>
+      <c r="N687" t="n">
+        <v>0.02529680595269041</v>
+      </c>
+      <c r="O687" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P687" t="n">
+        <v>-0.02433319702277346</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>258.45</v>
+      </c>
+      <c r="F688" t="n">
+        <v>2787722657792</v>
+      </c>
+      <c r="G688" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H688" t="n">
+        <v>10.38846</v>
+      </c>
+      <c r="I688" t="n">
+        <v>20.792439</v>
+      </c>
+      <c r="J688" t="n">
+        <v>24.878569</v>
+      </c>
+      <c r="K688" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L688" t="n">
+        <v>3.593908</v>
+      </c>
+      <c r="M688" t="n">
+        <v>0.04809440897659122</v>
+      </c>
+      <c r="N688" t="n">
+        <v>0.04019524085896692</v>
+      </c>
+      <c r="O688" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P688" t="n">
+        <v>-0.00943476211649695</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="F689" t="n">
+        <v>1731204612096</v>
+      </c>
+      <c r="G689" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H689" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I689" t="n">
+        <v>46.31673</v>
+      </c>
+      <c r="J689" t="n">
+        <v>18.709333</v>
+      </c>
+      <c r="K689" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L689" t="n">
+        <v>19.429033</v>
+      </c>
+      <c r="M689" t="n">
+        <v>0.02159047041305906</v>
+      </c>
+      <c r="N689" t="n">
+        <v>0.05344926377323112</v>
+      </c>
+      <c r="O689" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P689" t="n">
+        <v>0.003819260797767253</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>350.87</v>
+      </c>
+      <c r="F690" t="n">
+        <v>4291117187072</v>
+      </c>
+      <c r="G690" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H690" t="n">
+        <v>14.88187</v>
+      </c>
+      <c r="I690" t="n">
+        <v>17.596289</v>
+      </c>
+      <c r="J690" t="n">
+        <v>23.57701</v>
+      </c>
+      <c r="K690" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L690" t="n">
+        <v>9.624231</v>
+      </c>
+      <c r="M690" t="n">
+        <v>0.05683016501838288</v>
+      </c>
+      <c r="N690" t="n">
+        <v>0.04241419899107932</v>
+      </c>
+      <c r="O690" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P690" t="n">
+        <v>-0.007215803984384553</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>741.245</v>
+      </c>
+      <c r="F691" t="n">
+        <v>1888326254592</v>
+      </c>
+      <c r="G691" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H691" t="n">
+        <v>34.83968</v>
+      </c>
+      <c r="I691" t="n">
+        <v>27.908321</v>
+      </c>
+      <c r="J691" t="n">
+        <v>21.275885</v>
+      </c>
+      <c r="K691" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L691" t="n">
+        <v>8.27317</v>
+      </c>
+      <c r="M691" t="n">
+        <v>0.03583160763310377</v>
+      </c>
+      <c r="N691" t="n">
+        <v>0.04700157168007879</v>
+      </c>
+      <c r="O691" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P691" t="n">
+        <v>-0.002628431295385078</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>501.61</v>
+      </c>
+      <c r="F692" t="n">
+        <v>3724727812096</v>
+      </c>
+      <c r="G692" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H692" t="n">
+        <v>23.67588</v>
+      </c>
+      <c r="I692" t="n">
+        <v>27.913746</v>
+      </c>
+      <c r="J692" t="n">
+        <v>21.18654</v>
+      </c>
+      <c r="K692" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L692" t="n">
+        <v>11.224503</v>
+      </c>
+      <c r="M692" t="n">
+        <v>0.03582464464424553</v>
+      </c>
+      <c r="N692" t="n">
+        <v>0.04719977671896493</v>
+      </c>
+      <c r="O692" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P692" t="n">
+        <v>-0.002430226256498941</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>73.36</v>
+      </c>
+      <c r="F693" t="n">
+        <v>305466605568</v>
+      </c>
+      <c r="G693" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H693" t="n">
+        <v>3.81882</v>
+      </c>
+      <c r="I693" t="n">
+        <v>23.069181</v>
+      </c>
+      <c r="J693" t="n">
+        <v>19.210123</v>
+      </c>
+      <c r="K693" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L693" t="n">
+        <v>6.315108</v>
+      </c>
+      <c r="M693" t="n">
+        <v>0.04334787350054526</v>
+      </c>
+      <c r="N693" t="n">
+        <v>0.05205588876772083</v>
+      </c>
+      <c r="O693" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P693" t="n">
+        <v>0.002425885792256964</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:56:54</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>227.38</v>
+      </c>
+      <c r="F694" t="n">
+        <v>5490544738304</v>
+      </c>
+      <c r="G694" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H694" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I694" t="n">
+        <v>28.745892</v>
+      </c>
+      <c r="J694" t="n">
+        <v>14.498844</v>
+      </c>
+      <c r="K694" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L694" t="n">
+        <v>18.122404</v>
+      </c>
+      <c r="M694" t="n">
+        <v>0.03478758026211629</v>
+      </c>
+      <c r="N694" t="n">
+        <v>0.0689710176796552</v>
+      </c>
+      <c r="O694" t="n">
+        <v>0.04963000297546387</v>
+      </c>
+      <c r="P694" t="n">
+        <v>0.01934101470419133</v>
       </c>
     </row>
   </sheetData>
@@ -40244,12 +40766,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -40263,51 +40785,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>344.41</v>
+        <v>350.87</v>
       </c>
       <c r="F2" t="n">
-        <v>4212111966208</v>
+        <v>4291117187072</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
-        <v>14.84399</v>
+        <v>14.88187</v>
       </c>
       <c r="I2" t="n">
-        <v>17.280983</v>
+        <v>17.596289</v>
       </c>
       <c r="J2" t="n">
-        <v>23.201982</v>
+        <v>23.57701</v>
       </c>
       <c r="K2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="L2" t="n">
-        <v>9.447036000000001</v>
+        <v>9.624231</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05786707703028367</v>
+        <v>0.05683016501838288</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04309976481519119</v>
+        <v>0.04241419899107932</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006880236634393772</v>
+        <v>-0.007215803984384553</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -40321,51 +40843,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="F3" t="n">
-        <v>3666585845760</v>
+        <v>3724727812096</v>
       </c>
       <c r="G3" t="n">
         <v>17.97</v>
       </c>
       <c r="H3" t="n">
-        <v>23.59268</v>
+        <v>23.67588</v>
       </c>
       <c r="I3" t="n">
-        <v>27.47802</v>
+        <v>27.913746</v>
       </c>
       <c r="J3" t="n">
-        <v>20.929373</v>
+        <v>21.18654</v>
       </c>
       <c r="K3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>11.049291</v>
+        <v>11.224503</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03639272550528575</v>
+        <v>0.03582464464424553</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04777973996516668</v>
+        <v>0.04719977671896493</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002200261484418285</v>
+        <v>-0.002430226256498941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -40379,51 +40901,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>665.75</v>
+        <v>741.245</v>
       </c>
       <c r="F4" t="n">
-        <v>1696002211840</v>
+        <v>1888326254592</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
-        <v>34.95966</v>
+        <v>34.83968</v>
       </c>
       <c r="I4" t="n">
-        <v>25.084776</v>
+        <v>27.908321</v>
       </c>
       <c r="J4" t="n">
-        <v>19.043377</v>
+        <v>21.275885</v>
       </c>
       <c r="K4" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>7.430557</v>
+        <v>8.27317</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03986481411941419</v>
+        <v>0.03583160763310377</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05251169357867067</v>
+        <v>0.04700157168007879</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002531692129085709</v>
+        <v>-0.002628431295385078</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -40437,51 +40959,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>253.71</v>
+        <v>258.45</v>
       </c>
       <c r="F5" t="n">
-        <v>2736595664896</v>
+        <v>2787722657792</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.37503</v>
+        <v>10.38846</v>
       </c>
       <c r="I5" t="n">
-        <v>20.411102</v>
+        <v>20.792439</v>
       </c>
       <c r="J5" t="n">
-        <v>24.453907</v>
+        <v>24.878569</v>
       </c>
       <c r="K5" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5279956</v>
+        <v>3.593908</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04899294470064246</v>
+        <v>0.04809440897659122</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04089326396279216</v>
+        <v>0.04019524085896692</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009086737486792798</v>
+        <v>-0.00943476211649695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -40495,51 +41017,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>336.13</v>
+        <v>338.98</v>
       </c>
       <c r="F6" t="n">
-        <v>4905541566464</v>
+        <v>4947135430656</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.5886</v>
       </c>
       <c r="I6" t="n">
-        <v>38.502865</v>
+        <v>38.918484</v>
       </c>
       <c r="J6" t="n">
-        <v>35.05517</v>
+        <v>35.352398</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="L6" t="n">
-        <v>10.508355</v>
+        <v>10.597455</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02597209413024723</v>
+        <v>0.02569473125258127</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02852646297563443</v>
+        <v>0.02828662457962122</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02145353847395054</v>
+        <v>-0.02134337839584265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -40553,51 +41075,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222.27</v>
+        <v>227.38</v>
       </c>
       <c r="F7" t="n">
-        <v>5367153557504</v>
+        <v>5490544738304</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.064394</v>
+        <v>28.745892</v>
       </c>
       <c r="J7" t="n">
-        <v>14.173006</v>
+        <v>14.498844</v>
       </c>
       <c r="K7" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>17.715132</v>
+        <v>18.122404</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03563233904710487</v>
+        <v>0.03478758026211629</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07055666531695685</v>
+        <v>0.0689710176796552</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02057666386737189</v>
+        <v>0.01934101470419133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -40611,10 +41133,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>559.8200000000001</v>
+        <v>615.52</v>
       </c>
       <c r="F8" t="n">
-        <v>913892179968</v>
+        <v>1004821020672</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -40623,39 +41145,39 @@
         <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>142.81122</v>
+        <v>157.02042</v>
       </c>
       <c r="J8" t="n">
-        <v>35.95345</v>
+        <v>39.53068</v>
       </c>
       <c r="K8" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="L8" t="n">
-        <v>22.12546</v>
+        <v>24.32686</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007002250723446821</v>
+        <v>0.006368598908240188</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02781374370333321</v>
+        <v>0.02529680595269041</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02216625774625175</v>
+        <v>-0.02433319702277346</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -40669,51 +41191,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>357.61</v>
+        <v>362.66</v>
       </c>
       <c r="F9" t="n">
-        <v>1707097718784</v>
+        <v>1731204612096</v>
       </c>
       <c r="G9" t="n">
-        <v>7.85</v>
+        <v>7.83</v>
       </c>
       <c r="H9" t="n">
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>45.555412</v>
+        <v>46.31673</v>
       </c>
       <c r="J9" t="n">
-        <v>18.448807</v>
+        <v>18.709333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.158485</v>
+        <v>19.429033</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0219512877156679</v>
+        <v>0.02159047041305906</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05420404910377227</v>
+        <v>0.05344926377323112</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004224047654187303</v>
+        <v>0.003819260797767253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-18 17:26:06</t>
+          <t>2026-09-21 17:56:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -40727,40 +41249,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.79000000000001</v>
+        <v>73.36</v>
       </c>
       <c r="F10" t="n">
-        <v>298929225728</v>
+        <v>305466605568</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.82091</v>
+        <v>3.81882</v>
       </c>
       <c r="I10" t="n">
-        <v>22.575472</v>
+        <v>23.069181</v>
       </c>
       <c r="J10" t="n">
-        <v>18.78872</v>
+        <v>19.210123</v>
       </c>
       <c r="K10" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1799564</v>
+        <v>6.315108</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0442958629335562</v>
+        <v>0.04334787350054526</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05322342944699818</v>
+        <v>0.05205588876772083</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.04963000297546387</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003243427997413222</v>
+        <v>0.002425885792256964</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P694"/>
+  <dimension ref="A1:P703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40191,16 +40191,16 @@
         <v>10.597455</v>
       </c>
       <c r="M686" t="n">
-        <v>0.02569473125258127</v>
+        <v>0.0256947312525812</v>
       </c>
       <c r="N686" t="n">
-        <v>0.02828662457962122</v>
+        <v>0.0282866245796212</v>
       </c>
       <c r="O686" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P686" t="n">
-        <v>-0.02134337839584265</v>
+        <v>-0.0213433783958426</v>
       </c>
     </row>
     <row r="687">
@@ -40249,16 +40249,16 @@
         <v>24.32686</v>
       </c>
       <c r="M687" t="n">
-        <v>0.006368598908240188</v>
+        <v>0.0063685989082401</v>
       </c>
       <c r="N687" t="n">
-        <v>0.02529680595269041</v>
+        <v>0.0252968059526904</v>
       </c>
       <c r="O687" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P687" t="n">
-        <v>-0.02433319702277346</v>
+        <v>-0.0243331970227734</v>
       </c>
     </row>
     <row r="688">
@@ -40307,16 +40307,16 @@
         <v>3.593908</v>
       </c>
       <c r="M688" t="n">
-        <v>0.04809440897659122</v>
+        <v>0.0480944089765912</v>
       </c>
       <c r="N688" t="n">
-        <v>0.04019524085896692</v>
+        <v>0.0401952408589669</v>
       </c>
       <c r="O688" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P688" t="n">
-        <v>-0.00943476211649695</v>
+        <v>-0.0094347621164969</v>
       </c>
     </row>
     <row r="689">
@@ -40365,16 +40365,16 @@
         <v>19.429033</v>
       </c>
       <c r="M689" t="n">
-        <v>0.02159047041305906</v>
+        <v>0.021590470413059</v>
       </c>
       <c r="N689" t="n">
-        <v>0.05344926377323112</v>
+        <v>0.0534492637732311</v>
       </c>
       <c r="O689" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P689" t="n">
-        <v>0.003819260797767253</v>
+        <v>0.0038192607977672</v>
       </c>
     </row>
     <row r="690">
@@ -40423,16 +40423,16 @@
         <v>9.624231</v>
       </c>
       <c r="M690" t="n">
-        <v>0.05683016501838288</v>
+        <v>0.0568301650183828</v>
       </c>
       <c r="N690" t="n">
-        <v>0.04241419899107932</v>
+        <v>0.0424141989910793</v>
       </c>
       <c r="O690" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P690" t="n">
-        <v>-0.007215803984384553</v>
+        <v>-0.0072158039843845</v>
       </c>
     </row>
     <row r="691">
@@ -40481,16 +40481,16 @@
         <v>8.27317</v>
       </c>
       <c r="M691" t="n">
-        <v>0.03583160763310377</v>
+        <v>0.0358316076331037</v>
       </c>
       <c r="N691" t="n">
-        <v>0.04700157168007879</v>
+        <v>0.0470015716800787</v>
       </c>
       <c r="O691" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P691" t="n">
-        <v>-0.002628431295385078</v>
+        <v>-0.002628431295385</v>
       </c>
     </row>
     <row r="692">
@@ -40539,16 +40539,16 @@
         <v>11.224503</v>
       </c>
       <c r="M692" t="n">
-        <v>0.03582464464424553</v>
+        <v>0.0358246446442455</v>
       </c>
       <c r="N692" t="n">
-        <v>0.04719977671896493</v>
+        <v>0.0471997767189649</v>
       </c>
       <c r="O692" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P692" t="n">
-        <v>-0.002430226256498941</v>
+        <v>-0.0024302262564989</v>
       </c>
     </row>
     <row r="693">
@@ -40597,16 +40597,16 @@
         <v>6.315108</v>
       </c>
       <c r="M693" t="n">
-        <v>0.04334787350054526</v>
+        <v>0.0433478735005452</v>
       </c>
       <c r="N693" t="n">
-        <v>0.05205588876772083</v>
+        <v>0.0520558887677208</v>
       </c>
       <c r="O693" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P693" t="n">
-        <v>0.002425885792256964</v>
+        <v>0.0024258857922569</v>
       </c>
     </row>
     <row r="694">
@@ -40655,16 +40655,538 @@
         <v>18.122404</v>
       </c>
       <c r="M694" t="n">
-        <v>0.03478758026211629</v>
+        <v>0.0347875802621162</v>
       </c>
       <c r="N694" t="n">
         <v>0.0689710176796552</v>
       </c>
       <c r="O694" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.0496300029754638</v>
       </c>
       <c r="P694" t="n">
-        <v>0.01934101470419133</v>
+        <v>0.0193410147041913</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>339.75</v>
+      </c>
+      <c r="F695" t="n">
+        <v>4958372495360</v>
+      </c>
+      <c r="G695" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H695" t="n">
+        <v>9.5886</v>
+      </c>
+      <c r="I695" t="n">
+        <v>39.00689</v>
+      </c>
+      <c r="J695" t="n">
+        <v>35.4327</v>
+      </c>
+      <c r="K695" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L695" t="n">
+        <v>10.621526</v>
+      </c>
+      <c r="M695" t="n">
+        <v>0.0256364974245769</v>
+      </c>
+      <c r="N695" t="n">
+        <v>0.02822251655629139</v>
+      </c>
+      <c r="O695" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P695" t="n">
+        <v>-0.02145748279521007</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>623.77</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1018288996352</v>
+      </c>
+      <c r="G696" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H696" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I696" t="n">
+        <v>158.31726</v>
+      </c>
+      <c r="J696" t="n">
+        <v>40.060524</v>
+      </c>
+      <c r="K696" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L696" t="n">
+        <v>24.652922</v>
+      </c>
+      <c r="M696" t="n">
+        <v>0.006316430735687834</v>
+      </c>
+      <c r="N696" t="n">
+        <v>0.0249622296679866</v>
+      </c>
+      <c r="O696" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P696" t="n">
+        <v>-0.02471776968351486</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>254.98</v>
+      </c>
+      <c r="F697" t="n">
+        <v>2750293999616</v>
+      </c>
+      <c r="G697" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H697" t="n">
+        <v>10.38846</v>
+      </c>
+      <c r="I697" t="n">
+        <v>20.513273</v>
+      </c>
+      <c r="J697" t="n">
+        <v>24.544542</v>
+      </c>
+      <c r="K697" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L697" t="n">
+        <v>3.5456553</v>
+      </c>
+      <c r="M697" t="n">
+        <v>0.04874892148403796</v>
+      </c>
+      <c r="N697" t="n">
+        <v>0.04074225429445447</v>
+      </c>
+      <c r="O697" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P697" t="n">
+        <v>-0.008937745057046996</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="F698" t="n">
+        <v>1740179111936</v>
+      </c>
+      <c r="G698" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H698" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I698" t="n">
+        <v>46.556835</v>
+      </c>
+      <c r="J698" t="n">
+        <v>18.80632</v>
+      </c>
+      <c r="K698" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L698" t="n">
+        <v>19.529753</v>
+      </c>
+      <c r="M698" t="n">
+        <v>0.02147912437592582</v>
+      </c>
+      <c r="N698" t="n">
+        <v>0.05317361606408075</v>
+      </c>
+      <c r="O698" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P698" t="n">
+        <v>0.003493616712579292</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>347.41</v>
+      </c>
+      <c r="F699" t="n">
+        <v>4248801902592</v>
+      </c>
+      <c r="G699" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H699" t="n">
+        <v>14.88187</v>
+      </c>
+      <c r="I699" t="n">
+        <v>17.43151</v>
+      </c>
+      <c r="J699" t="n">
+        <v>23.344513</v>
+      </c>
+      <c r="K699" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L699" t="n">
+        <v>9.529325500000001</v>
+      </c>
+      <c r="M699" t="n">
+        <v>0.05736737572320889</v>
+      </c>
+      <c r="N699" t="n">
+        <v>0.04283661955614403</v>
+      </c>
+      <c r="O699" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P699" t="n">
+        <v>-0.006843379795357429</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>736.595</v>
+      </c>
+      <c r="F700" t="n">
+        <v>1876480229376</v>
+      </c>
+      <c r="G700" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H700" t="n">
+        <v>34.83968</v>
+      </c>
+      <c r="I700" t="n">
+        <v>27.754143</v>
+      </c>
+      <c r="J700" t="n">
+        <v>21.142416</v>
+      </c>
+      <c r="K700" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L700" t="n">
+        <v>8.221271</v>
+      </c>
+      <c r="M700" t="n">
+        <v>0.03603065456594193</v>
+      </c>
+      <c r="N700" t="n">
+        <v>0.04729828467475343</v>
+      </c>
+      <c r="O700" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P700" t="n">
+        <v>-0.002381714676748033</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>498</v>
+      </c>
+      <c r="F701" t="n">
+        <v>3697921753088</v>
+      </c>
+      <c r="G701" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H701" t="n">
+        <v>23.67588</v>
+      </c>
+      <c r="I701" t="n">
+        <v>27.728287</v>
+      </c>
+      <c r="J701" t="n">
+        <v>21.034065</v>
+      </c>
+      <c r="K701" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L701" t="n">
+        <v>11.143723</v>
+      </c>
+      <c r="M701" t="n">
+        <v>0.03606425702811245</v>
+      </c>
+      <c r="N701" t="n">
+        <v>0.04754192771084337</v>
+      </c>
+      <c r="O701" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P701" t="n">
+        <v>-0.002138071640658087</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="F702" t="n">
+        <v>300469911552</v>
+      </c>
+      <c r="G702" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H702" t="n">
+        <v>3.81322</v>
+      </c>
+      <c r="I702" t="n">
+        <v>22.691824</v>
+      </c>
+      <c r="J702" t="n">
+        <v>18.92364</v>
+      </c>
+      <c r="K702" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L702" t="n">
+        <v>6.211808</v>
+      </c>
+      <c r="M702" t="n">
+        <v>0.04406873614190688</v>
+      </c>
+      <c r="N702" t="n">
+        <v>0.0528439578713969</v>
+      </c>
+      <c r="O702" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P702" t="n">
+        <v>0.003163958519895434</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:45:55</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>228.87</v>
+      </c>
+      <c r="F703" t="n">
+        <v>5526523478016</v>
+      </c>
+      <c r="G703" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H703" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I703" t="n">
+        <v>28.934261</v>
+      </c>
+      <c r="J703" t="n">
+        <v>14.593853</v>
+      </c>
+      <c r="K703" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L703" t="n">
+        <v>18.241158</v>
+      </c>
+      <c r="M703" t="n">
+        <v>0.03456110455717219</v>
+      </c>
+      <c r="N703" t="n">
+        <v>0.06852199938829903</v>
+      </c>
+      <c r="O703" t="n">
+        <v>0.04967999935150146</v>
+      </c>
+      <c r="P703" t="n">
+        <v>0.01884200003679757</v>
       </c>
     </row>
   </sheetData>
@@ -40766,12 +41288,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -40785,51 +41307,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>350.87</v>
+        <v>347.41</v>
       </c>
       <c r="F2" t="n">
-        <v>4291117187072</v>
+        <v>4248801902592</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
         <v>14.88187</v>
       </c>
       <c r="I2" t="n">
-        <v>17.596289</v>
+        <v>17.43151</v>
       </c>
       <c r="J2" t="n">
-        <v>23.57701</v>
+        <v>23.344513</v>
       </c>
       <c r="K2" t="n">
         <v>1.25</v>
       </c>
       <c r="L2" t="n">
-        <v>9.624231</v>
+        <v>9.529325500000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05683016501838288</v>
+        <v>0.05736737572320889</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04241419899107932</v>
+        <v>0.04283661955614403</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007215803984384553</v>
+        <v>-0.006843379795357429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -40843,51 +41365,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="F3" t="n">
-        <v>3724727812096</v>
+        <v>3697921753088</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.96</v>
       </c>
       <c r="H3" t="n">
         <v>23.67588</v>
       </c>
       <c r="I3" t="n">
-        <v>27.913746</v>
+        <v>27.728287</v>
       </c>
       <c r="J3" t="n">
-        <v>21.18654</v>
+        <v>21.034065</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="L3" t="n">
-        <v>11.224503</v>
+        <v>11.143723</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03582464464424553</v>
+        <v>0.03606425702811245</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04719977671896493</v>
+        <v>0.04754192771084337</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002430226256498941</v>
+        <v>-0.002138071640658087</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -40901,51 +41423,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>741.245</v>
+        <v>736.595</v>
       </c>
       <c r="F4" t="n">
-        <v>1888326254592</v>
+        <v>1876480229376</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.54</v>
       </c>
       <c r="H4" t="n">
         <v>34.83968</v>
       </c>
       <c r="I4" t="n">
-        <v>27.908321</v>
+        <v>27.754143</v>
       </c>
       <c r="J4" t="n">
-        <v>21.275885</v>
+        <v>21.142416</v>
       </c>
       <c r="K4" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="L4" t="n">
-        <v>8.27317</v>
+        <v>8.221271</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03583160763310377</v>
+        <v>0.03603065456594193</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04700157168007879</v>
+        <v>0.04729828467475343</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.002628431295385078</v>
+        <v>-0.002381714676748033</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -40959,10 +41481,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258.45</v>
+        <v>254.98</v>
       </c>
       <c r="F5" t="n">
-        <v>2787722657792</v>
+        <v>2750293999616</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -40971,39 +41493,39 @@
         <v>10.38846</v>
       </c>
       <c r="I5" t="n">
-        <v>20.792439</v>
+        <v>20.513273</v>
       </c>
       <c r="J5" t="n">
-        <v>24.878569</v>
+        <v>24.544542</v>
       </c>
       <c r="K5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="L5" t="n">
-        <v>3.593908</v>
+        <v>3.5456553</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04809440897659122</v>
+        <v>0.04874892148403796</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04019524085896692</v>
+        <v>0.04074225429445447</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00943476211649695</v>
+        <v>-0.008937745057046996</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -41017,10 +41539,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>338.98</v>
+        <v>339.75</v>
       </c>
       <c r="F6" t="n">
-        <v>4947135430656</v>
+        <v>4958372495360</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
@@ -41029,39 +41551,39 @@
         <v>9.5886</v>
       </c>
       <c r="I6" t="n">
-        <v>38.918484</v>
+        <v>39.00689</v>
       </c>
       <c r="J6" t="n">
-        <v>35.352398</v>
+        <v>35.4327</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="L6" t="n">
-        <v>10.597455</v>
+        <v>10.621526</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02569473125258127</v>
+        <v>0.0256364974245769</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02828662457962122</v>
+        <v>0.02822251655629139</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02134337839584265</v>
+        <v>-0.02145748279521007</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -41075,10 +41597,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>227.38</v>
+        <v>228.87</v>
       </c>
       <c r="F7" t="n">
-        <v>5490544738304</v>
+        <v>5526523478016</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -41087,39 +41609,39 @@
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.745892</v>
+        <v>28.934261</v>
       </c>
       <c r="J7" t="n">
-        <v>14.498844</v>
+        <v>14.593853</v>
       </c>
       <c r="K7" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L7" t="n">
-        <v>18.122404</v>
+        <v>18.241158</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03478758026211629</v>
+        <v>0.03456110455717219</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0689710176796552</v>
+        <v>0.06852199938829903</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01934101470419133</v>
+        <v>0.01884200003679757</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -41133,51 +41655,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>615.52</v>
+        <v>623.77</v>
       </c>
       <c r="F8" t="n">
-        <v>1004821020672</v>
+        <v>1018288996352</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="H8" t="n">
         <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>157.02042</v>
+        <v>158.31726</v>
       </c>
       <c r="J8" t="n">
-        <v>39.53068</v>
+        <v>40.060524</v>
       </c>
       <c r="K8" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="L8" t="n">
-        <v>24.32686</v>
+        <v>24.652922</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006368598908240188</v>
+        <v>0.006316430735687834</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02529680595269041</v>
+        <v>0.0249622296679866</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02433319702277346</v>
+        <v>-0.02471776968351486</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -41191,10 +41713,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>362.66</v>
+        <v>364.54</v>
       </c>
       <c r="F9" t="n">
-        <v>1731204612096</v>
+        <v>1740179111936</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -41203,39 +41725,39 @@
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>46.31673</v>
+        <v>46.556835</v>
       </c>
       <c r="J9" t="n">
-        <v>18.709333</v>
+        <v>18.80632</v>
       </c>
       <c r="K9" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="L9" t="n">
-        <v>19.429033</v>
+        <v>19.529753</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02159047041305906</v>
+        <v>0.02147912437592582</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05344926377323112</v>
+        <v>0.05317361606408075</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003819260797767253</v>
+        <v>0.003493616712579292</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 17:56:54</t>
+          <t>2026-09-22 17:45:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -41249,40 +41771,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.36</v>
+        <v>72.16</v>
       </c>
       <c r="F10" t="n">
-        <v>305466605568</v>
+        <v>300469911552</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81882</v>
+        <v>3.81322</v>
       </c>
       <c r="I10" t="n">
-        <v>23.069181</v>
+        <v>22.691824</v>
       </c>
       <c r="J10" t="n">
-        <v>19.210123</v>
+        <v>18.92364</v>
       </c>
       <c r="K10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="L10" t="n">
-        <v>6.315108</v>
+        <v>6.211808</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04334787350054526</v>
+        <v>0.04406873614190688</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05205588876772083</v>
+        <v>0.0528439578713969</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04967999935150146</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002425885792256964</v>
+        <v>0.003163958519895434</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P703"/>
+  <dimension ref="A1:P712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40713,16 +40713,16 @@
         <v>10.621526</v>
       </c>
       <c r="M695" t="n">
-        <v>0.0256364974245769</v>
+        <v>0.0256364974245768</v>
       </c>
       <c r="N695" t="n">
-        <v>0.02822251655629139</v>
+        <v>0.0282225165562913</v>
       </c>
       <c r="O695" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P695" t="n">
-        <v>-0.02145748279521007</v>
+        <v>-0.02145748279521</v>
       </c>
     </row>
     <row r="696">
@@ -40771,16 +40771,16 @@
         <v>24.652922</v>
       </c>
       <c r="M696" t="n">
-        <v>0.006316430735687834</v>
+        <v>0.0063164307356878</v>
       </c>
       <c r="N696" t="n">
         <v>0.0249622296679866</v>
       </c>
       <c r="O696" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P696" t="n">
-        <v>-0.02471776968351486</v>
+        <v>-0.0247177696835148</v>
       </c>
     </row>
     <row r="697">
@@ -40829,16 +40829,16 @@
         <v>3.5456553</v>
       </c>
       <c r="M697" t="n">
-        <v>0.04874892148403796</v>
+        <v>0.0487489214840379</v>
       </c>
       <c r="N697" t="n">
-        <v>0.04074225429445447</v>
+        <v>0.0407422542944544</v>
       </c>
       <c r="O697" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P697" t="n">
-        <v>-0.008937745057046996</v>
+        <v>-0.008937745057046901</v>
       </c>
     </row>
     <row r="698">
@@ -40887,16 +40887,16 @@
         <v>19.529753</v>
       </c>
       <c r="M698" t="n">
-        <v>0.02147912437592582</v>
+        <v>0.0214791243759258</v>
       </c>
       <c r="N698" t="n">
-        <v>0.05317361606408075</v>
+        <v>0.0531736160640807</v>
       </c>
       <c r="O698" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P698" t="n">
-        <v>0.003493616712579292</v>
+        <v>0.0034936167125792</v>
       </c>
     </row>
     <row r="699">
@@ -40945,16 +40945,16 @@
         <v>9.529325500000001</v>
       </c>
       <c r="M699" t="n">
-        <v>0.05736737572320889</v>
+        <v>0.0573673757232088</v>
       </c>
       <c r="N699" t="n">
-        <v>0.04283661955614403</v>
+        <v>0.042836619556144</v>
       </c>
       <c r="O699" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P699" t="n">
-        <v>-0.006843379795357429</v>
+        <v>-0.0068433797953574</v>
       </c>
     </row>
     <row r="700">
@@ -41003,16 +41003,16 @@
         <v>8.221271</v>
       </c>
       <c r="M700" t="n">
-        <v>0.03603065456594193</v>
+        <v>0.0360306545659419</v>
       </c>
       <c r="N700" t="n">
-        <v>0.04729828467475343</v>
+        <v>0.0472982846747534</v>
       </c>
       <c r="O700" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P700" t="n">
-        <v>-0.002381714676748033</v>
+        <v>-0.002381714676748</v>
       </c>
     </row>
     <row r="701">
@@ -41061,16 +41061,16 @@
         <v>11.143723</v>
       </c>
       <c r="M701" t="n">
-        <v>0.03606425702811245</v>
+        <v>0.0360642570281124</v>
       </c>
       <c r="N701" t="n">
-        <v>0.04754192771084337</v>
+        <v>0.0475419277108433</v>
       </c>
       <c r="O701" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P701" t="n">
-        <v>-0.002138071640658087</v>
+        <v>-0.002138071640658</v>
       </c>
     </row>
     <row r="702">
@@ -41119,16 +41119,16 @@
         <v>6.211808</v>
       </c>
       <c r="M702" t="n">
-        <v>0.04406873614190688</v>
+        <v>0.0440687361419068</v>
       </c>
       <c r="N702" t="n">
-        <v>0.0528439578713969</v>
+        <v>0.0528439578713968</v>
       </c>
       <c r="O702" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P702" t="n">
-        <v>0.003163958519895434</v>
+        <v>0.0031639585198954</v>
       </c>
     </row>
     <row r="703">
@@ -41177,16 +41177,538 @@
         <v>18.241158</v>
       </c>
       <c r="M703" t="n">
-        <v>0.03456110455717219</v>
+        <v>0.0345611045571721</v>
       </c>
       <c r="N703" t="n">
-        <v>0.06852199938829903</v>
+        <v>0.068521999388299</v>
       </c>
       <c r="O703" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.0496799993515014</v>
       </c>
       <c r="P703" t="n">
-        <v>0.01884200003679757</v>
+        <v>0.0188420000367975</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>337.02</v>
+      </c>
+      <c r="F704" t="n">
+        <v>4918530277376</v>
+      </c>
+      <c r="G704" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H704" t="n">
+        <v>9.559100000000001</v>
+      </c>
+      <c r="I704" t="n">
+        <v>38.604813</v>
+      </c>
+      <c r="J704" t="n">
+        <v>35.256454</v>
+      </c>
+      <c r="K704" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L704" t="n">
+        <v>10.536179</v>
+      </c>
+      <c r="M704" t="n">
+        <v>0.02590350721025459</v>
+      </c>
+      <c r="N704" t="n">
+        <v>0.02836359859948965</v>
+      </c>
+      <c r="O704" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P704" t="n">
+        <v>-0.02277639983648447</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>614.61</v>
+      </c>
+      <c r="F705" t="n">
+        <v>1003335450624</v>
+      </c>
+      <c r="G705" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H705" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I705" t="n">
+        <v>156.38931</v>
+      </c>
+      <c r="J705" t="n">
+        <v>39.472237</v>
+      </c>
+      <c r="K705" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L705" t="n">
+        <v>24.290895</v>
+      </c>
+      <c r="M705" t="n">
+        <v>0.006394298823644263</v>
+      </c>
+      <c r="N705" t="n">
+        <v>0.02533426075071997</v>
+      </c>
+      <c r="O705" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P705" t="n">
+        <v>-0.02580573768525415</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>249.27</v>
+      </c>
+      <c r="F706" t="n">
+        <v>2688704315392</v>
+      </c>
+      <c r="G706" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H706" t="n">
+        <v>10.38846</v>
+      </c>
+      <c r="I706" t="n">
+        <v>20.07005</v>
+      </c>
+      <c r="J706" t="n">
+        <v>23.994894</v>
+      </c>
+      <c r="K706" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L706" t="n">
+        <v>3.4662545</v>
+      </c>
+      <c r="M706" t="n">
+        <v>0.04982549043206162</v>
+      </c>
+      <c r="N706" t="n">
+        <v>0.04167553255506078</v>
+      </c>
+      <c r="O706" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P706" t="n">
+        <v>-0.009464465880913348</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="F707" t="n">
+        <v>1694590828544</v>
+      </c>
+      <c r="G707" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H707" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I707" t="n">
+        <v>45.337166</v>
+      </c>
+      <c r="J707" t="n">
+        <v>18.313643</v>
+      </c>
+      <c r="K707" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L707" t="n">
+        <v>19.018124</v>
+      </c>
+      <c r="M707" t="n">
+        <v>0.02205695935096763</v>
+      </c>
+      <c r="N707" t="n">
+        <v>0.05460410152398659</v>
+      </c>
+      <c r="O707" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P707" t="n">
+        <v>0.003464103088012468</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="F708" t="n">
+        <v>4096783810560</v>
+      </c>
+      <c r="G708" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H708" t="n">
+        <v>14.88187</v>
+      </c>
+      <c r="I708" t="n">
+        <v>16.799398</v>
+      </c>
+      <c r="J708" t="n">
+        <v>22.509268</v>
+      </c>
+      <c r="K708" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L708" t="n">
+        <v>9.1883745</v>
+      </c>
+      <c r="M708" t="n">
+        <v>0.05952594184727446</v>
+      </c>
+      <c r="N708" t="n">
+        <v>0.04442614484446832</v>
+      </c>
+      <c r="O708" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P708" t="n">
+        <v>-0.006713853591505801</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>744.1</v>
+      </c>
+      <c r="F709" t="n">
+        <v>1895599308800</v>
+      </c>
+      <c r="G709" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="H709" t="n">
+        <v>34.83968</v>
+      </c>
+      <c r="I709" t="n">
+        <v>28.058067</v>
+      </c>
+      <c r="J709" t="n">
+        <v>21.35783</v>
+      </c>
+      <c r="K709" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L709" t="n">
+        <v>8.305035999999999</v>
+      </c>
+      <c r="M709" t="n">
+        <v>0.03564037091788738</v>
+      </c>
+      <c r="N709" t="n">
+        <v>0.04682123370514716</v>
+      </c>
+      <c r="O709" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P709" t="n">
+        <v>-0.004318764730826964</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>500.59</v>
+      </c>
+      <c r="F710" t="n">
+        <v>3717153947648</v>
+      </c>
+      <c r="G710" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="H710" t="n">
+        <v>23.67588</v>
+      </c>
+      <c r="I710" t="n">
+        <v>28.075714</v>
+      </c>
+      <c r="J710" t="n">
+        <v>21.14346</v>
+      </c>
+      <c r="K710" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L710" t="n">
+        <v>11.201678</v>
+      </c>
+      <c r="M710" t="n">
+        <v>0.03561797079446253</v>
+      </c>
+      <c r="N710" t="n">
+        <v>0.04729595077808187</v>
+      </c>
+      <c r="O710" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P710" t="n">
+        <v>-0.003844047657892258</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>71.36</v>
+      </c>
+      <c r="F711" t="n">
+        <v>297138716672</v>
+      </c>
+      <c r="G711" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H711" t="n">
+        <v>3.81322</v>
+      </c>
+      <c r="I711" t="n">
+        <v>22.44025</v>
+      </c>
+      <c r="J711" t="n">
+        <v>18.713842</v>
+      </c>
+      <c r="K711" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L711" t="n">
+        <v>6.14294</v>
+      </c>
+      <c r="M711" t="n">
+        <v>0.0445627802690583</v>
+      </c>
+      <c r="N711" t="n">
+        <v>0.05343637892376681</v>
+      </c>
+      <c r="O711" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P711" t="n">
+        <v>0.002296380487792689</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:37:55</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>225.51</v>
+      </c>
+      <c r="F712" t="n">
+        <v>5445389910016</v>
+      </c>
+      <c r="G712" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H712" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I712" t="n">
+        <v>28.473484</v>
+      </c>
+      <c r="J712" t="n">
+        <v>14.379603</v>
+      </c>
+      <c r="K712" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L712" t="n">
+        <v>17.973362</v>
+      </c>
+      <c r="M712" t="n">
+        <v>0.03512039377411202</v>
+      </c>
+      <c r="N712" t="n">
+        <v>0.06954294709768968</v>
+      </c>
+      <c r="O712" t="n">
+        <v>0.05113999843597412</v>
+      </c>
+      <c r="P712" t="n">
+        <v>0.01840294866171556</v>
       </c>
     </row>
   </sheetData>
@@ -41288,12 +41810,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -41307,51 +41829,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>347.41</v>
+        <v>334.98</v>
       </c>
       <c r="F2" t="n">
-        <v>4248801902592</v>
+        <v>4096783810560</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
         <v>14.88187</v>
       </c>
       <c r="I2" t="n">
-        <v>17.43151</v>
+        <v>16.799398</v>
       </c>
       <c r="J2" t="n">
-        <v>23.344513</v>
+        <v>22.509268</v>
       </c>
       <c r="K2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="L2" t="n">
-        <v>9.529325500000001</v>
+        <v>9.1883745</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05736737572320889</v>
+        <v>0.05952594184727446</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04283661955614403</v>
+        <v>0.04442614484446832</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006843379795357429</v>
+        <v>-0.006713853591505801</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -41365,51 +41887,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="F3" t="n">
-        <v>3697921753088</v>
+        <v>3717153947648</v>
       </c>
       <c r="G3" t="n">
-        <v>17.96</v>
+        <v>17.83</v>
       </c>
       <c r="H3" t="n">
         <v>23.67588</v>
       </c>
       <c r="I3" t="n">
-        <v>27.728287</v>
+        <v>28.075714</v>
       </c>
       <c r="J3" t="n">
-        <v>21.034065</v>
+        <v>21.14346</v>
       </c>
       <c r="K3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L3" t="n">
-        <v>11.143723</v>
+        <v>11.201678</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03606425702811245</v>
+        <v>0.03561797079446253</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04754192771084337</v>
+        <v>0.04729595077808187</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002138071640658087</v>
+        <v>-0.003844047657892258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -41423,51 +41945,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>736.595</v>
+        <v>744.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1876480229376</v>
+        <v>1895599308800</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>26.52</v>
       </c>
       <c r="H4" t="n">
         <v>34.83968</v>
       </c>
       <c r="I4" t="n">
-        <v>27.754143</v>
+        <v>28.058067</v>
       </c>
       <c r="J4" t="n">
-        <v>21.142416</v>
+        <v>21.35783</v>
       </c>
       <c r="K4" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="L4" t="n">
-        <v>8.221271</v>
+        <v>8.305035999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03603065456594193</v>
+        <v>0.03564037091788738</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04729828467475343</v>
+        <v>0.04682123370514716</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.002381714676748033</v>
+        <v>-0.004318764730826964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -41481,51 +42003,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.98</v>
+        <v>249.27</v>
       </c>
       <c r="F5" t="n">
-        <v>2750293999616</v>
+        <v>2688704315392</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="H5" t="n">
         <v>10.38846</v>
       </c>
       <c r="I5" t="n">
-        <v>20.513273</v>
+        <v>20.07005</v>
       </c>
       <c r="J5" t="n">
-        <v>24.544542</v>
+        <v>23.994894</v>
       </c>
       <c r="K5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5456553</v>
+        <v>3.4662545</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04874892148403796</v>
+        <v>0.04982549043206162</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04074225429445447</v>
+        <v>0.04167553255506078</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008937745057046996</v>
+        <v>-0.009464465880913348</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -41539,51 +42061,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>339.75</v>
+        <v>337.02</v>
       </c>
       <c r="F6" t="n">
-        <v>4958372495360</v>
+        <v>4918530277376</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5886</v>
+        <v>9.559100000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>39.00689</v>
+        <v>38.604813</v>
       </c>
       <c r="J6" t="n">
-        <v>35.4327</v>
+        <v>35.256454</v>
       </c>
       <c r="K6" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L6" t="n">
-        <v>10.621526</v>
+        <v>10.536179</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0256364974245769</v>
+        <v>0.02590350721025459</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02822251655629139</v>
+        <v>0.02836359859948965</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02145748279521007</v>
+        <v>-0.02277639983648447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -41597,51 +42119,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228.87</v>
+        <v>225.51</v>
       </c>
       <c r="F7" t="n">
-        <v>5526523478016</v>
+        <v>5445389910016</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="H7" t="n">
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.934261</v>
+        <v>28.473484</v>
       </c>
       <c r="J7" t="n">
-        <v>14.593853</v>
+        <v>14.379603</v>
       </c>
       <c r="K7" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="L7" t="n">
-        <v>18.241158</v>
+        <v>17.973362</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03456110455717219</v>
+        <v>0.03512039377411202</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06852199938829903</v>
+        <v>0.06954294709768968</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01884200003679757</v>
+        <v>0.01840294866171556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -41655,51 +42177,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>623.77</v>
+        <v>614.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1018288996352</v>
+        <v>1003335450624</v>
       </c>
       <c r="G8" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="H8" t="n">
         <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>158.31726</v>
+        <v>156.38931</v>
       </c>
       <c r="J8" t="n">
-        <v>40.060524</v>
+        <v>39.472237</v>
       </c>
       <c r="K8" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="L8" t="n">
-        <v>24.652922</v>
+        <v>24.290895</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006316430735687834</v>
+        <v>0.006394298823644263</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0249622296679866</v>
+        <v>0.02533426075071997</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02471776968351486</v>
+        <v>-0.02580573768525415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -41713,10 +42235,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>364.54</v>
+        <v>354.99</v>
       </c>
       <c r="F9" t="n">
-        <v>1740179111936</v>
+        <v>1694590828544</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -41725,39 +42247,39 @@
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>46.556835</v>
+        <v>45.337166</v>
       </c>
       <c r="J9" t="n">
-        <v>18.80632</v>
+        <v>18.313643</v>
       </c>
       <c r="K9" t="n">
         <v>0.36</v>
       </c>
       <c r="L9" t="n">
-        <v>19.529753</v>
+        <v>19.018124</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02147912437592582</v>
+        <v>0.02205695935096763</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05317361606408075</v>
+        <v>0.05460410152398659</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003493616712579292</v>
+        <v>0.003464103088012468</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-22 17:45:55</t>
+          <t>2026-09-23 17:37:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -41771,10 +42293,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>72.16</v>
+        <v>71.36</v>
       </c>
       <c r="F10" t="n">
-        <v>300469911552</v>
+        <v>297138716672</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -41783,28 +42305,28 @@
         <v>3.81322</v>
       </c>
       <c r="I10" t="n">
-        <v>22.691824</v>
+        <v>22.44025</v>
       </c>
       <c r="J10" t="n">
-        <v>18.92364</v>
+        <v>18.713842</v>
       </c>
       <c r="K10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="L10" t="n">
-        <v>6.211808</v>
+        <v>6.14294</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04406873614190688</v>
+        <v>0.0445627802690583</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0528439578713969</v>
+        <v>0.05343637892376681</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04967999935150146</v>
+        <v>0.05113999843597412</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003163958519895434</v>
+        <v>0.002296380487792689</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P712"/>
+  <dimension ref="A1:P721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41235,16 +41235,16 @@
         <v>10.536179</v>
       </c>
       <c r="M704" t="n">
-        <v>0.02590350721025459</v>
+        <v>0.0259035072102545</v>
       </c>
       <c r="N704" t="n">
-        <v>0.02836359859948965</v>
+        <v>0.0283635985994896</v>
       </c>
       <c r="O704" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P704" t="n">
-        <v>-0.02277639983648447</v>
+        <v>-0.0227763998364844</v>
       </c>
     </row>
     <row r="705">
@@ -41293,16 +41293,16 @@
         <v>24.290895</v>
       </c>
       <c r="M705" t="n">
-        <v>0.006394298823644263</v>
+        <v>0.0063942988236442</v>
       </c>
       <c r="N705" t="n">
-        <v>0.02533426075071997</v>
+        <v>0.0253342607507199</v>
       </c>
       <c r="O705" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P705" t="n">
-        <v>-0.02580573768525415</v>
+        <v>-0.0258057376852541</v>
       </c>
     </row>
     <row r="706">
@@ -41351,16 +41351,16 @@
         <v>3.4662545</v>
       </c>
       <c r="M706" t="n">
-        <v>0.04982549043206162</v>
+        <v>0.0498254904320616</v>
       </c>
       <c r="N706" t="n">
-        <v>0.04167553255506078</v>
+        <v>0.0416755325550607</v>
       </c>
       <c r="O706" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P706" t="n">
-        <v>-0.009464465880913348</v>
+        <v>-0.009464465880913301</v>
       </c>
     </row>
     <row r="707">
@@ -41409,16 +41409,16 @@
         <v>19.018124</v>
       </c>
       <c r="M707" t="n">
-        <v>0.02205695935096763</v>
+        <v>0.0220569593509676</v>
       </c>
       <c r="N707" t="n">
-        <v>0.05460410152398659</v>
+        <v>0.0546041015239865</v>
       </c>
       <c r="O707" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P707" t="n">
-        <v>0.003464103088012468</v>
+        <v>0.0034641030880124</v>
       </c>
     </row>
     <row r="708">
@@ -41467,16 +41467,16 @@
         <v>9.1883745</v>
       </c>
       <c r="M708" t="n">
-        <v>0.05952594184727446</v>
+        <v>0.0595259418472744</v>
       </c>
       <c r="N708" t="n">
-        <v>0.04442614484446832</v>
+        <v>0.0444261448444683</v>
       </c>
       <c r="O708" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P708" t="n">
-        <v>-0.006713853591505801</v>
+        <v>-0.0067138535915058</v>
       </c>
     </row>
     <row r="709">
@@ -41525,16 +41525,16 @@
         <v>8.305035999999999</v>
       </c>
       <c r="M709" t="n">
-        <v>0.03564037091788738</v>
+        <v>0.0356403709178873</v>
       </c>
       <c r="N709" t="n">
-        <v>0.04682123370514716</v>
+        <v>0.0468212337051471</v>
       </c>
       <c r="O709" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P709" t="n">
-        <v>-0.004318764730826964</v>
+        <v>-0.0043187647308269</v>
       </c>
     </row>
     <row r="710">
@@ -41583,16 +41583,16 @@
         <v>11.201678</v>
       </c>
       <c r="M710" t="n">
-        <v>0.03561797079446253</v>
+        <v>0.0356179707944625</v>
       </c>
       <c r="N710" t="n">
-        <v>0.04729595077808187</v>
+        <v>0.0472959507780818</v>
       </c>
       <c r="O710" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P710" t="n">
-        <v>-0.003844047657892258</v>
+        <v>-0.0038440476578922</v>
       </c>
     </row>
     <row r="711">
@@ -41644,13 +41644,13 @@
         <v>0.0445627802690583</v>
       </c>
       <c r="N711" t="n">
-        <v>0.05343637892376681</v>
+        <v>0.0534363789237668</v>
       </c>
       <c r="O711" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P711" t="n">
-        <v>0.002296380487792689</v>
+        <v>0.0022963804877926</v>
       </c>
     </row>
     <row r="712">
@@ -41699,16 +41699,538 @@
         <v>17.973362</v>
       </c>
       <c r="M712" t="n">
-        <v>0.03512039377411202</v>
+        <v>0.035120393774112</v>
       </c>
       <c r="N712" t="n">
-        <v>0.06954294709768968</v>
+        <v>0.0695429470976896</v>
       </c>
       <c r="O712" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.0511399984359741</v>
       </c>
       <c r="P712" t="n">
-        <v>0.01840294866171556</v>
+        <v>0.0184029486617155</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>335.92</v>
+      </c>
+      <c r="F713" t="n">
+        <v>4902477103104</v>
+      </c>
+      <c r="G713" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H713" t="n">
+        <v>9.5886</v>
+      </c>
+      <c r="I713" t="n">
+        <v>38.478813</v>
+      </c>
+      <c r="J713" t="n">
+        <v>35.033268</v>
+      </c>
+      <c r="K713" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L713" t="n">
+        <v>10.50179</v>
+      </c>
+      <c r="M713" t="n">
+        <v>0.02598833055489402</v>
+      </c>
+      <c r="N713" t="n">
+        <v>0.02854429626101453</v>
+      </c>
+      <c r="O713" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P713" t="n">
+        <v>-0.0230757007635216</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>629.26</v>
+      </c>
+      <c r="F714" t="n">
+        <v>1027251240960</v>
+      </c>
+      <c r="G714" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H714" t="n">
+        <v>15.57069</v>
+      </c>
+      <c r="I714" t="n">
+        <v>160.11705</v>
+      </c>
+      <c r="J714" t="n">
+        <v>40.41311</v>
+      </c>
+      <c r="K714" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L714" t="n">
+        <v>24.8699</v>
+      </c>
+      <c r="M714" t="n">
+        <v>0.006245431141340622</v>
+      </c>
+      <c r="N714" t="n">
+        <v>0.02474444585703843</v>
+      </c>
+      <c r="O714" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P714" t="n">
+        <v>-0.0268755511674977</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>249.38</v>
+      </c>
+      <c r="F715" t="n">
+        <v>2689890779136</v>
+      </c>
+      <c r="G715" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H715" t="n">
+        <v>10.38846</v>
+      </c>
+      <c r="I715" t="n">
+        <v>20.046625</v>
+      </c>
+      <c r="J715" t="n">
+        <v>24.005484</v>
+      </c>
+      <c r="K715" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L715" t="n">
+        <v>3.467784</v>
+      </c>
+      <c r="M715" t="n">
+        <v>0.04988371160477986</v>
+      </c>
+      <c r="N715" t="n">
+        <v>0.04165714973133371</v>
+      </c>
+      <c r="O715" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P715" t="n">
+        <v>-0.009962847293202425</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>350.36</v>
+      </c>
+      <c r="F716" t="n">
+        <v>1672488943616</v>
+      </c>
+      <c r="G716" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H716" t="n">
+        <v>19.38135</v>
+      </c>
+      <c r="I716" t="n">
+        <v>44.631847</v>
+      </c>
+      <c r="J716" t="n">
+        <v>18.077171</v>
+      </c>
+      <c r="K716" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L716" t="n">
+        <v>18.770077</v>
+      </c>
+      <c r="M716" t="n">
+        <v>0.02240552574494805</v>
+      </c>
+      <c r="N716" t="n">
+        <v>0.05531838680214637</v>
+      </c>
+      <c r="O716" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P716" t="n">
+        <v>0.003698389777610236</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>339.01</v>
+      </c>
+      <c r="F717" t="n">
+        <v>4146070290432</v>
+      </c>
+      <c r="G717" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H717" t="n">
+        <v>14.89921</v>
+      </c>
+      <c r="I717" t="n">
+        <v>17.010035</v>
+      </c>
+      <c r="J717" t="n">
+        <v>22.753555</v>
+      </c>
+      <c r="K717" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L717" t="n">
+        <v>9.298916</v>
+      </c>
+      <c r="M717" t="n">
+        <v>0.05878882628831008</v>
+      </c>
+      <c r="N717" t="n">
+        <v>0.04394917554054453</v>
+      </c>
+      <c r="O717" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P717" t="n">
+        <v>-0.007670821483991605</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>777.59</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1980915384320</v>
+      </c>
+      <c r="G718" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H718" t="n">
+        <v>34.9278</v>
+      </c>
+      <c r="I718" t="n">
+        <v>29.276733</v>
+      </c>
+      <c r="J718" t="n">
+        <v>22.262783</v>
+      </c>
+      <c r="K718" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L718" t="n">
+        <v>8.678823</v>
+      </c>
+      <c r="M718" t="n">
+        <v>0.03415681786031199</v>
+      </c>
+      <c r="N718" t="n">
+        <v>0.04491801592098663</v>
+      </c>
+      <c r="O718" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P718" t="n">
+        <v>-0.006701981103549498</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>497.93</v>
+      </c>
+      <c r="F719" t="n">
+        <v>3697401921536</v>
+      </c>
+      <c r="G719" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H719" t="n">
+        <v>23.67588</v>
+      </c>
+      <c r="I719" t="n">
+        <v>27.70896</v>
+      </c>
+      <c r="J719" t="n">
+        <v>21.031107</v>
+      </c>
+      <c r="K719" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L719" t="n">
+        <v>11.142156</v>
+      </c>
+      <c r="M719" t="n">
+        <v>0.03608941015805434</v>
+      </c>
+      <c r="N719" t="n">
+        <v>0.04754861125057739</v>
+      </c>
+      <c r="O719" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P719" t="n">
+        <v>-0.004071385773958741</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="F720" t="n">
+        <v>298637754368</v>
+      </c>
+      <c r="G720" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H720" t="n">
+        <v>3.81322</v>
+      </c>
+      <c r="I720" t="n">
+        <v>22.55346</v>
+      </c>
+      <c r="J720" t="n">
+        <v>18.808252</v>
+      </c>
+      <c r="K720" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L720" t="n">
+        <v>6.1739306</v>
+      </c>
+      <c r="M720" t="n">
+        <v>0.04433909648633575</v>
+      </c>
+      <c r="N720" t="n">
+        <v>0.05316815393195761</v>
+      </c>
+      <c r="O720" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P720" t="n">
+        <v>0.00154815690742148</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>224.58</v>
+      </c>
+      <c r="F721" t="n">
+        <v>5422933082112</v>
+      </c>
+      <c r="G721" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H721" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I721" t="n">
+        <v>28.35606</v>
+      </c>
+      <c r="J721" t="n">
+        <v>14.320303</v>
+      </c>
+      <c r="K721" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L721" t="n">
+        <v>17.89924</v>
+      </c>
+      <c r="M721" t="n">
+        <v>0.03526582954849052</v>
+      </c>
+      <c r="N721" t="n">
+        <v>0.06983092884495502</v>
+      </c>
+      <c r="O721" t="n">
+        <v>0.05161999702453613</v>
+      </c>
+      <c r="P721" t="n">
+        <v>0.01821093182041889</v>
       </c>
     </row>
   </sheetData>
@@ -41810,12 +42332,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -41829,51 +42351,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>334.98</v>
+        <v>339.01</v>
       </c>
       <c r="F2" t="n">
-        <v>4096783810560</v>
+        <v>4146070290432</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>14.88187</v>
+        <v>14.89921</v>
       </c>
       <c r="I2" t="n">
-        <v>16.799398</v>
+        <v>17.010035</v>
       </c>
       <c r="J2" t="n">
-        <v>22.509268</v>
+        <v>22.753555</v>
       </c>
       <c r="K2" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="L2" t="n">
-        <v>9.1883745</v>
+        <v>9.298916</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05952594184727446</v>
+        <v>0.05878882628831008</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04442614484446832</v>
+        <v>0.04394917554054453</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006713853591505801</v>
+        <v>-0.007670821483991605</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -41887,51 +42409,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="F3" t="n">
-        <v>3717153947648</v>
+        <v>3697401921536</v>
       </c>
       <c r="G3" t="n">
-        <v>17.83</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
         <v>23.67588</v>
       </c>
       <c r="I3" t="n">
-        <v>28.075714</v>
+        <v>27.70896</v>
       </c>
       <c r="J3" t="n">
-        <v>21.14346</v>
+        <v>21.031107</v>
       </c>
       <c r="K3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="L3" t="n">
-        <v>11.201678</v>
+        <v>11.142156</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03561797079446253</v>
+        <v>0.03608941015805434</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04729595077808187</v>
+        <v>0.04754861125057739</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.003844047657892258</v>
+        <v>-0.004071385773958741</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -41945,51 +42467,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>744.1</v>
+        <v>777.59</v>
       </c>
       <c r="F4" t="n">
-        <v>1895599308800</v>
+        <v>1980915384320</v>
       </c>
       <c r="G4" t="n">
-        <v>26.52</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
-        <v>34.83968</v>
+        <v>34.9278</v>
       </c>
       <c r="I4" t="n">
-        <v>28.058067</v>
+        <v>29.276733</v>
       </c>
       <c r="J4" t="n">
-        <v>21.35783</v>
+        <v>22.262783</v>
       </c>
       <c r="K4" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="L4" t="n">
-        <v>8.305035999999999</v>
+        <v>8.678823</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03564037091788738</v>
+        <v>0.03415681786031199</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04682123370514716</v>
+        <v>0.04491801592098663</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.004318764730826964</v>
+        <v>-0.006701981103549498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -42003,51 +42525,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>249.27</v>
+        <v>249.38</v>
       </c>
       <c r="F5" t="n">
-        <v>2688704315392</v>
+        <v>2689890779136</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
         <v>10.38846</v>
       </c>
       <c r="I5" t="n">
-        <v>20.07005</v>
+        <v>20.046625</v>
       </c>
       <c r="J5" t="n">
-        <v>23.994894</v>
+        <v>24.005484</v>
       </c>
       <c r="K5" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4662545</v>
+        <v>3.467784</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04982549043206162</v>
+        <v>0.04988371160477986</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04167553255506078</v>
+        <v>0.04165714973133371</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009464465880913348</v>
+        <v>-0.009962847293202425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -42061,51 +42583,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>337.02</v>
+        <v>335.92</v>
       </c>
       <c r="F6" t="n">
-        <v>4918530277376</v>
+        <v>4902477103104</v>
       </c>
       <c r="G6" t="n">
         <v>8.73</v>
       </c>
       <c r="H6" t="n">
-        <v>9.559100000000001</v>
+        <v>9.5886</v>
       </c>
       <c r="I6" t="n">
-        <v>38.604813</v>
+        <v>38.478813</v>
       </c>
       <c r="J6" t="n">
-        <v>35.256454</v>
+        <v>35.033268</v>
       </c>
       <c r="K6" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="L6" t="n">
-        <v>10.536179</v>
+        <v>10.50179</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02590350721025459</v>
+        <v>0.02598833055489402</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02836359859948965</v>
+        <v>0.02854429626101453</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02277639983648447</v>
+        <v>-0.0230757007635216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -42119,10 +42641,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>225.51</v>
+        <v>224.58</v>
       </c>
       <c r="F7" t="n">
-        <v>5445389910016</v>
+        <v>5422933082112</v>
       </c>
       <c r="G7" t="n">
         <v>7.92</v>
@@ -42131,39 +42653,39 @@
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.473484</v>
+        <v>28.35606</v>
       </c>
       <c r="J7" t="n">
-        <v>14.379603</v>
+        <v>14.320303</v>
       </c>
       <c r="K7" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="L7" t="n">
-        <v>17.973362</v>
+        <v>17.89924</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03512039377411202</v>
+        <v>0.03526582954849052</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06954294709768968</v>
+        <v>0.06983092884495502</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01840294866171556</v>
+        <v>0.01821093182041889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -42177,10 +42699,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>614.61</v>
+        <v>629.26</v>
       </c>
       <c r="F8" t="n">
-        <v>1003335450624</v>
+        <v>1027251240960</v>
       </c>
       <c r="G8" t="n">
         <v>3.93</v>
@@ -42189,39 +42711,39 @@
         <v>15.57069</v>
       </c>
       <c r="I8" t="n">
-        <v>156.38931</v>
+        <v>160.11705</v>
       </c>
       <c r="J8" t="n">
-        <v>39.472237</v>
+        <v>40.41311</v>
       </c>
       <c r="K8" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="L8" t="n">
-        <v>24.290895</v>
+        <v>24.8699</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006394298823644263</v>
+        <v>0.006245431141340622</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02533426075071997</v>
+        <v>0.02474444585703843</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02580573768525415</v>
+        <v>-0.0268755511674977</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -42235,51 +42757,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>354.99</v>
+        <v>350.36</v>
       </c>
       <c r="F9" t="n">
-        <v>1694590828544</v>
+        <v>1672488943616</v>
       </c>
       <c r="G9" t="n">
-        <v>7.83</v>
+        <v>7.85</v>
       </c>
       <c r="H9" t="n">
-        <v>19.38391</v>
+        <v>19.38135</v>
       </c>
       <c r="I9" t="n">
-        <v>45.337166</v>
+        <v>44.631847</v>
       </c>
       <c r="J9" t="n">
-        <v>18.313643</v>
+        <v>18.077171</v>
       </c>
       <c r="K9" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.018124</v>
+        <v>18.770077</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02205695935096763</v>
+        <v>0.02240552574494805</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05460410152398659</v>
+        <v>0.05531838680214637</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003464103088012468</v>
+        <v>0.003698389777610236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-23 17:37:55</t>
+          <t>2026-09-24 17:38:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -42293,10 +42815,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.36</v>
+        <v>71.72</v>
       </c>
       <c r="F10" t="n">
-        <v>297138716672</v>
+        <v>298637754368</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -42305,28 +42827,28 @@
         <v>3.81322</v>
       </c>
       <c r="I10" t="n">
-        <v>22.44025</v>
+        <v>22.55346</v>
       </c>
       <c r="J10" t="n">
-        <v>18.713842</v>
+        <v>18.808252</v>
       </c>
       <c r="K10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="L10" t="n">
-        <v>6.14294</v>
+        <v>6.1739306</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0445627802690583</v>
+        <v>0.04433909648633575</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05343637892376681</v>
+        <v>0.05316815393195761</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05113999843597412</v>
+        <v>0.05161999702453613</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002296380487792689</v>
+        <v>0.00154815690742148</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P721"/>
+  <dimension ref="A1:P730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41757,13 +41757,13 @@
         <v>10.50179</v>
       </c>
       <c r="M713" t="n">
-        <v>0.02598833055489402</v>
+        <v>0.025988330554894</v>
       </c>
       <c r="N713" t="n">
-        <v>0.02854429626101453</v>
+        <v>0.0285442962610145</v>
       </c>
       <c r="O713" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P713" t="n">
         <v>-0.0230757007635216</v>
@@ -41815,13 +41815,13 @@
         <v>24.8699</v>
       </c>
       <c r="M714" t="n">
-        <v>0.006245431141340622</v>
+        <v>0.0062454311413406</v>
       </c>
       <c r="N714" t="n">
-        <v>0.02474444585703843</v>
+        <v>0.0247444458570384</v>
       </c>
       <c r="O714" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P714" t="n">
         <v>-0.0268755511674977</v>
@@ -41873,16 +41873,16 @@
         <v>3.467784</v>
       </c>
       <c r="M715" t="n">
-        <v>0.04988371160477986</v>
+        <v>0.0498837116047798</v>
       </c>
       <c r="N715" t="n">
-        <v>0.04165714973133371</v>
+        <v>0.0416571497313337</v>
       </c>
       <c r="O715" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P715" t="n">
-        <v>-0.009962847293202425</v>
+        <v>-0.0099628472932024</v>
       </c>
     </row>
     <row r="716">
@@ -41931,16 +41931,16 @@
         <v>18.770077</v>
       </c>
       <c r="M716" t="n">
-        <v>0.02240552574494805</v>
+        <v>0.022405525744948</v>
       </c>
       <c r="N716" t="n">
-        <v>0.05531838680214637</v>
+        <v>0.0553183868021463</v>
       </c>
       <c r="O716" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P716" t="n">
-        <v>0.003698389777610236</v>
+        <v>0.0036983897776102</v>
       </c>
     </row>
     <row r="717">
@@ -41989,16 +41989,16 @@
         <v>9.298916</v>
       </c>
       <c r="M717" t="n">
-        <v>0.05878882628831008</v>
+        <v>0.05878882628831</v>
       </c>
       <c r="N717" t="n">
-        <v>0.04394917554054453</v>
+        <v>0.0439491755405445</v>
       </c>
       <c r="O717" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P717" t="n">
-        <v>-0.007670821483991605</v>
+        <v>-0.0076708214839916</v>
       </c>
     </row>
     <row r="718">
@@ -42047,16 +42047,16 @@
         <v>8.678823</v>
       </c>
       <c r="M718" t="n">
-        <v>0.03415681786031199</v>
+        <v>0.0341568178603119</v>
       </c>
       <c r="N718" t="n">
-        <v>0.04491801592098663</v>
+        <v>0.0449180159209866</v>
       </c>
       <c r="O718" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P718" t="n">
-        <v>-0.006701981103549498</v>
+        <v>-0.0067019811035494</v>
       </c>
     </row>
     <row r="719">
@@ -42105,16 +42105,16 @@
         <v>11.142156</v>
       </c>
       <c r="M719" t="n">
-        <v>0.03608941015805434</v>
+        <v>0.0360894101580543</v>
       </c>
       <c r="N719" t="n">
-        <v>0.04754861125057739</v>
+        <v>0.0475486112505773</v>
       </c>
       <c r="O719" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P719" t="n">
-        <v>-0.004071385773958741</v>
+        <v>-0.0040713857739587</v>
       </c>
     </row>
     <row r="720">
@@ -42163,16 +42163,16 @@
         <v>6.1739306</v>
       </c>
       <c r="M720" t="n">
-        <v>0.04433909648633575</v>
+        <v>0.0443390964863357</v>
       </c>
       <c r="N720" t="n">
-        <v>0.05316815393195761</v>
+        <v>0.0531681539319576</v>
       </c>
       <c r="O720" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P720" t="n">
-        <v>0.00154815690742148</v>
+        <v>0.0015481569074214</v>
       </c>
     </row>
     <row r="721">
@@ -42221,16 +42221,538 @@
         <v>17.89924</v>
       </c>
       <c r="M721" t="n">
-        <v>0.03526582954849052</v>
+        <v>0.0352658295484905</v>
       </c>
       <c r="N721" t="n">
-        <v>0.06983092884495502</v>
+        <v>0.069830928844955</v>
       </c>
       <c r="O721" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.0516199970245361</v>
       </c>
       <c r="P721" t="n">
-        <v>0.01821093182041889</v>
+        <v>0.0182109318204188</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>341.07</v>
+      </c>
+      <c r="F722" t="n">
+        <v>4977636933632</v>
+      </c>
+      <c r="G722" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H722" t="n">
+        <v>9.58535</v>
+      </c>
+      <c r="I722" t="n">
+        <v>39.068733</v>
+      </c>
+      <c r="J722" t="n">
+        <v>35.582424</v>
+      </c>
+      <c r="K722" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L722" t="n">
+        <v>10.662793</v>
+      </c>
+      <c r="M722" t="n">
+        <v>0.02559591872636116</v>
+      </c>
+      <c r="N722" t="n">
+        <v>0.02810376169114845</v>
+      </c>
+      <c r="O722" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P722" t="n">
+        <v>-0.02373623846143945</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>630.63</v>
+      </c>
+      <c r="F723" t="n">
+        <v>1029487722496</v>
+      </c>
+      <c r="G723" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H723" t="n">
+        <v>15.57829</v>
+      </c>
+      <c r="I723" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="J723" t="n">
+        <v>40.48134</v>
+      </c>
+      <c r="K723" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L723" t="n">
+        <v>24.924046</v>
+      </c>
+      <c r="M723" t="n">
+        <v>0.006184291898577613</v>
+      </c>
+      <c r="N723" t="n">
+        <v>0.02470274170274171</v>
+      </c>
+      <c r="O723" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P723" t="n">
+        <v>-0.02713725844984619</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>249.67</v>
+      </c>
+      <c r="F724" t="n">
+        <v>2693018681344</v>
+      </c>
+      <c r="G724" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H724" t="n">
+        <v>10.38846</v>
+      </c>
+      <c r="I724" t="n">
+        <v>20.102255</v>
+      </c>
+      <c r="J724" t="n">
+        <v>24.033398</v>
+      </c>
+      <c r="K724" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L724" t="n">
+        <v>3.4718165</v>
+      </c>
+      <c r="M724" t="n">
+        <v>0.04974566427684544</v>
+      </c>
+      <c r="N724" t="n">
+        <v>0.04160876356790964</v>
+      </c>
+      <c r="O724" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P724" t="n">
+        <v>-0.01023123658467825</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>352.81</v>
+      </c>
+      <c r="F725" t="n">
+        <v>1684184367104</v>
+      </c>
+      <c r="G725" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="H725" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I725" t="n">
+        <v>45.582687</v>
+      </c>
+      <c r="J725" t="n">
+        <v>18.20118</v>
+      </c>
+      <c r="K725" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L725" t="n">
+        <v>18.901333</v>
+      </c>
+      <c r="M725" t="n">
+        <v>0.02193815368045124</v>
+      </c>
+      <c r="N725" t="n">
+        <v>0.05494149825685213</v>
+      </c>
+      <c r="O725" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P725" t="n">
+        <v>0.003101498104264237</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="F726" t="n">
+        <v>4171386060800</v>
+      </c>
+      <c r="G726" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H726" t="n">
+        <v>14.89921</v>
+      </c>
+      <c r="I726" t="n">
+        <v>17.113897</v>
+      </c>
+      <c r="J726" t="n">
+        <v>22.892488</v>
+      </c>
+      <c r="K726" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L726" t="n">
+        <v>9.355695000000001</v>
+      </c>
+      <c r="M726" t="n">
+        <v>0.05843203940424534</v>
+      </c>
+      <c r="N726" t="n">
+        <v>0.04368244986513428</v>
+      </c>
+      <c r="O726" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P726" t="n">
+        <v>-0.008157550287453609</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>751.66</v>
+      </c>
+      <c r="F727" t="n">
+        <v>1914858373120</v>
+      </c>
+      <c r="G727" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="H727" t="n">
+        <v>34.96656</v>
+      </c>
+      <c r="I727" t="n">
+        <v>28.343136</v>
+      </c>
+      <c r="J727" t="n">
+        <v>21.496538</v>
+      </c>
+      <c r="K727" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L727" t="n">
+        <v>8.389412999999999</v>
+      </c>
+      <c r="M727" t="n">
+        <v>0.03528190937391906</v>
+      </c>
+      <c r="N727" t="n">
+        <v>0.04651911768618791</v>
+      </c>
+      <c r="O727" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P727" t="n">
+        <v>-0.00532088246639998</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>516.17</v>
+      </c>
+      <c r="F728" t="n">
+        <v>3832843862016</v>
+      </c>
+      <c r="G728" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H728" t="n">
+        <v>23.67588</v>
+      </c>
+      <c r="I728" t="n">
+        <v>28.788063</v>
+      </c>
+      <c r="J728" t="n">
+        <v>21.801512</v>
+      </c>
+      <c r="K728" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L728" t="n">
+        <v>11.550311</v>
+      </c>
+      <c r="M728" t="n">
+        <v>0.03473661778096364</v>
+      </c>
+      <c r="N728" t="n">
+        <v>0.04586837669759963</v>
+      </c>
+      <c r="O728" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P728" t="n">
+        <v>-0.005971623454988258</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>71.145</v>
+      </c>
+      <c r="F729" t="n">
+        <v>296243462144</v>
+      </c>
+      <c r="G729" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H729" t="n">
+        <v>3.81322</v>
+      </c>
+      <c r="I729" t="n">
+        <v>22.37264</v>
+      </c>
+      <c r="J729" t="n">
+        <v>18.65746</v>
+      </c>
+      <c r="K729" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L729" t="n">
+        <v>6.124432</v>
+      </c>
+      <c r="M729" t="n">
+        <v>0.04469744887202193</v>
+      </c>
+      <c r="N729" t="n">
+        <v>0.05359786351816712</v>
+      </c>
+      <c r="O729" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P729" t="n">
+        <v>0.001757863365579232</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:42:45</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>225.07</v>
+      </c>
+      <c r="F730" t="n">
+        <v>5434765213696</v>
+      </c>
+      <c r="G730" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H730" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I730" t="n">
+        <v>28.453857</v>
+      </c>
+      <c r="J730" t="n">
+        <v>14.351548</v>
+      </c>
+      <c r="K730" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L730" t="n">
+        <v>17.938293</v>
+      </c>
+      <c r="M730" t="n">
+        <v>0.03514462167325721</v>
+      </c>
+      <c r="N730" t="n">
+        <v>0.06967889989780957</v>
+      </c>
+      <c r="O730" t="n">
+        <v>0.05184000015258789</v>
+      </c>
+      <c r="P730" t="n">
+        <v>0.01783889974522167</v>
       </c>
     </row>
   </sheetData>
@@ -42332,12 +42854,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -42351,10 +42873,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>339.01</v>
+        <v>341.08</v>
       </c>
       <c r="F2" t="n">
-        <v>4146070290432</v>
+        <v>4171386060800</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -42363,39 +42885,39 @@
         <v>14.89921</v>
       </c>
       <c r="I2" t="n">
-        <v>17.010035</v>
+        <v>17.113897</v>
       </c>
       <c r="J2" t="n">
-        <v>22.753555</v>
+        <v>22.892488</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.298916</v>
+        <v>9.355695000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05878882628831008</v>
+        <v>0.05843203940424534</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04394917554054453</v>
+        <v>0.04368244986513428</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007670821483991605</v>
+        <v>-0.008157550287453609</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -42409,51 +42931,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="F3" t="n">
-        <v>3697401921536</v>
+        <v>3832843862016</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.93</v>
       </c>
       <c r="H3" t="n">
         <v>23.67588</v>
       </c>
       <c r="I3" t="n">
-        <v>27.70896</v>
+        <v>28.788063</v>
       </c>
       <c r="J3" t="n">
-        <v>21.031107</v>
+        <v>21.801512</v>
       </c>
       <c r="K3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L3" t="n">
-        <v>11.142156</v>
+        <v>11.550311</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03608941015805434</v>
+        <v>0.03473661778096364</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04754861125057739</v>
+        <v>0.04586837669759963</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.004071385773958741</v>
+        <v>-0.005971623454988258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -42467,51 +42989,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>777.59</v>
+        <v>751.66</v>
       </c>
       <c r="F4" t="n">
-        <v>1980915384320</v>
+        <v>1914858373120</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.52</v>
       </c>
       <c r="H4" t="n">
-        <v>34.9278</v>
+        <v>34.96656</v>
       </c>
       <c r="I4" t="n">
-        <v>29.276733</v>
+        <v>28.343136</v>
       </c>
       <c r="J4" t="n">
-        <v>22.262783</v>
+        <v>21.496538</v>
       </c>
       <c r="K4" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="L4" t="n">
-        <v>8.678823</v>
+        <v>8.389412999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03415681786031199</v>
+        <v>0.03528190937391906</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04491801592098663</v>
+        <v>0.04651911768618791</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.006701981103549498</v>
+        <v>-0.00532088246639998</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -42525,51 +43047,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>249.38</v>
+        <v>249.67</v>
       </c>
       <c r="F5" t="n">
-        <v>2689890779136</v>
+        <v>2693018681344</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.42</v>
       </c>
       <c r="H5" t="n">
         <v>10.38846</v>
       </c>
       <c r="I5" t="n">
-        <v>20.046625</v>
+        <v>20.102255</v>
       </c>
       <c r="J5" t="n">
-        <v>24.005484</v>
+        <v>24.033398</v>
       </c>
       <c r="K5" t="n">
         <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.467784</v>
+        <v>3.4718165</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04988371160477986</v>
+        <v>0.04974566427684544</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04165714973133371</v>
+        <v>0.04160876356790964</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009962847293202425</v>
+        <v>-0.01023123658467825</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -42583,51 +43105,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>335.92</v>
+        <v>341.07</v>
       </c>
       <c r="F6" t="n">
-        <v>4902477103104</v>
+        <v>4977636933632</v>
       </c>
       <c r="G6" t="n">
         <v>8.73</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5886</v>
+        <v>9.58535</v>
       </c>
       <c r="I6" t="n">
-        <v>38.478813</v>
+        <v>39.068733</v>
       </c>
       <c r="J6" t="n">
-        <v>35.033268</v>
+        <v>35.582424</v>
       </c>
       <c r="K6" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="L6" t="n">
-        <v>10.50179</v>
+        <v>10.662793</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02598833055489402</v>
+        <v>0.02559591872636116</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02854429626101453</v>
+        <v>0.02810376169114845</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0230757007635216</v>
+        <v>-0.02373623846143945</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -42641,51 +43163,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224.58</v>
+        <v>225.07</v>
       </c>
       <c r="F7" t="n">
-        <v>5422933082112</v>
+        <v>5434765213696</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.35606</v>
+        <v>28.453857</v>
       </c>
       <c r="J7" t="n">
-        <v>14.320303</v>
+        <v>14.351548</v>
       </c>
       <c r="K7" t="n">
         <v>0.48</v>
       </c>
       <c r="L7" t="n">
-        <v>17.89924</v>
+        <v>17.938293</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03526582954849052</v>
+        <v>0.03514462167325721</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06983092884495502</v>
+        <v>0.06967889989780957</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01821093182041889</v>
+        <v>0.01783889974522167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -42699,51 +43221,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>629.26</v>
+        <v>630.63</v>
       </c>
       <c r="F8" t="n">
-        <v>1027251240960</v>
+        <v>1029487722496</v>
       </c>
       <c r="G8" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
-        <v>15.57069</v>
+        <v>15.57829</v>
       </c>
       <c r="I8" t="n">
-        <v>160.11705</v>
+        <v>161.7</v>
       </c>
       <c r="J8" t="n">
-        <v>40.41311</v>
+        <v>40.48134</v>
       </c>
       <c r="K8" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="L8" t="n">
-        <v>24.8699</v>
+        <v>24.924046</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006245431141340622</v>
+        <v>0.006184291898577613</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02474444585703843</v>
+        <v>0.02470274170274171</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0268755511674977</v>
+        <v>-0.02713725844984619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -42757,51 +43279,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>350.36</v>
+        <v>352.81</v>
       </c>
       <c r="F9" t="n">
-        <v>1672488943616</v>
+        <v>1684184367104</v>
       </c>
       <c r="G9" t="n">
-        <v>7.85</v>
+        <v>7.74</v>
       </c>
       <c r="H9" t="n">
-        <v>19.38135</v>
+        <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>44.631847</v>
+        <v>45.582687</v>
       </c>
       <c r="J9" t="n">
-        <v>18.077171</v>
+        <v>18.20118</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>18.770077</v>
+        <v>18.901333</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02240552574494805</v>
+        <v>0.02193815368045124</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05531838680214637</v>
+        <v>0.05494149825685213</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003698389777610236</v>
+        <v>0.003101498104264237</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 17:38:03</t>
+          <t>2026-09-25 17:42:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -42815,10 +43337,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.72</v>
+        <v>71.145</v>
       </c>
       <c r="F10" t="n">
-        <v>298637754368</v>
+        <v>296243462144</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -42827,28 +43349,28 @@
         <v>3.81322</v>
       </c>
       <c r="I10" t="n">
-        <v>22.55346</v>
+        <v>22.37264</v>
       </c>
       <c r="J10" t="n">
-        <v>18.808252</v>
+        <v>18.65746</v>
       </c>
       <c r="K10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1739306</v>
+        <v>6.124432</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04433909648633575</v>
+        <v>0.04469744887202193</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05316815393195761</v>
+        <v>0.05359786351816712</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05161999702453613</v>
+        <v>0.05184000015258789</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00154815690742148</v>
+        <v>0.001757863365579232</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P730"/>
+  <dimension ref="A1:P739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42279,16 +42279,16 @@
         <v>10.662793</v>
       </c>
       <c r="M722" t="n">
-        <v>0.02559591872636116</v>
+        <v>0.0255959187263611</v>
       </c>
       <c r="N722" t="n">
-        <v>0.02810376169114845</v>
+        <v>0.0281037616911484</v>
       </c>
       <c r="O722" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P722" t="n">
-        <v>-0.02373623846143945</v>
+        <v>-0.0237362384614394</v>
       </c>
     </row>
     <row r="723">
@@ -42337,16 +42337,16 @@
         <v>24.924046</v>
       </c>
       <c r="M723" t="n">
-        <v>0.006184291898577613</v>
+        <v>0.0061842918985776</v>
       </c>
       <c r="N723" t="n">
-        <v>0.02470274170274171</v>
+        <v>0.0247027417027417</v>
       </c>
       <c r="O723" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P723" t="n">
-        <v>-0.02713725844984619</v>
+        <v>-0.0271372584498461</v>
       </c>
     </row>
     <row r="724">
@@ -42395,16 +42395,16 @@
         <v>3.4718165</v>
       </c>
       <c r="M724" t="n">
-        <v>0.04974566427684544</v>
+        <v>0.0497456642768454</v>
       </c>
       <c r="N724" t="n">
-        <v>0.04160876356790964</v>
+        <v>0.0416087635679096</v>
       </c>
       <c r="O724" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P724" t="n">
-        <v>-0.01023123658467825</v>
+        <v>-0.0102312365846782</v>
       </c>
     </row>
     <row r="725">
@@ -42453,16 +42453,16 @@
         <v>18.901333</v>
       </c>
       <c r="M725" t="n">
-        <v>0.02193815368045124</v>
+        <v>0.0219381536804512</v>
       </c>
       <c r="N725" t="n">
-        <v>0.05494149825685213</v>
+        <v>0.0549414982568521</v>
       </c>
       <c r="O725" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P725" t="n">
-        <v>0.003101498104264237</v>
+        <v>0.0031014981042642</v>
       </c>
     </row>
     <row r="726">
@@ -42511,16 +42511,16 @@
         <v>9.355695000000001</v>
       </c>
       <c r="M726" t="n">
-        <v>0.05843203940424534</v>
+        <v>0.0584320394042453</v>
       </c>
       <c r="N726" t="n">
-        <v>0.04368244986513428</v>
+        <v>0.0436824498651342</v>
       </c>
       <c r="O726" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P726" t="n">
-        <v>-0.008157550287453609</v>
+        <v>-0.0081575502874536</v>
       </c>
     </row>
     <row r="727">
@@ -42569,16 +42569,16 @@
         <v>8.389412999999999</v>
       </c>
       <c r="M727" t="n">
-        <v>0.03528190937391906</v>
+        <v>0.035281909373919</v>
       </c>
       <c r="N727" t="n">
-        <v>0.04651911768618791</v>
+        <v>0.0465191176861879</v>
       </c>
       <c r="O727" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P727" t="n">
-        <v>-0.00532088246639998</v>
+        <v>-0.0053208824663999</v>
       </c>
     </row>
     <row r="728">
@@ -42627,16 +42627,16 @@
         <v>11.550311</v>
       </c>
       <c r="M728" t="n">
-        <v>0.03473661778096364</v>
+        <v>0.0347366177809636</v>
       </c>
       <c r="N728" t="n">
-        <v>0.04586837669759963</v>
+        <v>0.0458683766975996</v>
       </c>
       <c r="O728" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P728" t="n">
-        <v>-0.005971623454988258</v>
+        <v>-0.0059716234549882</v>
       </c>
     </row>
     <row r="729">
@@ -42685,16 +42685,16 @@
         <v>6.124432</v>
       </c>
       <c r="M729" t="n">
-        <v>0.04469744887202193</v>
+        <v>0.0446974488720219</v>
       </c>
       <c r="N729" t="n">
-        <v>0.05359786351816712</v>
+        <v>0.0535978635181671</v>
       </c>
       <c r="O729" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P729" t="n">
-        <v>0.001757863365579232</v>
+        <v>0.0017578633655792</v>
       </c>
     </row>
     <row r="730">
@@ -42743,16 +42743,538 @@
         <v>17.938293</v>
       </c>
       <c r="M730" t="n">
-        <v>0.03514462167325721</v>
+        <v>0.0351446216732572</v>
       </c>
       <c r="N730" t="n">
-        <v>0.06967889989780957</v>
+        <v>0.0696788998978095</v>
       </c>
       <c r="O730" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.0518400001525878</v>
       </c>
       <c r="P730" t="n">
-        <v>0.01783889974522167</v>
+        <v>0.0178388997452216</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="F731" t="n">
+        <v>4938670276608</v>
+      </c>
+      <c r="G731" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="H731" t="n">
+        <v>9.58535</v>
+      </c>
+      <c r="I731" t="n">
+        <v>39.076214</v>
+      </c>
+      <c r="J731" t="n">
+        <v>35.303875</v>
+      </c>
+      <c r="K731" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L731" t="n">
+        <v>10.579321</v>
+      </c>
+      <c r="M731" t="n">
+        <v>0.02559101654846336</v>
+      </c>
+      <c r="N731" t="n">
+        <v>0.0283255023640662</v>
+      </c>
+      <c r="O731" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P731" t="n">
+        <v>-0.02407450011548703</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>607.87</v>
+      </c>
+      <c r="F732" t="n">
+        <v>992332546048</v>
+      </c>
+      <c r="G732" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H732" t="n">
+        <v>15.57829</v>
+      </c>
+      <c r="I732" t="n">
+        <v>155.46547</v>
+      </c>
+      <c r="J732" t="n">
+        <v>39.02033</v>
+      </c>
+      <c r="K732" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L732" t="n">
+        <v>24.024513</v>
+      </c>
+      <c r="M732" t="n">
+        <v>0.006432296379160018</v>
+      </c>
+      <c r="N732" t="n">
+        <v>0.02562766709987333</v>
+      </c>
+      <c r="O732" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P732" t="n">
+        <v>-0.0267723353796799</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>246.15</v>
+      </c>
+      <c r="F733" t="n">
+        <v>2655051055104</v>
+      </c>
+      <c r="G733" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H733" t="n">
+        <v>10.475</v>
+      </c>
+      <c r="I733" t="n">
+        <v>19.802895</v>
+      </c>
+      <c r="J733" t="n">
+        <v>23.498806</v>
+      </c>
+      <c r="K733" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L733" t="n">
+        <v>3.422869</v>
+      </c>
+      <c r="M733" t="n">
+        <v>0.0504976640260004</v>
+      </c>
+      <c r="N733" t="n">
+        <v>0.04255535242738168</v>
+      </c>
+      <c r="O733" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P733" t="n">
+        <v>-0.009844650052171548</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="F734" t="n">
+        <v>1668717871104</v>
+      </c>
+      <c r="G734" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H734" t="n">
+        <v>19.38135</v>
+      </c>
+      <c r="I734" t="n">
+        <v>44.53121</v>
+      </c>
+      <c r="J734" t="n">
+        <v>18.036411</v>
+      </c>
+      <c r="K734" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L734" t="n">
+        <v>18.727755</v>
+      </c>
+      <c r="M734" t="n">
+        <v>0.02245616042566582</v>
+      </c>
+      <c r="N734" t="n">
+        <v>0.05544340189375519</v>
+      </c>
+      <c r="O734" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P734" t="n">
+        <v>0.003043399414201967</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>339.16</v>
+      </c>
+      <c r="F735" t="n">
+        <v>4147904774144</v>
+      </c>
+      <c r="G735" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H735" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I735" t="n">
+        <v>17.026104</v>
+      </c>
+      <c r="J735" t="n">
+        <v>22.503342</v>
+      </c>
+      <c r="K735" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L735" t="n">
+        <v>9.30303</v>
+      </c>
+      <c r="M735" t="n">
+        <v>0.05873334119589575</v>
+      </c>
+      <c r="N735" t="n">
+        <v>0.04443784644415615</v>
+      </c>
+      <c r="O735" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P735" t="n">
+        <v>-0.007962156035397072</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>715.62</v>
+      </c>
+      <c r="F736" t="n">
+        <v>1823046369280</v>
+      </c>
+      <c r="G736" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="H736" t="n">
+        <v>34.82735</v>
+      </c>
+      <c r="I736" t="n">
+        <v>28.330166</v>
+      </c>
+      <c r="J736" t="n">
+        <v>20.547644</v>
+      </c>
+      <c r="K736" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L736" t="n">
+        <v>7.987165</v>
+      </c>
+      <c r="M736" t="n">
+        <v>0.03529806321790895</v>
+      </c>
+      <c r="N736" t="n">
+        <v>0.04866737933540147</v>
+      </c>
+      <c r="O736" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P736" t="n">
+        <v>-0.00373262314415175</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>509.22</v>
+      </c>
+      <c r="F737" t="n">
+        <v>3781236359168</v>
+      </c>
+      <c r="G737" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H737" t="n">
+        <v>23.67588</v>
+      </c>
+      <c r="I737" t="n">
+        <v>28.353008</v>
+      </c>
+      <c r="J737" t="n">
+        <v>21.507965</v>
+      </c>
+      <c r="K737" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L737" t="n">
+        <v>11.394792</v>
+      </c>
+      <c r="M737" t="n">
+        <v>0.03526962805859943</v>
+      </c>
+      <c r="N737" t="n">
+        <v>0.04649440320490161</v>
+      </c>
+      <c r="O737" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P737" t="n">
+        <v>-0.005905599274651611</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="F738" t="n">
+        <v>288269565952</v>
+      </c>
+      <c r="G738" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H738" t="n">
+        <v>3.81322</v>
+      </c>
+      <c r="I738" t="n">
+        <v>22.404533</v>
+      </c>
+      <c r="J738" t="n">
+        <v>18.15526</v>
+      </c>
+      <c r="K738" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L738" t="n">
+        <v>5.9595823</v>
+      </c>
+      <c r="M738" t="n">
+        <v>0.0446338292647696</v>
+      </c>
+      <c r="N738" t="n">
+        <v>0.0550804564495161</v>
+      </c>
+      <c r="O738" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P738" t="n">
+        <v>0.002680453969962873</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:06:02</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>228.86</v>
+      </c>
+      <c r="F739" t="n">
+        <v>5526282305536</v>
+      </c>
+      <c r="G739" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="H739" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I739" t="n">
+        <v>28.500624</v>
+      </c>
+      <c r="J739" t="n">
+        <v>14.593216</v>
+      </c>
+      <c r="K739" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L739" t="n">
+        <v>18.24036</v>
+      </c>
+      <c r="M739" t="n">
+        <v>0.03508695272218823</v>
+      </c>
+      <c r="N739" t="n">
+        <v>0.0685249934457747</v>
+      </c>
+      <c r="O739" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P739" t="n">
+        <v>0.01612499096622148</v>
       </c>
     </row>
   </sheetData>
@@ -42854,12 +43376,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -42873,51 +43395,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>341.08</v>
+        <v>339.16</v>
       </c>
       <c r="F2" t="n">
-        <v>4171386060800</v>
+        <v>4147904774144</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
-        <v>14.89921</v>
+        <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.113897</v>
+        <v>17.026104</v>
       </c>
       <c r="J2" t="n">
-        <v>22.892488</v>
+        <v>22.503342</v>
       </c>
       <c r="K2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="L2" t="n">
-        <v>9.355695000000001</v>
+        <v>9.30303</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05843203940424534</v>
+        <v>0.05873334119589575</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04368244986513428</v>
+        <v>0.04443784644415615</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.008157550287453609</v>
+        <v>-0.007962156035397072</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -42931,51 +43453,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="F3" t="n">
-        <v>3832843862016</v>
+        <v>3781236359168</v>
       </c>
       <c r="G3" t="n">
-        <v>17.93</v>
+        <v>17.96</v>
       </c>
       <c r="H3" t="n">
         <v>23.67588</v>
       </c>
       <c r="I3" t="n">
-        <v>28.788063</v>
+        <v>28.353008</v>
       </c>
       <c r="J3" t="n">
-        <v>21.801512</v>
+        <v>21.507965</v>
       </c>
       <c r="K3" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="L3" t="n">
-        <v>11.550311</v>
+        <v>11.394792</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03473661778096364</v>
+        <v>0.03526962805859943</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04586837669759963</v>
+        <v>0.04649440320490161</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.005971623454988258</v>
+        <v>-0.005905599274651611</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -42989,51 +43511,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>751.66</v>
+        <v>715.62</v>
       </c>
       <c r="F4" t="n">
-        <v>1914858373120</v>
+        <v>1823046369280</v>
       </c>
       <c r="G4" t="n">
-        <v>26.52</v>
+        <v>25.26</v>
       </c>
       <c r="H4" t="n">
-        <v>34.96656</v>
+        <v>34.82735</v>
       </c>
       <c r="I4" t="n">
-        <v>28.343136</v>
+        <v>28.330166</v>
       </c>
       <c r="J4" t="n">
-        <v>21.496538</v>
+        <v>20.547644</v>
       </c>
       <c r="K4" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="L4" t="n">
-        <v>8.389412999999999</v>
+        <v>7.987165</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03528190937391906</v>
+        <v>0.03529806321790895</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04651911768618791</v>
+        <v>0.04866737933540147</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.00532088246639998</v>
+        <v>-0.00373262314415175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -43047,51 +43569,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>249.67</v>
+        <v>246.15</v>
       </c>
       <c r="F5" t="n">
-        <v>2693018681344</v>
+        <v>2655051055104</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.38846</v>
+        <v>10.475</v>
       </c>
       <c r="I5" t="n">
-        <v>20.102255</v>
+        <v>19.802895</v>
       </c>
       <c r="J5" t="n">
-        <v>24.033398</v>
+        <v>23.498806</v>
       </c>
       <c r="K5" t="n">
         <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4718165</v>
+        <v>3.422869</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04974566427684544</v>
+        <v>0.0504976640260004</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04160876356790964</v>
+        <v>0.04255535242738168</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01023123658467825</v>
+        <v>-0.009844650052171548</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -43105,51 +43627,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>341.07</v>
+        <v>338.4</v>
       </c>
       <c r="F6" t="n">
-        <v>4977636933632</v>
+        <v>4938670276608</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>8.66</v>
       </c>
       <c r="H6" t="n">
         <v>9.58535</v>
       </c>
       <c r="I6" t="n">
-        <v>39.068733</v>
+        <v>39.076214</v>
       </c>
       <c r="J6" t="n">
-        <v>35.582424</v>
+        <v>35.303875</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>10.662793</v>
+        <v>10.579321</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02559591872636116</v>
+        <v>0.02559101654846336</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02810376169114845</v>
+        <v>0.0283255023640662</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02373623846143945</v>
+        <v>-0.02407450011548703</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -43163,51 +43685,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>225.07</v>
+        <v>228.86</v>
       </c>
       <c r="F7" t="n">
-        <v>5434765213696</v>
+        <v>5526282305536</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.453857</v>
+        <v>28.500624</v>
       </c>
       <c r="J7" t="n">
-        <v>14.351548</v>
+        <v>14.593216</v>
       </c>
       <c r="K7" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>17.938293</v>
+        <v>18.24036</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03514462167325721</v>
+        <v>0.03508695272218823</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06967889989780957</v>
+        <v>0.0685249934457747</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01783889974522167</v>
+        <v>0.01612499096622148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -43221,51 +43743,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>630.63</v>
+        <v>607.87</v>
       </c>
       <c r="F8" t="n">
-        <v>1029487722496</v>
+        <v>992332546048</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="H8" t="n">
         <v>15.57829</v>
       </c>
       <c r="I8" t="n">
-        <v>161.7</v>
+        <v>155.46547</v>
       </c>
       <c r="J8" t="n">
-        <v>40.48134</v>
+        <v>39.02033</v>
       </c>
       <c r="K8" t="n">
         <v>0.64</v>
       </c>
       <c r="L8" t="n">
-        <v>24.924046</v>
+        <v>24.024513</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006184291898577613</v>
+        <v>0.006432296379160018</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02470274170274171</v>
+        <v>0.02562766709987333</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02713725844984619</v>
+        <v>-0.0267723353796799</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -43279,51 +43801,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>352.81</v>
+        <v>349.57</v>
       </c>
       <c r="F9" t="n">
-        <v>1684184367104</v>
+        <v>1668717871104</v>
       </c>
       <c r="G9" t="n">
-        <v>7.74</v>
+        <v>7.85</v>
       </c>
       <c r="H9" t="n">
-        <v>19.38391</v>
+        <v>19.38135</v>
       </c>
       <c r="I9" t="n">
-        <v>45.582687</v>
+        <v>44.53121</v>
       </c>
       <c r="J9" t="n">
-        <v>18.20118</v>
+        <v>18.036411</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>18.901333</v>
+        <v>18.727755</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02193815368045124</v>
+        <v>0.02245616042566582</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05494149825685213</v>
+        <v>0.05544340189375519</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003101498104264237</v>
+        <v>0.003043399414201967</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-25 17:42:45</t>
+          <t>2026-09-28 19:06:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -43337,40 +43859,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.145</v>
+        <v>69.23</v>
       </c>
       <c r="F10" t="n">
-        <v>296243462144</v>
+        <v>288269565952</v>
       </c>
       <c r="G10" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="H10" t="n">
         <v>3.81322</v>
       </c>
       <c r="I10" t="n">
-        <v>22.37264</v>
+        <v>22.404533</v>
       </c>
       <c r="J10" t="n">
-        <v>18.65746</v>
+        <v>18.15526</v>
       </c>
       <c r="K10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="L10" t="n">
-        <v>6.124432</v>
+        <v>5.9595823</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04469744887202193</v>
+        <v>0.0446338292647696</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05359786351816712</v>
+        <v>0.0550804564495161</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05240000247955322</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001757863365579232</v>
+        <v>0.002680453969962873</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P739"/>
+  <dimension ref="A1:P748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42801,16 +42801,16 @@
         <v>10.579321</v>
       </c>
       <c r="M731" t="n">
-        <v>0.02559101654846336</v>
+        <v>0.0255910165484633</v>
       </c>
       <c r="N731" t="n">
-        <v>0.0283255023640662</v>
+        <v>0.0283255023640661</v>
       </c>
       <c r="O731" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P731" t="n">
-        <v>-0.02407450011548703</v>
+        <v>-0.024074500115487</v>
       </c>
     </row>
     <row r="732">
@@ -42859,16 +42859,16 @@
         <v>24.024513</v>
       </c>
       <c r="M732" t="n">
-        <v>0.006432296379160018</v>
+        <v>0.00643229637916</v>
       </c>
       <c r="N732" t="n">
-        <v>0.02562766709987333</v>
+        <v>0.0256276670998733</v>
       </c>
       <c r="O732" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P732" t="n">
-        <v>-0.0267723353796799</v>
+        <v>-0.0267723353796798</v>
       </c>
     </row>
     <row r="733">
@@ -42920,13 +42920,13 @@
         <v>0.0504976640260004</v>
       </c>
       <c r="N733" t="n">
-        <v>0.04255535242738168</v>
+        <v>0.0425553524273816</v>
       </c>
       <c r="O733" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P733" t="n">
-        <v>-0.009844650052171548</v>
+        <v>-0.0098446500521715</v>
       </c>
     </row>
     <row r="734">
@@ -42975,16 +42975,16 @@
         <v>18.727755</v>
       </c>
       <c r="M734" t="n">
-        <v>0.02245616042566582</v>
+        <v>0.0224561604256658</v>
       </c>
       <c r="N734" t="n">
-        <v>0.05544340189375519</v>
+        <v>0.0554434018937551</v>
       </c>
       <c r="O734" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P734" t="n">
-        <v>0.003043399414201967</v>
+        <v>0.0030433994142019</v>
       </c>
     </row>
     <row r="735">
@@ -43033,16 +43033,16 @@
         <v>9.30303</v>
       </c>
       <c r="M735" t="n">
-        <v>0.05873334119589575</v>
+        <v>0.0587333411958957</v>
       </c>
       <c r="N735" t="n">
-        <v>0.04443784644415615</v>
+        <v>0.0444378464441561</v>
       </c>
       <c r="O735" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P735" t="n">
-        <v>-0.007962156035397072</v>
+        <v>-0.007962156035396999</v>
       </c>
     </row>
     <row r="736">
@@ -43091,16 +43091,16 @@
         <v>7.987165</v>
       </c>
       <c r="M736" t="n">
-        <v>0.03529806321790895</v>
+        <v>0.0352980632179089</v>
       </c>
       <c r="N736" t="n">
-        <v>0.04866737933540147</v>
+        <v>0.0486673793354014</v>
       </c>
       <c r="O736" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P736" t="n">
-        <v>-0.00373262314415175</v>
+        <v>-0.0037326231441517</v>
       </c>
     </row>
     <row r="737">
@@ -43149,16 +43149,16 @@
         <v>11.394792</v>
       </c>
       <c r="M737" t="n">
-        <v>0.03526962805859943</v>
+        <v>0.0352696280585994</v>
       </c>
       <c r="N737" t="n">
-        <v>0.04649440320490161</v>
+        <v>0.0464944032049016</v>
       </c>
       <c r="O737" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P737" t="n">
-        <v>-0.005905599274651611</v>
+        <v>-0.0059055992746516</v>
       </c>
     </row>
     <row r="738">
@@ -43213,10 +43213,10 @@
         <v>0.0550804564495161</v>
       </c>
       <c r="O738" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P738" t="n">
-        <v>0.002680453969962873</v>
+        <v>0.0026804539699628</v>
       </c>
     </row>
     <row r="739">
@@ -43265,16 +43265,538 @@
         <v>18.24036</v>
       </c>
       <c r="M739" t="n">
-        <v>0.03508695272218823</v>
+        <v>0.0350869527221882</v>
       </c>
       <c r="N739" t="n">
         <v>0.0685249934457747</v>
       </c>
       <c r="O739" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P739" t="n">
-        <v>0.01612499096622148</v>
+        <v>0.0161249909662214</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>329.4</v>
+      </c>
+      <c r="F740" t="n">
+        <v>4807323025408</v>
+      </c>
+      <c r="G740" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H740" t="n">
+        <v>9.58535</v>
+      </c>
+      <c r="I740" t="n">
+        <v>37.73196</v>
+      </c>
+      <c r="J740" t="n">
+        <v>34.36494</v>
+      </c>
+      <c r="K740" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L740" t="n">
+        <v>10.297956</v>
+      </c>
+      <c r="M740" t="n">
+        <v>0.02650273224043716</v>
+      </c>
+      <c r="N740" t="n">
+        <v>0.02909942319368549</v>
+      </c>
+      <c r="O740" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P740" t="n">
+        <v>-0.02345057795072369</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>607.5700000000001</v>
+      </c>
+      <c r="F741" t="n">
+        <v>991842861056</v>
+      </c>
+      <c r="G741" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H741" t="n">
+        <v>15.57829</v>
+      </c>
+      <c r="I741" t="n">
+        <v>161.15915</v>
+      </c>
+      <c r="J741" t="n">
+        <v>39.001072</v>
+      </c>
+      <c r="K741" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L741" t="n">
+        <v>24.012657</v>
+      </c>
+      <c r="M741" t="n">
+        <v>0.00620504633210988</v>
+      </c>
+      <c r="N741" t="n">
+        <v>0.02564032127985253</v>
+      </c>
+      <c r="O741" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P741" t="n">
+        <v>-0.02690967986455665</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>246.67</v>
+      </c>
+      <c r="F742" t="n">
+        <v>2660659888128</v>
+      </c>
+      <c r="G742" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H742" t="n">
+        <v>10.475</v>
+      </c>
+      <c r="I742" t="n">
+        <v>19.84473</v>
+      </c>
+      <c r="J742" t="n">
+        <v>23.548449</v>
+      </c>
+      <c r="K742" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L742" t="n">
+        <v>3.4300997</v>
+      </c>
+      <c r="M742" t="n">
+        <v>0.05039121092958204</v>
+      </c>
+      <c r="N742" t="n">
+        <v>0.04246564235618438</v>
+      </c>
+      <c r="O742" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P742" t="n">
+        <v>-0.0100843587882248</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="F743" t="n">
+        <v>1695116034048</v>
+      </c>
+      <c r="G743" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H743" t="n">
+        <v>19.38135</v>
+      </c>
+      <c r="I743" t="n">
+        <v>45.235672</v>
+      </c>
+      <c r="J743" t="n">
+        <v>18.321737</v>
+      </c>
+      <c r="K743" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L743" t="n">
+        <v>19.024017</v>
+      </c>
+      <c r="M743" t="n">
+        <v>0.02210644888763728</v>
+      </c>
+      <c r="N743" t="n">
+        <v>0.05457997747113489</v>
+      </c>
+      <c r="O743" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P743" t="n">
+        <v>0.002029976326725712</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>337.32</v>
+      </c>
+      <c r="F744" t="n">
+        <v>4125401808896</v>
+      </c>
+      <c r="G744" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H744" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I744" t="n">
+        <v>16.91675</v>
+      </c>
+      <c r="J744" t="n">
+        <v>22.381256</v>
+      </c>
+      <c r="K744" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L744" t="n">
+        <v>9.252560000000001</v>
+      </c>
+      <c r="M744" t="n">
+        <v>0.05911300841930511</v>
+      </c>
+      <c r="N744" t="n">
+        <v>0.04468024427842998</v>
+      </c>
+      <c r="O744" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P744" t="n">
+        <v>-0.007869756865979197</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>738.79</v>
+      </c>
+      <c r="F745" t="n">
+        <v>1882072023040</v>
+      </c>
+      <c r="G745" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="H745" t="n">
+        <v>34.96656</v>
+      </c>
+      <c r="I745" t="n">
+        <v>27.826365</v>
+      </c>
+      <c r="J745" t="n">
+        <v>21.128471</v>
+      </c>
+      <c r="K745" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L745" t="n">
+        <v>8.2457695</v>
+      </c>
+      <c r="M745" t="n">
+        <v>0.03593714045939983</v>
+      </c>
+      <c r="N745" t="n">
+        <v>0.04732949823359819</v>
+      </c>
+      <c r="O745" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P745" t="n">
+        <v>-0.005220502910810991</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>508.96</v>
+      </c>
+      <c r="F746" t="n">
+        <v>3779305668608</v>
+      </c>
+      <c r="G746" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H746" t="n">
+        <v>23.67588</v>
+      </c>
+      <c r="I746" t="n">
+        <v>28.338531</v>
+      </c>
+      <c r="J746" t="n">
+        <v>21.496983</v>
+      </c>
+      <c r="K746" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L746" t="n">
+        <v>11.388973</v>
+      </c>
+      <c r="M746" t="n">
+        <v>0.03528764539453003</v>
+      </c>
+      <c r="N746" t="n">
+        <v>0.04651815466834329</v>
+      </c>
+      <c r="O746" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P746" t="n">
+        <v>-0.006031846476065889</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="F747" t="n">
+        <v>292724965376</v>
+      </c>
+      <c r="G747" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H747" t="n">
+        <v>3.81254</v>
+      </c>
+      <c r="I747" t="n">
+        <v>22.106918</v>
+      </c>
+      <c r="J747" t="n">
+        <v>18.439152</v>
+      </c>
+      <c r="K747" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L747" t="n">
+        <v>6.0516915</v>
+      </c>
+      <c r="M747" t="n">
+        <v>0.04523470839260314</v>
+      </c>
+      <c r="N747" t="n">
+        <v>0.05423243243243243</v>
+      </c>
+      <c r="O747" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P747" t="n">
+        <v>0.001682431288023256</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:21:43</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>227.21</v>
+      </c>
+      <c r="F748" t="n">
+        <v>5486440087552</v>
+      </c>
+      <c r="G748" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="H748" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I748" t="n">
+        <v>28.907125</v>
+      </c>
+      <c r="J748" t="n">
+        <v>14.488005</v>
+      </c>
+      <c r="K748" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L748" t="n">
+        <v>18.108856</v>
+      </c>
+      <c r="M748" t="n">
+        <v>0.0345935478191981</v>
+      </c>
+      <c r="N748" t="n">
+        <v>0.06902262224373927</v>
+      </c>
+      <c r="O748" t="n">
+        <v>0.05255000114440918</v>
+      </c>
+      <c r="P748" t="n">
+        <v>0.01647262109933009</v>
       </c>
     </row>
   </sheetData>
@@ -43376,12 +43898,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -43395,51 +43917,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>339.16</v>
+        <v>337.32</v>
       </c>
       <c r="F2" t="n">
-        <v>4147904774144</v>
+        <v>4125401808896</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.026104</v>
+        <v>16.91675</v>
       </c>
       <c r="J2" t="n">
-        <v>22.503342</v>
+        <v>22.381256</v>
       </c>
       <c r="K2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.30303</v>
+        <v>9.252560000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05873334119589575</v>
+        <v>0.05911300841930511</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04443784644415615</v>
+        <v>0.04468024427842998</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007962156035397072</v>
+        <v>-0.007869756865979197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -43453,10 +43975,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="F3" t="n">
-        <v>3781236359168</v>
+        <v>3779305668608</v>
       </c>
       <c r="G3" t="n">
         <v>17.96</v>
@@ -43465,39 +43987,39 @@
         <v>23.67588</v>
       </c>
       <c r="I3" t="n">
-        <v>28.353008</v>
+        <v>28.338531</v>
       </c>
       <c r="J3" t="n">
-        <v>21.507965</v>
+        <v>21.496983</v>
       </c>
       <c r="K3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>11.394792</v>
+        <v>11.388973</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03526962805859943</v>
+        <v>0.03528764539453003</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04649440320490161</v>
+        <v>0.04651815466834329</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.005905599274651611</v>
+        <v>-0.006031846476065889</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -43511,51 +44033,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>715.62</v>
+        <v>738.79</v>
       </c>
       <c r="F4" t="n">
-        <v>1823046369280</v>
+        <v>1882072023040</v>
       </c>
       <c r="G4" t="n">
-        <v>25.26</v>
+        <v>26.55</v>
       </c>
       <c r="H4" t="n">
-        <v>34.82735</v>
+        <v>34.96656</v>
       </c>
       <c r="I4" t="n">
-        <v>28.330166</v>
+        <v>27.826365</v>
       </c>
       <c r="J4" t="n">
-        <v>20.547644</v>
+        <v>21.128471</v>
       </c>
       <c r="K4" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L4" t="n">
-        <v>7.987165</v>
+        <v>8.2457695</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03529806321790895</v>
+        <v>0.03593714045939983</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04866737933540147</v>
+        <v>0.04732949823359819</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.00373262314415175</v>
+        <v>-0.005220502910810991</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -43569,10 +44091,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>246.15</v>
+        <v>246.67</v>
       </c>
       <c r="F5" t="n">
-        <v>2655051055104</v>
+        <v>2660659888128</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -43581,39 +44103,39 @@
         <v>10.475</v>
       </c>
       <c r="I5" t="n">
-        <v>19.802895</v>
+        <v>19.84473</v>
       </c>
       <c r="J5" t="n">
-        <v>23.498806</v>
+        <v>23.548449</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="L5" t="n">
-        <v>3.422869</v>
+        <v>3.4300997</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0504976640260004</v>
+        <v>0.05039121092958204</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04255535242738168</v>
+        <v>0.04246564235618438</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009844650052171548</v>
+        <v>-0.0100843587882248</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -43627,51 +44149,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>338.4</v>
+        <v>329.4</v>
       </c>
       <c r="F6" t="n">
-        <v>4938670276608</v>
+        <v>4807323025408</v>
       </c>
       <c r="G6" t="n">
-        <v>8.66</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
         <v>9.58535</v>
       </c>
       <c r="I6" t="n">
-        <v>39.076214</v>
+        <v>37.73196</v>
       </c>
       <c r="J6" t="n">
-        <v>35.303875</v>
+        <v>34.36494</v>
       </c>
       <c r="K6" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="L6" t="n">
-        <v>10.579321</v>
+        <v>10.297956</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02559101654846336</v>
+        <v>0.02650273224043716</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0283255023640662</v>
+        <v>0.02909942319368549</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02407450011548703</v>
+        <v>-0.02345057795072369</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -43685,51 +44207,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228.86</v>
+        <v>227.21</v>
       </c>
       <c r="F7" t="n">
-        <v>5526282305536</v>
+        <v>5486440087552</v>
       </c>
       <c r="G7" t="n">
-        <v>8.029999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="H7" t="n">
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.500624</v>
+        <v>28.907125</v>
       </c>
       <c r="J7" t="n">
-        <v>14.593216</v>
+        <v>14.488005</v>
       </c>
       <c r="K7" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L7" t="n">
-        <v>18.24036</v>
+        <v>18.108856</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03508695272218823</v>
+        <v>0.0345935478191981</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0685249934457747</v>
+        <v>0.06902262224373927</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01612499096622148</v>
+        <v>0.01647262109933009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -43743,51 +44265,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>607.87</v>
+        <v>607.5700000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>992332546048</v>
+        <v>991842861056</v>
       </c>
       <c r="G8" t="n">
-        <v>3.91</v>
+        <v>3.77</v>
       </c>
       <c r="H8" t="n">
         <v>15.57829</v>
       </c>
       <c r="I8" t="n">
-        <v>155.46547</v>
+        <v>161.15915</v>
       </c>
       <c r="J8" t="n">
-        <v>39.02033</v>
+        <v>39.001072</v>
       </c>
       <c r="K8" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="L8" t="n">
-        <v>24.024513</v>
+        <v>24.012657</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006432296379160018</v>
+        <v>0.00620504633210988</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02562766709987333</v>
+        <v>0.02564032127985253</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0267723353796799</v>
+        <v>-0.02690967986455665</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -43801,10 +44323,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>349.57</v>
+        <v>355.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1668717871104</v>
+        <v>1695116034048</v>
       </c>
       <c r="G9" t="n">
         <v>7.85</v>
@@ -43813,39 +44335,39 @@
         <v>19.38135</v>
       </c>
       <c r="I9" t="n">
-        <v>44.53121</v>
+        <v>45.235672</v>
       </c>
       <c r="J9" t="n">
-        <v>18.036411</v>
+        <v>18.321737</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>18.727755</v>
+        <v>19.024017</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02245616042566582</v>
+        <v>0.02210644888763728</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05544340189375519</v>
+        <v>0.05457997747113489</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003043399414201967</v>
+        <v>0.002029976326725712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-28 19:06:02</t>
+          <t>2026-09-29 18:21:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -43859,40 +44381,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69.23</v>
+        <v>70.3</v>
       </c>
       <c r="F10" t="n">
-        <v>288269565952</v>
+        <v>292724965376</v>
       </c>
       <c r="G10" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81322</v>
+        <v>3.81254</v>
       </c>
       <c r="I10" t="n">
-        <v>22.404533</v>
+        <v>22.106918</v>
       </c>
       <c r="J10" t="n">
-        <v>18.15526</v>
+        <v>18.439152</v>
       </c>
       <c r="K10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="L10" t="n">
-        <v>5.9595823</v>
+        <v>6.0516915</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0446338292647696</v>
+        <v>0.04523470839260314</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0550804564495161</v>
+        <v>0.05423243243243243</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05255000114440918</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002680453969962873</v>
+        <v>0.001682431288023256</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P748"/>
+  <dimension ref="A1:P757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43323,16 +43323,16 @@
         <v>10.297956</v>
       </c>
       <c r="M740" t="n">
-        <v>0.02650273224043716</v>
+        <v>0.0265027322404371</v>
       </c>
       <c r="N740" t="n">
-        <v>0.02909942319368549</v>
+        <v>0.0290994231936854</v>
       </c>
       <c r="O740" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P740" t="n">
-        <v>-0.02345057795072369</v>
+        <v>-0.0234505779507236</v>
       </c>
     </row>
     <row r="741">
@@ -43381,16 +43381,16 @@
         <v>24.012657</v>
       </c>
       <c r="M741" t="n">
-        <v>0.00620504633210988</v>
+        <v>0.0062050463321098</v>
       </c>
       <c r="N741" t="n">
-        <v>0.02564032127985253</v>
+        <v>0.0256403212798525</v>
       </c>
       <c r="O741" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P741" t="n">
-        <v>-0.02690967986455665</v>
+        <v>-0.0269096798645566</v>
       </c>
     </row>
     <row r="742">
@@ -43439,13 +43439,13 @@
         <v>3.4300997</v>
       </c>
       <c r="M742" t="n">
-        <v>0.05039121092958204</v>
+        <v>0.050391210929582</v>
       </c>
       <c r="N742" t="n">
-        <v>0.04246564235618438</v>
+        <v>0.0424656423561843</v>
       </c>
       <c r="O742" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P742" t="n">
         <v>-0.0100843587882248</v>
@@ -43497,16 +43497,16 @@
         <v>19.024017</v>
       </c>
       <c r="M743" t="n">
-        <v>0.02210644888763728</v>
+        <v>0.0221064488876372</v>
       </c>
       <c r="N743" t="n">
-        <v>0.05457997747113489</v>
+        <v>0.0545799774711348</v>
       </c>
       <c r="O743" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P743" t="n">
-        <v>0.002029976326725712</v>
+        <v>0.0020299763267257</v>
       </c>
     </row>
     <row r="744">
@@ -43555,16 +43555,16 @@
         <v>9.252560000000001</v>
       </c>
       <c r="M744" t="n">
-        <v>0.05911300841930511</v>
+        <v>0.0591130084193051</v>
       </c>
       <c r="N744" t="n">
-        <v>0.04468024427842998</v>
+        <v>0.0446802442784299</v>
       </c>
       <c r="O744" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P744" t="n">
-        <v>-0.007869756865979197</v>
+        <v>-0.0078697568659791</v>
       </c>
     </row>
     <row r="745">
@@ -43613,16 +43613,16 @@
         <v>8.2457695</v>
       </c>
       <c r="M745" t="n">
-        <v>0.03593714045939983</v>
+        <v>0.0359371404593998</v>
       </c>
       <c r="N745" t="n">
-        <v>0.04732949823359819</v>
+        <v>0.0473294982335981</v>
       </c>
       <c r="O745" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P745" t="n">
-        <v>-0.005220502910810991</v>
+        <v>-0.0052205029108109</v>
       </c>
     </row>
     <row r="746">
@@ -43671,16 +43671,16 @@
         <v>11.388973</v>
       </c>
       <c r="M746" t="n">
-        <v>0.03528764539453003</v>
+        <v>0.03528764539453</v>
       </c>
       <c r="N746" t="n">
-        <v>0.04651815466834329</v>
+        <v>0.0465181546683432</v>
       </c>
       <c r="O746" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P746" t="n">
-        <v>-0.006031846476065889</v>
+        <v>-0.0060318464760658</v>
       </c>
     </row>
     <row r="747">
@@ -43729,16 +43729,16 @@
         <v>6.0516915</v>
       </c>
       <c r="M747" t="n">
-        <v>0.04523470839260314</v>
+        <v>0.0452347083926031</v>
       </c>
       <c r="N747" t="n">
-        <v>0.05423243243243243</v>
+        <v>0.0542324324324324</v>
       </c>
       <c r="O747" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P747" t="n">
-        <v>0.001682431288023256</v>
+        <v>0.0016824312880232</v>
       </c>
     </row>
     <row r="748">
@@ -43790,13 +43790,535 @@
         <v>0.0345935478191981</v>
       </c>
       <c r="N748" t="n">
-        <v>0.06902262224373927</v>
+        <v>0.0690226222437392</v>
       </c>
       <c r="O748" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.0525500011444091</v>
       </c>
       <c r="P748" t="n">
-        <v>0.01647262109933009</v>
+        <v>0.01647262109933</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="F749" t="n">
+        <v>4860153954304</v>
+      </c>
+      <c r="G749" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H749" t="n">
+        <v>9.58535</v>
+      </c>
+      <c r="I749" t="n">
+        <v>38.14662</v>
+      </c>
+      <c r="J749" t="n">
+        <v>34.7426</v>
+      </c>
+      <c r="K749" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L749" t="n">
+        <v>10.411128</v>
+      </c>
+      <c r="M749" t="n">
+        <v>0.02621464176325746</v>
+      </c>
+      <c r="N749" t="n">
+        <v>0.02878310611975257</v>
+      </c>
+      <c r="O749" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P749" t="n">
+        <v>-0.02414689609277184</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>611.76</v>
+      </c>
+      <c r="F750" t="n">
+        <v>998682918912</v>
+      </c>
+      <c r="G750" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H750" t="n">
+        <v>15.57829</v>
+      </c>
+      <c r="I750" t="n">
+        <v>154.87595</v>
+      </c>
+      <c r="J750" t="n">
+        <v>39.270035</v>
+      </c>
+      <c r="K750" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L750" t="n">
+        <v>24.178257</v>
+      </c>
+      <c r="M750" t="n">
+        <v>0.006456780436772591</v>
+      </c>
+      <c r="N750" t="n">
+        <v>0.02546470838237217</v>
+      </c>
+      <c r="O750" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P750" t="n">
+        <v>-0.02746529383015224</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>249.15</v>
+      </c>
+      <c r="F751" t="n">
+        <v>2687409848320</v>
+      </c>
+      <c r="G751" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H751" t="n">
+        <v>10.47571</v>
+      </c>
+      <c r="I751" t="n">
+        <v>20.044247</v>
+      </c>
+      <c r="J751" t="n">
+        <v>23.78359</v>
+      </c>
+      <c r="K751" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L751" t="n">
+        <v>3.4645855</v>
+      </c>
+      <c r="M751" t="n">
+        <v>0.04988962472406181</v>
+      </c>
+      <c r="N751" t="n">
+        <v>0.04204579570539835</v>
+      </c>
+      <c r="O751" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P751" t="n">
+        <v>-0.01088420650712606</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="F752" t="n">
+        <v>1676451119104</v>
+      </c>
+      <c r="G752" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="H752" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I752" t="n">
+        <v>45.256443</v>
+      </c>
+      <c r="J752" t="n">
+        <v>18.117605</v>
+      </c>
+      <c r="K752" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L752" t="n">
+        <v>18.814545</v>
+      </c>
+      <c r="M752" t="n">
+        <v>0.02209630114752698</v>
+      </c>
+      <c r="N752" t="n">
+        <v>0.05519493721347419</v>
+      </c>
+      <c r="O752" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P752" t="n">
+        <v>0.002264935000949778</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>340.74</v>
+      </c>
+      <c r="F753" t="n">
+        <v>4167227932672</v>
+      </c>
+      <c r="G753" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H753" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I753" t="n">
+        <v>17.088264</v>
+      </c>
+      <c r="J753" t="n">
+        <v>22.608173</v>
+      </c>
+      <c r="K753" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L753" t="n">
+        <v>9.346368999999999</v>
+      </c>
+      <c r="M753" t="n">
+        <v>0.05851969243411399</v>
+      </c>
+      <c r="N753" t="n">
+        <v>0.04423178963432529</v>
+      </c>
+      <c r="O753" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P753" t="n">
+        <v>-0.008698212578199117</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>725.1799999999999</v>
+      </c>
+      <c r="F754" t="n">
+        <v>1847400464384</v>
+      </c>
+      <c r="G754" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="H754" t="n">
+        <v>34.83566</v>
+      </c>
+      <c r="I754" t="n">
+        <v>27.344645</v>
+      </c>
+      <c r="J754" t="n">
+        <v>20.817175</v>
+      </c>
+      <c r="K754" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L754" t="n">
+        <v>8.093864999999999</v>
+      </c>
+      <c r="M754" t="n">
+        <v>0.03657023083923992</v>
+      </c>
+      <c r="N754" t="n">
+        <v>0.04803725971482942</v>
+      </c>
+      <c r="O754" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P754" t="n">
+        <v>-0.004892742497694988</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="F755" t="n">
+        <v>3808562511872</v>
+      </c>
+      <c r="G755" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H755" t="n">
+        <v>23.64389</v>
+      </c>
+      <c r="I755" t="n">
+        <v>28.542017</v>
+      </c>
+      <c r="J755" t="n">
+        <v>21.692709</v>
+      </c>
+      <c r="K755" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L755" t="n">
+        <v>11.477139</v>
+      </c>
+      <c r="M755" t="n">
+        <v>0.03503606940924157</v>
+      </c>
+      <c r="N755" t="n">
+        <v>0.04609844024176252</v>
+      </c>
+      <c r="O755" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P755" t="n">
+        <v>-0.006831561970761887</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="F756" t="n">
+        <v>289726922752</v>
+      </c>
+      <c r="G756" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H756" t="n">
+        <v>3.81254</v>
+      </c>
+      <c r="I756" t="n">
+        <v>21.880503</v>
+      </c>
+      <c r="J756" t="n">
+        <v>18.250301</v>
+      </c>
+      <c r="K756" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L756" t="n">
+        <v>5.9897113</v>
+      </c>
+      <c r="M756" t="n">
+        <v>0.04570278815751653</v>
+      </c>
+      <c r="N756" t="n">
+        <v>0.0547936188559931</v>
+      </c>
+      <c r="O756" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P756" t="n">
+        <v>0.001863616643468687</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:22:07</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>228.38</v>
+      </c>
+      <c r="F757" t="n">
+        <v>5514691870720</v>
+      </c>
+      <c r="G757" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H757" t="n">
+        <v>15.68263</v>
+      </c>
+      <c r="I757" t="n">
+        <v>28.872314</v>
+      </c>
+      <c r="J757" t="n">
+        <v>14.562609</v>
+      </c>
+      <c r="K757" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L757" t="n">
+        <v>18.202105</v>
+      </c>
+      <c r="M757" t="n">
+        <v>0.03463525702776075</v>
+      </c>
+      <c r="N757" t="n">
+        <v>0.06866901655136176</v>
+      </c>
+      <c r="O757" t="n">
+        <v>0.05293000221252441</v>
+      </c>
+      <c r="P757" t="n">
+        <v>0.01573901433883735</v>
       </c>
     </row>
   </sheetData>
@@ -43898,12 +44420,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -43917,10 +44439,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>337.32</v>
+        <v>340.74</v>
       </c>
       <c r="F2" t="n">
-        <v>4125401808896</v>
+        <v>4167227932672</v>
       </c>
       <c r="G2" t="n">
         <v>19.94</v>
@@ -43929,39 +44451,39 @@
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>16.91675</v>
+        <v>17.088264</v>
       </c>
       <c r="J2" t="n">
-        <v>22.381256</v>
+        <v>22.608173</v>
       </c>
       <c r="K2" t="n">
         <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.252560000000001</v>
+        <v>9.346368999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05911300841930511</v>
+        <v>0.05851969243411399</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04468024427842998</v>
+        <v>0.04423178963432529</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007869756865979197</v>
+        <v>-0.008698212578199117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -43975,51 +44497,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="F3" t="n">
-        <v>3779305668608</v>
+        <v>3808562511872</v>
       </c>
       <c r="G3" t="n">
-        <v>17.96</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
-        <v>23.67588</v>
+        <v>23.64389</v>
       </c>
       <c r="I3" t="n">
-        <v>28.338531</v>
+        <v>28.542017</v>
       </c>
       <c r="J3" t="n">
-        <v>21.496983</v>
+        <v>21.692709</v>
       </c>
       <c r="K3" t="n">
         <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>11.388973</v>
+        <v>11.477139</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03528764539453003</v>
+        <v>0.03503606940924157</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04651815466834329</v>
+        <v>0.04609844024176252</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.006031846476065889</v>
+        <v>-0.006831561970761887</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -44033,51 +44555,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>738.79</v>
+        <v>725.1799999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1882072023040</v>
+        <v>1847400464384</v>
       </c>
       <c r="G4" t="n">
-        <v>26.55</v>
+        <v>26.52</v>
       </c>
       <c r="H4" t="n">
-        <v>34.96656</v>
+        <v>34.83566</v>
       </c>
       <c r="I4" t="n">
-        <v>27.826365</v>
+        <v>27.344645</v>
       </c>
       <c r="J4" t="n">
-        <v>21.128471</v>
+        <v>20.817175</v>
       </c>
       <c r="K4" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L4" t="n">
-        <v>8.2457695</v>
+        <v>8.093864999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03593714045939983</v>
+        <v>0.03657023083923992</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04732949823359819</v>
+        <v>0.04803725971482942</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.005220502910810991</v>
+        <v>-0.004892742497694988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44091,51 +44613,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>246.67</v>
+        <v>249.15</v>
       </c>
       <c r="F5" t="n">
-        <v>2660659888128</v>
+        <v>2687409848320</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.475</v>
+        <v>10.47571</v>
       </c>
       <c r="I5" t="n">
-        <v>19.84473</v>
+        <v>20.044247</v>
       </c>
       <c r="J5" t="n">
-        <v>23.548449</v>
+        <v>23.78359</v>
       </c>
       <c r="K5" t="n">
         <v>1.46</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4300997</v>
+        <v>3.4645855</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05039121092958204</v>
+        <v>0.04988962472406181</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04246564235618438</v>
+        <v>0.04204579570539835</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0100843587882248</v>
+        <v>-0.01088420650712606</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -44149,10 +44671,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>329.4</v>
+        <v>333.02</v>
       </c>
       <c r="F6" t="n">
-        <v>4807323025408</v>
+        <v>4860153954304</v>
       </c>
       <c r="G6" t="n">
         <v>8.73</v>
@@ -44161,39 +44683,39 @@
         <v>9.58535</v>
       </c>
       <c r="I6" t="n">
-        <v>37.73196</v>
+        <v>38.14662</v>
       </c>
       <c r="J6" t="n">
-        <v>34.36494</v>
+        <v>34.7426</v>
       </c>
       <c r="K6" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="L6" t="n">
-        <v>10.297956</v>
+        <v>10.411128</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02650273224043716</v>
+        <v>0.02621464176325746</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02909942319368549</v>
+        <v>0.02878310611975257</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02345057795072369</v>
+        <v>-0.02414689609277184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44207,51 +44729,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>227.21</v>
+        <v>228.38</v>
       </c>
       <c r="F7" t="n">
-        <v>5486440087552</v>
+        <v>5514691870720</v>
       </c>
       <c r="G7" t="n">
-        <v>7.86</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.68263</v>
       </c>
       <c r="I7" t="n">
-        <v>28.907125</v>
+        <v>28.872314</v>
       </c>
       <c r="J7" t="n">
-        <v>14.488005</v>
+        <v>14.562609</v>
       </c>
       <c r="K7" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>18.108856</v>
+        <v>18.202105</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0345935478191981</v>
+        <v>0.03463525702776075</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06902262224373927</v>
+        <v>0.06866901655136176</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01647262109933009</v>
+        <v>0.01573901433883735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -44265,51 +44787,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>607.5700000000001</v>
+        <v>611.76</v>
       </c>
       <c r="F8" t="n">
-        <v>991842861056</v>
+        <v>998682918912</v>
       </c>
       <c r="G8" t="n">
-        <v>3.77</v>
+        <v>3.95</v>
       </c>
       <c r="H8" t="n">
         <v>15.57829</v>
       </c>
       <c r="I8" t="n">
-        <v>161.15915</v>
+        <v>154.87595</v>
       </c>
       <c r="J8" t="n">
-        <v>39.001072</v>
+        <v>39.270035</v>
       </c>
       <c r="K8" t="n">
         <v>0.62</v>
       </c>
       <c r="L8" t="n">
-        <v>24.012657</v>
+        <v>24.178257</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00620504633210988</v>
+        <v>0.006456780436772591</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02564032127985253</v>
+        <v>0.02546470838237217</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02690967986455665</v>
+        <v>-0.02746529383015224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -44323,51 +44845,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>355.1</v>
+        <v>351.19</v>
       </c>
       <c r="F9" t="n">
-        <v>1695116034048</v>
+        <v>1676451119104</v>
       </c>
       <c r="G9" t="n">
-        <v>7.85</v>
+        <v>7.76</v>
       </c>
       <c r="H9" t="n">
-        <v>19.38135</v>
+        <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>45.235672</v>
+        <v>45.256443</v>
       </c>
       <c r="J9" t="n">
-        <v>18.321737</v>
+        <v>18.117605</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.024017</v>
+        <v>18.814545</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02210644888763728</v>
+        <v>0.02209630114752698</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05457997747113489</v>
+        <v>0.05519493721347419</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002029976326725712</v>
+        <v>0.002264935000949778</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 18:21:43</t>
+          <t>2026-09-30 18:22:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -44381,10 +44903,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.3</v>
+        <v>69.58</v>
       </c>
       <c r="F10" t="n">
-        <v>292724965376</v>
+        <v>289726922752</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -44393,28 +44915,28 @@
         <v>3.81254</v>
       </c>
       <c r="I10" t="n">
-        <v>22.106918</v>
+        <v>21.880503</v>
       </c>
       <c r="J10" t="n">
-        <v>18.439152</v>
+        <v>18.250301</v>
       </c>
       <c r="K10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="L10" t="n">
-        <v>6.0516915</v>
+        <v>5.9897113</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04523470839260314</v>
+        <v>0.04570278815751653</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05423243243243243</v>
+        <v>0.0547936188559931</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05255000114440918</v>
+        <v>0.05293000221252441</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001682431288023256</v>
+        <v>0.001863616643468687</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P757"/>
+  <dimension ref="A1:P766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43845,16 +43845,16 @@
         <v>10.411128</v>
       </c>
       <c r="M749" t="n">
-        <v>0.02621464176325746</v>
+        <v>0.0262146417632574</v>
       </c>
       <c r="N749" t="n">
-        <v>0.02878310611975257</v>
+        <v>0.0287831061197525</v>
       </c>
       <c r="O749" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P749" t="n">
-        <v>-0.02414689609277184</v>
+        <v>-0.0241468960927718</v>
       </c>
     </row>
     <row r="750">
@@ -43903,16 +43903,16 @@
         <v>24.178257</v>
       </c>
       <c r="M750" t="n">
-        <v>0.006456780436772591</v>
+        <v>0.0064567804367725</v>
       </c>
       <c r="N750" t="n">
-        <v>0.02546470838237217</v>
+        <v>0.0254647083823721</v>
       </c>
       <c r="O750" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P750" t="n">
-        <v>-0.02746529383015224</v>
+        <v>-0.0274652938301522</v>
       </c>
     </row>
     <row r="751">
@@ -43961,16 +43961,16 @@
         <v>3.4645855</v>
       </c>
       <c r="M751" t="n">
-        <v>0.04988962472406181</v>
+        <v>0.0498896247240618</v>
       </c>
       <c r="N751" t="n">
-        <v>0.04204579570539835</v>
+        <v>0.0420457957053983</v>
       </c>
       <c r="O751" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P751" t="n">
-        <v>-0.01088420650712606</v>
+        <v>-0.010884206507126</v>
       </c>
     </row>
     <row r="752">
@@ -44019,16 +44019,16 @@
         <v>18.814545</v>
       </c>
       <c r="M752" t="n">
-        <v>0.02209630114752698</v>
+        <v>0.0220963011475269</v>
       </c>
       <c r="N752" t="n">
-        <v>0.05519493721347419</v>
+        <v>0.0551949372134741</v>
       </c>
       <c r="O752" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P752" t="n">
-        <v>0.002264935000949778</v>
+        <v>0.0022649350009497</v>
       </c>
     </row>
     <row r="753">
@@ -44077,16 +44077,16 @@
         <v>9.346368999999999</v>
       </c>
       <c r="M753" t="n">
-        <v>0.05851969243411399</v>
+        <v>0.0585196924341139</v>
       </c>
       <c r="N753" t="n">
-        <v>0.04423178963432529</v>
+        <v>0.0442317896343252</v>
       </c>
       <c r="O753" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P753" t="n">
-        <v>-0.008698212578199117</v>
+        <v>-0.0086982125781991</v>
       </c>
     </row>
     <row r="754">
@@ -44135,16 +44135,16 @@
         <v>8.093864999999999</v>
       </c>
       <c r="M754" t="n">
-        <v>0.03657023083923992</v>
+        <v>0.0365702308392399</v>
       </c>
       <c r="N754" t="n">
-        <v>0.04803725971482942</v>
+        <v>0.0480372597148294</v>
       </c>
       <c r="O754" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P754" t="n">
-        <v>-0.004892742497694988</v>
+        <v>-0.0048927424976949</v>
       </c>
     </row>
     <row r="755">
@@ -44193,16 +44193,16 @@
         <v>11.477139</v>
       </c>
       <c r="M755" t="n">
-        <v>0.03503606940924157</v>
+        <v>0.0350360694092415</v>
       </c>
       <c r="N755" t="n">
-        <v>0.04609844024176252</v>
+        <v>0.0460984402417625</v>
       </c>
       <c r="O755" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P755" t="n">
-        <v>-0.006831561970761887</v>
+        <v>-0.0068315619707618</v>
       </c>
     </row>
     <row r="756">
@@ -44251,16 +44251,16 @@
         <v>5.9897113</v>
       </c>
       <c r="M756" t="n">
-        <v>0.04570278815751653</v>
+        <v>0.0457027881575165</v>
       </c>
       <c r="N756" t="n">
         <v>0.0547936188559931</v>
       </c>
       <c r="O756" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P756" t="n">
-        <v>0.001863616643468687</v>
+        <v>0.0018636166434686</v>
       </c>
     </row>
     <row r="757">
@@ -44309,16 +44309,538 @@
         <v>18.202105</v>
       </c>
       <c r="M757" t="n">
-        <v>0.03463525702776075</v>
+        <v>0.0346352570277607</v>
       </c>
       <c r="N757" t="n">
-        <v>0.06866901655136176</v>
+        <v>0.06866901655136171</v>
       </c>
       <c r="O757" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.0529300022125244</v>
       </c>
       <c r="P757" t="n">
-        <v>0.01573901433883735</v>
+        <v>0.0157390143388373</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>330.32</v>
+      </c>
+      <c r="F758" t="n">
+        <v>4820749516800</v>
+      </c>
+      <c r="G758" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H758" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I758" t="n">
+        <v>37.837345</v>
+      </c>
+      <c r="J758" t="n">
+        <v>34.46991</v>
+      </c>
+      <c r="K758" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L758" t="n">
+        <v>10.326718</v>
+      </c>
+      <c r="M758" t="n">
+        <v>0.02642891741341729</v>
+      </c>
+      <c r="N758" t="n">
+        <v>0.02901080770162267</v>
+      </c>
+      <c r="O758" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P758" t="n">
+        <v>-0.02335919218393641</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>615.73</v>
+      </c>
+      <c r="F759" t="n">
+        <v>1005163773952</v>
+      </c>
+      <c r="G759" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H759" t="n">
+        <v>15.58329</v>
+      </c>
+      <c r="I759" t="n">
+        <v>156.27664</v>
+      </c>
+      <c r="J759" t="n">
+        <v>39.512196</v>
+      </c>
+      <c r="K759" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L759" t="n">
+        <v>24.33516</v>
+      </c>
+      <c r="M759" t="n">
+        <v>0.006398908612541211</v>
+      </c>
+      <c r="N759" t="n">
+        <v>0.02530864177480389</v>
+      </c>
+      <c r="O759" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P759" t="n">
+        <v>-0.02706135811075519</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>248.23</v>
+      </c>
+      <c r="F760" t="n">
+        <v>2677486387200</v>
+      </c>
+      <c r="G760" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="H760" t="n">
+        <v>10.47571</v>
+      </c>
+      <c r="I760" t="n">
+        <v>20.034704</v>
+      </c>
+      <c r="J760" t="n">
+        <v>23.695768</v>
+      </c>
+      <c r="K760" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L760" t="n">
+        <v>3.4517922</v>
+      </c>
+      <c r="M760" t="n">
+        <v>0.04991338677839102</v>
+      </c>
+      <c r="N760" t="n">
+        <v>0.04220162752286186</v>
+      </c>
+      <c r="O760" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P760" t="n">
+        <v>-0.01016837236269722</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>343.64</v>
+      </c>
+      <c r="F761" t="n">
+        <v>1640410251264</v>
+      </c>
+      <c r="G761" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H761" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I761" t="n">
+        <v>43.887615</v>
+      </c>
+      <c r="J761" t="n">
+        <v>17.728107</v>
+      </c>
+      <c r="K761" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L761" t="n">
+        <v>18.410063</v>
+      </c>
+      <c r="M761" t="n">
+        <v>0.02278547316959609</v>
+      </c>
+      <c r="N761" t="n">
+        <v>0.05640760679781166</v>
+      </c>
+      <c r="O761" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P761" t="n">
+        <v>0.004037606912252578</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>334.93</v>
+      </c>
+      <c r="F762" t="n">
+        <v>4096171966464</v>
+      </c>
+      <c r="G762" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="H762" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I762" t="n">
+        <v>17.096989</v>
+      </c>
+      <c r="J762" t="n">
+        <v>22.22268</v>
+      </c>
+      <c r="K762" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L762" t="n">
+        <v>9.187002</v>
+      </c>
+      <c r="M762" t="n">
+        <v>0.05848983369659332</v>
+      </c>
+      <c r="N762" t="n">
+        <v>0.04499907443346371</v>
+      </c>
+      <c r="O762" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P762" t="n">
+        <v>-0.007370925452095375</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>725.9299999999999</v>
+      </c>
+      <c r="F763" t="n">
+        <v>1849311100928</v>
+      </c>
+      <c r="G763" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H763" t="n">
+        <v>34.90593</v>
+      </c>
+      <c r="I763" t="n">
+        <v>27.321415</v>
+      </c>
+      <c r="J763" t="n">
+        <v>20.796753</v>
+      </c>
+      <c r="K763" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L763" t="n">
+        <v>8.102237000000001</v>
+      </c>
+      <c r="M763" t="n">
+        <v>0.03660132519664431</v>
+      </c>
+      <c r="N763" t="n">
+        <v>0.04808442962820107</v>
+      </c>
+      <c r="O763" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P763" t="n">
+        <v>-0.004285570257358019</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>512.8</v>
+      </c>
+      <c r="F764" t="n">
+        <v>3807819857920</v>
+      </c>
+      <c r="G764" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H764" t="n">
+        <v>23.64732</v>
+      </c>
+      <c r="I764" t="n">
+        <v>28.568243</v>
+      </c>
+      <c r="J764" t="n">
+        <v>21.685333</v>
+      </c>
+      <c r="K764" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L764" t="n">
+        <v>11.474901</v>
+      </c>
+      <c r="M764" t="n">
+        <v>0.03500390015600624</v>
+      </c>
+      <c r="N764" t="n">
+        <v>0.0461141185647426</v>
+      </c>
+      <c r="O764" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P764" t="n">
+        <v>-0.006255881320816489</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="F765" t="n">
+        <v>282523303936</v>
+      </c>
+      <c r="G765" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H765" t="n">
+        <v>3.813</v>
+      </c>
+      <c r="I765" t="n">
+        <v>21.887096</v>
+      </c>
+      <c r="J765" t="n">
+        <v>17.794388</v>
+      </c>
+      <c r="K765" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L765" t="n">
+        <v>5.8407865</v>
+      </c>
+      <c r="M765" t="n">
+        <v>0.04568901989683125</v>
+      </c>
+      <c r="N765" t="n">
+        <v>0.05619749447310244</v>
+      </c>
+      <c r="O765" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P765" t="n">
+        <v>0.003827494587543355</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:43:57</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>230.86</v>
+      </c>
+      <c r="F766" t="n">
+        <v>5574576046080</v>
+      </c>
+      <c r="G766" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H766" t="n">
+        <v>15.69508</v>
+      </c>
+      <c r="I766" t="n">
+        <v>29.222784</v>
+      </c>
+      <c r="J766" t="n">
+        <v>14.709068</v>
+      </c>
+      <c r="K766" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L766" t="n">
+        <v>18.399761</v>
+      </c>
+      <c r="M766" t="n">
+        <v>0.03421987351641687</v>
+      </c>
+      <c r="N766" t="n">
+        <v>0.06798527245949926</v>
+      </c>
+      <c r="O766" t="n">
+        <v>0.05236999988555908</v>
+      </c>
+      <c r="P766" t="n">
+        <v>0.01561527257394017</v>
       </c>
     </row>
   </sheetData>
@@ -44420,12 +44942,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -44439,51 +44961,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>340.74</v>
+        <v>334.93</v>
       </c>
       <c r="F2" t="n">
-        <v>4167227932672</v>
+        <v>4096171966464</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.59</v>
       </c>
       <c r="H2" t="n">
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.088264</v>
+        <v>17.096989</v>
       </c>
       <c r="J2" t="n">
-        <v>22.608173</v>
+        <v>22.22268</v>
       </c>
       <c r="K2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="L2" t="n">
-        <v>9.346368999999999</v>
+        <v>9.187002</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05851969243411399</v>
+        <v>0.05848983369659332</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04423178963432529</v>
+        <v>0.04499907443346371</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.008698212578199117</v>
+        <v>-0.007370925452095375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -44497,51 +45019,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="F3" t="n">
-        <v>3808562511872</v>
+        <v>3807819857920</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.64389</v>
+        <v>23.64732</v>
       </c>
       <c r="I3" t="n">
-        <v>28.542017</v>
+        <v>28.568243</v>
       </c>
       <c r="J3" t="n">
-        <v>21.692709</v>
+        <v>21.685333</v>
       </c>
       <c r="K3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="L3" t="n">
-        <v>11.477139</v>
+        <v>11.474901</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03503606940924157</v>
+        <v>0.03500390015600624</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04609844024176252</v>
+        <v>0.0461141185647426</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.006831561970761887</v>
+        <v>-0.006255881320816489</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -44555,51 +45077,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>725.1799999999999</v>
+        <v>725.9299999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1847400464384</v>
+        <v>1849311100928</v>
       </c>
       <c r="G4" t="n">
-        <v>26.52</v>
+        <v>26.57</v>
       </c>
       <c r="H4" t="n">
-        <v>34.83566</v>
+        <v>34.90593</v>
       </c>
       <c r="I4" t="n">
-        <v>27.344645</v>
+        <v>27.321415</v>
       </c>
       <c r="J4" t="n">
-        <v>20.817175</v>
+        <v>20.796753</v>
       </c>
       <c r="K4" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L4" t="n">
-        <v>8.093864999999999</v>
+        <v>8.102237000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03657023083923992</v>
+        <v>0.03660132519664431</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04803725971482942</v>
+        <v>0.04808442962820107</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.004892742497694988</v>
+        <v>-0.004285570257358019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44613,51 +45135,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>249.15</v>
+        <v>248.23</v>
       </c>
       <c r="F5" t="n">
-        <v>2687409848320</v>
+        <v>2677486387200</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.39</v>
       </c>
       <c r="H5" t="n">
         <v>10.47571</v>
       </c>
       <c r="I5" t="n">
-        <v>20.044247</v>
+        <v>20.034704</v>
       </c>
       <c r="J5" t="n">
-        <v>23.78359</v>
+        <v>23.695768</v>
       </c>
       <c r="K5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4645855</v>
+        <v>3.4517922</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04988962472406181</v>
+        <v>0.04991338677839102</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04204579570539835</v>
+        <v>0.04220162752286186</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01088420650712606</v>
+        <v>-0.01016837236269722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -44671,51 +45193,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.02</v>
+        <v>330.32</v>
       </c>
       <c r="F6" t="n">
-        <v>4860153954304</v>
+        <v>4820749516800</v>
       </c>
       <c r="G6" t="n">
         <v>8.73</v>
       </c>
       <c r="H6" t="n">
-        <v>9.58535</v>
+        <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.14662</v>
+        <v>37.837345</v>
       </c>
       <c r="J6" t="n">
-        <v>34.7426</v>
+        <v>34.46991</v>
       </c>
       <c r="K6" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.411128</v>
+        <v>10.326718</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02621464176325746</v>
+        <v>0.02642891741341729</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02878310611975257</v>
+        <v>0.02901080770162267</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02414689609277184</v>
+        <v>-0.02335919218393641</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44729,51 +45251,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228.38</v>
+        <v>230.86</v>
       </c>
       <c r="F7" t="n">
-        <v>5514691870720</v>
+        <v>5574576046080</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="H7" t="n">
-        <v>15.68263</v>
+        <v>15.69508</v>
       </c>
       <c r="I7" t="n">
-        <v>28.872314</v>
+        <v>29.222784</v>
       </c>
       <c r="J7" t="n">
-        <v>14.562609</v>
+        <v>14.709068</v>
       </c>
       <c r="K7" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L7" t="n">
-        <v>18.202105</v>
+        <v>18.399761</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03463525702776075</v>
+        <v>0.03421987351641687</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06866901655136176</v>
+        <v>0.06798527245949926</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01573901433883735</v>
+        <v>0.01561527257394017</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -44787,51 +45309,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>611.76</v>
+        <v>615.73</v>
       </c>
       <c r="F8" t="n">
-        <v>998682918912</v>
+        <v>1005163773952</v>
       </c>
       <c r="G8" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="H8" t="n">
-        <v>15.57829</v>
+        <v>15.58329</v>
       </c>
       <c r="I8" t="n">
-        <v>154.87595</v>
+        <v>156.27664</v>
       </c>
       <c r="J8" t="n">
-        <v>39.270035</v>
+        <v>39.512196</v>
       </c>
       <c r="K8" t="n">
         <v>0.62</v>
       </c>
       <c r="L8" t="n">
-        <v>24.178257</v>
+        <v>24.33516</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006456780436772591</v>
+        <v>0.006398908612541211</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02546470838237217</v>
+        <v>0.02530864177480389</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02746529383015224</v>
+        <v>-0.02706135811075519</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -44845,51 +45367,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>351.19</v>
+        <v>343.64</v>
       </c>
       <c r="F9" t="n">
-        <v>1676451119104</v>
+        <v>1640410251264</v>
       </c>
       <c r="G9" t="n">
-        <v>7.76</v>
+        <v>7.83</v>
       </c>
       <c r="H9" t="n">
         <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>45.256443</v>
+        <v>43.887615</v>
       </c>
       <c r="J9" t="n">
-        <v>18.117605</v>
+        <v>17.728107</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>18.814545</v>
+        <v>18.410063</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02209630114752698</v>
+        <v>0.02278547316959609</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05519493721347419</v>
+        <v>0.05640760679781166</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002264935000949778</v>
+        <v>0.004037606912252578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-30 18:22:07</t>
+          <t>2026-10-01 18:43:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -44903,40 +45425,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69.58</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>289726922752</v>
+        <v>282523303936</v>
       </c>
       <c r="G10" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81254</v>
+        <v>3.813</v>
       </c>
       <c r="I10" t="n">
-        <v>21.880503</v>
+        <v>21.887096</v>
       </c>
       <c r="J10" t="n">
-        <v>18.250301</v>
+        <v>17.794388</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="L10" t="n">
-        <v>5.9897113</v>
+        <v>5.8407865</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04570278815751653</v>
+        <v>0.04568901989683125</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0547936188559931</v>
+        <v>0.05619749447310244</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05236999988555908</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001863616643468687</v>
+        <v>0.003827494587543355</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P766"/>
+  <dimension ref="A1:P775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44367,16 +44367,16 @@
         <v>10.326718</v>
       </c>
       <c r="M758" t="n">
-        <v>0.02642891741341729</v>
+        <v>0.0264289174134172</v>
       </c>
       <c r="N758" t="n">
-        <v>0.02901080770162267</v>
+        <v>0.0290108077016226</v>
       </c>
       <c r="O758" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P758" t="n">
-        <v>-0.02335919218393641</v>
+        <v>-0.0233591921839364</v>
       </c>
     </row>
     <row r="759">
@@ -44425,16 +44425,16 @@
         <v>24.33516</v>
       </c>
       <c r="M759" t="n">
-        <v>0.006398908612541211</v>
+        <v>0.0063989086125412</v>
       </c>
       <c r="N759" t="n">
-        <v>0.02530864177480389</v>
+        <v>0.0253086417748038</v>
       </c>
       <c r="O759" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P759" t="n">
-        <v>-0.02706135811075519</v>
+        <v>-0.0270613581107551</v>
       </c>
     </row>
     <row r="760">
@@ -44483,16 +44483,16 @@
         <v>3.4517922</v>
       </c>
       <c r="M760" t="n">
-        <v>0.04991338677839102</v>
+        <v>0.049913386778391</v>
       </c>
       <c r="N760" t="n">
-        <v>0.04220162752286186</v>
+        <v>0.0422016275228618</v>
       </c>
       <c r="O760" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P760" t="n">
-        <v>-0.01016837236269722</v>
+        <v>-0.0101683723626972</v>
       </c>
     </row>
     <row r="761">
@@ -44541,16 +44541,16 @@
         <v>18.410063</v>
       </c>
       <c r="M761" t="n">
-        <v>0.02278547316959609</v>
+        <v>0.022785473169596</v>
       </c>
       <c r="N761" t="n">
-        <v>0.05640760679781166</v>
+        <v>0.0564076067978116</v>
       </c>
       <c r="O761" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P761" t="n">
-        <v>0.004037606912252578</v>
+        <v>0.0040376069122525</v>
       </c>
     </row>
     <row r="762">
@@ -44599,16 +44599,16 @@
         <v>9.187002</v>
       </c>
       <c r="M762" t="n">
-        <v>0.05848983369659332</v>
+        <v>0.0584898336965933</v>
       </c>
       <c r="N762" t="n">
-        <v>0.04499907443346371</v>
+        <v>0.0449990744334637</v>
       </c>
       <c r="O762" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P762" t="n">
-        <v>-0.007370925452095375</v>
+        <v>-0.0073709254520953</v>
       </c>
     </row>
     <row r="763">
@@ -44657,16 +44657,16 @@
         <v>8.102237000000001</v>
       </c>
       <c r="M763" t="n">
-        <v>0.03660132519664431</v>
+        <v>0.0366013251966443</v>
       </c>
       <c r="N763" t="n">
-        <v>0.04808442962820107</v>
+        <v>0.048084429628201</v>
       </c>
       <c r="O763" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P763" t="n">
-        <v>-0.004285570257358019</v>
+        <v>-0.004285570257358</v>
       </c>
     </row>
     <row r="764">
@@ -44715,16 +44715,16 @@
         <v>11.474901</v>
       </c>
       <c r="M764" t="n">
-        <v>0.03500390015600624</v>
+        <v>0.0350039001560062</v>
       </c>
       <c r="N764" t="n">
-        <v>0.0461141185647426</v>
+        <v>0.0461141185647425</v>
       </c>
       <c r="O764" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P764" t="n">
-        <v>-0.006255881320816489</v>
+        <v>-0.0062558813208164</v>
       </c>
     </row>
     <row r="765">
@@ -44773,16 +44773,16 @@
         <v>5.8407865</v>
       </c>
       <c r="M765" t="n">
-        <v>0.04568901989683125</v>
+        <v>0.0456890198968312</v>
       </c>
       <c r="N765" t="n">
-        <v>0.05619749447310244</v>
+        <v>0.0561974944731024</v>
       </c>
       <c r="O765" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P765" t="n">
-        <v>0.003827494587543355</v>
+        <v>0.0038274945875433</v>
       </c>
     </row>
     <row r="766">
@@ -44831,16 +44831,538 @@
         <v>18.399761</v>
       </c>
       <c r="M766" t="n">
-        <v>0.03421987351641687</v>
+        <v>0.0342198735164168</v>
       </c>
       <c r="N766" t="n">
-        <v>0.06798527245949926</v>
+        <v>0.0679852724594992</v>
       </c>
       <c r="O766" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.052369999885559</v>
       </c>
       <c r="P766" t="n">
-        <v>0.01561527257394017</v>
+        <v>0.0156152725739401</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>333.69</v>
+      </c>
+      <c r="F767" t="n">
+        <v>4869931925504</v>
+      </c>
+      <c r="G767" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H767" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I767" t="n">
+        <v>38.2672</v>
+      </c>
+      <c r="J767" t="n">
+        <v>34.821583</v>
+      </c>
+      <c r="K767" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L767" t="n">
+        <v>10.432074</v>
+      </c>
+      <c r="M767" t="n">
+        <v>0.02613203871857113</v>
+      </c>
+      <c r="N767" t="n">
+        <v>0.02871782193053433</v>
+      </c>
+      <c r="O767" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P767" t="n">
+        <v>-0.02405217757355503</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>633.91</v>
+      </c>
+      <c r="F768" t="n">
+        <v>1034842210304</v>
+      </c>
+      <c r="G768" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H768" t="n">
+        <v>15.57829</v>
+      </c>
+      <c r="I768" t="n">
+        <v>160.48354</v>
+      </c>
+      <c r="J768" t="n">
+        <v>40.691883</v>
+      </c>
+      <c r="K768" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L768" t="n">
+        <v>25.053679</v>
+      </c>
+      <c r="M768" t="n">
+        <v>0.006231168462400026</v>
+      </c>
+      <c r="N768" t="n">
+        <v>0.0245749238850941</v>
+      </c>
+      <c r="O768" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P768" t="n">
+        <v>-0.02819507561899526</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>251.52</v>
+      </c>
+      <c r="F769" t="n">
+        <v>2712973606912</v>
+      </c>
+      <c r="G769" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H769" t="n">
+        <v>10.47571</v>
+      </c>
+      <c r="I769" t="n">
+        <v>20.21865</v>
+      </c>
+      <c r="J769" t="n">
+        <v>24.009829</v>
+      </c>
+      <c r="K769" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L769" t="n">
+        <v>3.4975421</v>
+      </c>
+      <c r="M769" t="n">
+        <v>0.04945928753180661</v>
+      </c>
+      <c r="N769" t="n">
+        <v>0.04164961036895674</v>
+      </c>
+      <c r="O769" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P769" t="n">
+        <v>-0.01112038913513262</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="F770" t="n">
+        <v>1695307005952</v>
+      </c>
+      <c r="G770" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H770" t="n">
+        <v>19.38135</v>
+      </c>
+      <c r="I770" t="n">
+        <v>45.24077</v>
+      </c>
+      <c r="J770" t="n">
+        <v>18.323803</v>
+      </c>
+      <c r="K770" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L770" t="n">
+        <v>19.026161</v>
+      </c>
+      <c r="M770" t="n">
+        <v>0.02210395900208369</v>
+      </c>
+      <c r="N770" t="n">
+        <v>0.05457383003885792</v>
+      </c>
+      <c r="O770" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P770" t="n">
+        <v>0.001803830534768562</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>340.35</v>
+      </c>
+      <c r="F771" t="n">
+        <v>4162458484736</v>
+      </c>
+      <c r="G771" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H771" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I771" t="n">
+        <v>17.07727</v>
+      </c>
+      <c r="J771" t="n">
+        <v>22.582298</v>
+      </c>
+      <c r="K771" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L771" t="n">
+        <v>9.335671</v>
+      </c>
+      <c r="M771" t="n">
+        <v>0.0585573674158954</v>
+      </c>
+      <c r="N771" t="n">
+        <v>0.04428247392390187</v>
+      </c>
+      <c r="O771" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P771" t="n">
+        <v>-0.008487525580187491</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>728.08</v>
+      </c>
+      <c r="F772" t="n">
+        <v>1854788337664</v>
+      </c>
+      <c r="G772" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H772" t="n">
+        <v>34.90593</v>
+      </c>
+      <c r="I772" t="n">
+        <v>27.402334</v>
+      </c>
+      <c r="J772" t="n">
+        <v>20.858347</v>
+      </c>
+      <c r="K772" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L772" t="n">
+        <v>8.126232999999999</v>
+      </c>
+      <c r="M772" t="n">
+        <v>0.03649324250082409</v>
+      </c>
+      <c r="N772" t="n">
+        <v>0.04794243764421491</v>
+      </c>
+      <c r="O772" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P772" t="n">
+        <v>-0.004827561859874444</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>517.53</v>
+      </c>
+      <c r="F773" t="n">
+        <v>3842942959616</v>
+      </c>
+      <c r="G773" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H773" t="n">
+        <v>23.64732</v>
+      </c>
+      <c r="I773" t="n">
+        <v>28.831755</v>
+      </c>
+      <c r="J773" t="n">
+        <v>21.885357</v>
+      </c>
+      <c r="K773" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L773" t="n">
+        <v>11.580745</v>
+      </c>
+      <c r="M773" t="n">
+        <v>0.03468397967267598</v>
+      </c>
+      <c r="N773" t="n">
+        <v>0.04569265549823199</v>
+      </c>
+      <c r="O773" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P773" t="n">
+        <v>-0.007077344005857369</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>67.06</v>
+      </c>
+      <c r="F774" t="n">
+        <v>279233789952</v>
+      </c>
+      <c r="G774" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H774" t="n">
+        <v>3.81458</v>
+      </c>
+      <c r="I774" t="n">
+        <v>21.088049</v>
+      </c>
+      <c r="J774" t="n">
+        <v>17.579916</v>
+      </c>
+      <c r="K774" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L774" t="n">
+        <v>5.77278</v>
+      </c>
+      <c r="M774" t="n">
+        <v>0.04742022069788249</v>
+      </c>
+      <c r="N774" t="n">
+        <v>0.0568830897703549</v>
+      </c>
+      <c r="O774" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P774" t="n">
+        <v>0.004113090266265544</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:15:21</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>233.95</v>
+      </c>
+      <c r="F775" t="n">
+        <v>5649190617088</v>
+      </c>
+      <c r="G775" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H775" t="n">
+        <v>15.69508</v>
+      </c>
+      <c r="I775" t="n">
+        <v>29.53914</v>
+      </c>
+      <c r="J775" t="n">
+        <v>14.905945</v>
+      </c>
+      <c r="K775" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L775" t="n">
+        <v>18.646038</v>
+      </c>
+      <c r="M775" t="n">
+        <v>0.0338533874759564</v>
+      </c>
+      <c r="N775" t="n">
+        <v>0.06708732635178458</v>
+      </c>
+      <c r="O775" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P775" t="n">
+        <v>0.01431732684769522</v>
       </c>
     </row>
   </sheetData>
@@ -44942,12 +45464,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -44961,51 +45483,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>334.93</v>
+        <v>340.35</v>
       </c>
       <c r="F2" t="n">
-        <v>4096171966464</v>
+        <v>4162458484736</v>
       </c>
       <c r="G2" t="n">
-        <v>19.59</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.096989</v>
+        <v>17.07727</v>
       </c>
       <c r="J2" t="n">
-        <v>22.22268</v>
+        <v>22.582298</v>
       </c>
       <c r="K2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="L2" t="n">
-        <v>9.187002</v>
+        <v>9.335671</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05848983369659332</v>
+        <v>0.0585573674158954</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04499907443346371</v>
+        <v>0.04428247392390187</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007370925452095375</v>
+        <v>-0.008487525580187491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -45019,10 +45541,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="F3" t="n">
-        <v>3807819857920</v>
+        <v>3842942959616</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
@@ -45031,39 +45553,39 @@
         <v>23.64732</v>
       </c>
       <c r="I3" t="n">
-        <v>28.568243</v>
+        <v>28.831755</v>
       </c>
       <c r="J3" t="n">
-        <v>21.685333</v>
+        <v>21.885357</v>
       </c>
       <c r="K3" t="n">
         <v>1.67</v>
       </c>
       <c r="L3" t="n">
-        <v>11.474901</v>
+        <v>11.580745</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03500390015600624</v>
+        <v>0.03468397967267598</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0461141185647426</v>
+        <v>0.04569265549823199</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.006255881320816489</v>
+        <v>-0.007077344005857369</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -45077,10 +45599,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>725.9299999999999</v>
+        <v>728.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1849311100928</v>
+        <v>1854788337664</v>
       </c>
       <c r="G4" t="n">
         <v>26.57</v>
@@ -45089,39 +45611,39 @@
         <v>34.90593</v>
       </c>
       <c r="I4" t="n">
-        <v>27.321415</v>
+        <v>27.402334</v>
       </c>
       <c r="J4" t="n">
-        <v>20.796753</v>
+        <v>20.858347</v>
       </c>
       <c r="K4" t="n">
         <v>0.96</v>
       </c>
       <c r="L4" t="n">
-        <v>8.102237000000001</v>
+        <v>8.126232999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03660132519664431</v>
+        <v>0.03649324250082409</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04808442962820107</v>
+        <v>0.04794243764421491</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.004285570257358019</v>
+        <v>-0.004827561859874444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -45135,51 +45657,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248.23</v>
+        <v>251.52</v>
       </c>
       <c r="F5" t="n">
-        <v>2677486387200</v>
+        <v>2712973606912</v>
       </c>
       <c r="G5" t="n">
-        <v>12.39</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
         <v>10.47571</v>
       </c>
       <c r="I5" t="n">
-        <v>20.034704</v>
+        <v>20.21865</v>
       </c>
       <c r="J5" t="n">
-        <v>23.695768</v>
+        <v>24.009829</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4517922</v>
+        <v>3.4975421</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04991338677839102</v>
+        <v>0.04945928753180661</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04220162752286186</v>
+        <v>0.04164961036895674</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01016837236269722</v>
+        <v>-0.01112038913513262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -45193,51 +45715,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>330.32</v>
+        <v>333.69</v>
       </c>
       <c r="F6" t="n">
-        <v>4820749516800</v>
+        <v>4869931925504</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>37.837345</v>
+        <v>38.2672</v>
       </c>
       <c r="J6" t="n">
-        <v>34.46991</v>
+        <v>34.821583</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L6" t="n">
-        <v>10.326718</v>
+        <v>10.432074</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02642891741341729</v>
+        <v>0.02613203871857113</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02901080770162267</v>
+        <v>0.02871782193053433</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02335919218393641</v>
+        <v>-0.02405217757355503</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -45251,51 +45773,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230.86</v>
+        <v>233.95</v>
       </c>
       <c r="F7" t="n">
-        <v>5574576046080</v>
+        <v>5649190617088</v>
       </c>
       <c r="G7" t="n">
-        <v>7.9</v>
+        <v>7.92</v>
       </c>
       <c r="H7" t="n">
         <v>15.69508</v>
       </c>
       <c r="I7" t="n">
-        <v>29.222784</v>
+        <v>29.53914</v>
       </c>
       <c r="J7" t="n">
-        <v>14.709068</v>
+        <v>14.905945</v>
       </c>
       <c r="K7" t="n">
-        <v>0.48</v>
+        <v>0.28</v>
       </c>
       <c r="L7" t="n">
-        <v>18.399761</v>
+        <v>18.646038</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03421987351641687</v>
+        <v>0.0338533874759564</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06798527245949926</v>
+        <v>0.06708732635178458</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01561527257394017</v>
+        <v>0.01431732684769522</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -45309,51 +45831,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>615.73</v>
+        <v>633.91</v>
       </c>
       <c r="F8" t="n">
-        <v>1005163773952</v>
+        <v>1034842210304</v>
       </c>
       <c r="G8" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="H8" t="n">
-        <v>15.58329</v>
+        <v>15.57829</v>
       </c>
       <c r="I8" t="n">
-        <v>156.27664</v>
+        <v>160.48354</v>
       </c>
       <c r="J8" t="n">
-        <v>39.512196</v>
+        <v>40.691883</v>
       </c>
       <c r="K8" t="n">
         <v>0.62</v>
       </c>
       <c r="L8" t="n">
-        <v>24.33516</v>
+        <v>25.053679</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006398908612541211</v>
+        <v>0.006231168462400026</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02530864177480389</v>
+        <v>0.0245749238850941</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02706135811075519</v>
+        <v>-0.02819507561899526</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -45367,51 +45889,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>343.64</v>
+        <v>355.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1640410251264</v>
+        <v>1695307005952</v>
       </c>
       <c r="G9" t="n">
-        <v>7.83</v>
+        <v>7.85</v>
       </c>
       <c r="H9" t="n">
-        <v>19.38391</v>
+        <v>19.38135</v>
       </c>
       <c r="I9" t="n">
-        <v>43.887615</v>
+        <v>45.24077</v>
       </c>
       <c r="J9" t="n">
-        <v>17.728107</v>
+        <v>18.323803</v>
       </c>
       <c r="K9" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.410063</v>
+        <v>19.026161</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02278547316959609</v>
+        <v>0.02210395900208369</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05640760679781166</v>
+        <v>0.05457383003885792</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004037606912252578</v>
+        <v>0.001803830534768562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-01 18:43:57</t>
+          <t>2026-10-02 18:15:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -45425,40 +45947,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67.84999999999999</v>
+        <v>67.06</v>
       </c>
       <c r="F10" t="n">
-        <v>282523303936</v>
+        <v>279233789952</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.813</v>
+        <v>3.81458</v>
       </c>
       <c r="I10" t="n">
-        <v>21.887096</v>
+        <v>21.088049</v>
       </c>
       <c r="J10" t="n">
-        <v>17.794388</v>
+        <v>17.579916</v>
       </c>
       <c r="K10" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="L10" t="n">
-        <v>5.8407865</v>
+        <v>5.77278</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04568901989683125</v>
+        <v>0.04742022069788249</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05619749447310244</v>
+        <v>0.0568830897703549</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05236999988555908</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003827494587543355</v>
+        <v>0.004113090266265544</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P775"/>
+  <dimension ref="A1:P784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44889,16 +44889,16 @@
         <v>10.432074</v>
       </c>
       <c r="M767" t="n">
-        <v>0.02613203871857113</v>
+        <v>0.0261320387185711</v>
       </c>
       <c r="N767" t="n">
-        <v>0.02871782193053433</v>
+        <v>0.0287178219305343</v>
       </c>
       <c r="O767" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P767" t="n">
-        <v>-0.02405217757355503</v>
+        <v>-0.024052177573555</v>
       </c>
     </row>
     <row r="768">
@@ -44947,16 +44947,16 @@
         <v>25.053679</v>
       </c>
       <c r="M768" t="n">
-        <v>0.006231168462400026</v>
+        <v>0.0062311684624</v>
       </c>
       <c r="N768" t="n">
         <v>0.0245749238850941</v>
       </c>
       <c r="O768" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P768" t="n">
-        <v>-0.02819507561899526</v>
+        <v>-0.0281950756189952</v>
       </c>
     </row>
     <row r="769">
@@ -45005,16 +45005,16 @@
         <v>3.4975421</v>
       </c>
       <c r="M769" t="n">
-        <v>0.04945928753180661</v>
+        <v>0.0494592875318066</v>
       </c>
       <c r="N769" t="n">
-        <v>0.04164961036895674</v>
+        <v>0.0416496103689567</v>
       </c>
       <c r="O769" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P769" t="n">
-        <v>-0.01112038913513262</v>
+        <v>-0.0111203891351326</v>
       </c>
     </row>
     <row r="770">
@@ -45063,16 +45063,16 @@
         <v>19.026161</v>
       </c>
       <c r="M770" t="n">
-        <v>0.02210395900208369</v>
+        <v>0.0221039590020836</v>
       </c>
       <c r="N770" t="n">
-        <v>0.05457383003885792</v>
+        <v>0.0545738300388579</v>
       </c>
       <c r="O770" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P770" t="n">
-        <v>0.001803830534768562</v>
+        <v>0.0018038305347685</v>
       </c>
     </row>
     <row r="771">
@@ -45124,13 +45124,13 @@
         <v>0.0585573674158954</v>
       </c>
       <c r="N771" t="n">
-        <v>0.04428247392390187</v>
+        <v>0.0442824739239018</v>
       </c>
       <c r="O771" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P771" t="n">
-        <v>-0.008487525580187491</v>
+        <v>-0.008487525580187401</v>
       </c>
     </row>
     <row r="772">
@@ -45179,16 +45179,16 @@
         <v>8.126232999999999</v>
       </c>
       <c r="M772" t="n">
-        <v>0.03649324250082409</v>
+        <v>0.036493242500824</v>
       </c>
       <c r="N772" t="n">
-        <v>0.04794243764421491</v>
+        <v>0.0479424376442149</v>
       </c>
       <c r="O772" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P772" t="n">
-        <v>-0.004827561859874444</v>
+        <v>-0.0048275618598744</v>
       </c>
     </row>
     <row r="773">
@@ -45237,16 +45237,16 @@
         <v>11.580745</v>
       </c>
       <c r="M773" t="n">
-        <v>0.03468397967267598</v>
+        <v>0.0346839796726759</v>
       </c>
       <c r="N773" t="n">
-        <v>0.04569265549823199</v>
+        <v>0.0456926554982319</v>
       </c>
       <c r="O773" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P773" t="n">
-        <v>-0.007077344005857369</v>
+        <v>-0.0070773440058573</v>
       </c>
     </row>
     <row r="774">
@@ -45295,16 +45295,16 @@
         <v>5.77278</v>
       </c>
       <c r="M774" t="n">
-        <v>0.04742022069788249</v>
+        <v>0.0474202206978824</v>
       </c>
       <c r="N774" t="n">
         <v>0.0568830897703549</v>
       </c>
       <c r="O774" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P774" t="n">
-        <v>0.004113090266265544</v>
+        <v>0.0041130902662655</v>
       </c>
     </row>
     <row r="775">
@@ -45356,13 +45356,535 @@
         <v>0.0338533874759564</v>
       </c>
       <c r="N775" t="n">
-        <v>0.06708732635178458</v>
+        <v>0.06708732635178449</v>
       </c>
       <c r="O775" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P775" t="n">
-        <v>0.01431732684769522</v>
+        <v>0.0143173268476952</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="F776" t="n">
+        <v>4858257080320</v>
+      </c>
+      <c r="G776" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H776" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I776" t="n">
+        <v>38.17546</v>
+      </c>
+      <c r="J776" t="n">
+        <v>34.7381</v>
+      </c>
+      <c r="K776" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L776" t="n">
+        <v>10.407064</v>
+      </c>
+      <c r="M776" t="n">
+        <v>0.02619483913605095</v>
+      </c>
+      <c r="N776" t="n">
+        <v>0.02878683649253507</v>
+      </c>
+      <c r="O776" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P776" t="n">
+        <v>-0.02432316221046786</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>631.75</v>
+      </c>
+      <c r="F777" t="n">
+        <v>1031316111360</v>
+      </c>
+      <c r="G777" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H777" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I777" t="n">
+        <v>161.1607</v>
+      </c>
+      <c r="J777" t="n">
+        <v>40.182827</v>
+      </c>
+      <c r="K777" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L777" t="n">
+        <v>24.968311</v>
+      </c>
+      <c r="M777" t="n">
+        <v>0.006204986149584487</v>
+      </c>
+      <c r="N777" t="n">
+        <v>0.02488625247328849</v>
+      </c>
+      <c r="O777" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P777" t="n">
+        <v>-0.02822374622971445</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="F778" t="n">
+        <v>2711679139840</v>
+      </c>
+      <c r="G778" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H778" t="n">
+        <v>10.47571</v>
+      </c>
+      <c r="I778" t="n">
+        <v>20.22526</v>
+      </c>
+      <c r="J778" t="n">
+        <v>23.998373</v>
+      </c>
+      <c r="K778" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L778" t="n">
+        <v>3.4958732</v>
+      </c>
+      <c r="M778" t="n">
+        <v>0.0494431185361973</v>
+      </c>
+      <c r="N778" t="n">
+        <v>0.04166949085123309</v>
+      </c>
+      <c r="O778" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P778" t="n">
+        <v>-0.01144050785176984</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>362.51</v>
+      </c>
+      <c r="F779" t="n">
+        <v>1730488696832</v>
+      </c>
+      <c r="G779" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H779" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I779" t="n">
+        <v>46.297577</v>
+      </c>
+      <c r="J779" t="n">
+        <v>18.692038</v>
+      </c>
+      <c r="K779" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L779" t="n">
+        <v>19.421</v>
+      </c>
+      <c r="M779" t="n">
+        <v>0.02159940415436816</v>
+      </c>
+      <c r="N779" t="n">
+        <v>0.05349871727676479</v>
+      </c>
+      <c r="O779" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P779" t="n">
+        <v>0.0003887185737618537</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>343.83</v>
+      </c>
+      <c r="F780" t="n">
+        <v>4205018349568</v>
+      </c>
+      <c r="G780" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H780" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I780" t="n">
+        <v>17.25188</v>
+      </c>
+      <c r="J780" t="n">
+        <v>22.813196</v>
+      </c>
+      <c r="K780" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L780" t="n">
+        <v>9.431127</v>
+      </c>
+      <c r="M780" t="n">
+        <v>0.05796469185353227</v>
+      </c>
+      <c r="N780" t="n">
+        <v>0.04383427856789693</v>
+      </c>
+      <c r="O780" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P780" t="n">
+        <v>-0.009275720135106004</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>741.9</v>
+      </c>
+      <c r="F781" t="n">
+        <v>1889994932224</v>
+      </c>
+      <c r="G781" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H781" t="n">
+        <v>34.90593</v>
+      </c>
+      <c r="I781" t="n">
+        <v>27.954031</v>
+      </c>
+      <c r="J781" t="n">
+        <v>21.254269</v>
+      </c>
+      <c r="K781" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L781" t="n">
+        <v>8.280481</v>
+      </c>
+      <c r="M781" t="n">
+        <v>0.03577301523116323</v>
+      </c>
+      <c r="N781" t="n">
+        <v>0.04704937323089365</v>
+      </c>
+      <c r="O781" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P781" t="n">
+        <v>-0.006060625472109282</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E782" t="n">
+        <v>525.1799999999999</v>
+      </c>
+      <c r="F782" t="n">
+        <v>3899747991552</v>
+      </c>
+      <c r="G782" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H782" t="n">
+        <v>23.67702</v>
+      </c>
+      <c r="I782" t="n">
+        <v>29.257936</v>
+      </c>
+      <c r="J782" t="n">
+        <v>22.181002</v>
+      </c>
+      <c r="K782" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L782" t="n">
+        <v>11.751927</v>
+      </c>
+      <c r="M782" t="n">
+        <v>0.03417875775924445</v>
+      </c>
+      <c r="N782" t="n">
+        <v>0.04508362847023878</v>
+      </c>
+      <c r="O782" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P782" t="n">
+        <v>-0.008026370232764153</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E783" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F783" t="n">
+        <v>281065914368</v>
+      </c>
+      <c r="G783" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H783" t="n">
+        <v>3.81039</v>
+      </c>
+      <c r="I783" t="n">
+        <v>21.226414</v>
+      </c>
+      <c r="J783" t="n">
+        <v>17.714722</v>
+      </c>
+      <c r="K783" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L783" t="n">
+        <v>5.8106565</v>
+      </c>
+      <c r="M783" t="n">
+        <v>0.04711111111111111</v>
+      </c>
+      <c r="N783" t="n">
+        <v>0.05645022222222222</v>
+      </c>
+      <c r="O783" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P783" t="n">
+        <v>0.003340223519219289</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:21:40</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>238.9</v>
+      </c>
+      <c r="F784" t="n">
+        <v>5768717795328</v>
+      </c>
+      <c r="G784" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H784" t="n">
+        <v>15.79923</v>
+      </c>
+      <c r="I784" t="n">
+        <v>30.202276</v>
+      </c>
+      <c r="J784" t="n">
+        <v>15.12099</v>
+      </c>
+      <c r="K784" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L784" t="n">
+        <v>19.040558</v>
+      </c>
+      <c r="M784" t="n">
+        <v>0.03311008790288824</v>
+      </c>
+      <c r="N784" t="n">
+        <v>0.06613323566345751</v>
+      </c>
+      <c r="O784" t="n">
+        <v>0.05310999870300293</v>
+      </c>
+      <c r="P784" t="n">
+        <v>0.01302323696045458</v>
       </c>
     </row>
   </sheetData>
@@ -45464,12 +45986,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -45483,10 +46005,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>340.35</v>
+        <v>343.83</v>
       </c>
       <c r="F2" t="n">
-        <v>4162458484736</v>
+        <v>4205018349568</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -45495,39 +46017,39 @@
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.07727</v>
+        <v>17.25188</v>
       </c>
       <c r="J2" t="n">
-        <v>22.582298</v>
+        <v>22.813196</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="L2" t="n">
-        <v>9.335671</v>
+        <v>9.431127</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0585573674158954</v>
+        <v>0.05796469185353227</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04428247392390187</v>
+        <v>0.04383427856789693</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.008487525580187491</v>
+        <v>-0.009275720135106004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -45541,51 +46063,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3842942959616</v>
+        <v>3899747991552</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.64732</v>
+        <v>23.67702</v>
       </c>
       <c r="I3" t="n">
-        <v>28.831755</v>
+        <v>29.257936</v>
       </c>
       <c r="J3" t="n">
-        <v>21.885357</v>
+        <v>22.181002</v>
       </c>
       <c r="K3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="L3" t="n">
-        <v>11.580745</v>
+        <v>11.751927</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03468397967267598</v>
+        <v>0.03417875775924445</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04569265549823199</v>
+        <v>0.04508362847023878</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.007077344005857369</v>
+        <v>-0.008026370232764153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -45599,51 +46121,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>728.08</v>
+        <v>741.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1854788337664</v>
+        <v>1889994932224</v>
       </c>
       <c r="G4" t="n">
-        <v>26.57</v>
+        <v>26.54</v>
       </c>
       <c r="H4" t="n">
         <v>34.90593</v>
       </c>
       <c r="I4" t="n">
-        <v>27.402334</v>
+        <v>27.954031</v>
       </c>
       <c r="J4" t="n">
-        <v>20.858347</v>
+        <v>21.254269</v>
       </c>
       <c r="K4" t="n">
         <v>0.96</v>
       </c>
       <c r="L4" t="n">
-        <v>8.126232999999999</v>
+        <v>8.280481</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03649324250082409</v>
+        <v>0.03577301523116323</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04794243764421491</v>
+        <v>0.04704937323089365</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.004827561859874444</v>
+        <v>-0.006060625472109282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -45657,51 +46179,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>251.52</v>
+        <v>251.4</v>
       </c>
       <c r="F5" t="n">
-        <v>2712973606912</v>
+        <v>2711679139840</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.47571</v>
       </c>
       <c r="I5" t="n">
-        <v>20.21865</v>
+        <v>20.22526</v>
       </c>
       <c r="J5" t="n">
-        <v>24.009829</v>
+        <v>23.998373</v>
       </c>
       <c r="K5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4975421</v>
+        <v>3.4958732</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04945928753180661</v>
+        <v>0.0494431185361973</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04164961036895674</v>
+        <v>0.04166949085123309</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01112038913513262</v>
+        <v>-0.01144050785176984</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -45715,10 +46237,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.69</v>
+        <v>332.89</v>
       </c>
       <c r="F6" t="n">
-        <v>4869931925504</v>
+        <v>4858257080320</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
@@ -45727,39 +46249,39 @@
         <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.2672</v>
+        <v>38.17546</v>
       </c>
       <c r="J6" t="n">
-        <v>34.821583</v>
+        <v>34.7381</v>
       </c>
       <c r="K6" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.432074</v>
+        <v>10.407064</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02613203871857113</v>
+        <v>0.02619483913605095</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02871782193053433</v>
+        <v>0.02878683649253507</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02405217757355503</v>
+        <v>-0.02432316221046786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -45773,51 +46295,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>233.95</v>
+        <v>238.9</v>
       </c>
       <c r="F7" t="n">
-        <v>5649190617088</v>
+        <v>5768717795328</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
-        <v>15.69508</v>
+        <v>15.79923</v>
       </c>
       <c r="I7" t="n">
-        <v>29.53914</v>
+        <v>30.202276</v>
       </c>
       <c r="J7" t="n">
-        <v>14.905945</v>
+        <v>15.12099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="L7" t="n">
-        <v>18.646038</v>
+        <v>19.040558</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0338533874759564</v>
+        <v>0.03311008790288824</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06708732635178458</v>
+        <v>0.06613323566345751</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01431732684769522</v>
+        <v>0.01302323696045458</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -45831,51 +46353,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>633.91</v>
+        <v>631.75</v>
       </c>
       <c r="F8" t="n">
-        <v>1034842210304</v>
+        <v>1031316111360</v>
       </c>
       <c r="G8" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.57829</v>
+        <v>15.72189</v>
       </c>
       <c r="I8" t="n">
-        <v>160.48354</v>
+        <v>161.1607</v>
       </c>
       <c r="J8" t="n">
-        <v>40.691883</v>
+        <v>40.182827</v>
       </c>
       <c r="K8" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="L8" t="n">
-        <v>25.053679</v>
+        <v>24.968311</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006231168462400026</v>
+        <v>0.006204986149584487</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0245749238850941</v>
+        <v>0.02488625247328849</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02819507561899526</v>
+        <v>-0.02822374622971445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -45889,51 +46411,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>355.14</v>
+        <v>362.51</v>
       </c>
       <c r="F9" t="n">
-        <v>1695307005952</v>
+        <v>1730488696832</v>
       </c>
       <c r="G9" t="n">
-        <v>7.85</v>
+        <v>7.83</v>
       </c>
       <c r="H9" t="n">
-        <v>19.38135</v>
+        <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>45.24077</v>
+        <v>46.297577</v>
       </c>
       <c r="J9" t="n">
-        <v>18.323803</v>
+        <v>18.692038</v>
       </c>
       <c r="K9" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.026161</v>
+        <v>19.421</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02210395900208369</v>
+        <v>0.02159940415436816</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05457383003885792</v>
+        <v>0.05349871727676479</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001803830534768562</v>
+        <v>0.0003887185737618537</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 18:15:21</t>
+          <t>2026-10-05 19:21:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -45947,40 +46469,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67.06</v>
+        <v>67.5</v>
       </c>
       <c r="F10" t="n">
-        <v>279233789952</v>
+        <v>281065914368</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81458</v>
+        <v>3.81039</v>
       </c>
       <c r="I10" t="n">
-        <v>21.088049</v>
+        <v>21.226414</v>
       </c>
       <c r="J10" t="n">
-        <v>17.579916</v>
+        <v>17.714722</v>
       </c>
       <c r="K10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="L10" t="n">
-        <v>5.77278</v>
+        <v>5.8106565</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04742022069788249</v>
+        <v>0.04711111111111111</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0568830897703549</v>
+        <v>0.05645022222222222</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05310999870300293</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004113090266265544</v>
+        <v>0.003340223519219289</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P784"/>
+  <dimension ref="A1:P793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45411,16 +45411,16 @@
         <v>10.407064</v>
       </c>
       <c r="M776" t="n">
-        <v>0.02619483913605095</v>
+        <v>0.0261948391360509</v>
       </c>
       <c r="N776" t="n">
-        <v>0.02878683649253507</v>
+        <v>0.028786836492535</v>
       </c>
       <c r="O776" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P776" t="n">
-        <v>-0.02432316221046786</v>
+        <v>-0.0243231622104678</v>
       </c>
     </row>
     <row r="777">
@@ -45469,16 +45469,16 @@
         <v>24.968311</v>
       </c>
       <c r="M777" t="n">
-        <v>0.006204986149584487</v>
+        <v>0.0062049861495844</v>
       </c>
       <c r="N777" t="n">
-        <v>0.02488625247328849</v>
+        <v>0.0248862524732884</v>
       </c>
       <c r="O777" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P777" t="n">
-        <v>-0.02822374622971445</v>
+        <v>-0.0282237462297144</v>
       </c>
     </row>
     <row r="778">
@@ -45527,16 +45527,16 @@
         <v>3.4958732</v>
       </c>
       <c r="M778" t="n">
-        <v>0.0494431185361973</v>
+        <v>0.0494431185361972</v>
       </c>
       <c r="N778" t="n">
-        <v>0.04166949085123309</v>
+        <v>0.041669490851233</v>
       </c>
       <c r="O778" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P778" t="n">
-        <v>-0.01144050785176984</v>
+        <v>-0.0114405078517698</v>
       </c>
     </row>
     <row r="779">
@@ -45585,16 +45585,16 @@
         <v>19.421</v>
       </c>
       <c r="M779" t="n">
-        <v>0.02159940415436816</v>
+        <v>0.0215994041543681</v>
       </c>
       <c r="N779" t="n">
-        <v>0.05349871727676479</v>
+        <v>0.0534987172767647</v>
       </c>
       <c r="O779" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P779" t="n">
-        <v>0.0003887185737618537</v>
+        <v>0.0003887185737618</v>
       </c>
     </row>
     <row r="780">
@@ -45643,16 +45643,16 @@
         <v>9.431127</v>
       </c>
       <c r="M780" t="n">
-        <v>0.05796469185353227</v>
+        <v>0.0579646918535322</v>
       </c>
       <c r="N780" t="n">
-        <v>0.04383427856789693</v>
+        <v>0.0438342785678969</v>
       </c>
       <c r="O780" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P780" t="n">
-        <v>-0.009275720135106004</v>
+        <v>-0.009275720135106</v>
       </c>
     </row>
     <row r="781">
@@ -45701,16 +45701,16 @@
         <v>8.280481</v>
       </c>
       <c r="M781" t="n">
-        <v>0.03577301523116323</v>
+        <v>0.0357730152311632</v>
       </c>
       <c r="N781" t="n">
-        <v>0.04704937323089365</v>
+        <v>0.0470493732308936</v>
       </c>
       <c r="O781" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P781" t="n">
-        <v>-0.006060625472109282</v>
+        <v>-0.0060606254721092</v>
       </c>
     </row>
     <row r="782">
@@ -45759,16 +45759,16 @@
         <v>11.751927</v>
       </c>
       <c r="M782" t="n">
-        <v>0.03417875775924445</v>
+        <v>0.0341787577592444</v>
       </c>
       <c r="N782" t="n">
-        <v>0.04508362847023878</v>
+        <v>0.0450836284702387</v>
       </c>
       <c r="O782" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P782" t="n">
-        <v>-0.008026370232764153</v>
+        <v>-0.008026370232764099</v>
       </c>
     </row>
     <row r="783">
@@ -45817,16 +45817,16 @@
         <v>5.8106565</v>
       </c>
       <c r="M783" t="n">
-        <v>0.04711111111111111</v>
+        <v>0.0471111111111111</v>
       </c>
       <c r="N783" t="n">
-        <v>0.05645022222222222</v>
+        <v>0.0564502222222222</v>
       </c>
       <c r="O783" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P783" t="n">
-        <v>0.003340223519219289</v>
+        <v>0.0033402235192192</v>
       </c>
     </row>
     <row r="784">
@@ -45875,16 +45875,538 @@
         <v>19.040558</v>
       </c>
       <c r="M784" t="n">
-        <v>0.03311008790288824</v>
+        <v>0.0331100879028882</v>
       </c>
       <c r="N784" t="n">
-        <v>0.06613323566345751</v>
+        <v>0.0661332356634575</v>
       </c>
       <c r="O784" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.0531099987030029</v>
       </c>
       <c r="P784" t="n">
-        <v>0.01302323696045458</v>
+        <v>0.0130232369604545</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="F785" t="n">
+        <v>4869056364544</v>
+      </c>
+      <c r="G785" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H785" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I785" t="n">
+        <v>38.17277</v>
+      </c>
+      <c r="J785" t="n">
+        <v>34.81532</v>
+      </c>
+      <c r="K785" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L785" t="n">
+        <v>10.430199</v>
+      </c>
+      <c r="M785" t="n">
+        <v>0.02619668495039415</v>
+      </c>
+      <c r="N785" t="n">
+        <v>0.02872298654197764</v>
+      </c>
+      <c r="O785" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P785" t="n">
+        <v>-0.02396701399207998</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>649.42</v>
+      </c>
+      <c r="F786" t="n">
+        <v>1060161912832</v>
+      </c>
+      <c r="G786" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H786" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I786" t="n">
+        <v>165.66837</v>
+      </c>
+      <c r="J786" t="n">
+        <v>41.306736</v>
+      </c>
+      <c r="K786" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L786" t="n">
+        <v>25.666672</v>
+      </c>
+      <c r="M786" t="n">
+        <v>0.006036155338609837</v>
+      </c>
+      <c r="N786" t="n">
+        <v>0.02420912506544301</v>
+      </c>
+      <c r="O786" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P786" t="n">
+        <v>-0.0284808754686146</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="F787" t="n">
+        <v>2764424347648</v>
+      </c>
+      <c r="G787" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H787" t="n">
+        <v>10.46643</v>
+      </c>
+      <c r="I787" t="n">
+        <v>20.618664</v>
+      </c>
+      <c r="J787" t="n">
+        <v>24.48686</v>
+      </c>
+      <c r="K787" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L787" t="n">
+        <v>3.563872</v>
+      </c>
+      <c r="M787" t="n">
+        <v>0.04849974638105271</v>
+      </c>
+      <c r="N787" t="n">
+        <v>0.04083823012993094</v>
+      </c>
+      <c r="O787" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P787" t="n">
+        <v>-0.01185177040412668</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="F788" t="n">
+        <v>1793977876480</v>
+      </c>
+      <c r="G788" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H788" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I788" t="n">
+        <v>47.99617</v>
+      </c>
+      <c r="J788" t="n">
+        <v>19.377823</v>
+      </c>
+      <c r="K788" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L788" t="n">
+        <v>20.133528</v>
+      </c>
+      <c r="M788" t="n">
+        <v>0.02083499640775924</v>
+      </c>
+      <c r="N788" t="n">
+        <v>0.05160538570022086</v>
+      </c>
+      <c r="O788" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P788" t="n">
+        <v>-0.001084614833836761</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>344.59</v>
+      </c>
+      <c r="F789" t="n">
+        <v>4214313189376</v>
+      </c>
+      <c r="G789" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H789" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I789" t="n">
+        <v>17.290014</v>
+      </c>
+      <c r="J789" t="n">
+        <v>22.863623</v>
+      </c>
+      <c r="K789" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L789" t="n">
+        <v>9.451973000000001</v>
+      </c>
+      <c r="M789" t="n">
+        <v>0.05783684958936708</v>
+      </c>
+      <c r="N789" t="n">
+        <v>0.04373760120723179</v>
+      </c>
+      <c r="O789" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P789" t="n">
+        <v>-0.00895239932682583</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>738.88</v>
+      </c>
+      <c r="F790" t="n">
+        <v>1882301399040</v>
+      </c>
+      <c r="G790" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H790" t="n">
+        <v>34.90593</v>
+      </c>
+      <c r="I790" t="n">
+        <v>27.84024</v>
+      </c>
+      <c r="J790" t="n">
+        <v>21.167751</v>
+      </c>
+      <c r="K790" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L790" t="n">
+        <v>8.246774</v>
+      </c>
+      <c r="M790" t="n">
+        <v>0.03591922910350801</v>
+      </c>
+      <c r="N790" t="n">
+        <v>0.04724167659159809</v>
+      </c>
+      <c r="O790" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P790" t="n">
+        <v>-0.005448323942459525</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E791" t="n">
+        <v>529.3</v>
+      </c>
+      <c r="F791" t="n">
+        <v>3930341244928</v>
+      </c>
+      <c r="G791" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H791" t="n">
+        <v>23.67702</v>
+      </c>
+      <c r="I791" t="n">
+        <v>29.487463</v>
+      </c>
+      <c r="J791" t="n">
+        <v>22.35501</v>
+      </c>
+      <c r="K791" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L791" t="n">
+        <v>11.84412</v>
+      </c>
+      <c r="M791" t="n">
+        <v>0.03391271490648026</v>
+      </c>
+      <c r="N791" t="n">
+        <v>0.04473270357075382</v>
+      </c>
+      <c r="O791" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P791" t="n">
+        <v>-0.007957296963303793</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E792" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="F792" t="n">
+        <v>286021025792</v>
+      </c>
+      <c r="G792" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H792" t="n">
+        <v>3.80806</v>
+      </c>
+      <c r="I792" t="n">
+        <v>21.60063</v>
+      </c>
+      <c r="J792" t="n">
+        <v>18.038057</v>
+      </c>
+      <c r="K792" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L792" t="n">
+        <v>5.913097</v>
+      </c>
+      <c r="M792" t="n">
+        <v>0.04629494831853254</v>
+      </c>
+      <c r="N792" t="n">
+        <v>0.0554383461930412</v>
+      </c>
+      <c r="O792" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P792" t="n">
+        <v>0.002748345658983582</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:40:46</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>239.24</v>
+      </c>
+      <c r="F793" t="n">
+        <v>5776928145408</v>
+      </c>
+      <c r="G793" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H793" t="n">
+        <v>15.79923</v>
+      </c>
+      <c r="I793" t="n">
+        <v>30.207071</v>
+      </c>
+      <c r="J793" t="n">
+        <v>15.14251</v>
+      </c>
+      <c r="K793" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L793" t="n">
+        <v>19.067657</v>
+      </c>
+      <c r="M793" t="n">
+        <v>0.03310483196789835</v>
+      </c>
+      <c r="N793" t="n">
+        <v>0.06603924928941649</v>
+      </c>
+      <c r="O793" t="n">
+        <v>0.05269000053405762</v>
+      </c>
+      <c r="P793" t="n">
+        <v>0.01334924875535887</v>
       </c>
     </row>
   </sheetData>
@@ -45986,12 +46508,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -46005,10 +46527,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>343.83</v>
+        <v>344.59</v>
       </c>
       <c r="F2" t="n">
-        <v>4205018349568</v>
+        <v>4214313189376</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -46017,39 +46539,39 @@
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.25188</v>
+        <v>17.290014</v>
       </c>
       <c r="J2" t="n">
-        <v>22.813196</v>
+        <v>22.863623</v>
       </c>
       <c r="K2" t="n">
         <v>1.22</v>
       </c>
       <c r="L2" t="n">
-        <v>9.431127</v>
+        <v>9.451973000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05796469185353227</v>
+        <v>0.05783684958936708</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04383427856789693</v>
+        <v>0.04373760120723179</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.009275720135106004</v>
+        <v>-0.00895239932682583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -46063,10 +46585,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="F3" t="n">
-        <v>3899747991552</v>
+        <v>3930341244928</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
@@ -46075,39 +46597,39 @@
         <v>23.67702</v>
       </c>
       <c r="I3" t="n">
-        <v>29.257936</v>
+        <v>29.487463</v>
       </c>
       <c r="J3" t="n">
-        <v>22.181002</v>
+        <v>22.35501</v>
       </c>
       <c r="K3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="L3" t="n">
-        <v>11.751927</v>
+        <v>11.84412</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03417875775924445</v>
+        <v>0.03391271490648026</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04508362847023878</v>
+        <v>0.04473270357075382</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.008026370232764153</v>
+        <v>-0.007957296963303793</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -46121,10 +46643,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>741.9</v>
+        <v>738.88</v>
       </c>
       <c r="F4" t="n">
-        <v>1889994932224</v>
+        <v>1882301399040</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
@@ -46133,39 +46655,39 @@
         <v>34.90593</v>
       </c>
       <c r="I4" t="n">
-        <v>27.954031</v>
+        <v>27.84024</v>
       </c>
       <c r="J4" t="n">
-        <v>21.254269</v>
+        <v>21.167751</v>
       </c>
       <c r="K4" t="n">
         <v>0.96</v>
       </c>
       <c r="L4" t="n">
-        <v>8.280481</v>
+        <v>8.246774</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03577301523116323</v>
+        <v>0.03591922910350801</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04704937323089365</v>
+        <v>0.04724167659159809</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.006060625472109282</v>
+        <v>-0.005448323942459525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -46179,51 +46701,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>251.4</v>
+        <v>256.29</v>
       </c>
       <c r="F5" t="n">
-        <v>2711679139840</v>
+        <v>2764424347648</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.47571</v>
+        <v>10.46643</v>
       </c>
       <c r="I5" t="n">
-        <v>20.22526</v>
+        <v>20.618664</v>
       </c>
       <c r="J5" t="n">
-        <v>23.998373</v>
+        <v>24.48686</v>
       </c>
       <c r="K5" t="n">
         <v>1.49</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4958732</v>
+        <v>3.563872</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0494431185361973</v>
+        <v>0.04849974638105271</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04166949085123309</v>
+        <v>0.04083823012993094</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01144050785176984</v>
+        <v>-0.01185177040412668</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -46237,51 +46759,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>332.89</v>
+        <v>333.63</v>
       </c>
       <c r="F6" t="n">
-        <v>4858257080320</v>
+        <v>4869056364544</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
         <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.17546</v>
+        <v>38.17277</v>
       </c>
       <c r="J6" t="n">
-        <v>34.7381</v>
+        <v>34.81532</v>
       </c>
       <c r="K6" t="n">
         <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.407064</v>
+        <v>10.430199</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02619483913605095</v>
+        <v>0.02619668495039415</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02878683649253507</v>
+        <v>0.02872298654197764</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02432316221046786</v>
+        <v>-0.02396701399207998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -46295,51 +46817,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>238.9</v>
+        <v>239.24</v>
       </c>
       <c r="F7" t="n">
-        <v>5768717795328</v>
+        <v>5776928145408</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="H7" t="n">
         <v>15.79923</v>
       </c>
       <c r="I7" t="n">
-        <v>30.202276</v>
+        <v>30.207071</v>
       </c>
       <c r="J7" t="n">
-        <v>15.12099</v>
+        <v>15.14251</v>
       </c>
       <c r="K7" t="n">
         <v>0.29</v>
       </c>
       <c r="L7" t="n">
-        <v>19.040558</v>
+        <v>19.067657</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03311008790288824</v>
+        <v>0.03310483196789835</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06613323566345751</v>
+        <v>0.06603924928941649</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01302323696045458</v>
+        <v>0.01334924875535887</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -46353,10 +46875,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>631.75</v>
+        <v>649.42</v>
       </c>
       <c r="F8" t="n">
-        <v>1031316111360</v>
+        <v>1060161912832</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -46365,39 +46887,39 @@
         <v>15.72189</v>
       </c>
       <c r="I8" t="n">
-        <v>161.1607</v>
+        <v>165.66837</v>
       </c>
       <c r="J8" t="n">
-        <v>40.182827</v>
+        <v>41.306736</v>
       </c>
       <c r="K8" t="n">
         <v>0.64</v>
       </c>
       <c r="L8" t="n">
-        <v>24.968311</v>
+        <v>25.666672</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006204986149584487</v>
+        <v>0.006036155338609837</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02488625247328849</v>
+        <v>0.02420912506544301</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02822374622971445</v>
+        <v>-0.0284808754686146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -46411,10 +46933,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>362.51</v>
+        <v>375.81</v>
       </c>
       <c r="F9" t="n">
-        <v>1730488696832</v>
+        <v>1793977876480</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -46423,39 +46945,39 @@
         <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>46.297577</v>
+        <v>47.99617</v>
       </c>
       <c r="J9" t="n">
-        <v>18.692038</v>
+        <v>19.377823</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.421</v>
+        <v>20.133528</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02159940415436816</v>
+        <v>0.02083499640775924</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05349871727676479</v>
+        <v>0.05160538570022086</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003887185737618537</v>
+        <v>-0.001084614833836761</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-05 19:21:40</t>
+          <t>2026-10-06 18:40:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -46469,40 +46991,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67.5</v>
+        <v>68.69</v>
       </c>
       <c r="F10" t="n">
-        <v>281065914368</v>
+        <v>286021025792</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81039</v>
+        <v>3.80806</v>
       </c>
       <c r="I10" t="n">
-        <v>21.226414</v>
+        <v>21.60063</v>
       </c>
       <c r="J10" t="n">
-        <v>17.714722</v>
+        <v>18.038057</v>
       </c>
       <c r="K10" t="n">
         <v>1.15</v>
       </c>
       <c r="L10" t="n">
-        <v>5.8106565</v>
+        <v>5.913097</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04711111111111111</v>
+        <v>0.04629494831853254</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05645022222222222</v>
+        <v>0.0554383461930412</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05310999870300293</v>
+        <v>0.05269000053405762</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003340223519219289</v>
+        <v>0.002748345658983582</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P793"/>
+  <dimension ref="A1:P802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45933,16 +45933,16 @@
         <v>10.430199</v>
       </c>
       <c r="M785" t="n">
-        <v>0.02619668495039415</v>
+        <v>0.0261966849503941</v>
       </c>
       <c r="N785" t="n">
-        <v>0.02872298654197764</v>
+        <v>0.0287229865419776</v>
       </c>
       <c r="O785" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P785" t="n">
-        <v>-0.02396701399207998</v>
+        <v>-0.0239670139920799</v>
       </c>
     </row>
     <row r="786">
@@ -45991,13 +45991,13 @@
         <v>25.666672</v>
       </c>
       <c r="M786" t="n">
-        <v>0.006036155338609837</v>
+        <v>0.0060361553386098</v>
       </c>
       <c r="N786" t="n">
-        <v>0.02420912506544301</v>
+        <v>0.024209125065443</v>
       </c>
       <c r="O786" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P786" t="n">
         <v>-0.0284808754686146</v>
@@ -46049,16 +46049,16 @@
         <v>3.563872</v>
       </c>
       <c r="M787" t="n">
-        <v>0.04849974638105271</v>
+        <v>0.0484997463810527</v>
       </c>
       <c r="N787" t="n">
-        <v>0.04083823012993094</v>
+        <v>0.0408382301299309</v>
       </c>
       <c r="O787" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P787" t="n">
-        <v>-0.01185177040412668</v>
+        <v>-0.0118517704041266</v>
       </c>
     </row>
     <row r="788">
@@ -46107,16 +46107,16 @@
         <v>20.133528</v>
       </c>
       <c r="M788" t="n">
-        <v>0.02083499640775924</v>
+        <v>0.0208349964077592</v>
       </c>
       <c r="N788" t="n">
-        <v>0.05160538570022086</v>
+        <v>0.0516053857002208</v>
       </c>
       <c r="O788" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P788" t="n">
-        <v>-0.001084614833836761</v>
+        <v>-0.0010846148338367</v>
       </c>
     </row>
     <row r="789">
@@ -46165,16 +46165,16 @@
         <v>9.451973000000001</v>
       </c>
       <c r="M789" t="n">
-        <v>0.05783684958936708</v>
+        <v>0.057836849589367</v>
       </c>
       <c r="N789" t="n">
-        <v>0.04373760120723179</v>
+        <v>0.0437376012072317</v>
       </c>
       <c r="O789" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P789" t="n">
-        <v>-0.00895239932682583</v>
+        <v>-0.008952399326825801</v>
       </c>
     </row>
     <row r="790">
@@ -46223,16 +46223,16 @@
         <v>8.246774</v>
       </c>
       <c r="M790" t="n">
-        <v>0.03591922910350801</v>
+        <v>0.035919229103508</v>
       </c>
       <c r="N790" t="n">
-        <v>0.04724167659159809</v>
+        <v>0.047241676591598</v>
       </c>
       <c r="O790" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P790" t="n">
-        <v>-0.005448323942459525</v>
+        <v>-0.0054483239424595</v>
       </c>
     </row>
     <row r="791">
@@ -46281,16 +46281,16 @@
         <v>11.84412</v>
       </c>
       <c r="M791" t="n">
-        <v>0.03391271490648026</v>
+        <v>0.0339127149064802</v>
       </c>
       <c r="N791" t="n">
-        <v>0.04473270357075382</v>
+        <v>0.0447327035707538</v>
       </c>
       <c r="O791" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P791" t="n">
-        <v>-0.007957296963303793</v>
+        <v>-0.0079572969633037</v>
       </c>
     </row>
     <row r="792">
@@ -46339,16 +46339,16 @@
         <v>5.913097</v>
       </c>
       <c r="M792" t="n">
-        <v>0.04629494831853254</v>
+        <v>0.0462949483185325</v>
       </c>
       <c r="N792" t="n">
         <v>0.0554383461930412</v>
       </c>
       <c r="O792" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P792" t="n">
-        <v>0.002748345658983582</v>
+        <v>0.0027483456589835</v>
       </c>
     </row>
     <row r="793">
@@ -46397,16 +46397,538 @@
         <v>19.067657</v>
       </c>
       <c r="M793" t="n">
-        <v>0.03310483196789835</v>
+        <v>0.0331048319678983</v>
       </c>
       <c r="N793" t="n">
-        <v>0.06603924928941649</v>
+        <v>0.0660392492894164</v>
       </c>
       <c r="O793" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.0526900005340576</v>
       </c>
       <c r="P793" t="n">
-        <v>0.01334924875535887</v>
+        <v>0.0133492487553588</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>336.67</v>
+      </c>
+      <c r="F794" t="n">
+        <v>4913422663680</v>
+      </c>
+      <c r="G794" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H794" t="n">
+        <v>9.582850000000001</v>
+      </c>
+      <c r="I794" t="n">
+        <v>38.608944</v>
+      </c>
+      <c r="J794" t="n">
+        <v>35.132553</v>
+      </c>
+      <c r="K794" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L794" t="n">
+        <v>10.525237</v>
+      </c>
+      <c r="M794" t="n">
+        <v>0.02590073365610241</v>
+      </c>
+      <c r="N794" t="n">
+        <v>0.02846362907297948</v>
+      </c>
+      <c r="O794" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P794" t="n">
+        <v>-0.02430637043110988</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>645.86</v>
+      </c>
+      <c r="F795" t="n">
+        <v>1054350311424</v>
+      </c>
+      <c r="G795" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H795" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I795" t="n">
+        <v>164.7602</v>
+      </c>
+      <c r="J795" t="n">
+        <v>41.0803</v>
+      </c>
+      <c r="K795" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L795" t="n">
+        <v>25.525972</v>
+      </c>
+      <c r="M795" t="n">
+        <v>0.006069426810763942</v>
+      </c>
+      <c r="N795" t="n">
+        <v>0.02434256650047998</v>
+      </c>
+      <c r="O795" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P795" t="n">
+        <v>-0.02842743300360938</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>259.92</v>
+      </c>
+      <c r="F796" t="n">
+        <v>2803578699776</v>
+      </c>
+      <c r="G796" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H796" t="n">
+        <v>10.46643</v>
+      </c>
+      <c r="I796" t="n">
+        <v>20.9107</v>
+      </c>
+      <c r="J796" t="n">
+        <v>24.833685</v>
+      </c>
+      <c r="K796" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L796" t="n">
+        <v>3.6143494</v>
+      </c>
+      <c r="M796" t="n">
+        <v>0.04782240689442905</v>
+      </c>
+      <c r="N796" t="n">
+        <v>0.04026789012003693</v>
+      </c>
+      <c r="O796" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P796" t="n">
+        <v>-0.01250210938405243</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>376.51</v>
+      </c>
+      <c r="F797" t="n">
+        <v>1797319426048</v>
+      </c>
+      <c r="G797" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H797" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I797" t="n">
+        <v>46.36823</v>
+      </c>
+      <c r="J797" t="n">
+        <v>19.413918</v>
+      </c>
+      <c r="K797" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L797" t="n">
+        <v>20.17103</v>
+      </c>
+      <c r="M797" t="n">
+        <v>0.02156649225784175</v>
+      </c>
+      <c r="N797" t="n">
+        <v>0.05150944198029269</v>
+      </c>
+      <c r="O797" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P797" t="n">
+        <v>-0.001260557523796668</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="F798" t="n">
+        <v>4248312479744</v>
+      </c>
+      <c r="G798" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H798" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I798" t="n">
+        <v>17.429502</v>
+      </c>
+      <c r="J798" t="n">
+        <v>23.048077</v>
+      </c>
+      <c r="K798" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L798" t="n">
+        <v>9.528228</v>
+      </c>
+      <c r="M798" t="n">
+        <v>0.05737398163341682</v>
+      </c>
+      <c r="N798" t="n">
+        <v>0.04338756945044189</v>
+      </c>
+      <c r="O798" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P798" t="n">
+        <v>-0.009382430053647466</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>721.3099999999999</v>
+      </c>
+      <c r="F799" t="n">
+        <v>1837541621760</v>
+      </c>
+      <c r="G799" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H799" t="n">
+        <v>34.90593</v>
+      </c>
+      <c r="I799" t="n">
+        <v>27.17822</v>
+      </c>
+      <c r="J799" t="n">
+        <v>20.664398</v>
+      </c>
+      <c r="K799" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L799" t="n">
+        <v>8.050672</v>
+      </c>
+      <c r="M799" t="n">
+        <v>0.03679416616988535</v>
+      </c>
+      <c r="N799" t="n">
+        <v>0.04839241102993165</v>
+      </c>
+      <c r="O799" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P799" t="n">
+        <v>-0.004377588474157708</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>529.76</v>
+      </c>
+      <c r="F800" t="n">
+        <v>3933757243392</v>
+      </c>
+      <c r="G800" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H800" t="n">
+        <v>23.67732</v>
+      </c>
+      <c r="I800" t="n">
+        <v>29.513092</v>
+      </c>
+      <c r="J800" t="n">
+        <v>22.374153</v>
+      </c>
+      <c r="K800" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L800" t="n">
+        <v>11.854415</v>
+      </c>
+      <c r="M800" t="n">
+        <v>0.0338832678948958</v>
+      </c>
+      <c r="N800" t="n">
+        <v>0.0446944276653579</v>
+      </c>
+      <c r="O800" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P800" t="n">
+        <v>-0.008075571838731456</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="F801" t="n">
+        <v>290226569216</v>
+      </c>
+      <c r="G801" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H801" t="n">
+        <v>3.80709</v>
+      </c>
+      <c r="I801" t="n">
+        <v>21.918238</v>
+      </c>
+      <c r="J801" t="n">
+        <v>18.307945</v>
+      </c>
+      <c r="K801" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L801" t="n">
+        <v>6.000041</v>
+      </c>
+      <c r="M801" t="n">
+        <v>0.04562410329985653</v>
+      </c>
+      <c r="N801" t="n">
+        <v>0.05462109038737446</v>
+      </c>
+      <c r="O801" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P801" t="n">
+        <v>0.001851090883285104</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:05:53</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>237.47</v>
+      </c>
+      <c r="F802" t="n">
+        <v>5734188187648</v>
+      </c>
+      <c r="G802" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H802" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I802" t="n">
+        <v>30.021492</v>
+      </c>
+      <c r="J802" t="n">
+        <v>14.921518</v>
+      </c>
+      <c r="K802" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L802" t="n">
+        <v>18.926586</v>
+      </c>
+      <c r="M802" t="n">
+        <v>0.03330947066997936</v>
+      </c>
+      <c r="N802" t="n">
+        <v>0.06701730744936203</v>
+      </c>
+      <c r="O802" t="n">
+        <v>0.05276999950408936</v>
+      </c>
+      <c r="P802" t="n">
+        <v>0.01424730794527267</v>
       </c>
     </row>
   </sheetData>
@@ -46508,12 +47030,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -46527,10 +47049,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>344.59</v>
+        <v>347.37</v>
       </c>
       <c r="F2" t="n">
-        <v>4214313189376</v>
+        <v>4248312479744</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -46539,39 +47061,39 @@
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.290014</v>
+        <v>17.429502</v>
       </c>
       <c r="J2" t="n">
-        <v>22.863623</v>
+        <v>23.048077</v>
       </c>
       <c r="K2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="L2" t="n">
-        <v>9.451973000000001</v>
+        <v>9.528228</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05783684958936708</v>
+        <v>0.05737398163341682</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04373760120723179</v>
+        <v>0.04338756945044189</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.00895239932682583</v>
+        <v>-0.009382430053647466</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -46585,51 +47107,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="F3" t="n">
-        <v>3930341244928</v>
+        <v>3933757243392</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.67702</v>
+        <v>23.67732</v>
       </c>
       <c r="I3" t="n">
-        <v>29.487463</v>
+        <v>29.513092</v>
       </c>
       <c r="J3" t="n">
-        <v>22.35501</v>
+        <v>22.374153</v>
       </c>
       <c r="K3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="L3" t="n">
-        <v>11.84412</v>
+        <v>11.854415</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03391271490648026</v>
+        <v>0.0338832678948958</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04473270357075382</v>
+        <v>0.0446944276653579</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.007957296963303793</v>
+        <v>-0.008075571838731456</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -46643,10 +47165,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>738.88</v>
+        <v>721.3099999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1882301399040</v>
+        <v>1837541621760</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
@@ -46655,39 +47177,39 @@
         <v>34.90593</v>
       </c>
       <c r="I4" t="n">
-        <v>27.84024</v>
+        <v>27.17822</v>
       </c>
       <c r="J4" t="n">
-        <v>21.167751</v>
+        <v>20.664398</v>
       </c>
       <c r="K4" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="L4" t="n">
-        <v>8.246774</v>
+        <v>8.050672</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03591922910350801</v>
+        <v>0.03679416616988535</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04724167659159809</v>
+        <v>0.04839241102993165</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.005448323942459525</v>
+        <v>-0.004377588474157708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -46701,10 +47223,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256.29</v>
+        <v>259.92</v>
       </c>
       <c r="F5" t="n">
-        <v>2764424347648</v>
+        <v>2803578699776</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -46713,39 +47235,39 @@
         <v>10.46643</v>
       </c>
       <c r="I5" t="n">
-        <v>20.618664</v>
+        <v>20.9107</v>
       </c>
       <c r="J5" t="n">
-        <v>24.48686</v>
+        <v>24.833685</v>
       </c>
       <c r="K5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="L5" t="n">
-        <v>3.563872</v>
+        <v>3.6143494</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04849974638105271</v>
+        <v>0.04782240689442905</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04083823012993094</v>
+        <v>0.04026789012003693</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01185177040412668</v>
+        <v>-0.01250210938405243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -46759,51 +47281,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.63</v>
+        <v>336.67</v>
       </c>
       <c r="F6" t="n">
-        <v>4869056364544</v>
+        <v>4913422663680</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.582850000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.17277</v>
+        <v>38.608944</v>
       </c>
       <c r="J6" t="n">
-        <v>34.81532</v>
+        <v>35.132553</v>
       </c>
       <c r="K6" t="n">
         <v>2.67</v>
       </c>
       <c r="L6" t="n">
-        <v>10.430199</v>
+        <v>10.525237</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02619668495039415</v>
+        <v>0.02590073365610241</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02872298654197764</v>
+        <v>0.02846362907297948</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02396701399207998</v>
+        <v>-0.02430637043110988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -46817,51 +47339,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>239.24</v>
+        <v>237.47</v>
       </c>
       <c r="F7" t="n">
-        <v>5776928145408</v>
+        <v>5734188187648</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
-        <v>15.79923</v>
+        <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>30.207071</v>
+        <v>30.021492</v>
       </c>
       <c r="J7" t="n">
-        <v>15.14251</v>
+        <v>14.921518</v>
       </c>
       <c r="K7" t="n">
         <v>0.29</v>
       </c>
       <c r="L7" t="n">
-        <v>19.067657</v>
+        <v>18.926586</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03310483196789835</v>
+        <v>0.03330947066997936</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06603924928941649</v>
+        <v>0.06701730744936203</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01334924875535887</v>
+        <v>0.01424730794527267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -46875,10 +47397,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>649.42</v>
+        <v>645.86</v>
       </c>
       <c r="F8" t="n">
-        <v>1060161912832</v>
+        <v>1054350311424</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -46887,39 +47409,39 @@
         <v>15.72189</v>
       </c>
       <c r="I8" t="n">
-        <v>165.66837</v>
+        <v>164.7602</v>
       </c>
       <c r="J8" t="n">
-        <v>41.306736</v>
+        <v>41.0803</v>
       </c>
       <c r="K8" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="L8" t="n">
-        <v>25.666672</v>
+        <v>25.525972</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006036155338609837</v>
+        <v>0.006069426810763942</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02420912506544301</v>
+        <v>0.02434256650047998</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0284808754686146</v>
+        <v>-0.02842743300360938</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -46933,51 +47455,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>375.81</v>
+        <v>376.51</v>
       </c>
       <c r="F9" t="n">
-        <v>1793977876480</v>
+        <v>1797319426048</v>
       </c>
       <c r="G9" t="n">
-        <v>7.83</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>47.99617</v>
+        <v>46.36823</v>
       </c>
       <c r="J9" t="n">
-        <v>19.377823</v>
+        <v>19.413918</v>
       </c>
       <c r="K9" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="L9" t="n">
-        <v>20.133528</v>
+        <v>20.17103</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02083499640775924</v>
+        <v>0.02156649225784175</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05160538570022086</v>
+        <v>0.05150944198029269</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.001084614833836761</v>
+        <v>-0.001260557523796668</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 18:40:46</t>
+          <t>2026-10-07 19:05:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -46991,40 +47513,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68.69</v>
+        <v>69.7</v>
       </c>
       <c r="F10" t="n">
-        <v>286021025792</v>
+        <v>290226569216</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.80806</v>
+        <v>3.80709</v>
       </c>
       <c r="I10" t="n">
-        <v>21.60063</v>
+        <v>21.918238</v>
       </c>
       <c r="J10" t="n">
-        <v>18.038057</v>
+        <v>18.307945</v>
       </c>
       <c r="K10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="L10" t="n">
-        <v>5.913097</v>
+        <v>6.000041</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04629494831853254</v>
+        <v>0.04562410329985653</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0554383461930412</v>
+        <v>0.05462109038737446</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05269000053405762</v>
+        <v>0.05276999950408936</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002748345658983582</v>
+        <v>0.001851090883285104</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P802"/>
+  <dimension ref="A1:P811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46455,16 +46455,16 @@
         <v>10.525237</v>
       </c>
       <c r="M794" t="n">
-        <v>0.02590073365610241</v>
+        <v>0.0259007336561024</v>
       </c>
       <c r="N794" t="n">
-        <v>0.02846362907297948</v>
+        <v>0.0284636290729794</v>
       </c>
       <c r="O794" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P794" t="n">
-        <v>-0.02430637043110988</v>
+        <v>-0.0243063704311098</v>
       </c>
     </row>
     <row r="795">
@@ -46513,16 +46513,16 @@
         <v>25.525972</v>
       </c>
       <c r="M795" t="n">
-        <v>0.006069426810763942</v>
+        <v>0.0060694268107639</v>
       </c>
       <c r="N795" t="n">
-        <v>0.02434256650047998</v>
+        <v>0.0243425665004799</v>
       </c>
       <c r="O795" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P795" t="n">
-        <v>-0.02842743300360938</v>
+        <v>-0.0284274330036093</v>
       </c>
     </row>
     <row r="796">
@@ -46571,16 +46571,16 @@
         <v>3.6143494</v>
       </c>
       <c r="M796" t="n">
-        <v>0.04782240689442905</v>
+        <v>0.047822406894429</v>
       </c>
       <c r="N796" t="n">
-        <v>0.04026789012003693</v>
+        <v>0.0402678901200369</v>
       </c>
       <c r="O796" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P796" t="n">
-        <v>-0.01250210938405243</v>
+        <v>-0.0125021093840524</v>
       </c>
     </row>
     <row r="797">
@@ -46629,16 +46629,16 @@
         <v>20.17103</v>
       </c>
       <c r="M797" t="n">
-        <v>0.02156649225784175</v>
+        <v>0.0215664922578417</v>
       </c>
       <c r="N797" t="n">
-        <v>0.05150944198029269</v>
+        <v>0.0515094419802926</v>
       </c>
       <c r="O797" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P797" t="n">
-        <v>-0.001260557523796668</v>
+        <v>-0.0012605575237966</v>
       </c>
     </row>
     <row r="798">
@@ -46687,16 +46687,16 @@
         <v>9.528228</v>
       </c>
       <c r="M798" t="n">
-        <v>0.05737398163341682</v>
+        <v>0.0573739816334168</v>
       </c>
       <c r="N798" t="n">
-        <v>0.04338756945044189</v>
+        <v>0.0433875694504418</v>
       </c>
       <c r="O798" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P798" t="n">
-        <v>-0.009382430053647466</v>
+        <v>-0.0093824300536474</v>
       </c>
     </row>
     <row r="799">
@@ -46745,16 +46745,16 @@
         <v>8.050672</v>
       </c>
       <c r="M799" t="n">
-        <v>0.03679416616988535</v>
+        <v>0.0367941661698853</v>
       </c>
       <c r="N799" t="n">
-        <v>0.04839241102993165</v>
+        <v>0.0483924110299316</v>
       </c>
       <c r="O799" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P799" t="n">
-        <v>-0.004377588474157708</v>
+        <v>-0.0043775884741577</v>
       </c>
     </row>
     <row r="800">
@@ -46809,10 +46809,10 @@
         <v>0.0446944276653579</v>
       </c>
       <c r="O800" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P800" t="n">
-        <v>-0.008075571838731456</v>
+        <v>-0.0080755718387314</v>
       </c>
     </row>
     <row r="801">
@@ -46861,16 +46861,16 @@
         <v>6.000041</v>
       </c>
       <c r="M801" t="n">
-        <v>0.04562410329985653</v>
+        <v>0.0456241032998565</v>
       </c>
       <c r="N801" t="n">
-        <v>0.05462109038737446</v>
+        <v>0.0546210903873744</v>
       </c>
       <c r="O801" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P801" t="n">
-        <v>0.001851090883285104</v>
+        <v>0.0018510908832851</v>
       </c>
     </row>
     <row r="802">
@@ -46919,16 +46919,538 @@
         <v>18.926586</v>
       </c>
       <c r="M802" t="n">
-        <v>0.03330947066997936</v>
+        <v>0.0333094706699793</v>
       </c>
       <c r="N802" t="n">
-        <v>0.06701730744936203</v>
+        <v>0.067017307449362</v>
       </c>
       <c r="O802" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.0527699995040893</v>
       </c>
       <c r="P802" t="n">
-        <v>0.01424730794527267</v>
+        <v>0.0142473079452726</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>340.42</v>
+      </c>
+      <c r="F803" t="n">
+        <v>4968150990848</v>
+      </c>
+      <c r="G803" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H803" t="n">
+        <v>9.587490000000001</v>
+      </c>
+      <c r="I803" t="n">
+        <v>39.03899</v>
+      </c>
+      <c r="J803" t="n">
+        <v>35.506687</v>
+      </c>
+      <c r="K803" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L803" t="n">
+        <v>10.642473</v>
+      </c>
+      <c r="M803" t="n">
+        <v>0.02561541625051407</v>
+      </c>
+      <c r="N803" t="n">
+        <v>0.02816370953527995</v>
+      </c>
+      <c r="O803" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P803" t="n">
+        <v>-0.02414628993066244</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>620.6799999999999</v>
+      </c>
+      <c r="F804" t="n">
+        <v>1013244559360</v>
+      </c>
+      <c r="G804" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H804" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I804" t="n">
+        <v>158.33673</v>
+      </c>
+      <c r="J804" t="n">
+        <v>39.478714</v>
+      </c>
+      <c r="K804" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L804" t="n">
+        <v>24.530796</v>
+      </c>
+      <c r="M804" t="n">
+        <v>0.006315653799059097</v>
+      </c>
+      <c r="N804" t="n">
+        <v>0.02533010569053297</v>
+      </c>
+      <c r="O804" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P804" t="n">
+        <v>-0.02697989377540942</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>254.06</v>
+      </c>
+      <c r="F805" t="n">
+        <v>2740370800640</v>
+      </c>
+      <c r="G805" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H805" t="n">
+        <v>10.46643</v>
+      </c>
+      <c r="I805" t="n">
+        <v>20.439259</v>
+      </c>
+      <c r="J805" t="n">
+        <v>24.273798</v>
+      </c>
+      <c r="K805" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L805" t="n">
+        <v>3.5328624</v>
+      </c>
+      <c r="M805" t="n">
+        <v>0.04892545068094151</v>
+      </c>
+      <c r="N805" t="n">
+        <v>0.04119668582224672</v>
+      </c>
+      <c r="O805" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P805" t="n">
+        <v>-0.01111331364369567</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="F806" t="n">
+        <v>1719175217152</v>
+      </c>
+      <c r="G806" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H806" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I806" t="n">
+        <v>45.994892</v>
+      </c>
+      <c r="J806" t="n">
+        <v>18.569834</v>
+      </c>
+      <c r="K806" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L806" t="n">
+        <v>19.29403</v>
+      </c>
+      <c r="M806" t="n">
+        <v>0.02174154495473982</v>
+      </c>
+      <c r="N806" t="n">
+        <v>0.05385078025212418</v>
+      </c>
+      <c r="O806" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P806" t="n">
+        <v>0.001540780786181799</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>344.86</v>
+      </c>
+      <c r="F807" t="n">
+        <v>4217615155200</v>
+      </c>
+      <c r="G807" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H807" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I807" t="n">
+        <v>17.303562</v>
+      </c>
+      <c r="J807" t="n">
+        <v>22.881536</v>
+      </c>
+      <c r="K807" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L807" t="n">
+        <v>9.459377999999999</v>
+      </c>
+      <c r="M807" t="n">
+        <v>0.05779156759264629</v>
+      </c>
+      <c r="N807" t="n">
+        <v>0.04370335788435887</v>
+      </c>
+      <c r="O807" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P807" t="n">
+        <v>-0.008606641581583516</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>720.89</v>
+      </c>
+      <c r="F808" t="n">
+        <v>1836471812096</v>
+      </c>
+      <c r="G808" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H808" t="n">
+        <v>34.54533</v>
+      </c>
+      <c r="I808" t="n">
+        <v>27.162395</v>
+      </c>
+      <c r="J808" t="n">
+        <v>20.867945</v>
+      </c>
+      <c r="K808" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L808" t="n">
+        <v>8.045984000000001</v>
+      </c>
+      <c r="M808" t="n">
+        <v>0.03681560293526058</v>
+      </c>
+      <c r="N808" t="n">
+        <v>0.04792039007338152</v>
+      </c>
+      <c r="O808" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P808" t="n">
+        <v>-0.004389609392560868</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E809" t="n">
+        <v>522.61</v>
+      </c>
+      <c r="F809" t="n">
+        <v>3880664432640</v>
+      </c>
+      <c r="G809" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H809" t="n">
+        <v>23.67732</v>
+      </c>
+      <c r="I809" t="n">
+        <v>29.114761</v>
+      </c>
+      <c r="J809" t="n">
+        <v>22.072176</v>
+      </c>
+      <c r="K809" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L809" t="n">
+        <v>11.694419</v>
+      </c>
+      <c r="M809" t="n">
+        <v>0.0343468360727885</v>
+      </c>
+      <c r="N809" t="n">
+        <v>0.04530590689041541</v>
+      </c>
+      <c r="O809" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P809" t="n">
+        <v>-0.00700409257552697</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E810" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="F810" t="n">
+        <v>298013163520</v>
+      </c>
+      <c r="G810" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H810" t="n">
+        <v>3.80662</v>
+      </c>
+      <c r="I810" t="n">
+        <v>22.506289</v>
+      </c>
+      <c r="J810" t="n">
+        <v>18.801456</v>
+      </c>
+      <c r="K810" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L810" t="n">
+        <v>6.161018</v>
+      </c>
+      <c r="M810" t="n">
+        <v>0.04443202459130922</v>
+      </c>
+      <c r="N810" t="n">
+        <v>0.05318736900936147</v>
+      </c>
+      <c r="O810" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P810" t="n">
+        <v>0.0008773695434190834</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:20:04</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E811" t="n">
+        <v>230.48</v>
+      </c>
+      <c r="F811" t="n">
+        <v>5565400481792</v>
+      </c>
+      <c r="G811" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H811" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I811" t="n">
+        <v>29.1378</v>
+      </c>
+      <c r="J811" t="n">
+        <v>14.482299</v>
+      </c>
+      <c r="K811" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L811" t="n">
+        <v>18.369476</v>
+      </c>
+      <c r="M811" t="n">
+        <v>0.03431968066643527</v>
+      </c>
+      <c r="N811" t="n">
+        <v>0.06904980909406457</v>
+      </c>
+      <c r="O811" t="n">
+        <v>0.05230999946594238</v>
+      </c>
+      <c r="P811" t="n">
+        <v>0.01673980962812218</v>
       </c>
     </row>
   </sheetData>
@@ -47030,12 +47552,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -47049,10 +47571,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>347.37</v>
+        <v>344.86</v>
       </c>
       <c r="F2" t="n">
-        <v>4248312479744</v>
+        <v>4217615155200</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -47061,39 +47583,39 @@
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.429502</v>
+        <v>17.303562</v>
       </c>
       <c r="J2" t="n">
-        <v>23.048077</v>
+        <v>22.881536</v>
       </c>
       <c r="K2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="L2" t="n">
-        <v>9.528228</v>
+        <v>9.459377999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05737398163341682</v>
+        <v>0.05779156759264629</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04338756945044189</v>
+        <v>0.04370335788435887</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.009382430053647466</v>
+        <v>-0.008606641581583516</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -47107,10 +47629,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="F3" t="n">
-        <v>3933757243392</v>
+        <v>3880664432640</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
@@ -47119,39 +47641,39 @@
         <v>23.67732</v>
       </c>
       <c r="I3" t="n">
-        <v>29.513092</v>
+        <v>29.114761</v>
       </c>
       <c r="J3" t="n">
-        <v>22.374153</v>
+        <v>22.072176</v>
       </c>
       <c r="K3" t="n">
         <v>1.72</v>
       </c>
       <c r="L3" t="n">
-        <v>11.854415</v>
+        <v>11.694419</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0338832678948958</v>
+        <v>0.0343468360727885</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0446944276653579</v>
+        <v>0.04530590689041541</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.008075571838731456</v>
+        <v>-0.00700409257552697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -47165,51 +47687,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>721.3099999999999</v>
+        <v>720.89</v>
       </c>
       <c r="F4" t="n">
-        <v>1837541621760</v>
+        <v>1836471812096</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
       </c>
       <c r="H4" t="n">
-        <v>34.90593</v>
+        <v>34.54533</v>
       </c>
       <c r="I4" t="n">
-        <v>27.17822</v>
+        <v>27.162395</v>
       </c>
       <c r="J4" t="n">
-        <v>20.664398</v>
+        <v>20.867945</v>
       </c>
       <c r="K4" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L4" t="n">
-        <v>8.050672</v>
+        <v>8.045984000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03679416616988535</v>
+        <v>0.03681560293526058</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04839241102993165</v>
+        <v>0.04792039007338152</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.004377588474157708</v>
+        <v>-0.004389609392560868</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -47223,10 +47745,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>259.92</v>
+        <v>254.06</v>
       </c>
       <c r="F5" t="n">
-        <v>2803578699776</v>
+        <v>2740370800640</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -47235,39 +47757,39 @@
         <v>10.46643</v>
       </c>
       <c r="I5" t="n">
-        <v>20.9107</v>
+        <v>20.439259</v>
       </c>
       <c r="J5" t="n">
-        <v>24.833685</v>
+        <v>24.273798</v>
       </c>
       <c r="K5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6143494</v>
+        <v>3.5328624</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04782240689442905</v>
+        <v>0.04892545068094151</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04026789012003693</v>
+        <v>0.04119668582224672</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01250210938405243</v>
+        <v>-0.01111331364369567</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -47281,51 +47803,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>336.67</v>
+        <v>340.42</v>
       </c>
       <c r="F6" t="n">
-        <v>4913422663680</v>
+        <v>4968150990848</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.582850000000001</v>
+        <v>9.587490000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.608944</v>
+        <v>39.03899</v>
       </c>
       <c r="J6" t="n">
-        <v>35.132553</v>
+        <v>35.506687</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="L6" t="n">
-        <v>10.525237</v>
+        <v>10.642473</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02590073365610241</v>
+        <v>0.02561541625051407</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02846362907297948</v>
+        <v>0.02816370953527995</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02430637043110988</v>
+        <v>-0.02414628993066244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -47339,10 +47861,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>237.47</v>
+        <v>230.48</v>
       </c>
       <c r="F7" t="n">
-        <v>5734188187648</v>
+        <v>5565400481792</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -47351,39 +47873,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>30.021492</v>
+        <v>29.1378</v>
       </c>
       <c r="J7" t="n">
-        <v>14.921518</v>
+        <v>14.482299</v>
       </c>
       <c r="K7" t="n">
         <v>0.29</v>
       </c>
       <c r="L7" t="n">
-        <v>18.926586</v>
+        <v>18.369476</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03330947066997936</v>
+        <v>0.03431968066643527</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06701730744936203</v>
+        <v>0.06904980909406457</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01424730794527267</v>
+        <v>0.01673980962812218</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -47397,10 +47919,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>645.86</v>
+        <v>620.6799999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1054350311424</v>
+        <v>1013244559360</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -47409,39 +47931,39 @@
         <v>15.72189</v>
       </c>
       <c r="I8" t="n">
-        <v>164.7602</v>
+        <v>158.33673</v>
       </c>
       <c r="J8" t="n">
-        <v>41.0803</v>
+        <v>39.478714</v>
       </c>
       <c r="K8" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L8" t="n">
-        <v>25.525972</v>
+        <v>24.530796</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006069426810763942</v>
+        <v>0.006315653799059097</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02434256650047998</v>
+        <v>0.02533010569053297</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02842743300360938</v>
+        <v>-0.02697989377540942</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -47455,51 +47977,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>376.51</v>
+        <v>360.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1797319426048</v>
+        <v>1719175217152</v>
       </c>
       <c r="G9" t="n">
-        <v>8.119999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="H9" t="n">
         <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>46.36823</v>
+        <v>45.994892</v>
       </c>
       <c r="J9" t="n">
-        <v>19.413918</v>
+        <v>18.569834</v>
       </c>
       <c r="K9" t="n">
         <v>0.37</v>
       </c>
       <c r="L9" t="n">
-        <v>20.17103</v>
+        <v>19.29403</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02156649225784175</v>
+        <v>0.02174154495473982</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05150944198029269</v>
+        <v>0.05385078025212418</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.001260557523796668</v>
+        <v>0.001540780786181799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-07 19:05:53</t>
+          <t>2026-10-08 19:20:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -47513,40 +48035,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69.7</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>290226569216</v>
+        <v>298013163520</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.80709</v>
+        <v>3.80662</v>
       </c>
       <c r="I10" t="n">
-        <v>21.918238</v>
+        <v>22.506289</v>
       </c>
       <c r="J10" t="n">
-        <v>18.307945</v>
+        <v>18.801456</v>
       </c>
       <c r="K10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="L10" t="n">
-        <v>6.000041</v>
+        <v>6.161018</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04562410329985653</v>
+        <v>0.04443202459130922</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05462109038737446</v>
+        <v>0.05318736900936147</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05230999946594238</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001851090883285104</v>
+        <v>0.0008773695434190834</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P811"/>
+  <dimension ref="A1:P820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46977,16 +46977,16 @@
         <v>10.642473</v>
       </c>
       <c r="M803" t="n">
-        <v>0.02561541625051407</v>
+        <v>0.025615416250514</v>
       </c>
       <c r="N803" t="n">
-        <v>0.02816370953527995</v>
+        <v>0.0281637095352799</v>
       </c>
       <c r="O803" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P803" t="n">
-        <v>-0.02414628993066244</v>
+        <v>-0.0241462899306624</v>
       </c>
     </row>
     <row r="804">
@@ -47035,16 +47035,16 @@
         <v>24.530796</v>
       </c>
       <c r="M804" t="n">
-        <v>0.006315653799059097</v>
+        <v>0.006315653799059</v>
       </c>
       <c r="N804" t="n">
-        <v>0.02533010569053297</v>
+        <v>0.0253301056905329</v>
       </c>
       <c r="O804" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P804" t="n">
-        <v>-0.02697989377540942</v>
+        <v>-0.0269798937754094</v>
       </c>
     </row>
     <row r="805">
@@ -47093,16 +47093,16 @@
         <v>3.5328624</v>
       </c>
       <c r="M805" t="n">
-        <v>0.04892545068094151</v>
+        <v>0.0489254506809415</v>
       </c>
       <c r="N805" t="n">
-        <v>0.04119668582224672</v>
+        <v>0.0411966858222467</v>
       </c>
       <c r="O805" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P805" t="n">
-        <v>-0.01111331364369567</v>
+        <v>-0.0111133136436956</v>
       </c>
     </row>
     <row r="806">
@@ -47151,16 +47151,16 @@
         <v>19.29403</v>
       </c>
       <c r="M806" t="n">
-        <v>0.02174154495473982</v>
+        <v>0.0217415449547398</v>
       </c>
       <c r="N806" t="n">
-        <v>0.05385078025212418</v>
+        <v>0.0538507802521241</v>
       </c>
       <c r="O806" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P806" t="n">
-        <v>0.001540780786181799</v>
+        <v>0.0015407807861817</v>
       </c>
     </row>
     <row r="807">
@@ -47209,16 +47209,16 @@
         <v>9.459377999999999</v>
       </c>
       <c r="M807" t="n">
-        <v>0.05779156759264629</v>
+        <v>0.0577915675926462</v>
       </c>
       <c r="N807" t="n">
-        <v>0.04370335788435887</v>
+        <v>0.0437033578843588</v>
       </c>
       <c r="O807" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P807" t="n">
-        <v>-0.008606641581583516</v>
+        <v>-0.0086066415815835</v>
       </c>
     </row>
     <row r="808">
@@ -47267,16 +47267,16 @@
         <v>8.045984000000001</v>
       </c>
       <c r="M808" t="n">
-        <v>0.03681560293526058</v>
+        <v>0.0368156029352605</v>
       </c>
       <c r="N808" t="n">
-        <v>0.04792039007338152</v>
+        <v>0.0479203900733815</v>
       </c>
       <c r="O808" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P808" t="n">
-        <v>-0.004389609392560868</v>
+        <v>-0.0043896093925608</v>
       </c>
     </row>
     <row r="809">
@@ -47328,13 +47328,13 @@
         <v>0.0343468360727885</v>
       </c>
       <c r="N809" t="n">
-        <v>0.04530590689041541</v>
+        <v>0.0453059068904154</v>
       </c>
       <c r="O809" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P809" t="n">
-        <v>-0.00700409257552697</v>
+        <v>-0.0070040925755269</v>
       </c>
     </row>
     <row r="810">
@@ -47383,16 +47383,16 @@
         <v>6.161018</v>
       </c>
       <c r="M810" t="n">
-        <v>0.04443202459130922</v>
+        <v>0.0444320245913092</v>
       </c>
       <c r="N810" t="n">
-        <v>0.05318736900936147</v>
+        <v>0.0531873690093614</v>
       </c>
       <c r="O810" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P810" t="n">
-        <v>0.0008773695434190834</v>
+        <v>0.000877369543419</v>
       </c>
     </row>
     <row r="811">
@@ -47441,16 +47441,538 @@
         <v>18.369476</v>
       </c>
       <c r="M811" t="n">
-        <v>0.03431968066643527</v>
+        <v>0.0343196806664352</v>
       </c>
       <c r="N811" t="n">
-        <v>0.06904980909406457</v>
+        <v>0.0690498090940645</v>
       </c>
       <c r="O811" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0523099994659423</v>
       </c>
       <c r="P811" t="n">
-        <v>0.01673980962812218</v>
+        <v>0.0167398096281221</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E812" t="n">
+        <v>336.64</v>
+      </c>
+      <c r="F812" t="n">
+        <v>4912984883200</v>
+      </c>
+      <c r="G812" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="H812" t="n">
+        <v>9.587680000000001</v>
+      </c>
+      <c r="I812" t="n">
+        <v>39.053368</v>
+      </c>
+      <c r="J812" t="n">
+        <v>35.11173</v>
+      </c>
+      <c r="K812" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L812" t="n">
+        <v>10.5243</v>
+      </c>
+      <c r="M812" t="n">
+        <v>0.02560598859315589</v>
+      </c>
+      <c r="N812" t="n">
+        <v>0.02848051330798479</v>
+      </c>
+      <c r="O812" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P812" t="n">
+        <v>-0.02395948627239851</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E813" t="n">
+        <v>608.1</v>
+      </c>
+      <c r="F813" t="n">
+        <v>992708001792</v>
+      </c>
+      <c r="G813" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H813" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I813" t="n">
+        <v>158.35938</v>
+      </c>
+      <c r="J813" t="n">
+        <v>38.678555</v>
+      </c>
+      <c r="K813" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L813" t="n">
+        <v>24.033602</v>
+      </c>
+      <c r="M813" t="n">
+        <v>0.006314750863344844</v>
+      </c>
+      <c r="N813" t="n">
+        <v>0.02585411938825851</v>
+      </c>
+      <c r="O813" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P813" t="n">
+        <v>-0.02658588019212479</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E814" t="n">
+        <v>262.43</v>
+      </c>
+      <c r="F814" t="n">
+        <v>2830652145664</v>
+      </c>
+      <c r="G814" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="H814" t="n">
+        <v>10.46643</v>
+      </c>
+      <c r="I814" t="n">
+        <v>20.438473</v>
+      </c>
+      <c r="J814" t="n">
+        <v>25.073498</v>
+      </c>
+      <c r="K814" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L814" t="n">
+        <v>3.6492524</v>
+      </c>
+      <c r="M814" t="n">
+        <v>0.04892733300308653</v>
+      </c>
+      <c r="N814" t="n">
+        <v>0.03988274968563046</v>
+      </c>
+      <c r="O814" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P814" t="n">
+        <v>-0.01255724989475284</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E815" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="F815" t="n">
+        <v>1725858185216</v>
+      </c>
+      <c r="G815" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H815" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I815" t="n">
+        <v>46.17369</v>
+      </c>
+      <c r="J815" t="n">
+        <v>18.642021</v>
+      </c>
+      <c r="K815" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L815" t="n">
+        <v>19.369032</v>
+      </c>
+      <c r="M815" t="n">
+        <v>0.02165735464955468</v>
+      </c>
+      <c r="N815" t="n">
+        <v>0.05364225258615921</v>
+      </c>
+      <c r="O815" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P815" t="n">
+        <v>0.001202253005775908</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E816" t="n">
+        <v>347.86</v>
+      </c>
+      <c r="F816" t="n">
+        <v>4254305091584</v>
+      </c>
+      <c r="G816" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H816" t="n">
+        <v>15.07154</v>
+      </c>
+      <c r="I816" t="n">
+        <v>17.306467</v>
+      </c>
+      <c r="J816" t="n">
+        <v>23.080587</v>
+      </c>
+      <c r="K816" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L816" t="n">
+        <v>9.541668</v>
+      </c>
+      <c r="M816" t="n">
+        <v>0.05778186626803887</v>
+      </c>
+      <c r="N816" t="n">
+        <v>0.04332645317081585</v>
+      </c>
+      <c r="O816" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P816" t="n">
+        <v>-0.00911354640956745</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E817" t="n">
+        <v>718.67</v>
+      </c>
+      <c r="F817" t="n">
+        <v>1830816186368</v>
+      </c>
+      <c r="G817" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="H817" t="n">
+        <v>34.54533</v>
+      </c>
+      <c r="I817" t="n">
+        <v>27.16062</v>
+      </c>
+      <c r="J817" t="n">
+        <v>20.80368</v>
+      </c>
+      <c r="K817" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L817" t="n">
+        <v>8.021205999999999</v>
+      </c>
+      <c r="M817" t="n">
+        <v>0.03681801104818624</v>
+      </c>
+      <c r="N817" t="n">
+        <v>0.04806841805000905</v>
+      </c>
+      <c r="O817" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P817" t="n">
+        <v>-0.004371581530374251</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E818" t="n">
+        <v>535.0700000000001</v>
+      </c>
+      <c r="F818" t="n">
+        <v>3973186846720</v>
+      </c>
+      <c r="G818" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H818" t="n">
+        <v>23.67732</v>
+      </c>
+      <c r="I818" t="n">
+        <v>29.808912</v>
+      </c>
+      <c r="J818" t="n">
+        <v>22.59842</v>
+      </c>
+      <c r="K818" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L818" t="n">
+        <v>11.973236</v>
+      </c>
+      <c r="M818" t="n">
+        <v>0.03354701254041527</v>
+      </c>
+      <c r="N818" t="n">
+        <v>0.04425088306202927</v>
+      </c>
+      <c r="O818" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P818" t="n">
+        <v>-0.00818911651835403</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E819" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="F819" t="n">
+        <v>292724965376</v>
+      </c>
+      <c r="G819" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H819" t="n">
+        <v>3.80662</v>
+      </c>
+      <c r="I819" t="n">
+        <v>22.532053</v>
+      </c>
+      <c r="J819" t="n">
+        <v>18.467829</v>
+      </c>
+      <c r="K819" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L819" t="n">
+        <v>6.0516915</v>
+      </c>
+      <c r="M819" t="n">
+        <v>0.04438122332859176</v>
+      </c>
+      <c r="N819" t="n">
+        <v>0.05414822190611664</v>
+      </c>
+      <c r="O819" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P819" t="n">
+        <v>0.001708222325733345</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:49:36</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E820" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="F820" t="n">
+        <v>5536424132608</v>
+      </c>
+      <c r="G820" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H820" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I820" t="n">
+        <v>28.986094</v>
+      </c>
+      <c r="J820" t="n">
+        <v>14.406897</v>
+      </c>
+      <c r="K820" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L820" t="n">
+        <v>18.273836</v>
+      </c>
+      <c r="M820" t="n">
+        <v>0.03449930216329379</v>
+      </c>
+      <c r="N820" t="n">
+        <v>0.06941120027913468</v>
+      </c>
+      <c r="O820" t="n">
+        <v>0.0524399995803833</v>
+      </c>
+      <c r="P820" t="n">
+        <v>0.01697120069875138</v>
       </c>
     </row>
   </sheetData>
@@ -47552,12 +48074,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -47571,51 +48093,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>344.86</v>
+        <v>347.86</v>
       </c>
       <c r="F2" t="n">
-        <v>4217615155200</v>
+        <v>4254305091584</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>20.1</v>
       </c>
       <c r="H2" t="n">
         <v>15.07154</v>
       </c>
       <c r="I2" t="n">
-        <v>17.303562</v>
+        <v>17.306467</v>
       </c>
       <c r="J2" t="n">
-        <v>22.881536</v>
+        <v>23.080587</v>
       </c>
       <c r="K2" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.459377999999999</v>
+        <v>9.541668</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05779156759264629</v>
+        <v>0.05778186626803887</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04370335788435887</v>
+        <v>0.04332645317081585</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.008606641581583516</v>
+        <v>-0.00911354640956745</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -47629,10 +48151,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3880664432640</v>
+        <v>3973186846720</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
@@ -47641,39 +48163,39 @@
         <v>23.67732</v>
       </c>
       <c r="I3" t="n">
-        <v>29.114761</v>
+        <v>29.808912</v>
       </c>
       <c r="J3" t="n">
-        <v>22.072176</v>
+        <v>22.59842</v>
       </c>
       <c r="K3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="L3" t="n">
-        <v>11.694419</v>
+        <v>11.973236</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0343468360727885</v>
+        <v>0.03354701254041527</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04530590689041541</v>
+        <v>0.04425088306202927</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.00700409257552697</v>
+        <v>-0.00818911651835403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -47687,51 +48209,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>720.89</v>
+        <v>718.67</v>
       </c>
       <c r="F4" t="n">
-        <v>1836471812096</v>
+        <v>1830816186368</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>26.46</v>
       </c>
       <c r="H4" t="n">
         <v>34.54533</v>
       </c>
       <c r="I4" t="n">
-        <v>27.162395</v>
+        <v>27.16062</v>
       </c>
       <c r="J4" t="n">
-        <v>20.867945</v>
+        <v>20.80368</v>
       </c>
       <c r="K4" t="n">
         <v>0.95</v>
       </c>
       <c r="L4" t="n">
-        <v>8.045984000000001</v>
+        <v>8.021205999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03681560293526058</v>
+        <v>0.03681801104818624</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04792039007338152</v>
+        <v>0.04806841805000905</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.004389609392560868</v>
+        <v>-0.004371581530374251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -47745,51 +48267,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.06</v>
+        <v>262.43</v>
       </c>
       <c r="F5" t="n">
-        <v>2740370800640</v>
+        <v>2830652145664</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.84</v>
       </c>
       <c r="H5" t="n">
         <v>10.46643</v>
       </c>
       <c r="I5" t="n">
-        <v>20.439259</v>
+        <v>20.438473</v>
       </c>
       <c r="J5" t="n">
-        <v>24.273798</v>
+        <v>25.073498</v>
       </c>
       <c r="K5" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5328624</v>
+        <v>3.6492524</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04892545068094151</v>
+        <v>0.04892733300308653</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04119668582224672</v>
+        <v>0.03988274968563046</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01111331364369567</v>
+        <v>-0.01255724989475284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -47803,51 +48325,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340.42</v>
+        <v>336.64</v>
       </c>
       <c r="F6" t="n">
-        <v>4968150990848</v>
+        <v>4912984883200</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>9.587490000000001</v>
+        <v>9.587680000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>39.03899</v>
+        <v>39.053368</v>
       </c>
       <c r="J6" t="n">
-        <v>35.506687</v>
+        <v>35.11173</v>
       </c>
       <c r="K6" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="L6" t="n">
-        <v>10.642473</v>
+        <v>10.5243</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02561541625051407</v>
+        <v>0.02560598859315589</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02816370953527995</v>
+        <v>0.02848051330798479</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02414628993066244</v>
+        <v>-0.02395948627239851</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -47861,10 +48383,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230.48</v>
+        <v>229.28</v>
       </c>
       <c r="F7" t="n">
-        <v>5565400481792</v>
+        <v>5536424132608</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -47873,39 +48395,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>29.1378</v>
+        <v>28.986094</v>
       </c>
       <c r="J7" t="n">
-        <v>14.482299</v>
+        <v>14.406897</v>
       </c>
       <c r="K7" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="L7" t="n">
-        <v>18.369476</v>
+        <v>18.273836</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03431968066643527</v>
+        <v>0.03449930216329379</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06904980909406457</v>
+        <v>0.06941120027913468</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01673980962812218</v>
+        <v>0.01697120069875138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -47919,51 +48441,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>620.6799999999999</v>
+        <v>608.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1013244559360</v>
+        <v>992708001792</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="H8" t="n">
         <v>15.72189</v>
       </c>
       <c r="I8" t="n">
-        <v>158.33673</v>
+        <v>158.35938</v>
       </c>
       <c r="J8" t="n">
-        <v>39.478714</v>
+        <v>38.678555</v>
       </c>
       <c r="K8" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="L8" t="n">
-        <v>24.530796</v>
+        <v>24.033602</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006315653799059097</v>
+        <v>0.006314750863344844</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02533010569053297</v>
+        <v>0.02585411938825851</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02697989377540942</v>
+        <v>-0.02658588019212479</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -47977,10 +48499,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>360.14</v>
+        <v>361.54</v>
       </c>
       <c r="F9" t="n">
-        <v>1719175217152</v>
+        <v>1725858185216</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -47989,39 +48511,39 @@
         <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>45.994892</v>
+        <v>46.17369</v>
       </c>
       <c r="J9" t="n">
-        <v>18.569834</v>
+        <v>18.642021</v>
       </c>
       <c r="K9" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="L9" t="n">
-        <v>19.29403</v>
+        <v>19.369032</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02174154495473982</v>
+        <v>0.02165735464955468</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05385078025212418</v>
+        <v>0.05364225258615921</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001540780786181799</v>
+        <v>0.001202253005775908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 19:20:04</t>
+          <t>2026-10-09 18:49:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -48035,40 +48557,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.56999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="F10" t="n">
-        <v>298013163520</v>
+        <v>292724965376</v>
       </c>
       <c r="G10" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="H10" t="n">
         <v>3.80662</v>
       </c>
       <c r="I10" t="n">
-        <v>22.506289</v>
+        <v>22.532053</v>
       </c>
       <c r="J10" t="n">
-        <v>18.801456</v>
+        <v>18.467829</v>
       </c>
       <c r="K10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="L10" t="n">
-        <v>6.161018</v>
+        <v>6.0516915</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04443202459130922</v>
+        <v>0.04438122332859176</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05318736900936147</v>
+        <v>0.05414822190611664</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05230999946594238</v>
+        <v>0.0524399995803833</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0008773695434190834</v>
+        <v>0.001708222325733345</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P820"/>
+  <dimension ref="A1:P829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47499,16 +47499,16 @@
         <v>10.5243</v>
       </c>
       <c r="M812" t="n">
-        <v>0.02560598859315589</v>
+        <v>0.0256059885931558</v>
       </c>
       <c r="N812" t="n">
-        <v>0.02848051330798479</v>
+        <v>0.0284805133079847</v>
       </c>
       <c r="O812" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P812" t="n">
-        <v>-0.02395948627239851</v>
+        <v>-0.0239594862723985</v>
       </c>
     </row>
     <row r="813">
@@ -47557,16 +47557,16 @@
         <v>24.033602</v>
       </c>
       <c r="M813" t="n">
-        <v>0.006314750863344844</v>
+        <v>0.0063147508633448</v>
       </c>
       <c r="N813" t="n">
-        <v>0.02585411938825851</v>
+        <v>0.0258541193882585</v>
       </c>
       <c r="O813" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P813" t="n">
-        <v>-0.02658588019212479</v>
+        <v>-0.0265858801921247</v>
       </c>
     </row>
     <row r="814">
@@ -47615,16 +47615,16 @@
         <v>3.6492524</v>
       </c>
       <c r="M814" t="n">
-        <v>0.04892733300308653</v>
+        <v>0.0489273330030865</v>
       </c>
       <c r="N814" t="n">
-        <v>0.03988274968563046</v>
+        <v>0.0398827496856304</v>
       </c>
       <c r="O814" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P814" t="n">
-        <v>-0.01255724989475284</v>
+        <v>-0.0125572498947528</v>
       </c>
     </row>
     <row r="815">
@@ -47673,16 +47673,16 @@
         <v>19.369032</v>
       </c>
       <c r="M815" t="n">
-        <v>0.02165735464955468</v>
+        <v>0.0216573546495546</v>
       </c>
       <c r="N815" t="n">
-        <v>0.05364225258615921</v>
+        <v>0.0536422525861592</v>
       </c>
       <c r="O815" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P815" t="n">
-        <v>0.001202253005775908</v>
+        <v>0.0012022530057759</v>
       </c>
     </row>
     <row r="816">
@@ -47731,16 +47731,16 @@
         <v>9.541668</v>
       </c>
       <c r="M816" t="n">
-        <v>0.05778186626803887</v>
+        <v>0.0577818662680388</v>
       </c>
       <c r="N816" t="n">
-        <v>0.04332645317081585</v>
+        <v>0.0433264531708158</v>
       </c>
       <c r="O816" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P816" t="n">
-        <v>-0.00911354640956745</v>
+        <v>-0.009113546409567399</v>
       </c>
     </row>
     <row r="817">
@@ -47789,16 +47789,16 @@
         <v>8.021205999999999</v>
       </c>
       <c r="M817" t="n">
-        <v>0.03681801104818624</v>
+        <v>0.0368180110481862</v>
       </c>
       <c r="N817" t="n">
-        <v>0.04806841805000905</v>
+        <v>0.048068418050009</v>
       </c>
       <c r="O817" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P817" t="n">
-        <v>-0.004371581530374251</v>
+        <v>-0.0043715815303742</v>
       </c>
     </row>
     <row r="818">
@@ -47847,16 +47847,16 @@
         <v>11.973236</v>
       </c>
       <c r="M818" t="n">
-        <v>0.03354701254041527</v>
+        <v>0.0335470125404152</v>
       </c>
       <c r="N818" t="n">
-        <v>0.04425088306202927</v>
+        <v>0.0442508830620292</v>
       </c>
       <c r="O818" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P818" t="n">
-        <v>-0.00818911651835403</v>
+        <v>-0.008189116518354</v>
       </c>
     </row>
     <row r="819">
@@ -47905,16 +47905,16 @@
         <v>6.0516915</v>
       </c>
       <c r="M819" t="n">
-        <v>0.04438122332859176</v>
+        <v>0.0443812233285917</v>
       </c>
       <c r="N819" t="n">
-        <v>0.05414822190611664</v>
+        <v>0.0541482219061166</v>
       </c>
       <c r="O819" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P819" t="n">
-        <v>0.001708222325733345</v>
+        <v>0.0017082223257333</v>
       </c>
     </row>
     <row r="820">
@@ -47963,17 +47963,359 @@
         <v>18.273836</v>
       </c>
       <c r="M820" t="n">
-        <v>0.03449930216329379</v>
+        <v>0.0344993021632937</v>
       </c>
       <c r="N820" t="n">
-        <v>0.06941120027913468</v>
+        <v>0.0694112002791346</v>
       </c>
       <c r="O820" t="n">
         <v>0.0524399995803833</v>
       </c>
       <c r="P820" t="n">
-        <v>0.01697120069875138</v>
-      </c>
+        <v>0.0169712006987513</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E821" t="n">
+        <v>340.9700012207031</v>
+      </c>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="inlineStr"/>
+      <c r="J821" t="inlineStr"/>
+      <c r="K821" t="inlineStr"/>
+      <c r="L821" t="inlineStr"/>
+      <c r="M821" t="inlineStr"/>
+      <c r="N821" t="inlineStr"/>
+      <c r="O821" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E822" t="n">
+        <v>594.239990234375</v>
+      </c>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="inlineStr"/>
+      <c r="J822" t="inlineStr"/>
+      <c r="K822" t="inlineStr"/>
+      <c r="L822" t="inlineStr"/>
+      <c r="M822" t="inlineStr"/>
+      <c r="N822" t="inlineStr"/>
+      <c r="O822" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E823" t="n">
+        <v>259.5299987792969</v>
+      </c>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="inlineStr"/>
+      <c r="J823" t="inlineStr"/>
+      <c r="K823" t="inlineStr"/>
+      <c r="L823" t="inlineStr"/>
+      <c r="M823" t="inlineStr"/>
+      <c r="N823" t="inlineStr"/>
+      <c r="O823" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E824" t="n">
+        <v>354.7300109863281</v>
+      </c>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="inlineStr"/>
+      <c r="J824" t="inlineStr"/>
+      <c r="K824" t="inlineStr"/>
+      <c r="L824" t="inlineStr"/>
+      <c r="M824" t="inlineStr"/>
+      <c r="N824" t="inlineStr"/>
+      <c r="O824" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E825" t="n">
+        <v>348.9700012207031</v>
+      </c>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr"/>
+      <c r="H825" t="inlineStr"/>
+      <c r="I825" t="inlineStr"/>
+      <c r="J825" t="inlineStr"/>
+      <c r="K825" t="inlineStr"/>
+      <c r="L825" t="inlineStr"/>
+      <c r="M825" t="inlineStr"/>
+      <c r="N825" t="inlineStr"/>
+      <c r="O825" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E826" t="n">
+        <v>742.9600219726562</v>
+      </c>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr"/>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="inlineStr"/>
+      <c r="J826" t="inlineStr"/>
+      <c r="K826" t="inlineStr"/>
+      <c r="L826" t="inlineStr"/>
+      <c r="M826" t="inlineStr"/>
+      <c r="N826" t="inlineStr"/>
+      <c r="O826" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E827" t="n">
+        <v>541.1500244140625</v>
+      </c>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr"/>
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="inlineStr"/>
+      <c r="J827" t="inlineStr"/>
+      <c r="K827" t="inlineStr"/>
+      <c r="L827" t="inlineStr"/>
+      <c r="M827" t="inlineStr"/>
+      <c r="N827" t="inlineStr"/>
+      <c r="O827" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E828" t="n">
+        <v>70.61000061035156</v>
+      </c>
+      <c r="F828" t="inlineStr"/>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="inlineStr"/>
+      <c r="J828" t="inlineStr"/>
+      <c r="K828" t="inlineStr"/>
+      <c r="L828" t="inlineStr"/>
+      <c r="M828" t="inlineStr"/>
+      <c r="N828" t="inlineStr"/>
+      <c r="O828" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:05:12</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E829" t="n">
+        <v>226.3200073242188</v>
+      </c>
+      <c r="F829" t="inlineStr"/>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="inlineStr"/>
+      <c r="J829" t="inlineStr"/>
+      <c r="K829" t="inlineStr"/>
+      <c r="L829" t="inlineStr"/>
+      <c r="M829" t="inlineStr"/>
+      <c r="N829" t="inlineStr"/>
+      <c r="O829" t="n">
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P829" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -48074,12 +48416,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -48089,55 +48431,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>347.86</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4254305091584</v>
-      </c>
-      <c r="G2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>15.07154</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17.306467</v>
-      </c>
-      <c r="J2" t="n">
-        <v>23.080587</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="L2" t="n">
-        <v>9.541668</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.05778186626803887</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.04332645317081585</v>
-      </c>
+        <v>348.9700012207031</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.00911354640956745</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -48147,55 +48469,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>535.0700000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3973186846720</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H3" t="n">
-        <v>23.67732</v>
-      </c>
-      <c r="I3" t="n">
-        <v>29.808912</v>
-      </c>
-      <c r="J3" t="n">
-        <v>22.59842</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>11.973236</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.03354701254041527</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.04425088306202927</v>
-      </c>
+        <v>541.1500244140625</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.00818911651835403</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -48205,55 +48507,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>718.67</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1830816186368</v>
-      </c>
-      <c r="G4" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="H4" t="n">
-        <v>34.54533</v>
-      </c>
-      <c r="I4" t="n">
-        <v>27.16062</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20.80368</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8.021205999999999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.03681801104818624</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.04806841805000905</v>
-      </c>
+        <v>742.9600219726562</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.004371581530374251</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -48263,55 +48545,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>262.43</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2830652145664</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10.46643</v>
-      </c>
-      <c r="I5" t="n">
-        <v>20.438473</v>
-      </c>
-      <c r="J5" t="n">
-        <v>25.073498</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3.6492524</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.04892733300308653</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.03988274968563046</v>
-      </c>
+        <v>259.5299987792969</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.01255724989475284</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -48321,55 +48583,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>336.64</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4912984883200</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>9.587680000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>39.053368</v>
-      </c>
-      <c r="J6" t="n">
-        <v>35.11173</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="L6" t="n">
-        <v>10.5243</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.02560598859315589</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.02848051330798479</v>
-      </c>
+        <v>340.9700012207031</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.02395948627239851</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -48379,55 +48621,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229.28</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5536424132608</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15.9146</v>
-      </c>
-      <c r="I7" t="n">
-        <v>28.986094</v>
-      </c>
-      <c r="J7" t="n">
-        <v>14.406897</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L7" t="n">
-        <v>18.273836</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.03449930216329379</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.06941120027913468</v>
-      </c>
+        <v>226.3200073242188</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.01697120069875138</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -48437,55 +48659,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>608.1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>992708001792</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="H8" t="n">
-        <v>15.72189</v>
-      </c>
-      <c r="I8" t="n">
-        <v>158.35938</v>
-      </c>
-      <c r="J8" t="n">
-        <v>38.678555</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L8" t="n">
-        <v>24.033602</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.006314750863344844</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.02585411938825851</v>
-      </c>
+        <v>594.239990234375</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.02658588019212479</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -48495,55 +48697,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>361.54</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1725858185216</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="H9" t="n">
-        <v>19.39382</v>
-      </c>
-      <c r="I9" t="n">
-        <v>46.17369</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18.642021</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L9" t="n">
-        <v>19.369032</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.02165735464955468</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.05364225258615921</v>
-      </c>
+        <v>354.7300109863281</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.001202253005775908</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-09 18:49:36</t>
+          <t>2026-10-12 20:05:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -48553,45 +48735,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="F10" t="n">
-        <v>292724965376</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.80662</v>
-      </c>
-      <c r="I10" t="n">
-        <v>22.532053</v>
-      </c>
-      <c r="J10" t="n">
-        <v>18.467829</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.0516915</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.04438122332859176</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.05414822190611664</v>
-      </c>
+        <v>70.61000061035156</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>0.0524399995803833</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.001708222325733345</v>
-      </c>
+        <v>0.05240000247955322</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P829"/>
+  <dimension ref="A1:P838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47991,11 +47991,7 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D821" t="inlineStr"/>
       <c r="E821" t="n">
         <v>340.9700012207031</v>
       </c>
@@ -48009,7 +48005,7 @@
       <c r="M821" t="inlineStr"/>
       <c r="N821" t="inlineStr"/>
       <c r="O821" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P821" t="inlineStr"/>
     </row>
@@ -48029,11 +48025,7 @@
           <t>AMD</t>
         </is>
       </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D822" t="inlineStr"/>
       <c r="E822" t="n">
         <v>594.239990234375</v>
       </c>
@@ -48047,7 +48039,7 @@
       <c r="M822" t="inlineStr"/>
       <c r="N822" t="inlineStr"/>
       <c r="O822" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P822" t="inlineStr"/>
     </row>
@@ -48067,11 +48059,7 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D823" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D823" t="inlineStr"/>
       <c r="E823" t="n">
         <v>259.5299987792969</v>
       </c>
@@ -48085,7 +48073,7 @@
       <c r="M823" t="inlineStr"/>
       <c r="N823" t="inlineStr"/>
       <c r="O823" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P823" t="inlineStr"/>
     </row>
@@ -48105,11 +48093,7 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="D824" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D824" t="inlineStr"/>
       <c r="E824" t="n">
         <v>354.7300109863281</v>
       </c>
@@ -48123,7 +48107,7 @@
       <c r="M824" t="inlineStr"/>
       <c r="N824" t="inlineStr"/>
       <c r="O824" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P824" t="inlineStr"/>
     </row>
@@ -48143,11 +48127,7 @@
           <t>GOOG</t>
         </is>
       </c>
-      <c r="D825" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D825" t="inlineStr"/>
       <c r="E825" t="n">
         <v>348.9700012207031</v>
       </c>
@@ -48161,7 +48141,7 @@
       <c r="M825" t="inlineStr"/>
       <c r="N825" t="inlineStr"/>
       <c r="O825" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P825" t="inlineStr"/>
     </row>
@@ -48181,11 +48161,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D826" t="inlineStr"/>
       <c r="E826" t="n">
         <v>742.9600219726562</v>
       </c>
@@ -48199,7 +48175,7 @@
       <c r="M826" t="inlineStr"/>
       <c r="N826" t="inlineStr"/>
       <c r="O826" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P826" t="inlineStr"/>
     </row>
@@ -48219,11 +48195,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D827" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D827" t="inlineStr"/>
       <c r="E827" t="n">
         <v>541.1500244140625</v>
       </c>
@@ -48237,7 +48209,7 @@
       <c r="M827" t="inlineStr"/>
       <c r="N827" t="inlineStr"/>
       <c r="O827" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P827" t="inlineStr"/>
     </row>
@@ -48257,11 +48229,7 @@
           <t>NFLX</t>
         </is>
       </c>
-      <c r="D828" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D828" t="inlineStr"/>
       <c r="E828" t="n">
         <v>70.61000061035156</v>
       </c>
@@ -48275,7 +48243,7 @@
       <c r="M828" t="inlineStr"/>
       <c r="N828" t="inlineStr"/>
       <c r="O828" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P828" t="inlineStr"/>
     </row>
@@ -48295,11 +48263,7 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D829" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D829" t="inlineStr"/>
       <c r="E829" t="n">
         <v>226.3200073242188</v>
       </c>
@@ -48313,9 +48277,531 @@
       <c r="M829" t="inlineStr"/>
       <c r="N829" t="inlineStr"/>
       <c r="O829" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.0524000024795532</v>
       </c>
       <c r="P829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E830" t="n">
+        <v>341.27</v>
+      </c>
+      <c r="F830" t="n">
+        <v>4980555644928</v>
+      </c>
+      <c r="G830" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H830" t="n">
+        <v>9.590350000000001</v>
+      </c>
+      <c r="I830" t="n">
+        <v>39.136467</v>
+      </c>
+      <c r="J830" t="n">
+        <v>35.58473</v>
+      </c>
+      <c r="K830" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L830" t="n">
+        <v>10.669045</v>
+      </c>
+      <c r="M830" t="n">
+        <v>0.02555161602250418</v>
+      </c>
+      <c r="N830" t="n">
+        <v>0.02810194274328245</v>
+      </c>
+      <c r="O830" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P830" t="n">
+        <v>-0.0240680573330115</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E831" t="n">
+        <v>605.53</v>
+      </c>
+      <c r="F831" t="n">
+        <v>988512649216</v>
+      </c>
+      <c r="G831" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H831" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I831" t="n">
+        <v>154.47194</v>
+      </c>
+      <c r="J831" t="n">
+        <v>38.51509</v>
+      </c>
+      <c r="K831" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L831" t="n">
+        <v>23.932032</v>
+      </c>
+      <c r="M831" t="n">
+        <v>0.006473667696067908</v>
+      </c>
+      <c r="N831" t="n">
+        <v>0.02596384985054415</v>
+      </c>
+      <c r="O831" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P831" t="n">
+        <v>-0.02620615022574979</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E832" t="n">
+        <v>258.58</v>
+      </c>
+      <c r="F832" t="n">
+        <v>2789124603904</v>
+      </c>
+      <c r="G832" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H832" t="n">
+        <v>10.45377</v>
+      </c>
+      <c r="I832" t="n">
+        <v>20.802895</v>
+      </c>
+      <c r="J832" t="n">
+        <v>24.735573</v>
+      </c>
+      <c r="K832" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L832" t="n">
+        <v>3.5957153</v>
+      </c>
+      <c r="M832" t="n">
+        <v>0.04807022971614201</v>
+      </c>
+      <c r="N832" t="n">
+        <v>0.04042760460979195</v>
+      </c>
+      <c r="O832" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P832" t="n">
+        <v>-0.011742395466502</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E833" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="F833" t="n">
+        <v>1705665757184</v>
+      </c>
+      <c r="G833" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H833" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I833" t="n">
+        <v>45.63346</v>
+      </c>
+      <c r="J833" t="n">
+        <v>18.42391</v>
+      </c>
+      <c r="K833" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L833" t="n">
+        <v>19.142416</v>
+      </c>
+      <c r="M833" t="n">
+        <v>0.02191374436763594</v>
+      </c>
+      <c r="N833" t="n">
+        <v>0.05427729422630209</v>
+      </c>
+      <c r="O833" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P833" t="n">
+        <v>0.002107294150008147</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E834" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="F834" t="n">
+        <v>4274606833664</v>
+      </c>
+      <c r="G834" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H834" t="n">
+        <v>15.24397</v>
+      </c>
+      <c r="I834" t="n">
+        <v>17.53738</v>
+      </c>
+      <c r="J834" t="n">
+        <v>22.92841</v>
+      </c>
+      <c r="K834" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L834" t="n">
+        <v>9.587201</v>
+      </c>
+      <c r="M834" t="n">
+        <v>0.05702105745021745</v>
+      </c>
+      <c r="N834" t="n">
+        <v>0.04361401350423438</v>
+      </c>
+      <c r="O834" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P834" t="n">
+        <v>-0.008555986572059568</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E835" t="n">
+        <v>762.5</v>
+      </c>
+      <c r="F835" t="n">
+        <v>1942473408512</v>
+      </c>
+      <c r="G835" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H835" t="n">
+        <v>34.65286</v>
+      </c>
+      <c r="I835" t="n">
+        <v>28.730217</v>
+      </c>
+      <c r="J835" t="n">
+        <v>22.003956</v>
+      </c>
+      <c r="K835" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L835" t="n">
+        <v>8.510401</v>
+      </c>
+      <c r="M835" t="n">
+        <v>0.03480655737704918</v>
+      </c>
+      <c r="N835" t="n">
+        <v>0.0454463737704918</v>
+      </c>
+      <c r="O835" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P835" t="n">
+        <v>-0.006723626305802144</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E836" t="n">
+        <v>543.45</v>
+      </c>
+      <c r="F836" t="n">
+        <v>4035413016576</v>
+      </c>
+      <c r="G836" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="H836" t="n">
+        <v>23.67408</v>
+      </c>
+      <c r="I836" t="n">
+        <v>30.616901</v>
+      </c>
+      <c r="J836" t="n">
+        <v>22.955486</v>
+      </c>
+      <c r="K836" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L836" t="n">
+        <v>12.160755</v>
+      </c>
+      <c r="M836" t="n">
+        <v>0.03266169840831723</v>
+      </c>
+      <c r="N836" t="n">
+        <v>0.04356257245376759</v>
+      </c>
+      <c r="O836" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P836" t="n">
+        <v>-0.008607427622526351</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E837" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="F837" t="n">
+        <v>293391171584</v>
+      </c>
+      <c r="G837" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H837" t="n">
+        <v>3.80154</v>
+      </c>
+      <c r="I837" t="n">
+        <v>22.157232</v>
+      </c>
+      <c r="J837" t="n">
+        <v>18.534594</v>
+      </c>
+      <c r="K837" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L837" t="n">
+        <v>6.0654645</v>
+      </c>
+      <c r="M837" t="n">
+        <v>0.04513198978143628</v>
+      </c>
+      <c r="N837" t="n">
+        <v>0.05395316491626456</v>
+      </c>
+      <c r="O837" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P837" t="n">
+        <v>0.001783164839970611</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:17:18</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E838" t="n">
+        <v>228.52</v>
+      </c>
+      <c r="F838" t="n">
+        <v>5518072479744</v>
+      </c>
+      <c r="G838" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H838" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I838" t="n">
+        <v>28.890015</v>
+      </c>
+      <c r="J838" t="n">
+        <v>14.359142</v>
+      </c>
+      <c r="K838" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L838" t="n">
+        <v>18.213263</v>
+      </c>
+      <c r="M838" t="n">
+        <v>0.03461403815858568</v>
+      </c>
+      <c r="N838" t="n">
+        <v>0.06964204446000349</v>
+      </c>
+      <c r="O838" t="n">
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P838" t="n">
+        <v>0.01747204438370955</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -48416,12 +48902,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -48431,35 +48917,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>348.9700012207031</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>349.52</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4274606833664</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15.24397</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17.53738</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.92841</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.587201</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05702105745021745</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.04361401350423438</v>
+      </c>
       <c r="O2" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.008555986572059568</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -48469,35 +48975,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>541.1500244140625</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>543.45</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4035413016576</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.67408</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30.616901</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22.955486</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L3" t="n">
+        <v>12.160755</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.03266169840831723</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04356257245376759</v>
+      </c>
       <c r="O3" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.008607427622526351</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -48507,35 +49033,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>742.9600219726562</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>762.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1942473408512</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H4" t="n">
+        <v>34.65286</v>
+      </c>
+      <c r="I4" t="n">
+        <v>28.730217</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.003956</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.510401</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.03480655737704918</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0454463737704918</v>
+      </c>
       <c r="O4" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.006723626305802144</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -48545,35 +49091,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>259.5299987792969</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>258.58</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2789124603904</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.45377</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20.802895</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.735573</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.5957153</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04807022971614201</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.04042760460979195</v>
+      </c>
       <c r="O5" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.011742395466502</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -48583,35 +49149,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340.9700012207031</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>341.27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4980555644928</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.590350000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>39.136467</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.58473</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10.669045</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02555161602250418</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02810194274328245</v>
+      </c>
       <c r="O6" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.0240680573330115</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -48621,35 +49207,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>226.3200073242188</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>228.52</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5518072479744</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I7" t="n">
+        <v>28.890015</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14.359142</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L7" t="n">
+        <v>18.213263</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.03461403815858568</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.06964204446000349</v>
+      </c>
       <c r="O7" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.01747204438370955</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -48659,35 +49265,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>594.239990234375</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>605.53</v>
+      </c>
+      <c r="F8" t="n">
+        <v>988512649216</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I8" t="n">
+        <v>154.47194</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38.51509</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23.932032</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.006473667696067908</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.02596384985054415</v>
+      </c>
       <c r="O8" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.02620615022574979</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -48697,35 +49323,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>354.7300109863281</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>357.31</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1705665757184</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H9" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I9" t="n">
+        <v>45.63346</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.42391</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19.142416</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02191374436763594</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.05427729422630209</v>
+      </c>
       <c r="O9" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.002107294150008147</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-12 20:05:12</t>
+          <t>2026-10-13 18:17:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -48735,25 +49381,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.61000061035156</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>70.45999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>293391171584</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.80154</v>
+      </c>
+      <c r="I10" t="n">
+        <v>22.157232</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.534594</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.0654645</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.04513198978143628</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.05395316491626456</v>
+      </c>
       <c r="O10" t="n">
-        <v>0.05240000247955322</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
+        <v>0.05217000007629394</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.001783164839970611</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P838"/>
+  <dimension ref="A1:P847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48327,16 +48327,16 @@
         <v>10.669045</v>
       </c>
       <c r="M830" t="n">
-        <v>0.02555161602250418</v>
+        <v>0.0255516160225041</v>
       </c>
       <c r="N830" t="n">
-        <v>0.02810194274328245</v>
+        <v>0.0281019427432824</v>
       </c>
       <c r="O830" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P830" t="n">
-        <v>-0.0240680573330115</v>
+        <v>-0.0240680573330114</v>
       </c>
     </row>
     <row r="831">
@@ -48385,16 +48385,16 @@
         <v>23.932032</v>
       </c>
       <c r="M831" t="n">
-        <v>0.006473667696067908</v>
+        <v>0.0064736676960679</v>
       </c>
       <c r="N831" t="n">
-        <v>0.02596384985054415</v>
+        <v>0.0259638498505441</v>
       </c>
       <c r="O831" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P831" t="n">
-        <v>-0.02620615022574979</v>
+        <v>-0.0262061502257497</v>
       </c>
     </row>
     <row r="832">
@@ -48443,13 +48443,13 @@
         <v>3.5957153</v>
       </c>
       <c r="M832" t="n">
-        <v>0.04807022971614201</v>
+        <v>0.048070229716142</v>
       </c>
       <c r="N832" t="n">
-        <v>0.04042760460979195</v>
+        <v>0.0404276046097919</v>
       </c>
       <c r="O832" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P832" t="n">
         <v>-0.011742395466502</v>
@@ -48501,16 +48501,16 @@
         <v>19.142416</v>
       </c>
       <c r="M833" t="n">
-        <v>0.02191374436763594</v>
+        <v>0.0219137443676359</v>
       </c>
       <c r="N833" t="n">
-        <v>0.05427729422630209</v>
+        <v>0.054277294226302</v>
       </c>
       <c r="O833" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P833" t="n">
-        <v>0.002107294150008147</v>
+        <v>0.0021072941500081</v>
       </c>
     </row>
     <row r="834">
@@ -48559,16 +48559,16 @@
         <v>9.587201</v>
       </c>
       <c r="M834" t="n">
-        <v>0.05702105745021745</v>
+        <v>0.0570210574502174</v>
       </c>
       <c r="N834" t="n">
-        <v>0.04361401350423438</v>
+        <v>0.0436140135042343</v>
       </c>
       <c r="O834" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P834" t="n">
-        <v>-0.008555986572059568</v>
+        <v>-0.0085559865720595</v>
       </c>
     </row>
     <row r="835">
@@ -48617,16 +48617,16 @@
         <v>8.510401</v>
       </c>
       <c r="M835" t="n">
-        <v>0.03480655737704918</v>
+        <v>0.0348065573770491</v>
       </c>
       <c r="N835" t="n">
         <v>0.0454463737704918</v>
       </c>
       <c r="O835" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P835" t="n">
-        <v>-0.006723626305802144</v>
+        <v>-0.0067236263058021</v>
       </c>
     </row>
     <row r="836">
@@ -48675,16 +48675,16 @@
         <v>12.160755</v>
       </c>
       <c r="M836" t="n">
-        <v>0.03266169840831723</v>
+        <v>0.0326616984083172</v>
       </c>
       <c r="N836" t="n">
-        <v>0.04356257245376759</v>
+        <v>0.0435625724537675</v>
       </c>
       <c r="O836" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P836" t="n">
-        <v>-0.008607427622526351</v>
+        <v>-0.0086074276225263</v>
       </c>
     </row>
     <row r="837">
@@ -48733,16 +48733,16 @@
         <v>6.0654645</v>
       </c>
       <c r="M837" t="n">
-        <v>0.04513198978143628</v>
+        <v>0.0451319897814362</v>
       </c>
       <c r="N837" t="n">
-        <v>0.05395316491626456</v>
+        <v>0.0539531649162645</v>
       </c>
       <c r="O837" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P837" t="n">
-        <v>0.001783164839970611</v>
+        <v>0.0017831648399706</v>
       </c>
     </row>
     <row r="838">
@@ -48791,16 +48791,538 @@
         <v>18.213263</v>
       </c>
       <c r="M838" t="n">
-        <v>0.03461403815858568</v>
+        <v>0.0346140381585856</v>
       </c>
       <c r="N838" t="n">
         <v>0.06964204446000349</v>
       </c>
       <c r="O838" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.0521700000762939</v>
       </c>
       <c r="P838" t="n">
-        <v>0.01747204438370955</v>
+        <v>0.0174720443837095</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E839" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="F839" t="n">
+        <v>5005219725312</v>
+      </c>
+      <c r="G839" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H839" t="n">
+        <v>9.5906</v>
+      </c>
+      <c r="I839" t="n">
+        <v>39.330273</v>
+      </c>
+      <c r="J839" t="n">
+        <v>35.760014</v>
+      </c>
+      <c r="K839" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L839" t="n">
+        <v>10.721879</v>
+      </c>
+      <c r="M839" t="n">
+        <v>0.02542570562164684</v>
+      </c>
+      <c r="N839" t="n">
+        <v>0.0279641940751108</v>
+      </c>
+      <c r="O839" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P839" t="n">
+        <v>-0.02393580649709379</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E840" t="n">
+        <v>570.8200000000001</v>
+      </c>
+      <c r="F840" t="n">
+        <v>931849371648</v>
+      </c>
+      <c r="G840" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H840" t="n">
+        <v>15.72189</v>
+      </c>
+      <c r="I840" t="n">
+        <v>145.61734</v>
+      </c>
+      <c r="J840" t="n">
+        <v>36.30734</v>
+      </c>
+      <c r="K840" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L840" t="n">
+        <v>22.560207</v>
+      </c>
+      <c r="M840" t="n">
+        <v>0.006867313689078869</v>
+      </c>
+      <c r="N840" t="n">
+        <v>0.02754264041203882</v>
+      </c>
+      <c r="O840" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P840" t="n">
+        <v>-0.02435736016016577</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E841" t="n">
+        <v>254.08</v>
+      </c>
+      <c r="F841" t="n">
+        <v>2740586545152</v>
+      </c>
+      <c r="G841" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H841" t="n">
+        <v>10.45377</v>
+      </c>
+      <c r="I841" t="n">
+        <v>20.440868</v>
+      </c>
+      <c r="J841" t="n">
+        <v>24.305107</v>
+      </c>
+      <c r="K841" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L841" t="n">
+        <v>3.5331404</v>
+      </c>
+      <c r="M841" t="n">
+        <v>0.04892159949622166</v>
+      </c>
+      <c r="N841" t="n">
+        <v>0.04114361618387909</v>
+      </c>
+      <c r="O841" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P841" t="n">
+        <v>-0.0107563843883255</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E842" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="F842" t="n">
+        <v>1652869431296</v>
+      </c>
+      <c r="G842" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="H842" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I842" t="n">
+        <v>43.389725</v>
+      </c>
+      <c r="J842" t="n">
+        <v>17.853626</v>
+      </c>
+      <c r="K842" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L842" t="n">
+        <v>18.54989</v>
+      </c>
+      <c r="M842" t="n">
+        <v>0.02304693140794224</v>
+      </c>
+      <c r="N842" t="n">
+        <v>0.05601103249097474</v>
+      </c>
+      <c r="O842" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P842" t="n">
+        <v>0.004111031918770144</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E843" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="F843" t="n">
+        <v>4202817126400</v>
+      </c>
+      <c r="G843" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H843" t="n">
+        <v>15.25175</v>
+      </c>
+      <c r="I843" t="n">
+        <v>17.24285</v>
+      </c>
+      <c r="J843" t="n">
+        <v>22.53184</v>
+      </c>
+      <c r="K843" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L843" t="n">
+        <v>9.426189000000001</v>
+      </c>
+      <c r="M843" t="n">
+        <v>0.05799505310635822</v>
+      </c>
+      <c r="N843" t="n">
+        <v>0.04438163829477666</v>
+      </c>
+      <c r="O843" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P843" t="n">
+        <v>-0.007518362277427929</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E844" t="n">
+        <v>737.54</v>
+      </c>
+      <c r="F844" t="n">
+        <v>1878887628800</v>
+      </c>
+      <c r="G844" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H844" t="n">
+        <v>34.65286</v>
+      </c>
+      <c r="I844" t="n">
+        <v>27.78975</v>
+      </c>
+      <c r="J844" t="n">
+        <v>21.283669</v>
+      </c>
+      <c r="K844" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L844" t="n">
+        <v>8.231816999999999</v>
+      </c>
+      <c r="M844" t="n">
+        <v>0.03598448897686905</v>
+      </c>
+      <c r="N844" t="n">
+        <v>0.04698438050817583</v>
+      </c>
+      <c r="O844" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P844" t="n">
+        <v>-0.004915620064028764</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E845" t="n">
+        <v>533.6900000000001</v>
+      </c>
+      <c r="F845" t="n">
+        <v>3962939637760</v>
+      </c>
+      <c r="G845" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H845" t="n">
+        <v>23.69909</v>
+      </c>
+      <c r="I845" t="n">
+        <v>29.732033</v>
+      </c>
+      <c r="J845" t="n">
+        <v>22.51943</v>
+      </c>
+      <c r="K845" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L845" t="n">
+        <v>11.942356</v>
+      </c>
+      <c r="M845" t="n">
+        <v>0.03363375742472221</v>
+      </c>
+      <c r="N845" t="n">
+        <v>0.04440609717251588</v>
+      </c>
+      <c r="O845" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P845" t="n">
+        <v>-0.007493903399688709</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E846" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="F846" t="n">
+        <v>293849202688</v>
+      </c>
+      <c r="G846" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H846" t="n">
+        <v>3.80154</v>
+      </c>
+      <c r="I846" t="n">
+        <v>22.191824</v>
+      </c>
+      <c r="J846" t="n">
+        <v>18.56353</v>
+      </c>
+      <c r="K846" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L846" t="n">
+        <v>6.074934</v>
+      </c>
+      <c r="M846" t="n">
+        <v>0.04506164092390535</v>
+      </c>
+      <c r="N846" t="n">
+        <v>0.05386906617542866</v>
+      </c>
+      <c r="O846" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P846" t="n">
+        <v>0.001969065603224067</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:38:26</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E847" t="n">
+        <v>221.3</v>
+      </c>
+      <c r="F847" t="n">
+        <v>5343730991104</v>
+      </c>
+      <c r="G847" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H847" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I847" t="n">
+        <v>27.977245</v>
+      </c>
+      <c r="J847" t="n">
+        <v>13.90547</v>
+      </c>
+      <c r="K847" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L847" t="n">
+        <v>17.637821</v>
+      </c>
+      <c r="M847" t="n">
+        <v>0.03574333483958427</v>
+      </c>
+      <c r="N847" t="n">
+        <v>0.07191414369633981</v>
+      </c>
+      <c r="O847" t="n">
+        <v>0.05190000057220459</v>
+      </c>
+      <c r="P847" t="n">
+        <v>0.02001414312413521</v>
       </c>
     </row>
   </sheetData>
@@ -48902,12 +49424,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -48921,51 +49443,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>349.52</v>
+        <v>343.65</v>
       </c>
       <c r="F2" t="n">
-        <v>4274606833664</v>
+        <v>4202817126400</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>15.24397</v>
+        <v>15.25175</v>
       </c>
       <c r="I2" t="n">
-        <v>17.53738</v>
+        <v>17.24285</v>
       </c>
       <c r="J2" t="n">
-        <v>22.92841</v>
+        <v>22.53184</v>
       </c>
       <c r="K2" t="n">
         <v>1.23</v>
       </c>
       <c r="L2" t="n">
-        <v>9.587201</v>
+        <v>9.426189000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05702105745021745</v>
+        <v>0.05799505310635822</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04361401350423438</v>
+        <v>0.04438163829477666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.008555986572059568</v>
+        <v>-0.007518362277427929</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -48979,51 +49501,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4035413016576</v>
+        <v>3962939637760</v>
       </c>
       <c r="G3" t="n">
-        <v>17.75</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.67408</v>
+        <v>23.69909</v>
       </c>
       <c r="I3" t="n">
-        <v>30.616901</v>
+        <v>29.732033</v>
       </c>
       <c r="J3" t="n">
-        <v>22.955486</v>
+        <v>22.51943</v>
       </c>
       <c r="K3" t="n">
         <v>1.76</v>
       </c>
       <c r="L3" t="n">
-        <v>12.160755</v>
+        <v>11.942356</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03266169840831723</v>
+        <v>0.03363375742472221</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04356257245376759</v>
+        <v>0.04440609717251588</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.008607427622526351</v>
+        <v>-0.007493903399688709</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -49037,10 +49559,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>762.5</v>
+        <v>737.54</v>
       </c>
       <c r="F4" t="n">
-        <v>1942473408512</v>
+        <v>1878887628800</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
@@ -49049,39 +49571,39 @@
         <v>34.65286</v>
       </c>
       <c r="I4" t="n">
-        <v>28.730217</v>
+        <v>27.78975</v>
       </c>
       <c r="J4" t="n">
-        <v>22.003956</v>
+        <v>21.283669</v>
       </c>
       <c r="K4" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="L4" t="n">
-        <v>8.510401</v>
+        <v>8.231816999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03480655737704918</v>
+        <v>0.03598448897686905</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0454463737704918</v>
+        <v>0.04698438050817583</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.006723626305802144</v>
+        <v>-0.004915620064028764</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -49095,10 +49617,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258.58</v>
+        <v>254.08</v>
       </c>
       <c r="F5" t="n">
-        <v>2789124603904</v>
+        <v>2740586545152</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -49107,39 +49629,39 @@
         <v>10.45377</v>
       </c>
       <c r="I5" t="n">
-        <v>20.802895</v>
+        <v>20.440868</v>
       </c>
       <c r="J5" t="n">
-        <v>24.735573</v>
+        <v>24.305107</v>
       </c>
       <c r="K5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5957153</v>
+        <v>3.5331404</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04807022971614201</v>
+        <v>0.04892159949622166</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04042760460979195</v>
+        <v>0.04114361618387909</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.011742395466502</v>
+        <v>-0.0107563843883255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -49153,51 +49675,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>341.27</v>
+        <v>342.96</v>
       </c>
       <c r="F6" t="n">
-        <v>4980555644928</v>
+        <v>5005219725312</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.590350000000001</v>
+        <v>9.5906</v>
       </c>
       <c r="I6" t="n">
-        <v>39.136467</v>
+        <v>39.330273</v>
       </c>
       <c r="J6" t="n">
-        <v>35.58473</v>
+        <v>35.760014</v>
       </c>
       <c r="K6" t="n">
         <v>2.73</v>
       </c>
       <c r="L6" t="n">
-        <v>10.669045</v>
+        <v>10.721879</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02555161602250418</v>
+        <v>0.02542570562164684</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02810194274328245</v>
+        <v>0.0279641940751108</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0240680573330115</v>
+        <v>-0.02393580649709379</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -49211,10 +49733,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228.52</v>
+        <v>221.3</v>
       </c>
       <c r="F7" t="n">
-        <v>5518072479744</v>
+        <v>5343730991104</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -49223,39 +49745,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>28.890015</v>
+        <v>27.977245</v>
       </c>
       <c r="J7" t="n">
-        <v>14.359142</v>
+        <v>13.90547</v>
       </c>
       <c r="K7" t="n">
         <v>0.28</v>
       </c>
       <c r="L7" t="n">
-        <v>18.213263</v>
+        <v>17.637821</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03461403815858568</v>
+        <v>0.03574333483958427</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06964204446000349</v>
+        <v>0.07191414369633981</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01747204438370955</v>
+        <v>0.02001414312413521</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -49269,10 +49791,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>605.53</v>
+        <v>570.8200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>988512649216</v>
+        <v>931849371648</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -49281,39 +49803,39 @@
         <v>15.72189</v>
       </c>
       <c r="I8" t="n">
-        <v>154.47194</v>
+        <v>145.61734</v>
       </c>
       <c r="J8" t="n">
-        <v>38.51509</v>
+        <v>36.30734</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L8" t="n">
-        <v>23.932032</v>
+        <v>22.560207</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006473667696067908</v>
+        <v>0.006867313689078869</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02596384985054415</v>
+        <v>0.02754264041203882</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02620615022574979</v>
+        <v>-0.02435736016016577</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -49327,51 +49849,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>357.31</v>
+        <v>346.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1705665757184</v>
+        <v>1652869431296</v>
       </c>
       <c r="G9" t="n">
-        <v>7.83</v>
+        <v>7.98</v>
       </c>
       <c r="H9" t="n">
         <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>45.63346</v>
+        <v>43.389725</v>
       </c>
       <c r="J9" t="n">
-        <v>18.42391</v>
+        <v>17.853626</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.142416</v>
+        <v>18.54989</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02191374436763594</v>
+        <v>0.02304693140794224</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05427729422630209</v>
+        <v>0.05601103249097474</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002107294150008147</v>
+        <v>0.004111031918770144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-13 18:17:18</t>
+          <t>2026-10-14 17:38:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -49385,10 +49907,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>293391171584</v>
+        <v>293849202688</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -49397,28 +49919,28 @@
         <v>3.80154</v>
       </c>
       <c r="I10" t="n">
-        <v>22.157232</v>
+        <v>22.191824</v>
       </c>
       <c r="J10" t="n">
-        <v>18.534594</v>
+        <v>18.56353</v>
       </c>
       <c r="K10" t="n">
         <v>1.21</v>
       </c>
       <c r="L10" t="n">
-        <v>6.0654645</v>
+        <v>6.074934</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04513198978143628</v>
+        <v>0.04506164092390535</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05395316491626456</v>
+        <v>0.05386906617542866</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05217000007629394</v>
+        <v>0.05190000057220459</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001783164839970611</v>
+        <v>0.001969065603224067</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P847"/>
+  <dimension ref="A1:P856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48849,16 +48849,16 @@
         <v>10.721879</v>
       </c>
       <c r="M839" t="n">
-        <v>0.02542570562164684</v>
+        <v>0.0254257056216468</v>
       </c>
       <c r="N839" t="n">
         <v>0.0279641940751108</v>
       </c>
       <c r="O839" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P839" t="n">
-        <v>-0.02393580649709379</v>
+        <v>-0.0239358064970937</v>
       </c>
     </row>
     <row r="840">
@@ -48907,16 +48907,16 @@
         <v>22.560207</v>
       </c>
       <c r="M840" t="n">
-        <v>0.006867313689078869</v>
+        <v>0.0068673136890788</v>
       </c>
       <c r="N840" t="n">
-        <v>0.02754264041203882</v>
+        <v>0.0275426404120388</v>
       </c>
       <c r="O840" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P840" t="n">
-        <v>-0.02435736016016577</v>
+        <v>-0.0243573601601657</v>
       </c>
     </row>
     <row r="841">
@@ -48965,16 +48965,16 @@
         <v>3.5331404</v>
       </c>
       <c r="M841" t="n">
-        <v>0.04892159949622166</v>
+        <v>0.0489215994962216</v>
       </c>
       <c r="N841" t="n">
-        <v>0.04114361618387909</v>
+        <v>0.041143616183879</v>
       </c>
       <c r="O841" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P841" t="n">
-        <v>-0.0107563843883255</v>
+        <v>-0.0107563843883254</v>
       </c>
     </row>
     <row r="842">
@@ -49023,16 +49023,16 @@
         <v>18.54989</v>
       </c>
       <c r="M842" t="n">
-        <v>0.02304693140794224</v>
+        <v>0.0230469314079422</v>
       </c>
       <c r="N842" t="n">
-        <v>0.05601103249097474</v>
+        <v>0.0560110324909747</v>
       </c>
       <c r="O842" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P842" t="n">
-        <v>0.004111031918770144</v>
+        <v>0.0041110319187701</v>
       </c>
     </row>
     <row r="843">
@@ -49081,16 +49081,16 @@
         <v>9.426189000000001</v>
       </c>
       <c r="M843" t="n">
-        <v>0.05799505310635822</v>
+        <v>0.0579950531063582</v>
       </c>
       <c r="N843" t="n">
-        <v>0.04438163829477666</v>
+        <v>0.0443816382947766</v>
       </c>
       <c r="O843" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P843" t="n">
-        <v>-0.007518362277427929</v>
+        <v>-0.0075183622774279</v>
       </c>
     </row>
     <row r="844">
@@ -49139,16 +49139,16 @@
         <v>8.231816999999999</v>
       </c>
       <c r="M844" t="n">
-        <v>0.03598448897686905</v>
+        <v>0.035984488976869</v>
       </c>
       <c r="N844" t="n">
-        <v>0.04698438050817583</v>
+        <v>0.0469843805081758</v>
       </c>
       <c r="O844" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P844" t="n">
-        <v>-0.004915620064028764</v>
+        <v>-0.0049156200640287</v>
       </c>
     </row>
     <row r="845">
@@ -49197,16 +49197,16 @@
         <v>11.942356</v>
       </c>
       <c r="M845" t="n">
-        <v>0.03363375742472221</v>
+        <v>0.0336337574247222</v>
       </c>
       <c r="N845" t="n">
-        <v>0.04440609717251588</v>
+        <v>0.0444060971725158</v>
       </c>
       <c r="O845" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P845" t="n">
-        <v>-0.007493903399688709</v>
+        <v>-0.0074939033996887</v>
       </c>
     </row>
     <row r="846">
@@ -49255,16 +49255,16 @@
         <v>6.074934</v>
       </c>
       <c r="M846" t="n">
-        <v>0.04506164092390535</v>
+        <v>0.0450616409239053</v>
       </c>
       <c r="N846" t="n">
-        <v>0.05386906617542866</v>
+        <v>0.0538690661754286</v>
       </c>
       <c r="O846" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P846" t="n">
-        <v>0.001969065603224067</v>
+        <v>0.001969065603224</v>
       </c>
     </row>
     <row r="847">
@@ -49313,16 +49313,538 @@
         <v>17.637821</v>
       </c>
       <c r="M847" t="n">
-        <v>0.03574333483958427</v>
+        <v>0.0357433348395842</v>
       </c>
       <c r="N847" t="n">
         <v>0.07191414369633981</v>
       </c>
       <c r="O847" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0519000005722045</v>
       </c>
       <c r="P847" t="n">
-        <v>0.02001414312413521</v>
+        <v>0.0200141431241352</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E848" t="n">
+        <v>342</v>
+      </c>
+      <c r="F848" t="n">
+        <v>4991209701376</v>
+      </c>
+      <c r="G848" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H848" t="n">
+        <v>9.57785</v>
+      </c>
+      <c r="I848" t="n">
+        <v>39.130436</v>
+      </c>
+      <c r="J848" t="n">
+        <v>35.707386</v>
+      </c>
+      <c r="K848" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L848" t="n">
+        <v>10.691868</v>
+      </c>
+      <c r="M848" t="n">
+        <v>0.02555555555555556</v>
+      </c>
+      <c r="N848" t="n">
+        <v>0.02800540935672514</v>
+      </c>
+      <c r="O848" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P848" t="n">
+        <v>-0.02288458812557466</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E849" t="n">
+        <v>562.23</v>
+      </c>
+      <c r="F849" t="n">
+        <v>917826371584</v>
+      </c>
+      <c r="G849" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H849" t="n">
+        <v>15.75529</v>
+      </c>
+      <c r="I849" t="n">
+        <v>151.95404</v>
+      </c>
+      <c r="J849" t="n">
+        <v>35.685154</v>
+      </c>
+      <c r="K849" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L849" t="n">
+        <v>22.220707</v>
+      </c>
+      <c r="M849" t="n">
+        <v>0.00658093662735891</v>
+      </c>
+      <c r="N849" t="n">
+        <v>0.02802285541504367</v>
+      </c>
+      <c r="O849" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P849" t="n">
+        <v>-0.02286714206725614</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>254.76</v>
+      </c>
+      <c r="F850" t="n">
+        <v>2747921072128</v>
+      </c>
+      <c r="G850" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="H850" t="n">
+        <v>10.45377</v>
+      </c>
+      <c r="I850" t="n">
+        <v>20.864864</v>
+      </c>
+      <c r="J850" t="n">
+        <v>24.370155</v>
+      </c>
+      <c r="K850" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L850" t="n">
+        <v>3.542596</v>
+      </c>
+      <c r="M850" t="n">
+        <v>0.04792746113989638</v>
+      </c>
+      <c r="N850" t="n">
+        <v>0.04103379651436646</v>
+      </c>
+      <c r="O850" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P850" t="n">
+        <v>-0.00985620096793334</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E851" t="n">
+        <v>344.33</v>
+      </c>
+      <c r="F851" t="n">
+        <v>1643703959552</v>
+      </c>
+      <c r="G851" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="H851" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I851" t="n">
+        <v>45.36627</v>
+      </c>
+      <c r="J851" t="n">
+        <v>17.754625</v>
+      </c>
+      <c r="K851" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L851" t="n">
+        <v>18.447027</v>
+      </c>
+      <c r="M851" t="n">
+        <v>0.02204280777161444</v>
+      </c>
+      <c r="N851" t="n">
+        <v>0.05632335259779863</v>
+      </c>
+      <c r="O851" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P851" t="n">
+        <v>0.005433355115498827</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E852" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="F852" t="n">
+        <v>4218226999296</v>
+      </c>
+      <c r="G852" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H852" t="n">
+        <v>15.25175</v>
+      </c>
+      <c r="I852" t="n">
+        <v>17.597448</v>
+      </c>
+      <c r="J852" t="n">
+        <v>22.614454</v>
+      </c>
+      <c r="K852" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L852" t="n">
+        <v>9.460751</v>
+      </c>
+      <c r="M852" t="n">
+        <v>0.05682641848598185</v>
+      </c>
+      <c r="N852" t="n">
+        <v>0.04421950653793743</v>
+      </c>
+      <c r="O852" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P852" t="n">
+        <v>-0.006670490944362374</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E853" t="n">
+        <v>736.72</v>
+      </c>
+      <c r="F853" t="n">
+        <v>1876798734336</v>
+      </c>
+      <c r="G853" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="H853" t="n">
+        <v>34.56071</v>
+      </c>
+      <c r="I853" t="n">
+        <v>28.699648</v>
+      </c>
+      <c r="J853" t="n">
+        <v>21.31669</v>
+      </c>
+      <c r="K853" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L853" t="n">
+        <v>8.222666</v>
+      </c>
+      <c r="M853" t="n">
+        <v>0.03484363123031817</v>
+      </c>
+      <c r="N853" t="n">
+        <v>0.04691159463568248</v>
+      </c>
+      <c r="O853" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P853" t="n">
+        <v>-0.003978402846617324</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E854" t="n">
+        <v>539.4400000000001</v>
+      </c>
+      <c r="F854" t="n">
+        <v>4005636341760</v>
+      </c>
+      <c r="G854" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="H854" t="n">
+        <v>23.67408</v>
+      </c>
+      <c r="I854" t="n">
+        <v>30.390985</v>
+      </c>
+      <c r="J854" t="n">
+        <v>22.786102</v>
+      </c>
+      <c r="K854" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L854" t="n">
+        <v>12.071023</v>
+      </c>
+      <c r="M854" t="n">
+        <v>0.03290449354886549</v>
+      </c>
+      <c r="N854" t="n">
+        <v>0.04388640071184932</v>
+      </c>
+      <c r="O854" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P854" t="n">
+        <v>-0.007003596770450482</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E855" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="F855" t="n">
+        <v>302343651328</v>
+      </c>
+      <c r="G855" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H855" t="n">
+        <v>3.80702</v>
+      </c>
+      <c r="I855" t="n">
+        <v>22.833334</v>
+      </c>
+      <c r="J855" t="n">
+        <v>19.07266</v>
+      </c>
+      <c r="K855" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L855" t="n">
+        <v>6.250545</v>
+      </c>
+      <c r="M855" t="n">
+        <v>0.04379562043795621</v>
+      </c>
+      <c r="N855" t="n">
+        <v>0.05243107010053712</v>
+      </c>
+      <c r="O855" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P855" t="n">
+        <v>0.001541072618237313</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:31:03</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E856" t="n">
+        <v>217.23</v>
+      </c>
+      <c r="F856" t="n">
+        <v>5245452681216</v>
+      </c>
+      <c r="G856" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="H856" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I856" t="n">
+        <v>28.359009</v>
+      </c>
+      <c r="J856" t="n">
+        <v>13.64973</v>
+      </c>
+      <c r="K856" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L856" t="n">
+        <v>17.313438</v>
+      </c>
+      <c r="M856" t="n">
+        <v>0.03526216452607835</v>
+      </c>
+      <c r="N856" t="n">
+        <v>0.07326152004787553</v>
+      </c>
+      <c r="O856" t="n">
+        <v>0.0508899974822998</v>
+      </c>
+      <c r="P856" t="n">
+        <v>0.02237152256557573</v>
       </c>
     </row>
   </sheetData>
@@ -49424,12 +49946,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -49443,51 +49965,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>343.65</v>
+        <v>344.91</v>
       </c>
       <c r="F2" t="n">
-        <v>4202817126400</v>
+        <v>4218226999296</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.6</v>
       </c>
       <c r="H2" t="n">
         <v>15.25175</v>
       </c>
       <c r="I2" t="n">
-        <v>17.24285</v>
+        <v>17.597448</v>
       </c>
       <c r="J2" t="n">
-        <v>22.53184</v>
+        <v>22.614454</v>
       </c>
       <c r="K2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.426189000000001</v>
+        <v>9.460751</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05799505310635822</v>
+        <v>0.05682641848598185</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04438163829477666</v>
+        <v>0.04421950653793743</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007518362277427929</v>
+        <v>-0.006670490944362374</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -49501,51 +50023,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3962939637760</v>
+        <v>4005636341760</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>17.75</v>
       </c>
       <c r="H3" t="n">
-        <v>23.69909</v>
+        <v>23.67408</v>
       </c>
       <c r="I3" t="n">
-        <v>29.732033</v>
+        <v>30.390985</v>
       </c>
       <c r="J3" t="n">
-        <v>22.51943</v>
+        <v>22.786102</v>
       </c>
       <c r="K3" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="L3" t="n">
-        <v>11.942356</v>
+        <v>12.071023</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03363375742472221</v>
+        <v>0.03290449354886549</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04440609717251588</v>
+        <v>0.04388640071184932</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.007493903399688709</v>
+        <v>-0.007003596770450482</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -49559,51 +50081,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>737.54</v>
+        <v>736.72</v>
       </c>
       <c r="F4" t="n">
-        <v>1878887628800</v>
+        <v>1876798734336</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>25.67</v>
       </c>
       <c r="H4" t="n">
-        <v>34.65286</v>
+        <v>34.56071</v>
       </c>
       <c r="I4" t="n">
-        <v>27.78975</v>
+        <v>28.699648</v>
       </c>
       <c r="J4" t="n">
-        <v>21.283669</v>
+        <v>21.31669</v>
       </c>
       <c r="K4" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="L4" t="n">
-        <v>8.231816999999999</v>
+        <v>8.222666</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03598448897686905</v>
+        <v>0.03484363123031817</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04698438050817583</v>
+        <v>0.04691159463568248</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.004915620064028764</v>
+        <v>-0.003978402846617324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -49617,51 +50139,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.08</v>
+        <v>254.76</v>
       </c>
       <c r="F5" t="n">
-        <v>2740586545152</v>
+        <v>2747921072128</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.21</v>
       </c>
       <c r="H5" t="n">
         <v>10.45377</v>
       </c>
       <c r="I5" t="n">
-        <v>20.440868</v>
+        <v>20.864864</v>
       </c>
       <c r="J5" t="n">
-        <v>24.305107</v>
+        <v>24.370155</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5331404</v>
+        <v>3.542596</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04892159949622166</v>
+        <v>0.04792746113989638</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04114361618387909</v>
+        <v>0.04103379651436646</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0107563843883255</v>
+        <v>-0.00985620096793334</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -49675,51 +50197,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>342.96</v>
+        <v>342</v>
       </c>
       <c r="F6" t="n">
-        <v>5005219725312</v>
+        <v>4991209701376</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5906</v>
+        <v>9.57785</v>
       </c>
       <c r="I6" t="n">
-        <v>39.330273</v>
+        <v>39.130436</v>
       </c>
       <c r="J6" t="n">
-        <v>35.760014</v>
+        <v>35.707386</v>
       </c>
       <c r="K6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="L6" t="n">
-        <v>10.721879</v>
+        <v>10.691868</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02542570562164684</v>
+        <v>0.02555555555555556</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0279641940751108</v>
+        <v>0.02800540935672514</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02393580649709379</v>
+        <v>-0.02288458812557466</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -49733,51 +50255,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221.3</v>
+        <v>217.23</v>
       </c>
       <c r="F7" t="n">
-        <v>5343730991104</v>
+        <v>5245452681216</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.66</v>
       </c>
       <c r="H7" t="n">
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.977245</v>
+        <v>28.359009</v>
       </c>
       <c r="J7" t="n">
-        <v>13.90547</v>
+        <v>13.64973</v>
       </c>
       <c r="K7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="L7" t="n">
-        <v>17.637821</v>
+        <v>17.313438</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03574333483958427</v>
+        <v>0.03526216452607835</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07191414369633981</v>
+        <v>0.07326152004787553</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02001414312413521</v>
+        <v>0.02237152256557573</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -49791,51 +50313,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>570.8200000000001</v>
+        <v>562.23</v>
       </c>
       <c r="F8" t="n">
-        <v>931849371648</v>
+        <v>917826371584</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="H8" t="n">
-        <v>15.72189</v>
+        <v>15.75529</v>
       </c>
       <c r="I8" t="n">
-        <v>145.61734</v>
+        <v>151.95404</v>
       </c>
       <c r="J8" t="n">
-        <v>36.30734</v>
+        <v>35.685154</v>
       </c>
       <c r="K8" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="L8" t="n">
-        <v>22.560207</v>
+        <v>22.220707</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006867313689078869</v>
+        <v>0.00658093662735891</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02754264041203882</v>
+        <v>0.02802285541504367</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02435736016016577</v>
+        <v>-0.02286714206725614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -49849,51 +50371,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>346.25</v>
+        <v>344.33</v>
       </c>
       <c r="F9" t="n">
-        <v>1652869431296</v>
+        <v>1643703959552</v>
       </c>
       <c r="G9" t="n">
-        <v>7.98</v>
+        <v>7.59</v>
       </c>
       <c r="H9" t="n">
         <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>43.389725</v>
+        <v>45.36627</v>
       </c>
       <c r="J9" t="n">
-        <v>17.853626</v>
+        <v>17.754625</v>
       </c>
       <c r="K9" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.54989</v>
+        <v>18.447027</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02304693140794224</v>
+        <v>0.02204280777161444</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05601103249097474</v>
+        <v>0.05632335259779863</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004111031918770144</v>
+        <v>0.005433355115498827</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 17:38:26</t>
+          <t>2026-10-15 17:31:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -49907,40 +50429,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F10" t="n">
-        <v>293849202688</v>
+        <v>302343651328</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.80154</v>
+        <v>3.80702</v>
       </c>
       <c r="I10" t="n">
-        <v>22.191824</v>
+        <v>22.833334</v>
       </c>
       <c r="J10" t="n">
-        <v>18.56353</v>
+        <v>19.07266</v>
       </c>
       <c r="K10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="L10" t="n">
-        <v>6.074934</v>
+        <v>6.250545</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04506164092390535</v>
+        <v>0.04379562043795621</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05386906617542866</v>
+        <v>0.05243107010053712</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05190000057220459</v>
+        <v>0.0508899974822998</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001969065603224067</v>
+        <v>0.001541072618237313</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P856"/>
+  <dimension ref="A1:P865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49371,16 +49371,16 @@
         <v>10.691868</v>
       </c>
       <c r="M848" t="n">
-        <v>0.02555555555555556</v>
+        <v>0.0255555555555555</v>
       </c>
       <c r="N848" t="n">
-        <v>0.02800540935672514</v>
+        <v>0.0280054093567251</v>
       </c>
       <c r="O848" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P848" t="n">
-        <v>-0.02288458812557466</v>
+        <v>-0.0228845881255746</v>
       </c>
     </row>
     <row r="849">
@@ -49429,16 +49429,16 @@
         <v>22.220707</v>
       </c>
       <c r="M849" t="n">
-        <v>0.00658093662735891</v>
+        <v>0.0065809366273589</v>
       </c>
       <c r="N849" t="n">
-        <v>0.02802285541504367</v>
+        <v>0.0280228554150436</v>
       </c>
       <c r="O849" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P849" t="n">
-        <v>-0.02286714206725614</v>
+        <v>-0.0228671420672561</v>
       </c>
     </row>
     <row r="850">
@@ -49487,16 +49487,16 @@
         <v>3.542596</v>
       </c>
       <c r="M850" t="n">
-        <v>0.04792746113989638</v>
+        <v>0.0479274611398963</v>
       </c>
       <c r="N850" t="n">
-        <v>0.04103379651436646</v>
+        <v>0.0410337965143664</v>
       </c>
       <c r="O850" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P850" t="n">
-        <v>-0.00985620096793334</v>
+        <v>-0.0098562009679333</v>
       </c>
     </row>
     <row r="851">
@@ -49545,16 +49545,16 @@
         <v>18.447027</v>
       </c>
       <c r="M851" t="n">
-        <v>0.02204280777161444</v>
+        <v>0.0220428077716144</v>
       </c>
       <c r="N851" t="n">
-        <v>0.05632335259779863</v>
+        <v>0.0563233525977986</v>
       </c>
       <c r="O851" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P851" t="n">
-        <v>0.005433355115498827</v>
+        <v>0.0054333551154988</v>
       </c>
     </row>
     <row r="852">
@@ -49603,16 +49603,16 @@
         <v>9.460751</v>
       </c>
       <c r="M852" t="n">
-        <v>0.05682641848598185</v>
+        <v>0.0568264184859818</v>
       </c>
       <c r="N852" t="n">
-        <v>0.04421950653793743</v>
+        <v>0.0442195065379374</v>
       </c>
       <c r="O852" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P852" t="n">
-        <v>-0.006670490944362374</v>
+        <v>-0.0066704909443623</v>
       </c>
     </row>
     <row r="853">
@@ -49661,16 +49661,16 @@
         <v>8.222666</v>
       </c>
       <c r="M853" t="n">
-        <v>0.03484363123031817</v>
+        <v>0.0348436312303181</v>
       </c>
       <c r="N853" t="n">
-        <v>0.04691159463568248</v>
+        <v>0.0469115946356824</v>
       </c>
       <c r="O853" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P853" t="n">
-        <v>-0.003978402846617324</v>
+        <v>-0.0039784028466173</v>
       </c>
     </row>
     <row r="854">
@@ -49719,16 +49719,16 @@
         <v>12.071023</v>
       </c>
       <c r="M854" t="n">
-        <v>0.03290449354886549</v>
+        <v>0.0329044935488654</v>
       </c>
       <c r="N854" t="n">
-        <v>0.04388640071184932</v>
+        <v>0.0438864007118493</v>
       </c>
       <c r="O854" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P854" t="n">
-        <v>-0.007003596770450482</v>
+        <v>-0.0070035967704504</v>
       </c>
     </row>
     <row r="855">
@@ -49777,16 +49777,16 @@
         <v>6.250545</v>
       </c>
       <c r="M855" t="n">
-        <v>0.04379562043795621</v>
+        <v>0.0437956204379562</v>
       </c>
       <c r="N855" t="n">
-        <v>0.05243107010053712</v>
+        <v>0.0524310701005371</v>
       </c>
       <c r="O855" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P855" t="n">
-        <v>0.001541072618237313</v>
+        <v>0.0015410726182373</v>
       </c>
     </row>
     <row r="856">
@@ -49835,16 +49835,538 @@
         <v>17.313438</v>
       </c>
       <c r="M856" t="n">
-        <v>0.03526216452607835</v>
+        <v>0.0352621645260783</v>
       </c>
       <c r="N856" t="n">
-        <v>0.07326152004787553</v>
+        <v>0.07326152004787551</v>
       </c>
       <c r="O856" t="n">
         <v>0.0508899974822998</v>
       </c>
       <c r="P856" t="n">
-        <v>0.02237152256557573</v>
+        <v>0.0223715225655757</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E857" t="n">
+        <v>343.46</v>
+      </c>
+      <c r="F857" t="n">
+        <v>5012516765696</v>
+      </c>
+      <c r="G857" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H857" t="n">
+        <v>9.57785</v>
+      </c>
+      <c r="I857" t="n">
+        <v>39.38761</v>
+      </c>
+      <c r="J857" t="n">
+        <v>35.85982</v>
+      </c>
+      <c r="K857" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L857" t="n">
+        <v>10.737511</v>
+      </c>
+      <c r="M857" t="n">
+        <v>0.02538869155069004</v>
+      </c>
+      <c r="N857" t="n">
+        <v>0.02788636231293309</v>
+      </c>
+      <c r="O857" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P857" t="n">
+        <v>-0.02309363818297755</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E858" t="n">
+        <v>528.75</v>
+      </c>
+      <c r="F858" t="n">
+        <v>863171182592</v>
+      </c>
+      <c r="G858" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H858" t="n">
+        <v>15.75529</v>
+      </c>
+      <c r="I858" t="n">
+        <v>134.88521</v>
+      </c>
+      <c r="J858" t="n">
+        <v>33.560158</v>
+      </c>
+      <c r="K858" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L858" t="n">
+        <v>20.897497</v>
+      </c>
+      <c r="M858" t="n">
+        <v>0.00741371158392435</v>
+      </c>
+      <c r="N858" t="n">
+        <v>0.02979723877068558</v>
+      </c>
+      <c r="O858" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P858" t="n">
+        <v>-0.02118276172522506</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E859" t="n">
+        <v>250</v>
+      </c>
+      <c r="F859" t="n">
+        <v>2696578334720</v>
+      </c>
+      <c r="G859" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H859" t="n">
+        <v>10.44315</v>
+      </c>
+      <c r="I859" t="n">
+        <v>20.11263</v>
+      </c>
+      <c r="J859" t="n">
+        <v>23.939138</v>
+      </c>
+      <c r="K859" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L859" t="n">
+        <v>3.4764056</v>
+      </c>
+      <c r="M859" t="n">
+        <v>0.04972</v>
+      </c>
+      <c r="N859" t="n">
+        <v>0.0417726</v>
+      </c>
+      <c r="O859" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P859" t="n">
+        <v>-0.009207400495910643</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E860" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="F860" t="n">
+        <v>1569330823168</v>
+      </c>
+      <c r="G860" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="H860" t="n">
+        <v>19.39382</v>
+      </c>
+      <c r="I860" t="n">
+        <v>43.31357</v>
+      </c>
+      <c r="J860" t="n">
+        <v>16.951277</v>
+      </c>
+      <c r="K860" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L860" t="n">
+        <v>17.61235</v>
+      </c>
+      <c r="M860" t="n">
+        <v>0.02308745247148289</v>
+      </c>
+      <c r="N860" t="n">
+        <v>0.05899260836501902</v>
+      </c>
+      <c r="O860" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P860" t="n">
+        <v>0.008012607869108374</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E861" t="n">
+        <v>336.91</v>
+      </c>
+      <c r="F861" t="n">
+        <v>4120387518464</v>
+      </c>
+      <c r="G861" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H861" t="n">
+        <v>15.28955</v>
+      </c>
+      <c r="I861" t="n">
+        <v>16.904667</v>
+      </c>
+      <c r="J861" t="n">
+        <v>22.035313</v>
+      </c>
+      <c r="K861" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L861" t="n">
+        <v>9.241313999999999</v>
+      </c>
+      <c r="M861" t="n">
+        <v>0.05915526401709655</v>
+      </c>
+      <c r="N861" t="n">
+        <v>0.04538170431272447</v>
+      </c>
+      <c r="O861" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P861" t="n">
+        <v>-0.005598296183186177</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E862" t="n">
+        <v>709.325</v>
+      </c>
+      <c r="F862" t="n">
+        <v>1807009841152</v>
+      </c>
+      <c r="G862" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H862" t="n">
+        <v>34.62667</v>
+      </c>
+      <c r="I862" t="n">
+        <v>26.726639</v>
+      </c>
+      <c r="J862" t="n">
+        <v>20.484932</v>
+      </c>
+      <c r="K862" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L862" t="n">
+        <v>7.9169054</v>
+      </c>
+      <c r="M862" t="n">
+        <v>0.03741585309977796</v>
+      </c>
+      <c r="N862" t="n">
+        <v>0.0488163676734924</v>
+      </c>
+      <c r="O862" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P862" t="n">
+        <v>-0.002163632822418243</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E863" t="n">
+        <v>529.05</v>
+      </c>
+      <c r="F863" t="n">
+        <v>3928485003264</v>
+      </c>
+      <c r="G863" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H863" t="n">
+        <v>23.72118</v>
+      </c>
+      <c r="I863" t="n">
+        <v>29.473536</v>
+      </c>
+      <c r="J863" t="n">
+        <v>22.302853</v>
+      </c>
+      <c r="K863" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L863" t="n">
+        <v>11.838527</v>
+      </c>
+      <c r="M863" t="n">
+        <v>0.0339287401946886</v>
+      </c>
+      <c r="N863" t="n">
+        <v>0.0448373121633116</v>
+      </c>
+      <c r="O863" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P863" t="n">
+        <v>-0.006142688332599046</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E864" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="F864" t="n">
+        <v>293682642944</v>
+      </c>
+      <c r="G864" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H864" t="n">
+        <v>3.80011</v>
+      </c>
+      <c r="I864" t="n">
+        <v>22.179245</v>
+      </c>
+      <c r="J864" t="n">
+        <v>18.559988</v>
+      </c>
+      <c r="K864" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L864" t="n">
+        <v>6.0714903</v>
+      </c>
+      <c r="M864" t="n">
+        <v>0.04508719693747341</v>
+      </c>
+      <c r="N864" t="n">
+        <v>0.0538793421239189</v>
+      </c>
+      <c r="O864" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P864" t="n">
+        <v>0.002899341628008256</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:37:09</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E865" t="n">
+        <v>214.13</v>
+      </c>
+      <c r="F865" t="n">
+        <v>5170596937728</v>
+      </c>
+      <c r="G865" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H865" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I865" t="n">
+        <v>27.070797</v>
+      </c>
+      <c r="J865" t="n">
+        <v>13.454941</v>
+      </c>
+      <c r="K865" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L865" t="n">
+        <v>17.066366</v>
+      </c>
+      <c r="M865" t="n">
+        <v>0.03694017652827722</v>
+      </c>
+      <c r="N865" t="n">
+        <v>0.07432214075561575</v>
+      </c>
+      <c r="O865" t="n">
+        <v>0.05098000049591064</v>
+      </c>
+      <c r="P865" t="n">
+        <v>0.0233421402597051</v>
       </c>
     </row>
   </sheetData>
@@ -49946,12 +50468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -49965,51 +50487,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>344.91</v>
+        <v>336.91</v>
       </c>
       <c r="F2" t="n">
-        <v>4218226999296</v>
+        <v>4120387518464</v>
       </c>
       <c r="G2" t="n">
-        <v>19.6</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>15.25175</v>
+        <v>15.28955</v>
       </c>
       <c r="I2" t="n">
-        <v>17.597448</v>
+        <v>16.904667</v>
       </c>
       <c r="J2" t="n">
-        <v>22.614454</v>
+        <v>22.035313</v>
       </c>
       <c r="K2" t="n">
         <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>9.460751</v>
+        <v>9.241313999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05682641848598185</v>
+        <v>0.05915526401709655</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04421950653793743</v>
+        <v>0.04538170431272447</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006670490944362374</v>
+        <v>-0.005598296183186177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -50023,51 +50545,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="F3" t="n">
-        <v>4005636341760</v>
+        <v>3928485003264</v>
       </c>
       <c r="G3" t="n">
-        <v>17.75</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.67408</v>
+        <v>23.72118</v>
       </c>
       <c r="I3" t="n">
-        <v>30.390985</v>
+        <v>29.473536</v>
       </c>
       <c r="J3" t="n">
-        <v>22.786102</v>
+        <v>22.302853</v>
       </c>
       <c r="K3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="L3" t="n">
-        <v>12.071023</v>
+        <v>11.838527</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03290449354886549</v>
+        <v>0.0339287401946886</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04388640071184932</v>
+        <v>0.0448373121633116</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.007003596770450482</v>
+        <v>-0.006142688332599046</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -50081,51 +50603,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>736.72</v>
+        <v>709.325</v>
       </c>
       <c r="F4" t="n">
-        <v>1876798734336</v>
+        <v>1807009841152</v>
       </c>
       <c r="G4" t="n">
-        <v>25.67</v>
+        <v>26.54</v>
       </c>
       <c r="H4" t="n">
-        <v>34.56071</v>
+        <v>34.62667</v>
       </c>
       <c r="I4" t="n">
-        <v>28.699648</v>
+        <v>26.726639</v>
       </c>
       <c r="J4" t="n">
-        <v>21.31669</v>
+        <v>20.484932</v>
       </c>
       <c r="K4" t="n">
         <v>0.97</v>
       </c>
       <c r="L4" t="n">
-        <v>8.222666</v>
+        <v>7.9169054</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03484363123031817</v>
+        <v>0.03741585309977796</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04691159463568248</v>
+        <v>0.0488163676734924</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.003978402846617324</v>
+        <v>-0.002163632822418243</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -50139,51 +50661,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.76</v>
+        <v>250</v>
       </c>
       <c r="F5" t="n">
-        <v>2747921072128</v>
+        <v>2696578334720</v>
       </c>
       <c r="G5" t="n">
-        <v>12.21</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.45377</v>
+        <v>10.44315</v>
       </c>
       <c r="I5" t="n">
-        <v>20.864864</v>
+        <v>20.11263</v>
       </c>
       <c r="J5" t="n">
-        <v>24.370155</v>
+        <v>23.939138</v>
       </c>
       <c r="K5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.542596</v>
+        <v>3.4764056</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04792746113989638</v>
+        <v>0.04972</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04103379651436646</v>
+        <v>0.0417726</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00985620096793334</v>
+        <v>-0.009207400495910643</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -50197,51 +50719,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>342</v>
+        <v>343.46</v>
       </c>
       <c r="F6" t="n">
-        <v>4991209701376</v>
+        <v>5012516765696</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.57785</v>
       </c>
       <c r="I6" t="n">
-        <v>39.130436</v>
+        <v>39.38761</v>
       </c>
       <c r="J6" t="n">
-        <v>35.707386</v>
+        <v>35.85982</v>
       </c>
       <c r="K6" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>10.691868</v>
+        <v>10.737511</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02555555555555556</v>
+        <v>0.02538869155069004</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02800540935672514</v>
+        <v>0.02788636231293309</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02288458812557466</v>
+        <v>-0.02309363818297755</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -50255,51 +50777,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.23</v>
+        <v>214.13</v>
       </c>
       <c r="F7" t="n">
-        <v>5245452681216</v>
+        <v>5170596937728</v>
       </c>
       <c r="G7" t="n">
-        <v>7.66</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>28.359009</v>
+        <v>27.070797</v>
       </c>
       <c r="J7" t="n">
-        <v>13.64973</v>
+        <v>13.454941</v>
       </c>
       <c r="K7" t="n">
         <v>0.27</v>
       </c>
       <c r="L7" t="n">
-        <v>17.313438</v>
+        <v>17.066366</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03526216452607835</v>
+        <v>0.03694017652827722</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07326152004787553</v>
+        <v>0.07432214075561575</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02237152256557573</v>
+        <v>0.0233421402597051</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -50313,51 +50835,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>562.23</v>
+        <v>528.75</v>
       </c>
       <c r="F8" t="n">
-        <v>917826371584</v>
+        <v>863171182592</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="n">
         <v>15.75529</v>
       </c>
       <c r="I8" t="n">
-        <v>151.95404</v>
+        <v>134.88521</v>
       </c>
       <c r="J8" t="n">
-        <v>35.685154</v>
+        <v>33.560158</v>
       </c>
       <c r="K8" t="n">
         <v>0.57</v>
       </c>
       <c r="L8" t="n">
-        <v>22.220707</v>
+        <v>20.897497</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00658093662735891</v>
+        <v>0.00741371158392435</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02802285541504367</v>
+        <v>0.02979723877068558</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02286714206725614</v>
+        <v>-0.02118276172522506</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -50371,10 +50893,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>344.33</v>
+        <v>328.75</v>
       </c>
       <c r="F9" t="n">
-        <v>1643703959552</v>
+        <v>1569330823168</v>
       </c>
       <c r="G9" t="n">
         <v>7.59</v>
@@ -50383,39 +50905,39 @@
         <v>19.39382</v>
       </c>
       <c r="I9" t="n">
-        <v>45.36627</v>
+        <v>43.31357</v>
       </c>
       <c r="J9" t="n">
-        <v>17.754625</v>
+        <v>16.951277</v>
       </c>
       <c r="K9" t="n">
         <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.447027</v>
+        <v>17.61235</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02204280777161444</v>
+        <v>0.02308745247148289</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05632335259779863</v>
+        <v>0.05899260836501902</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005433355115498827</v>
+        <v>0.008012607869108374</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-15 17:31:03</t>
+          <t>2026-10-16 17:37:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -50429,40 +50951,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>72.61</v>
+        <v>70.53</v>
       </c>
       <c r="F10" t="n">
-        <v>302343651328</v>
+        <v>293682642944</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.80702</v>
+        <v>3.80011</v>
       </c>
       <c r="I10" t="n">
-        <v>22.833334</v>
+        <v>22.179245</v>
       </c>
       <c r="J10" t="n">
-        <v>19.07266</v>
+        <v>18.559988</v>
       </c>
       <c r="K10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="L10" t="n">
-        <v>6.250545</v>
+        <v>6.0714903</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04379562043795621</v>
+        <v>0.04508719693747341</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05243107010053712</v>
+        <v>0.0538793421239189</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0508899974822998</v>
+        <v>0.05098000049591064</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001541072618237313</v>
+        <v>0.002899341628008256</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P865"/>
+  <dimension ref="A1:P874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49893,16 +49893,16 @@
         <v>10.737511</v>
       </c>
       <c r="M857" t="n">
-        <v>0.02538869155069004</v>
+        <v>0.02538869155069</v>
       </c>
       <c r="N857" t="n">
-        <v>0.02788636231293309</v>
+        <v>0.027886362312933</v>
       </c>
       <c r="O857" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P857" t="n">
-        <v>-0.02309363818297755</v>
+        <v>-0.0230936381829775</v>
       </c>
     </row>
     <row r="858">
@@ -49951,16 +49951,16 @@
         <v>20.897497</v>
       </c>
       <c r="M858" t="n">
-        <v>0.00741371158392435</v>
+        <v>0.0074137115839243</v>
       </c>
       <c r="N858" t="n">
-        <v>0.02979723877068558</v>
+        <v>0.0297972387706855</v>
       </c>
       <c r="O858" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P858" t="n">
-        <v>-0.02118276172522506</v>
+        <v>-0.021182761725225</v>
       </c>
     </row>
     <row r="859">
@@ -50015,10 +50015,10 @@
         <v>0.0417726</v>
       </c>
       <c r="O859" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P859" t="n">
-        <v>-0.009207400495910643</v>
+        <v>-0.0092074004959106</v>
       </c>
     </row>
     <row r="860">
@@ -50067,16 +50067,16 @@
         <v>17.61235</v>
       </c>
       <c r="M860" t="n">
-        <v>0.02308745247148289</v>
+        <v>0.0230874524714828</v>
       </c>
       <c r="N860" t="n">
-        <v>0.05899260836501902</v>
+        <v>0.058992608365019</v>
       </c>
       <c r="O860" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P860" t="n">
-        <v>0.008012607869108374</v>
+        <v>0.008012607869108301</v>
       </c>
     </row>
     <row r="861">
@@ -50125,16 +50125,16 @@
         <v>9.241313999999999</v>
       </c>
       <c r="M861" t="n">
-        <v>0.05915526401709655</v>
+        <v>0.0591552640170965</v>
       </c>
       <c r="N861" t="n">
-        <v>0.04538170431272447</v>
+        <v>0.0453817043127244</v>
       </c>
       <c r="O861" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P861" t="n">
-        <v>-0.005598296183186177</v>
+        <v>-0.0055982961831861</v>
       </c>
     </row>
     <row r="862">
@@ -50183,16 +50183,16 @@
         <v>7.9169054</v>
       </c>
       <c r="M862" t="n">
-        <v>0.03741585309977796</v>
+        <v>0.0374158530997779</v>
       </c>
       <c r="N862" t="n">
         <v>0.0488163676734924</v>
       </c>
       <c r="O862" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P862" t="n">
-        <v>-0.002163632822418243</v>
+        <v>-0.0021636328224182</v>
       </c>
     </row>
     <row r="863">
@@ -50247,10 +50247,10 @@
         <v>0.0448373121633116</v>
       </c>
       <c r="O863" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P863" t="n">
-        <v>-0.006142688332599046</v>
+        <v>-0.006142688332599</v>
       </c>
     </row>
     <row r="864">
@@ -50299,16 +50299,16 @@
         <v>6.0714903</v>
       </c>
       <c r="M864" t="n">
-        <v>0.04508719693747341</v>
+        <v>0.0450871969374734</v>
       </c>
       <c r="N864" t="n">
         <v>0.0538793421239189</v>
       </c>
       <c r="O864" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P864" t="n">
-        <v>0.002899341628008256</v>
+        <v>0.0028993416280082</v>
       </c>
     </row>
     <row r="865">
@@ -50357,16 +50357,538 @@
         <v>17.066366</v>
       </c>
       <c r="M865" t="n">
-        <v>0.03694017652827722</v>
+        <v>0.0369401765282772</v>
       </c>
       <c r="N865" t="n">
-        <v>0.07432214075561575</v>
+        <v>0.0743221407556157</v>
       </c>
       <c r="O865" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0509800004959106</v>
       </c>
       <c r="P865" t="n">
         <v>0.0233421402597051</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E866" t="n">
+        <v>342.94</v>
+      </c>
+      <c r="F866" t="n">
+        <v>5004928221184</v>
+      </c>
+      <c r="G866" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H866" t="n">
+        <v>9.57785</v>
+      </c>
+      <c r="I866" t="n">
+        <v>39.32798</v>
+      </c>
+      <c r="J866" t="n">
+        <v>35.80553</v>
+      </c>
+      <c r="K866" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L866" t="n">
+        <v>10.721255</v>
+      </c>
+      <c r="M866" t="n">
+        <v>0.02542718842946288</v>
+      </c>
+      <c r="N866" t="n">
+        <v>0.02792864641045081</v>
+      </c>
+      <c r="O866" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P866" t="n">
+        <v>-0.02343135515357507</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E867" t="n">
+        <v>538.05</v>
+      </c>
+      <c r="F867" t="n">
+        <v>878353186816</v>
+      </c>
+      <c r="G867" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H867" t="n">
+        <v>15.76209</v>
+      </c>
+      <c r="I867" t="n">
+        <v>137.25764</v>
+      </c>
+      <c r="J867" t="n">
+        <v>34.1357</v>
+      </c>
+      <c r="K867" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L867" t="n">
+        <v>21.265057</v>
+      </c>
+      <c r="M867" t="n">
+        <v>0.007285568255738315</v>
+      </c>
+      <c r="N867" t="n">
+        <v>0.02929484248675774</v>
+      </c>
+      <c r="O867" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P867" t="n">
+        <v>-0.02206515907726814</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E868" t="n">
+        <v>262.45</v>
+      </c>
+      <c r="F868" t="n">
+        <v>2830868152320</v>
+      </c>
+      <c r="G868" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H868" t="n">
+        <v>10.44315</v>
+      </c>
+      <c r="I868" t="n">
+        <v>21.11424</v>
+      </c>
+      <c r="J868" t="n">
+        <v>25.131308</v>
+      </c>
+      <c r="K868" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L868" t="n">
+        <v>3.649531</v>
+      </c>
+      <c r="M868" t="n">
+        <v>0.04736140217184226</v>
+      </c>
+      <c r="N868" t="n">
+        <v>0.03979100781101162</v>
+      </c>
+      <c r="O868" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P868" t="n">
+        <v>-0.01156899375301425</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E869" t="n">
+        <v>334.59</v>
+      </c>
+      <c r="F869" t="n">
+        <v>1597208788992</v>
+      </c>
+      <c r="G869" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H869" t="n">
+        <v>19.39695</v>
+      </c>
+      <c r="I869" t="n">
+        <v>42.7318</v>
+      </c>
+      <c r="J869" t="n">
+        <v>17.249619</v>
+      </c>
+      <c r="K869" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L869" t="n">
+        <v>17.92522</v>
+      </c>
+      <c r="M869" t="n">
+        <v>0.02340177530709226</v>
+      </c>
+      <c r="N869" t="n">
+        <v>0.05797229444992379</v>
+      </c>
+      <c r="O869" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P869" t="n">
+        <v>0.006612292885897916</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E870" t="n">
+        <v>340.16</v>
+      </c>
+      <c r="F870" t="n">
+        <v>4160134840320</v>
+      </c>
+      <c r="G870" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H870" t="n">
+        <v>15.29162</v>
+      </c>
+      <c r="I870" t="n">
+        <v>17.067738</v>
+      </c>
+      <c r="J870" t="n">
+        <v>22.244864</v>
+      </c>
+      <c r="K870" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L870" t="n">
+        <v>9.330461</v>
+      </c>
+      <c r="M870" t="n">
+        <v>0.05859007525870178</v>
+      </c>
+      <c r="N870" t="n">
+        <v>0.04495419802445907</v>
+      </c>
+      <c r="O870" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P870" t="n">
+        <v>-0.006405803539566803</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E871" t="n">
+        <v>705.4400000000001</v>
+      </c>
+      <c r="F871" t="n">
+        <v>1797112725504</v>
+      </c>
+      <c r="G871" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H871" t="n">
+        <v>34.65077</v>
+      </c>
+      <c r="I871" t="n">
+        <v>26.580256</v>
+      </c>
+      <c r="J871" t="n">
+        <v>20.358568</v>
+      </c>
+      <c r="K871" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L871" t="n">
+        <v>7.8735437</v>
+      </c>
+      <c r="M871" t="n">
+        <v>0.03762190973009753</v>
+      </c>
+      <c r="N871" t="n">
+        <v>0.0491193723066455</v>
+      </c>
+      <c r="O871" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P871" t="n">
+        <v>-0.002240629257380382</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E872" t="n">
+        <v>533.52</v>
+      </c>
+      <c r="F872" t="n">
+        <v>3961677414400</v>
+      </c>
+      <c r="G872" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H872" t="n">
+        <v>23.72118</v>
+      </c>
+      <c r="I872" t="n">
+        <v>29.722563</v>
+      </c>
+      <c r="J872" t="n">
+        <v>22.491293</v>
+      </c>
+      <c r="K872" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L872" t="n">
+        <v>11.938552</v>
+      </c>
+      <c r="M872" t="n">
+        <v>0.03364447443394812</v>
+      </c>
+      <c r="N872" t="n">
+        <v>0.04446165092217724</v>
+      </c>
+      <c r="O872" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P872" t="n">
+        <v>-0.006898350641848634</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E873" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="F873" t="n">
+        <v>290851160064</v>
+      </c>
+      <c r="G873" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H873" t="n">
+        <v>3.80035</v>
+      </c>
+      <c r="I873" t="n">
+        <v>21.965408</v>
+      </c>
+      <c r="J873" t="n">
+        <v>18.379887</v>
+      </c>
+      <c r="K873" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L873" t="n">
+        <v>6.0129533</v>
+      </c>
+      <c r="M873" t="n">
+        <v>0.0455261274158912</v>
+      </c>
+      <c r="N873" t="n">
+        <v>0.05440730136005727</v>
+      </c>
+      <c r="O873" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P873" t="n">
+        <v>0.00304729979603139</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:07:16</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E874" t="n">
+        <v>217.09</v>
+      </c>
+      <c r="F874" t="n">
+        <v>5242072072192</v>
+      </c>
+      <c r="G874" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H874" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I874" t="n">
+        <v>27.445007</v>
+      </c>
+      <c r="J874" t="n">
+        <v>13.640933</v>
+      </c>
+      <c r="K874" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L874" t="n">
+        <v>17.30228</v>
+      </c>
+      <c r="M874" t="n">
+        <v>0.03643650099037266</v>
+      </c>
+      <c r="N874" t="n">
+        <v>0.07330876594960616</v>
+      </c>
+      <c r="O874" t="n">
+        <v>0.05136000156402588</v>
+      </c>
+      <c r="P874" t="n">
+        <v>0.02194876438558028</v>
       </c>
     </row>
   </sheetData>
@@ -50468,12 +50990,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -50487,51 +51009,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>336.91</v>
+        <v>340.16</v>
       </c>
       <c r="F2" t="n">
-        <v>4120387518464</v>
+        <v>4160134840320</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>15.28955</v>
+        <v>15.29162</v>
       </c>
       <c r="I2" t="n">
-        <v>16.904667</v>
+        <v>17.067738</v>
       </c>
       <c r="J2" t="n">
-        <v>22.035313</v>
+        <v>22.244864</v>
       </c>
       <c r="K2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="L2" t="n">
-        <v>9.241313999999999</v>
+        <v>9.330461</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05915526401709655</v>
+        <v>0.05859007525870178</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04538170431272447</v>
+        <v>0.04495419802445907</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005598296183186177</v>
+        <v>-0.006405803539566803</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -50545,10 +51067,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="F3" t="n">
-        <v>3928485003264</v>
+        <v>3961677414400</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
@@ -50557,39 +51079,39 @@
         <v>23.72118</v>
       </c>
       <c r="I3" t="n">
-        <v>29.473536</v>
+        <v>29.722563</v>
       </c>
       <c r="J3" t="n">
-        <v>22.302853</v>
+        <v>22.491293</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="L3" t="n">
-        <v>11.838527</v>
+        <v>11.938552</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0339287401946886</v>
+        <v>0.03364447443394812</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0448373121633116</v>
+        <v>0.04446165092217724</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.006142688332599046</v>
+        <v>-0.006898350641848634</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -50603,51 +51125,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>709.325</v>
+        <v>705.4400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1807009841152</v>
+        <v>1797112725504</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
       </c>
       <c r="H4" t="n">
-        <v>34.62667</v>
+        <v>34.65077</v>
       </c>
       <c r="I4" t="n">
-        <v>26.726639</v>
+        <v>26.580256</v>
       </c>
       <c r="J4" t="n">
-        <v>20.484932</v>
+        <v>20.358568</v>
       </c>
       <c r="K4" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9169054</v>
+        <v>7.8735437</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03741585309977796</v>
+        <v>0.03762190973009753</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0488163676734924</v>
+        <v>0.0491193723066455</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.002163632822418243</v>
+        <v>-0.002240629257380382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -50661,10 +51183,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>250</v>
+        <v>262.45</v>
       </c>
       <c r="F5" t="n">
-        <v>2696578334720</v>
+        <v>2830868152320</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -50673,39 +51195,39 @@
         <v>10.44315</v>
       </c>
       <c r="I5" t="n">
-        <v>20.11263</v>
+        <v>21.11424</v>
       </c>
       <c r="J5" t="n">
-        <v>23.939138</v>
+        <v>25.131308</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4764056</v>
+        <v>3.649531</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04972</v>
+        <v>0.04736140217184226</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0417726</v>
+        <v>0.03979100781101162</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009207400495910643</v>
+        <v>-0.01156899375301425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -50719,10 +51241,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>343.46</v>
+        <v>342.94</v>
       </c>
       <c r="F6" t="n">
-        <v>5012516765696</v>
+        <v>5004928221184</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
@@ -50731,39 +51253,39 @@
         <v>9.57785</v>
       </c>
       <c r="I6" t="n">
-        <v>39.38761</v>
+        <v>39.32798</v>
       </c>
       <c r="J6" t="n">
-        <v>35.85982</v>
+        <v>35.80553</v>
       </c>
       <c r="K6" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="L6" t="n">
-        <v>10.737511</v>
+        <v>10.721255</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02538869155069004</v>
+        <v>0.02542718842946288</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02788636231293309</v>
+        <v>0.02792864641045081</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02309363818297755</v>
+        <v>-0.02343135515357507</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -50777,10 +51299,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>214.13</v>
+        <v>217.09</v>
       </c>
       <c r="F7" t="n">
-        <v>5170596937728</v>
+        <v>5242072072192</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -50789,39 +51311,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.070797</v>
+        <v>27.445007</v>
       </c>
       <c r="J7" t="n">
-        <v>13.454941</v>
+        <v>13.640933</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>17.066366</v>
+        <v>17.30228</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03694017652827722</v>
+        <v>0.03643650099037266</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07432214075561575</v>
+        <v>0.07330876594960616</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0233421402597051</v>
+        <v>0.02194876438558028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -50835,51 +51357,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>528.75</v>
+        <v>538.05</v>
       </c>
       <c r="F8" t="n">
-        <v>863171182592</v>
+        <v>878353186816</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.75529</v>
+        <v>15.76209</v>
       </c>
       <c r="I8" t="n">
-        <v>134.88521</v>
+        <v>137.25764</v>
       </c>
       <c r="J8" t="n">
-        <v>33.560158</v>
+        <v>34.1357</v>
       </c>
       <c r="K8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>20.897497</v>
+        <v>21.265057</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00741371158392435</v>
+        <v>0.007285568255738315</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02979723877068558</v>
+        <v>0.02929484248675774</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02118276172522506</v>
+        <v>-0.02206515907726814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -50893,51 +51415,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>328.75</v>
+        <v>334.59</v>
       </c>
       <c r="F9" t="n">
-        <v>1569330823168</v>
+        <v>1597208788992</v>
       </c>
       <c r="G9" t="n">
-        <v>7.59</v>
+        <v>7.83</v>
       </c>
       <c r="H9" t="n">
-        <v>19.39382</v>
+        <v>19.39695</v>
       </c>
       <c r="I9" t="n">
-        <v>43.31357</v>
+        <v>42.7318</v>
       </c>
       <c r="J9" t="n">
-        <v>16.951277</v>
+        <v>17.249619</v>
       </c>
       <c r="K9" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="L9" t="n">
-        <v>17.61235</v>
+        <v>17.92522</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02308745247148289</v>
+        <v>0.02340177530709226</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05899260836501902</v>
+        <v>0.05797229444992379</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P9" t="n">
-        <v>0.008012607869108374</v>
+        <v>0.006612292885897916</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-16 17:37:09</t>
+          <t>2026-10-19 18:07:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -50951,40 +51473,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.53</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>293682642944</v>
+        <v>290851160064</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.80011</v>
+        <v>3.80035</v>
       </c>
       <c r="I10" t="n">
-        <v>22.179245</v>
+        <v>21.965408</v>
       </c>
       <c r="J10" t="n">
-        <v>18.559988</v>
+        <v>18.379887</v>
       </c>
       <c r="K10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="L10" t="n">
-        <v>6.0714903</v>
+        <v>6.0129533</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04508719693747341</v>
+        <v>0.0455261274158912</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0538793421239189</v>
+        <v>0.05440730136005727</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.05136000156402588</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002899341628008256</v>
+        <v>0.00304729979603139</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P874"/>
+  <dimension ref="A1:P883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50415,16 +50415,16 @@
         <v>10.721255</v>
       </c>
       <c r="M866" t="n">
-        <v>0.02542718842946288</v>
+        <v>0.0254271884294628</v>
       </c>
       <c r="N866" t="n">
-        <v>0.02792864641045081</v>
+        <v>0.0279286464104508</v>
       </c>
       <c r="O866" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P866" t="n">
-        <v>-0.02343135515357507</v>
+        <v>-0.023431355153575</v>
       </c>
     </row>
     <row r="867">
@@ -50473,16 +50473,16 @@
         <v>21.265057</v>
       </c>
       <c r="M867" t="n">
-        <v>0.007285568255738315</v>
+        <v>0.0072855682557383</v>
       </c>
       <c r="N867" t="n">
-        <v>0.02929484248675774</v>
+        <v>0.0292948424867577</v>
       </c>
       <c r="O867" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P867" t="n">
-        <v>-0.02206515907726814</v>
+        <v>-0.0220651590772681</v>
       </c>
     </row>
     <row r="868">
@@ -50531,16 +50531,16 @@
         <v>3.649531</v>
       </c>
       <c r="M868" t="n">
-        <v>0.04736140217184226</v>
+        <v>0.0473614021718422</v>
       </c>
       <c r="N868" t="n">
-        <v>0.03979100781101162</v>
+        <v>0.0397910078110116</v>
       </c>
       <c r="O868" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P868" t="n">
-        <v>-0.01156899375301425</v>
+        <v>-0.0115689937530142</v>
       </c>
     </row>
     <row r="869">
@@ -50589,16 +50589,16 @@
         <v>17.92522</v>
       </c>
       <c r="M869" t="n">
-        <v>0.02340177530709226</v>
+        <v>0.0234017753070922</v>
       </c>
       <c r="N869" t="n">
-        <v>0.05797229444992379</v>
+        <v>0.0579722944499237</v>
       </c>
       <c r="O869" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P869" t="n">
-        <v>0.006612292885897916</v>
+        <v>0.0066122928858979</v>
       </c>
     </row>
     <row r="870">
@@ -50647,16 +50647,16 @@
         <v>9.330461</v>
       </c>
       <c r="M870" t="n">
-        <v>0.05859007525870178</v>
+        <v>0.0585900752587017</v>
       </c>
       <c r="N870" t="n">
-        <v>0.04495419802445907</v>
+        <v>0.044954198024459</v>
       </c>
       <c r="O870" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P870" t="n">
-        <v>-0.006405803539566803</v>
+        <v>-0.0064058035395668</v>
       </c>
     </row>
     <row r="871">
@@ -50705,16 +50705,16 @@
         <v>7.8735437</v>
       </c>
       <c r="M871" t="n">
-        <v>0.03762190973009753</v>
+        <v>0.0376219097300975</v>
       </c>
       <c r="N871" t="n">
-        <v>0.0491193723066455</v>
+        <v>0.0491193723066454</v>
       </c>
       <c r="O871" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P871" t="n">
-        <v>-0.002240629257380382</v>
+        <v>-0.0022406292573803</v>
       </c>
     </row>
     <row r="872">
@@ -50763,16 +50763,16 @@
         <v>11.938552</v>
       </c>
       <c r="M872" t="n">
-        <v>0.03364447443394812</v>
+        <v>0.0336444744339481</v>
       </c>
       <c r="N872" t="n">
-        <v>0.04446165092217724</v>
+        <v>0.0444616509221772</v>
       </c>
       <c r="O872" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P872" t="n">
-        <v>-0.006898350641848634</v>
+        <v>-0.0068983506418486</v>
       </c>
     </row>
     <row r="873">
@@ -50824,13 +50824,13 @@
         <v>0.0455261274158912</v>
       </c>
       <c r="N873" t="n">
-        <v>0.05440730136005727</v>
+        <v>0.0544073013600572</v>
       </c>
       <c r="O873" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P873" t="n">
-        <v>0.00304729979603139</v>
+        <v>0.0030472997960313</v>
       </c>
     </row>
     <row r="874">
@@ -50879,16 +50879,538 @@
         <v>17.30228</v>
       </c>
       <c r="M874" t="n">
-        <v>0.03643650099037266</v>
+        <v>0.0364365009903726</v>
       </c>
       <c r="N874" t="n">
-        <v>0.07330876594960616</v>
+        <v>0.0733087659496061</v>
       </c>
       <c r="O874" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.0513600015640258</v>
       </c>
       <c r="P874" t="n">
-        <v>0.02194876438558028</v>
+        <v>0.0219487643855802</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E875" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="F875" t="n">
+        <v>4954723975168</v>
+      </c>
+      <c r="G875" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H875" t="n">
+        <v>9.5707</v>
+      </c>
+      <c r="I875" t="n">
+        <v>38.933487</v>
+      </c>
+      <c r="J875" t="n">
+        <v>35.47285</v>
+      </c>
+      <c r="K875" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L875" t="n">
+        <v>10.61371</v>
+      </c>
+      <c r="M875" t="n">
+        <v>0.02568483063328424</v>
+      </c>
+      <c r="N875" t="n">
+        <v>0.02819057437407953</v>
+      </c>
+      <c r="O875" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P875" t="n">
+        <v>-0.02297942188751715</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E876" t="n">
+        <v>534.74</v>
+      </c>
+      <c r="F876" t="n">
+        <v>872949678080</v>
+      </c>
+      <c r="G876" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H876" t="n">
+        <v>15.76289</v>
+      </c>
+      <c r="I876" t="n">
+        <v>136.41325</v>
+      </c>
+      <c r="J876" t="n">
+        <v>33.92398</v>
+      </c>
+      <c r="K876" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L876" t="n">
+        <v>21.134237</v>
+      </c>
+      <c r="M876" t="n">
+        <v>0.007330665370086397</v>
+      </c>
+      <c r="N876" t="n">
+        <v>0.02947767139170438</v>
+      </c>
+      <c r="O876" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P876" t="n">
+        <v>-0.0216923248698923</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E877" t="n">
+        <v>262.63</v>
+      </c>
+      <c r="F877" t="n">
+        <v>2832809590784</v>
+      </c>
+      <c r="G877" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H877" t="n">
+        <v>10.44315</v>
+      </c>
+      <c r="I877" t="n">
+        <v>21.128721</v>
+      </c>
+      <c r="J877" t="n">
+        <v>25.148544</v>
+      </c>
+      <c r="K877" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L877" t="n">
+        <v>3.6520336</v>
+      </c>
+      <c r="M877" t="n">
+        <v>0.04732894185736588</v>
+      </c>
+      <c r="N877" t="n">
+        <v>0.03976373605452538</v>
+      </c>
+      <c r="O877" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P877" t="n">
+        <v>-0.0114062602070713</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E878" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="F878" t="n">
+        <v>1596158640128</v>
+      </c>
+      <c r="G878" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H878" t="n">
+        <v>19.39695</v>
+      </c>
+      <c r="I878" t="n">
+        <v>42.703705</v>
+      </c>
+      <c r="J878" t="n">
+        <v>17.238277</v>
+      </c>
+      <c r="K878" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L878" t="n">
+        <v>17.913435</v>
+      </c>
+      <c r="M878" t="n">
+        <v>0.02341717259323504</v>
+      </c>
+      <c r="N878" t="n">
+        <v>0.05801043753925293</v>
+      </c>
+      <c r="O878" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P878" t="n">
+        <v>0.006840441277656248</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E879" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="F879" t="n">
+        <v>4114150064128</v>
+      </c>
+      <c r="G879" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H879" t="n">
+        <v>15.34777</v>
+      </c>
+      <c r="I879" t="n">
+        <v>16.879076</v>
+      </c>
+      <c r="J879" t="n">
+        <v>21.918493</v>
+      </c>
+      <c r="K879" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L879" t="n">
+        <v>9.2273245</v>
+      </c>
+      <c r="M879" t="n">
+        <v>0.05924494649227111</v>
+      </c>
+      <c r="N879" t="n">
+        <v>0.04562357312722949</v>
+      </c>
+      <c r="O879" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P879" t="n">
+        <v>-0.005546423134367186</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E880" t="n">
+        <v>694.25</v>
+      </c>
+      <c r="F880" t="n">
+        <v>1768606138368</v>
+      </c>
+      <c r="G880" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H880" t="n">
+        <v>34.65077</v>
+      </c>
+      <c r="I880" t="n">
+        <v>26.158628</v>
+      </c>
+      <c r="J880" t="n">
+        <v>20.035631</v>
+      </c>
+      <c r="K880" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L880" t="n">
+        <v>7.74865</v>
+      </c>
+      <c r="M880" t="n">
+        <v>0.03822830392509902</v>
+      </c>
+      <c r="N880" t="n">
+        <v>0.04991108390349298</v>
+      </c>
+      <c r="O880" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P880" t="n">
+        <v>-0.0012589123581037</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E881" t="n">
+        <v>531.87</v>
+      </c>
+      <c r="F881" t="n">
+        <v>3949425065984</v>
+      </c>
+      <c r="G881" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H881" t="n">
+        <v>23.69881</v>
+      </c>
+      <c r="I881" t="n">
+        <v>29.63064</v>
+      </c>
+      <c r="J881" t="n">
+        <v>22.442898</v>
+      </c>
+      <c r="K881" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L881" t="n">
+        <v>11.901629</v>
+      </c>
+      <c r="M881" t="n">
+        <v>0.0337488484028052</v>
+      </c>
+      <c r="N881" t="n">
+        <v>0.0445575234549796</v>
+      </c>
+      <c r="O881" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P881" t="n">
+        <v>-0.006612472806617073</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E882" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="F882" t="n">
+        <v>286021025792</v>
+      </c>
+      <c r="G882" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H882" t="n">
+        <v>3.80035</v>
+      </c>
+      <c r="I882" t="n">
+        <v>21.60063</v>
+      </c>
+      <c r="J882" t="n">
+        <v>18.074652</v>
+      </c>
+      <c r="K882" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L882" t="n">
+        <v>5.913097</v>
+      </c>
+      <c r="M882" t="n">
+        <v>0.04629494831853254</v>
+      </c>
+      <c r="N882" t="n">
+        <v>0.05532610278060853</v>
+      </c>
+      <c r="O882" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P882" t="n">
+        <v>0.004156106519011854</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:42:16</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E883" t="n">
+        <v>216.47</v>
+      </c>
+      <c r="F883" t="n">
+        <v>5227101028352</v>
+      </c>
+      <c r="G883" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H883" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I883" t="n">
+        <v>27.366625</v>
+      </c>
+      <c r="J883" t="n">
+        <v>13.601975</v>
+      </c>
+      <c r="K883" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L883" t="n">
+        <v>17.252867</v>
+      </c>
+      <c r="M883" t="n">
+        <v>0.03654086016538088</v>
+      </c>
+      <c r="N883" t="n">
+        <v>0.07351873238785975</v>
+      </c>
+      <c r="O883" t="n">
+        <v>0.05116999626159668</v>
+      </c>
+      <c r="P883" t="n">
+        <v>0.02234873612626307</v>
       </c>
     </row>
   </sheetData>
@@ -50990,12 +51512,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -51009,51 +51531,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>340.16</v>
+        <v>336.4</v>
       </c>
       <c r="F2" t="n">
-        <v>4160134840320</v>
+        <v>4114150064128</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>15.29162</v>
+        <v>15.34777</v>
       </c>
       <c r="I2" t="n">
-        <v>17.067738</v>
+        <v>16.879076</v>
       </c>
       <c r="J2" t="n">
-        <v>22.244864</v>
+        <v>21.918493</v>
       </c>
       <c r="K2" t="n">
         <v>1.18</v>
       </c>
       <c r="L2" t="n">
-        <v>9.330461</v>
+        <v>9.2273245</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05859007525870178</v>
+        <v>0.05924494649227111</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04495419802445907</v>
+        <v>0.04562357312722949</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006405803539566803</v>
+        <v>-0.005546423134367186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -51067,51 +51589,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>533.52</v>
+        <v>531.87</v>
       </c>
       <c r="F3" t="n">
-        <v>3961677414400</v>
+        <v>3949425065984</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.72118</v>
+        <v>23.69881</v>
       </c>
       <c r="I3" t="n">
-        <v>29.722563</v>
+        <v>29.63064</v>
       </c>
       <c r="J3" t="n">
-        <v>22.491293</v>
+        <v>22.442898</v>
       </c>
       <c r="K3" t="n">
         <v>1.72</v>
       </c>
       <c r="L3" t="n">
-        <v>11.938552</v>
+        <v>11.901629</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03364447443394812</v>
+        <v>0.0337488484028052</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04446165092217724</v>
+        <v>0.0445575234549796</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.006898350641848634</v>
+        <v>-0.006612472806617073</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -51125,10 +51647,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>705.4400000000001</v>
+        <v>694.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1797112725504</v>
+        <v>1768606138368</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
@@ -51137,39 +51659,39 @@
         <v>34.65077</v>
       </c>
       <c r="I4" t="n">
-        <v>26.580256</v>
+        <v>26.158628</v>
       </c>
       <c r="J4" t="n">
-        <v>20.358568</v>
+        <v>20.035631</v>
       </c>
       <c r="K4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8735437</v>
+        <v>7.74865</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03762190973009753</v>
+        <v>0.03822830392509902</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0491193723066455</v>
+        <v>0.04991108390349298</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.002240629257380382</v>
+        <v>-0.0012589123581037</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -51183,10 +51705,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>262.45</v>
+        <v>262.63</v>
       </c>
       <c r="F5" t="n">
-        <v>2830868152320</v>
+        <v>2832809590784</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -51195,39 +51717,39 @@
         <v>10.44315</v>
       </c>
       <c r="I5" t="n">
-        <v>21.11424</v>
+        <v>21.128721</v>
       </c>
       <c r="J5" t="n">
-        <v>25.131308</v>
+        <v>25.148544</v>
       </c>
       <c r="K5" t="n">
         <v>1.45</v>
       </c>
       <c r="L5" t="n">
-        <v>3.649531</v>
+        <v>3.6520336</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04736140217184226</v>
+        <v>0.04732894185736588</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03979100781101162</v>
+        <v>0.03976373605452538</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01156899375301425</v>
+        <v>-0.0114062602070713</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -51241,51 +51763,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>342.94</v>
+        <v>339.5</v>
       </c>
       <c r="F6" t="n">
-        <v>5004928221184</v>
+        <v>4954723975168</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.57785</v>
+        <v>9.5707</v>
       </c>
       <c r="I6" t="n">
-        <v>39.32798</v>
+        <v>38.933487</v>
       </c>
       <c r="J6" t="n">
-        <v>35.80553</v>
+        <v>35.47285</v>
       </c>
       <c r="K6" t="n">
         <v>2.75</v>
       </c>
       <c r="L6" t="n">
-        <v>10.721255</v>
+        <v>10.61371</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02542718842946288</v>
+        <v>0.02568483063328424</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02792864641045081</v>
+        <v>0.02819057437407953</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02343135515357507</v>
+        <v>-0.02297942188751715</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -51299,10 +51821,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.09</v>
+        <v>216.47</v>
       </c>
       <c r="F7" t="n">
-        <v>5242072072192</v>
+        <v>5227101028352</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -51311,39 +51833,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.445007</v>
+        <v>27.366625</v>
       </c>
       <c r="J7" t="n">
-        <v>13.640933</v>
+        <v>13.601975</v>
       </c>
       <c r="K7" t="n">
         <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>17.30228</v>
+        <v>17.252867</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03643650099037266</v>
+        <v>0.03654086016538088</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07330876594960616</v>
+        <v>0.07351873238785975</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02194876438558028</v>
+        <v>0.02234873612626307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -51357,51 +51879,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>538.05</v>
+        <v>534.74</v>
       </c>
       <c r="F8" t="n">
-        <v>878353186816</v>
+        <v>872949678080</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.76209</v>
+        <v>15.76289</v>
       </c>
       <c r="I8" t="n">
-        <v>137.25764</v>
+        <v>136.41325</v>
       </c>
       <c r="J8" t="n">
-        <v>34.1357</v>
+        <v>33.92398</v>
       </c>
       <c r="K8" t="n">
         <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>21.265057</v>
+        <v>21.134237</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007285568255738315</v>
+        <v>0.007330665370086397</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02929484248675774</v>
+        <v>0.02947767139170438</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02206515907726814</v>
+        <v>-0.0216923248698923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -51415,10 +51937,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>334.59</v>
+        <v>334.37</v>
       </c>
       <c r="F9" t="n">
-        <v>1597208788992</v>
+        <v>1596158640128</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -51427,39 +51949,39 @@
         <v>19.39695</v>
       </c>
       <c r="I9" t="n">
-        <v>42.7318</v>
+        <v>42.703705</v>
       </c>
       <c r="J9" t="n">
-        <v>17.249619</v>
+        <v>17.238277</v>
       </c>
       <c r="K9" t="n">
         <v>0.33</v>
       </c>
       <c r="L9" t="n">
-        <v>17.92522</v>
+        <v>17.913435</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02340177530709226</v>
+        <v>0.02341717259323504</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05797229444992379</v>
+        <v>0.05801043753925293</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006612292885897916</v>
+        <v>0.006840441277656248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-19 18:07:16</t>
+          <t>2026-10-20 17:42:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -51473,10 +51995,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69.84999999999999</v>
+        <v>68.69</v>
       </c>
       <c r="F10" t="n">
-        <v>290851160064</v>
+        <v>286021025792</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -51485,28 +52007,28 @@
         <v>3.80035</v>
       </c>
       <c r="I10" t="n">
-        <v>21.965408</v>
+        <v>21.60063</v>
       </c>
       <c r="J10" t="n">
-        <v>18.379887</v>
+        <v>18.074652</v>
       </c>
       <c r="K10" t="n">
         <v>1.21</v>
       </c>
       <c r="L10" t="n">
-        <v>6.0129533</v>
+        <v>5.913097</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0455261274158912</v>
+        <v>0.04629494831853254</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05440730136005727</v>
+        <v>0.05532610278060853</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05136000156402588</v>
+        <v>0.05116999626159668</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00304729979603139</v>
+        <v>0.004156106519011854</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P883"/>
+  <dimension ref="A1:P892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50937,16 +50937,16 @@
         <v>10.61371</v>
       </c>
       <c r="M875" t="n">
-        <v>0.02568483063328424</v>
+        <v>0.0256848306332842</v>
       </c>
       <c r="N875" t="n">
-        <v>0.02819057437407953</v>
+        <v>0.0281905743740795</v>
       </c>
       <c r="O875" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P875" t="n">
-        <v>-0.02297942188751715</v>
+        <v>-0.0229794218875171</v>
       </c>
     </row>
     <row r="876">
@@ -50995,16 +50995,16 @@
         <v>21.134237</v>
       </c>
       <c r="M876" t="n">
-        <v>0.007330665370086397</v>
+        <v>0.0073306653700863</v>
       </c>
       <c r="N876" t="n">
-        <v>0.02947767139170438</v>
+        <v>0.0294776713917043</v>
       </c>
       <c r="O876" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P876" t="n">
-        <v>-0.0216923248698923</v>
+        <v>-0.0216923248698922</v>
       </c>
     </row>
     <row r="877">
@@ -51053,16 +51053,16 @@
         <v>3.6520336</v>
       </c>
       <c r="M877" t="n">
-        <v>0.04732894185736588</v>
+        <v>0.0473289418573658</v>
       </c>
       <c r="N877" t="n">
-        <v>0.03976373605452538</v>
+        <v>0.0397637360545253</v>
       </c>
       <c r="O877" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P877" t="n">
-        <v>-0.0114062602070713</v>
+        <v>-0.0114062602070712</v>
       </c>
     </row>
     <row r="878">
@@ -51111,16 +51111,16 @@
         <v>17.913435</v>
       </c>
       <c r="M878" t="n">
-        <v>0.02341717259323504</v>
+        <v>0.023417172593235</v>
       </c>
       <c r="N878" t="n">
-        <v>0.05801043753925293</v>
+        <v>0.0580104375392529</v>
       </c>
       <c r="O878" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P878" t="n">
-        <v>0.006840441277656248</v>
+        <v>0.0068404412776562</v>
       </c>
     </row>
     <row r="879">
@@ -51169,16 +51169,16 @@
         <v>9.2273245</v>
       </c>
       <c r="M879" t="n">
-        <v>0.05924494649227111</v>
+        <v>0.0592449464922711</v>
       </c>
       <c r="N879" t="n">
-        <v>0.04562357312722949</v>
+        <v>0.0456235731272294</v>
       </c>
       <c r="O879" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P879" t="n">
-        <v>-0.005546423134367186</v>
+        <v>-0.0055464231343671</v>
       </c>
     </row>
     <row r="880">
@@ -51227,13 +51227,13 @@
         <v>7.74865</v>
       </c>
       <c r="M880" t="n">
-        <v>0.03822830392509902</v>
+        <v>0.038228303925099</v>
       </c>
       <c r="N880" t="n">
-        <v>0.04991108390349298</v>
+        <v>0.0499110839034929</v>
       </c>
       <c r="O880" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P880" t="n">
         <v>-0.0012589123581037</v>
@@ -51291,10 +51291,10 @@
         <v>0.0445575234549796</v>
       </c>
       <c r="O881" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P881" t="n">
-        <v>-0.006612472806617073</v>
+        <v>-0.006612472806617</v>
       </c>
     </row>
     <row r="882">
@@ -51343,16 +51343,16 @@
         <v>5.913097</v>
       </c>
       <c r="M882" t="n">
-        <v>0.04629494831853254</v>
+        <v>0.0462949483185325</v>
       </c>
       <c r="N882" t="n">
-        <v>0.05532610278060853</v>
+        <v>0.0553261027806085</v>
       </c>
       <c r="O882" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P882" t="n">
-        <v>0.004156106519011854</v>
+        <v>0.0041561065190118</v>
       </c>
     </row>
     <row r="883">
@@ -51401,16 +51401,538 @@
         <v>17.252867</v>
       </c>
       <c r="M883" t="n">
-        <v>0.03654086016538088</v>
+        <v>0.0365408601653808</v>
       </c>
       <c r="N883" t="n">
-        <v>0.07351873238785975</v>
+        <v>0.07351873238785971</v>
       </c>
       <c r="O883" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.0511699962615966</v>
       </c>
       <c r="P883" t="n">
-        <v>0.02234873612626307</v>
+        <v>0.022348736126263</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E884" t="n">
+        <v>343.99</v>
+      </c>
+      <c r="F884" t="n">
+        <v>5020252110848</v>
+      </c>
+      <c r="G884" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="H884" t="n">
+        <v>9.5707</v>
+      </c>
+      <c r="I884" t="n">
+        <v>38.912895</v>
+      </c>
+      <c r="J884" t="n">
+        <v>35.94199</v>
+      </c>
+      <c r="K884" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L884" t="n">
+        <v>10.754081</v>
+      </c>
+      <c r="M884" t="n">
+        <v>0.02569842146574028</v>
+      </c>
+      <c r="N884" t="n">
+        <v>0.02782261112241635</v>
+      </c>
+      <c r="O884" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P884" t="n">
+        <v>-0.02363738796205631</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E885" t="n">
+        <v>552.72</v>
+      </c>
+      <c r="F885" t="n">
+        <v>902301548544</v>
+      </c>
+      <c r="G885" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H885" t="n">
+        <v>15.76289</v>
+      </c>
+      <c r="I885" t="n">
+        <v>140.99998</v>
+      </c>
+      <c r="J885" t="n">
+        <v>35.064636</v>
+      </c>
+      <c r="K885" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L885" t="n">
+        <v>21.844849</v>
+      </c>
+      <c r="M885" t="n">
+        <v>0.007092198581560284</v>
+      </c>
+      <c r="N885" t="n">
+        <v>0.02851876176002316</v>
+      </c>
+      <c r="O885" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P885" t="n">
+        <v>-0.0229412373244495</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E886" t="n">
+        <v>262.37</v>
+      </c>
+      <c r="F886" t="n">
+        <v>2830004912128</v>
+      </c>
+      <c r="G886" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H886" t="n">
+        <v>10.44808</v>
+      </c>
+      <c r="I886" t="n">
+        <v>21.124798</v>
+      </c>
+      <c r="J886" t="n">
+        <v>25.11179</v>
+      </c>
+      <c r="K886" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L886" t="n">
+        <v>3.648418</v>
+      </c>
+      <c r="M886" t="n">
+        <v>0.04733772916110836</v>
+      </c>
+      <c r="N886" t="n">
+        <v>0.03982193086099782</v>
+      </c>
+      <c r="O886" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P886" t="n">
+        <v>-0.01163806822347484</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E887" t="n">
+        <v>337.8</v>
+      </c>
+      <c r="F887" t="n">
+        <v>1612532154368</v>
+      </c>
+      <c r="G887" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H887" t="n">
+        <v>19.39695</v>
+      </c>
+      <c r="I887" t="n">
+        <v>43.14176</v>
+      </c>
+      <c r="J887" t="n">
+        <v>17.415108</v>
+      </c>
+      <c r="K887" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L887" t="n">
+        <v>18.09719</v>
+      </c>
+      <c r="M887" t="n">
+        <v>0.02317939609236234</v>
+      </c>
+      <c r="N887" t="n">
+        <v>0.05742140319715808</v>
+      </c>
+      <c r="O887" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P887" t="n">
+        <v>0.00596140411268542</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E888" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="F888" t="n">
+        <v>4047497068544</v>
+      </c>
+      <c r="G888" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H888" t="n">
+        <v>15.34777</v>
+      </c>
+      <c r="I888" t="n">
+        <v>16.60562</v>
+      </c>
+      <c r="J888" t="n">
+        <v>21.563395</v>
+      </c>
+      <c r="K888" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L888" t="n">
+        <v>9.077833</v>
+      </c>
+      <c r="M888" t="n">
+        <v>0.06022057712645415</v>
+      </c>
+      <c r="N888" t="n">
+        <v>0.0463748904668379</v>
+      </c>
+      <c r="O888" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P888" t="n">
+        <v>-0.005085108617634761</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E889" t="n">
+        <v>697.52</v>
+      </c>
+      <c r="F889" t="n">
+        <v>1776936550400</v>
+      </c>
+      <c r="G889" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H889" t="n">
+        <v>34.65077</v>
+      </c>
+      <c r="I889" t="n">
+        <v>26.28184</v>
+      </c>
+      <c r="J889" t="n">
+        <v>20.130001</v>
+      </c>
+      <c r="K889" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L889" t="n">
+        <v>7.7851477</v>
+      </c>
+      <c r="M889" t="n">
+        <v>0.03804908819818786</v>
+      </c>
+      <c r="N889" t="n">
+        <v>0.04967709886454869</v>
+      </c>
+      <c r="O889" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P889" t="n">
+        <v>-0.001782900219923965</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E890" t="n">
+        <v>532.95</v>
+      </c>
+      <c r="F890" t="n">
+        <v>3957444575232</v>
+      </c>
+      <c r="G890" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H890" t="n">
+        <v>23.70396</v>
+      </c>
+      <c r="I890" t="n">
+        <v>29.690807</v>
+      </c>
+      <c r="J890" t="n">
+        <v>22.483585</v>
+      </c>
+      <c r="K890" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L890" t="n">
+        <v>11.9257965</v>
+      </c>
+      <c r="M890" t="n">
+        <v>0.03368045782906463</v>
+      </c>
+      <c r="N890" t="n">
+        <v>0.04447689276667604</v>
+      </c>
+      <c r="O890" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P890" t="n">
+        <v>-0.006983106317796618</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E891" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="F891" t="n">
+        <v>270822637568</v>
+      </c>
+      <c r="G891" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H891" t="n">
+        <v>3.77848</v>
+      </c>
+      <c r="I891" t="n">
+        <v>18.797688</v>
+      </c>
+      <c r="J891" t="n">
+        <v>17.21327</v>
+      </c>
+      <c r="K891" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L891" t="n">
+        <v>5.445353</v>
+      </c>
+      <c r="M891" t="n">
+        <v>0.0531980319803198</v>
+      </c>
+      <c r="N891" t="n">
+        <v>0.05809471094710947</v>
+      </c>
+      <c r="O891" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P891" t="n">
+        <v>0.006634711862636811</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:45:39</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E892" t="n">
+        <v>221.97</v>
+      </c>
+      <c r="F892" t="n">
+        <v>5359909470208</v>
+      </c>
+      <c r="G892" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H892" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I892" t="n">
+        <v>28.061947</v>
+      </c>
+      <c r="J892" t="n">
+        <v>13.94757</v>
+      </c>
+      <c r="K892" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L892" t="n">
+        <v>17.691221</v>
+      </c>
+      <c r="M892" t="n">
+        <v>0.03563544623147272</v>
+      </c>
+      <c r="N892" t="n">
+        <v>0.07169707618146597</v>
+      </c>
+      <c r="O892" t="n">
+        <v>0.05145999908447266</v>
+      </c>
+      <c r="P892" t="n">
+        <v>0.02023707709699331</v>
       </c>
     </row>
   </sheetData>
@@ -51512,12 +52034,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -51531,10 +52053,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>336.4</v>
+        <v>330.95</v>
       </c>
       <c r="F2" t="n">
-        <v>4114150064128</v>
+        <v>4047497068544</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -51543,39 +52065,39 @@
         <v>15.34777</v>
       </c>
       <c r="I2" t="n">
-        <v>16.879076</v>
+        <v>16.60562</v>
       </c>
       <c r="J2" t="n">
-        <v>21.918493</v>
+        <v>21.563395</v>
       </c>
       <c r="K2" t="n">
         <v>1.18</v>
       </c>
       <c r="L2" t="n">
-        <v>9.2273245</v>
+        <v>9.077833</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05924494649227111</v>
+        <v>0.06022057712645415</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04562357312722949</v>
+        <v>0.0463748904668379</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005546423134367186</v>
+        <v>-0.005085108617634761</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -51589,51 +52111,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>531.87</v>
+        <v>532.95</v>
       </c>
       <c r="F3" t="n">
-        <v>3949425065984</v>
+        <v>3957444575232</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.69881</v>
+        <v>23.70396</v>
       </c>
       <c r="I3" t="n">
-        <v>29.63064</v>
+        <v>29.690807</v>
       </c>
       <c r="J3" t="n">
-        <v>22.442898</v>
+        <v>22.483585</v>
       </c>
       <c r="K3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="L3" t="n">
-        <v>11.901629</v>
+        <v>11.9257965</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0337488484028052</v>
+        <v>0.03368045782906463</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0445575234549796</v>
+        <v>0.04447689276667604</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.006612472806617073</v>
+        <v>-0.006983106317796618</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -51647,10 +52169,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>694.25</v>
+        <v>697.52</v>
       </c>
       <c r="F4" t="n">
-        <v>1768606138368</v>
+        <v>1776936550400</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
@@ -51659,39 +52181,39 @@
         <v>34.65077</v>
       </c>
       <c r="I4" t="n">
-        <v>26.158628</v>
+        <v>26.28184</v>
       </c>
       <c r="J4" t="n">
-        <v>20.035631</v>
+        <v>20.130001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="L4" t="n">
-        <v>7.74865</v>
+        <v>7.7851477</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03822830392509902</v>
+        <v>0.03804908819818786</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04991108390349298</v>
+        <v>0.04967709886454869</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0012589123581037</v>
+        <v>-0.001782900219923965</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -51705,51 +52227,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>262.63</v>
+        <v>262.37</v>
       </c>
       <c r="F5" t="n">
-        <v>2832809590784</v>
+        <v>2830004912128</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="H5" t="n">
-        <v>10.44315</v>
+        <v>10.44808</v>
       </c>
       <c r="I5" t="n">
-        <v>21.128721</v>
+        <v>21.124798</v>
       </c>
       <c r="J5" t="n">
-        <v>25.148544</v>
+        <v>25.11179</v>
       </c>
       <c r="K5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6520336</v>
+        <v>3.648418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04732894185736588</v>
+        <v>0.04733772916110836</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03976373605452538</v>
+        <v>0.03982193086099782</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0114062602070713</v>
+        <v>-0.01163806822347484</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -51763,51 +52285,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>339.5</v>
+        <v>343.99</v>
       </c>
       <c r="F6" t="n">
-        <v>4954723975168</v>
+        <v>5020252110848</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="H6" t="n">
         <v>9.5707</v>
       </c>
       <c r="I6" t="n">
-        <v>38.933487</v>
+        <v>38.912895</v>
       </c>
       <c r="J6" t="n">
-        <v>35.47285</v>
+        <v>35.94199</v>
       </c>
       <c r="K6" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="L6" t="n">
-        <v>10.61371</v>
+        <v>10.754081</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02568483063328424</v>
+        <v>0.02569842146574028</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02819057437407953</v>
+        <v>0.02782261112241635</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02297942188751715</v>
+        <v>-0.02363738796205631</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -51821,10 +52343,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>216.47</v>
+        <v>221.97</v>
       </c>
       <c r="F7" t="n">
-        <v>5227101028352</v>
+        <v>5359909470208</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -51833,39 +52355,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.366625</v>
+        <v>28.061947</v>
       </c>
       <c r="J7" t="n">
-        <v>13.601975</v>
+        <v>13.94757</v>
       </c>
       <c r="K7" t="n">
         <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>17.252867</v>
+        <v>17.691221</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03654086016538088</v>
+        <v>0.03563544623147272</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07351873238785975</v>
+        <v>0.07169707618146597</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02234873612626307</v>
+        <v>0.02023707709699331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -51879,10 +52401,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>534.74</v>
+        <v>552.72</v>
       </c>
       <c r="F8" t="n">
-        <v>872949678080</v>
+        <v>902301548544</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -51891,39 +52413,39 @@
         <v>15.76289</v>
       </c>
       <c r="I8" t="n">
-        <v>136.41325</v>
+        <v>140.99998</v>
       </c>
       <c r="J8" t="n">
-        <v>33.92398</v>
+        <v>35.064636</v>
       </c>
       <c r="K8" t="n">
         <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>21.134237</v>
+        <v>21.844849</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007330665370086397</v>
+        <v>0.007092198581560284</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02947767139170438</v>
+        <v>0.02851876176002316</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0216923248698923</v>
+        <v>-0.0229412373244495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -51937,10 +52459,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>334.37</v>
+        <v>337.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1596158640128</v>
+        <v>1612532154368</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -51949,39 +52471,39 @@
         <v>19.39695</v>
       </c>
       <c r="I9" t="n">
-        <v>42.703705</v>
+        <v>43.14176</v>
       </c>
       <c r="J9" t="n">
-        <v>17.238277</v>
+        <v>17.415108</v>
       </c>
       <c r="K9" t="n">
         <v>0.33</v>
       </c>
       <c r="L9" t="n">
-        <v>17.913435</v>
+        <v>18.09719</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02341717259323504</v>
+        <v>0.02317939609236234</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05801043753925293</v>
+        <v>0.05742140319715808</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006840441277656248</v>
+        <v>0.00596140411268542</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 17:42:16</t>
+          <t>2026-10-21 17:45:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -51995,40 +52517,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68.69</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>286021025792</v>
+        <v>270822637568</v>
       </c>
       <c r="G10" t="n">
-        <v>3.18</v>
+        <v>3.46</v>
       </c>
       <c r="H10" t="n">
-        <v>3.80035</v>
+        <v>3.77848</v>
       </c>
       <c r="I10" t="n">
-        <v>21.60063</v>
+        <v>18.797688</v>
       </c>
       <c r="J10" t="n">
-        <v>18.074652</v>
+        <v>17.21327</v>
       </c>
       <c r="K10" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="L10" t="n">
-        <v>5.913097</v>
+        <v>5.445353</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04629494831853254</v>
+        <v>0.0531980319803198</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05532610278060853</v>
+        <v>0.05809471094710947</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05116999626159668</v>
+        <v>0.05145999908447266</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004156106519011854</v>
+        <v>0.006634711862636811</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P892"/>
+  <dimension ref="A1:P901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51933,6 +51933,528 @@
       </c>
       <c r="P892" t="n">
         <v>0.02023707709699331</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E893" t="n">
+        <v>348.22</v>
+      </c>
+      <c r="F893" t="n">
+        <v>5081985449984</v>
+      </c>
+      <c r="G893" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="H893" t="n">
+        <v>9.5707</v>
+      </c>
+      <c r="I893" t="n">
+        <v>39.436012</v>
+      </c>
+      <c r="J893" t="n">
+        <v>36.383965</v>
+      </c>
+      <c r="K893" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L893" t="n">
+        <v>10.886322</v>
+      </c>
+      <c r="M893" t="n">
+        <v>0.02535753259433691</v>
+      </c>
+      <c r="N893" t="n">
+        <v>0.02748463614956062</v>
+      </c>
+      <c r="O893" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P893" t="n">
+        <v>-0.02204536453708489</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E894" t="n">
+        <v>507.93</v>
+      </c>
+      <c r="F894" t="n">
+        <v>829183033344</v>
+      </c>
+      <c r="G894" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H894" t="n">
+        <v>15.76289</v>
+      </c>
+      <c r="I894" t="n">
+        <v>129.57397</v>
+      </c>
+      <c r="J894" t="n">
+        <v>32.223152</v>
+      </c>
+      <c r="K894" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L894" t="n">
+        <v>20.07464</v>
+      </c>
+      <c r="M894" t="n">
+        <v>0.007717598881735672</v>
+      </c>
+      <c r="N894" t="n">
+        <v>0.03103358730533735</v>
+      </c>
+      <c r="O894" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P894" t="n">
+        <v>-0.01849641338130816</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E895" t="n">
+        <v>250.38</v>
+      </c>
+      <c r="F895" t="n">
+        <v>2700677218304</v>
+      </c>
+      <c r="G895" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H895" t="n">
+        <v>10.43091</v>
+      </c>
+      <c r="I895" t="n">
+        <v>20.143202</v>
+      </c>
+      <c r="J895" t="n">
+        <v>24.003658</v>
+      </c>
+      <c r="K895" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L895" t="n">
+        <v>3.4816897</v>
+      </c>
+      <c r="M895" t="n">
+        <v>0.0496445402987459</v>
+      </c>
+      <c r="N895" t="n">
+        <v>0.04166031631919483</v>
+      </c>
+      <c r="O895" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P895" t="n">
+        <v>-0.007869684367450683</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E896" t="n">
+        <v>323.24</v>
+      </c>
+      <c r="F896" t="n">
+        <v>1543028080640</v>
+      </c>
+      <c r="G896" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H896" t="n">
+        <v>19.39695</v>
+      </c>
+      <c r="I896" t="n">
+        <v>41.282246</v>
+      </c>
+      <c r="J896" t="n">
+        <v>16.664474</v>
+      </c>
+      <c r="K896" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L896" t="n">
+        <v>17.317158</v>
+      </c>
+      <c r="M896" t="n">
+        <v>0.02422348719217918</v>
+      </c>
+      <c r="N896" t="n">
+        <v>0.06000788887513921</v>
+      </c>
+      <c r="O896" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P896" t="n">
+        <v>0.0104778881884937</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E897" t="n">
+        <v>320.76</v>
+      </c>
+      <c r="F897" t="n">
+        <v>3922874073088</v>
+      </c>
+      <c r="G897" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H897" t="n">
+        <v>15.35864</v>
+      </c>
+      <c r="I897" t="n">
+        <v>16.09433</v>
+      </c>
+      <c r="J897" t="n">
+        <v>20.884663</v>
+      </c>
+      <c r="K897" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L897" t="n">
+        <v>8.798325999999999</v>
+      </c>
+      <c r="M897" t="n">
+        <v>0.06213368250405288</v>
+      </c>
+      <c r="N897" t="n">
+        <v>0.04788203017832647</v>
+      </c>
+      <c r="O897" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P897" t="n">
+        <v>-0.001647970508319038</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E898" t="n">
+        <v>648.85</v>
+      </c>
+      <c r="F898" t="n">
+        <v>1652949385216</v>
+      </c>
+      <c r="G898" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H898" t="n">
+        <v>34.80467</v>
+      </c>
+      <c r="I898" t="n">
+        <v>22.137495</v>
+      </c>
+      <c r="J898" t="n">
+        <v>18.642612</v>
+      </c>
+      <c r="K898" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L898" t="n">
+        <v>7.241933</v>
+      </c>
+      <c r="M898" t="n">
+        <v>0.04517222778762425</v>
+      </c>
+      <c r="N898" t="n">
+        <v>0.05364054866301919</v>
+      </c>
+      <c r="O898" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P898" t="n">
+        <v>0.004110547976373682</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E899" t="n">
+        <v>521.08</v>
+      </c>
+      <c r="F899" t="n">
+        <v>3869303373824</v>
+      </c>
+      <c r="G899" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H899" t="n">
+        <v>23.70396</v>
+      </c>
+      <c r="I899" t="n">
+        <v>29.029526</v>
+      </c>
+      <c r="J899" t="n">
+        <v>21.982824</v>
+      </c>
+      <c r="K899" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L899" t="n">
+        <v>11.660182</v>
+      </c>
+      <c r="M899" t="n">
+        <v>0.03444768557611115</v>
+      </c>
+      <c r="N899" t="n">
+        <v>0.04549005910800644</v>
+      </c>
+      <c r="O899" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P899" t="n">
+        <v>-0.004039941578639066</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E900" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="F900" t="n">
+        <v>279192174592</v>
+      </c>
+      <c r="G900" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H900" t="n">
+        <v>3.7692</v>
+      </c>
+      <c r="I900" t="n">
+        <v>18.781513</v>
+      </c>
+      <c r="J900" t="n">
+        <v>17.788921</v>
+      </c>
+      <c r="K900" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L900" t="n">
+        <v>5.613637</v>
+      </c>
+      <c r="M900" t="n">
+        <v>0.05324384787472036</v>
+      </c>
+      <c r="N900" t="n">
+        <v>0.05621476510067114</v>
+      </c>
+      <c r="O900" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P900" t="n">
+        <v>0.006684764414025636</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:45:15</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E901" t="n">
+        <v>212.21</v>
+      </c>
+      <c r="F901" t="n">
+        <v>5124234674176</v>
+      </c>
+      <c r="G901" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="H901" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I901" t="n">
+        <v>28.070107</v>
+      </c>
+      <c r="J901" t="n">
+        <v>13.334297</v>
+      </c>
+      <c r="K901" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L901" t="n">
+        <v>16.91334</v>
+      </c>
+      <c r="M901" t="n">
+        <v>0.03562508835587389</v>
+      </c>
+      <c r="N901" t="n">
+        <v>0.07499458083973422</v>
+      </c>
+      <c r="O901" t="n">
+        <v>0.04953000068664551</v>
+      </c>
+      <c r="P901" t="n">
+        <v>0.02546458015308871</v>
       </c>
     </row>
   </sheetData>
@@ -52034,12 +52556,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -52053,51 +52575,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>330.95</v>
+        <v>320.76</v>
       </c>
       <c r="F2" t="n">
-        <v>4047497068544</v>
+        <v>3922874073088</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>15.34777</v>
+        <v>15.35864</v>
       </c>
       <c r="I2" t="n">
-        <v>16.60562</v>
+        <v>16.09433</v>
       </c>
       <c r="J2" t="n">
-        <v>21.563395</v>
+        <v>20.884663</v>
       </c>
       <c r="K2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="L2" t="n">
-        <v>9.077833</v>
+        <v>8.798325999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06022057712645415</v>
+        <v>0.06213368250405288</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0463748904668379</v>
+        <v>0.04788203017832647</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005085108617634761</v>
+        <v>-0.001647970508319038</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -52111,10 +52633,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>532.95</v>
+        <v>521.08</v>
       </c>
       <c r="F3" t="n">
-        <v>3957444575232</v>
+        <v>3869303373824</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
@@ -52123,39 +52645,39 @@
         <v>23.70396</v>
       </c>
       <c r="I3" t="n">
-        <v>29.690807</v>
+        <v>29.029526</v>
       </c>
       <c r="J3" t="n">
-        <v>22.483585</v>
+        <v>21.982824</v>
       </c>
       <c r="K3" t="n">
         <v>1.73</v>
       </c>
       <c r="L3" t="n">
-        <v>11.9257965</v>
+        <v>11.660182</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03368045782906463</v>
+        <v>0.03444768557611115</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04447689276667604</v>
+        <v>0.04549005910800644</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.006983106317796618</v>
+        <v>-0.004039941578639066</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -52169,51 +52691,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>697.52</v>
+        <v>648.85</v>
       </c>
       <c r="F4" t="n">
-        <v>1776936550400</v>
+        <v>1652949385216</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>29.31</v>
       </c>
       <c r="H4" t="n">
-        <v>34.65077</v>
+        <v>34.80467</v>
       </c>
       <c r="I4" t="n">
-        <v>26.28184</v>
+        <v>22.137495</v>
       </c>
       <c r="J4" t="n">
-        <v>20.130001</v>
+        <v>18.642612</v>
       </c>
       <c r="K4" t="n">
         <v>0.92</v>
       </c>
       <c r="L4" t="n">
-        <v>7.7851477</v>
+        <v>7.241933</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03804908819818786</v>
+        <v>0.04517222778762425</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04967709886454869</v>
+        <v>0.05364054866301919</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.001782900219923965</v>
+        <v>0.004110547976373682</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -52227,51 +52749,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>262.37</v>
+        <v>250.38</v>
       </c>
       <c r="F5" t="n">
-        <v>2830004912128</v>
+        <v>2700677218304</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.44808</v>
+        <v>10.43091</v>
       </c>
       <c r="I5" t="n">
-        <v>21.124798</v>
+        <v>20.143202</v>
       </c>
       <c r="J5" t="n">
-        <v>25.11179</v>
+        <v>24.003658</v>
       </c>
       <c r="K5" t="n">
         <v>1.52</v>
       </c>
       <c r="L5" t="n">
-        <v>3.648418</v>
+        <v>3.4816897</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04733772916110836</v>
+        <v>0.0496445402987459</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03982193086099782</v>
+        <v>0.04166031631919483</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01163806822347484</v>
+        <v>-0.007869684367450683</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -52285,51 +52807,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>343.99</v>
+        <v>348.22</v>
       </c>
       <c r="F6" t="n">
-        <v>5020252110848</v>
+        <v>5081985449984</v>
       </c>
       <c r="G6" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
       <c r="H6" t="n">
         <v>9.5707</v>
       </c>
       <c r="I6" t="n">
-        <v>38.912895</v>
+        <v>39.436012</v>
       </c>
       <c r="J6" t="n">
-        <v>35.94199</v>
+        <v>36.383965</v>
       </c>
       <c r="K6" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="L6" t="n">
-        <v>10.754081</v>
+        <v>10.886322</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02569842146574028</v>
+        <v>0.02535753259433691</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02782261112241635</v>
+        <v>0.02748463614956062</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02363738796205631</v>
+        <v>-0.02204536453708489</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -52343,51 +52865,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221.97</v>
+        <v>212.21</v>
       </c>
       <c r="F7" t="n">
-        <v>5359909470208</v>
+        <v>5124234674176</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.56</v>
       </c>
       <c r="H7" t="n">
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>28.061947</v>
+        <v>28.070107</v>
       </c>
       <c r="J7" t="n">
-        <v>13.94757</v>
+        <v>13.334297</v>
       </c>
       <c r="K7" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="L7" t="n">
-        <v>17.691221</v>
+        <v>16.91334</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03563544623147272</v>
+        <v>0.03562508835587389</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07169707618146597</v>
+        <v>0.07499458083973422</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02023707709699331</v>
+        <v>0.02546458015308871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -52401,10 +52923,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>552.72</v>
+        <v>507.93</v>
       </c>
       <c r="F8" t="n">
-        <v>902301548544</v>
+        <v>829183033344</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -52413,39 +52935,39 @@
         <v>15.76289</v>
       </c>
       <c r="I8" t="n">
-        <v>140.99998</v>
+        <v>129.57397</v>
       </c>
       <c r="J8" t="n">
-        <v>35.064636</v>
+        <v>32.223152</v>
       </c>
       <c r="K8" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L8" t="n">
-        <v>21.844849</v>
+        <v>20.07464</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007092198581560284</v>
+        <v>0.007717598881735672</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02851876176002316</v>
+        <v>0.03103358730533735</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0229412373244495</v>
+        <v>-0.01849641338130816</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -52459,10 +52981,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>337.8</v>
+        <v>323.24</v>
       </c>
       <c r="F9" t="n">
-        <v>1612532154368</v>
+        <v>1543028080640</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -52471,39 +52993,39 @@
         <v>19.39695</v>
       </c>
       <c r="I9" t="n">
-        <v>43.14176</v>
+        <v>41.282246</v>
       </c>
       <c r="J9" t="n">
-        <v>17.415108</v>
+        <v>16.664474</v>
       </c>
       <c r="K9" t="n">
         <v>0.33</v>
       </c>
       <c r="L9" t="n">
-        <v>18.09719</v>
+        <v>17.317158</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02317939609236234</v>
+        <v>0.02422348719217918</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05742140319715808</v>
+        <v>0.06000788887513921</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00596140411268542</v>
+        <v>0.0104778881884937</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-21 17:45:39</t>
+          <t>2026-10-22 17:45:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -52517,40 +53039,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65.04000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="F10" t="n">
-        <v>270822637568</v>
+        <v>279192174592</v>
       </c>
       <c r="G10" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="H10" t="n">
-        <v>3.77848</v>
+        <v>3.7692</v>
       </c>
       <c r="I10" t="n">
-        <v>18.797688</v>
+        <v>18.781513</v>
       </c>
       <c r="J10" t="n">
-        <v>17.21327</v>
+        <v>17.788921</v>
       </c>
       <c r="K10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="L10" t="n">
-        <v>5.445353</v>
+        <v>5.613637</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0531980319803198</v>
+        <v>0.05324384787472036</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05809471094710947</v>
+        <v>0.05621476510067114</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05145999908447266</v>
+        <v>0.04953000068664551</v>
       </c>
       <c r="P10" t="n">
-        <v>0.006634711862636811</v>
+        <v>0.006684764414025636</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P901"/>
+  <dimension ref="A1:P910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52455,6 +52455,528 @@
       </c>
       <c r="P901" t="n">
         <v>0.02546458015308871</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E902" t="n">
+        <v>347.725</v>
+      </c>
+      <c r="F902" t="n">
+        <v>5074761285632</v>
+      </c>
+      <c r="G902" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H902" t="n">
+        <v>9.5707</v>
+      </c>
+      <c r="I902" t="n">
+        <v>39.87672</v>
+      </c>
+      <c r="J902" t="n">
+        <v>36.332245</v>
+      </c>
+      <c r="K902" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L902" t="n">
+        <v>10.870847</v>
+      </c>
+      <c r="M902" t="n">
+        <v>0.02507728808685024</v>
+      </c>
+      <c r="N902" t="n">
+        <v>0.02752376159321303</v>
+      </c>
+      <c r="O902" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P902" t="n">
+        <v>-0.02235623756755357</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E903" t="n">
+        <v>516.79</v>
+      </c>
+      <c r="F903" t="n">
+        <v>843646697472</v>
+      </c>
+      <c r="G903" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H903" t="n">
+        <v>15.76289</v>
+      </c>
+      <c r="I903" t="n">
+        <v>131.83418</v>
+      </c>
+      <c r="J903" t="n">
+        <v>32.78523</v>
+      </c>
+      <c r="K903" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L903" t="n">
+        <v>20.424807</v>
+      </c>
+      <c r="M903" t="n">
+        <v>0.007585286092997156</v>
+      </c>
+      <c r="N903" t="n">
+        <v>0.03050153834246019</v>
+      </c>
+      <c r="O903" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P903" t="n">
+        <v>-0.01937846081830641</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E904" t="n">
+        <v>248</v>
+      </c>
+      <c r="F904" t="n">
+        <v>2675005718528</v>
+      </c>
+      <c r="G904" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H904" t="n">
+        <v>10.43091</v>
+      </c>
+      <c r="I904" t="n">
+        <v>19.951729</v>
+      </c>
+      <c r="J904" t="n">
+        <v>23.77549</v>
+      </c>
+      <c r="K904" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L904" t="n">
+        <v>3.4485943</v>
+      </c>
+      <c r="M904" t="n">
+        <v>0.05012096774193548</v>
+      </c>
+      <c r="N904" t="n">
+        <v>0.04206012096774194</v>
+      </c>
+      <c r="O904" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P904" t="n">
+        <v>-0.007819878193024661</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E905" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="F905" t="n">
+        <v>1535581224960</v>
+      </c>
+      <c r="G905" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="H905" t="n">
+        <v>19.4315</v>
+      </c>
+      <c r="I905" t="n">
+        <v>42.94793</v>
+      </c>
+      <c r="J905" t="n">
+        <v>16.554564</v>
+      </c>
+      <c r="K905" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L905" t="n">
+        <v>17.233583</v>
+      </c>
+      <c r="M905" t="n">
+        <v>0.02328400895299677</v>
+      </c>
+      <c r="N905" t="n">
+        <v>0.06040630440189008</v>
+      </c>
+      <c r="O905" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P905" t="n">
+        <v>0.01052630524112348</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E906" t="n">
+        <v>317.28</v>
+      </c>
+      <c r="F906" t="n">
+        <v>3880313683968</v>
+      </c>
+      <c r="G906" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H906" t="n">
+        <v>15.35864</v>
+      </c>
+      <c r="I906" t="n">
+        <v>15.919719</v>
+      </c>
+      <c r="J906" t="n">
+        <v>20.65808</v>
+      </c>
+      <c r="K906" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L906" t="n">
+        <v>8.702870000000001</v>
+      </c>
+      <c r="M906" t="n">
+        <v>0.06281517902168432</v>
+      </c>
+      <c r="N906" t="n">
+        <v>0.04840721129601614</v>
+      </c>
+      <c r="O906" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P906" t="n">
+        <v>-0.001472787864750462</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E907" t="n">
+        <v>642.62</v>
+      </c>
+      <c r="F907" t="n">
+        <v>1637078401024</v>
+      </c>
+      <c r="G907" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H907" t="n">
+        <v>34.798</v>
+      </c>
+      <c r="I907" t="n">
+        <v>21.92494</v>
+      </c>
+      <c r="J907" t="n">
+        <v>18.467154</v>
+      </c>
+      <c r="K907" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L907" t="n">
+        <v>6.7758465</v>
+      </c>
+      <c r="M907" t="n">
+        <v>0.04561015841399271</v>
+      </c>
+      <c r="N907" t="n">
+        <v>0.0541501976284585</v>
+      </c>
+      <c r="O907" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P907" t="n">
+        <v>0.004270198467691895</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E908" t="n">
+        <v>524.51</v>
+      </c>
+      <c r="F908" t="n">
+        <v>3894773022720</v>
+      </c>
+      <c r="G908" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H908" t="n">
+        <v>23.70244</v>
+      </c>
+      <c r="I908" t="n">
+        <v>29.220612</v>
+      </c>
+      <c r="J908" t="n">
+        <v>22.128946</v>
+      </c>
+      <c r="K908" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L908" t="n">
+        <v>11.736936</v>
+      </c>
+      <c r="M908" t="n">
+        <v>0.0342224171131151</v>
+      </c>
+      <c r="N908" t="n">
+        <v>0.0451896817982498</v>
+      </c>
+      <c r="O908" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P908" t="n">
+        <v>-0.004690317362516808</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E909" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="F909" t="n">
+        <v>274195415040</v>
+      </c>
+      <c r="G909" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H909" t="n">
+        <v>3.7692</v>
+      </c>
+      <c r="I909" t="n">
+        <v>19.031792</v>
+      </c>
+      <c r="J909" t="n">
+        <v>17.47055</v>
+      </c>
+      <c r="K909" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L909" t="n">
+        <v>5.513169</v>
+      </c>
+      <c r="M909" t="n">
+        <v>0.05254365983295368</v>
+      </c>
+      <c r="N909" t="n">
+        <v>0.05723917995444192</v>
+      </c>
+      <c r="O909" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P909" t="n">
+        <v>0.00735918079367532</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:51:08</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E910" t="n">
+        <v>210.96</v>
+      </c>
+      <c r="F910" t="n">
+        <v>5094050889728</v>
+      </c>
+      <c r="G910" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H910" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I910" t="n">
+        <v>26.67004</v>
+      </c>
+      <c r="J910" t="n">
+        <v>13.255753</v>
+      </c>
+      <c r="K910" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L910" t="n">
+        <v>16.813713</v>
+      </c>
+      <c r="M910" t="n">
+        <v>0.03749525976488434</v>
+      </c>
+      <c r="N910" t="n">
+        <v>0.07543894577171027</v>
+      </c>
+      <c r="O910" t="n">
+        <v>0.0498799991607666</v>
+      </c>
+      <c r="P910" t="n">
+        <v>0.02555894661094367</v>
       </c>
     </row>
   </sheetData>
@@ -52556,12 +53078,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -52575,10 +53097,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>320.76</v>
+        <v>317.28</v>
       </c>
       <c r="F2" t="n">
-        <v>3922874073088</v>
+        <v>3880313683968</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -52587,39 +53109,39 @@
         <v>15.35864</v>
       </c>
       <c r="I2" t="n">
-        <v>16.09433</v>
+        <v>15.919719</v>
       </c>
       <c r="J2" t="n">
-        <v>20.884663</v>
+        <v>20.65808</v>
       </c>
       <c r="K2" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="L2" t="n">
-        <v>8.798325999999999</v>
+        <v>8.702870000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06213368250405288</v>
+        <v>0.06281517902168432</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04788203017832647</v>
+        <v>0.04840721129601614</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.001647970508319038</v>
+        <v>-0.001472787864750462</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -52633,51 +53155,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>521.08</v>
+        <v>524.51</v>
       </c>
       <c r="F3" t="n">
-        <v>3869303373824</v>
+        <v>3894773022720</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.70396</v>
+        <v>23.70244</v>
       </c>
       <c r="I3" t="n">
-        <v>29.029526</v>
+        <v>29.220612</v>
       </c>
       <c r="J3" t="n">
-        <v>21.982824</v>
+        <v>22.128946</v>
       </c>
       <c r="K3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="L3" t="n">
-        <v>11.660182</v>
+        <v>11.736936</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03444768557611115</v>
+        <v>0.0342224171131151</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04549005910800644</v>
+        <v>0.0451896817982498</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.004039941578639066</v>
+        <v>-0.004690317362516808</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -52691,51 +53213,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>648.85</v>
+        <v>642.62</v>
       </c>
       <c r="F4" t="n">
-        <v>1652949385216</v>
+        <v>1637078401024</v>
       </c>
       <c r="G4" t="n">
         <v>29.31</v>
       </c>
       <c r="H4" t="n">
-        <v>34.80467</v>
+        <v>34.798</v>
       </c>
       <c r="I4" t="n">
-        <v>22.137495</v>
+        <v>21.92494</v>
       </c>
       <c r="J4" t="n">
-        <v>18.642612</v>
+        <v>18.467154</v>
       </c>
       <c r="K4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="L4" t="n">
-        <v>7.241933</v>
+        <v>6.7758465</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04517222778762425</v>
+        <v>0.04561015841399271</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05364054866301919</v>
+        <v>0.0541501976284585</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004110547976373682</v>
+        <v>0.004270198467691895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -52749,10 +53271,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>250.38</v>
+        <v>248</v>
       </c>
       <c r="F5" t="n">
-        <v>2700677218304</v>
+        <v>2675005718528</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -52761,39 +53283,39 @@
         <v>10.43091</v>
       </c>
       <c r="I5" t="n">
-        <v>20.143202</v>
+        <v>19.951729</v>
       </c>
       <c r="J5" t="n">
-        <v>24.003658</v>
+        <v>23.77549</v>
       </c>
       <c r="K5" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4816897</v>
+        <v>3.4485943</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0496445402987459</v>
+        <v>0.05012096774193548</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04166031631919483</v>
+        <v>0.04206012096774194</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007869684367450683</v>
+        <v>-0.007819878193024661</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -52807,51 +53329,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>348.22</v>
+        <v>347.725</v>
       </c>
       <c r="F6" t="n">
-        <v>5081985449984</v>
+        <v>5074761285632</v>
       </c>
       <c r="G6" t="n">
-        <v>8.83</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.5707</v>
       </c>
       <c r="I6" t="n">
-        <v>39.436012</v>
+        <v>39.87672</v>
       </c>
       <c r="J6" t="n">
-        <v>36.383965</v>
+        <v>36.332245</v>
       </c>
       <c r="K6" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="L6" t="n">
-        <v>10.886322</v>
+        <v>10.870847</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02535753259433691</v>
+        <v>0.02507728808685024</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02748463614956062</v>
+        <v>0.02752376159321303</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02204536453708489</v>
+        <v>-0.02235623756755357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -52865,51 +53387,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>212.21</v>
+        <v>210.96</v>
       </c>
       <c r="F7" t="n">
-        <v>5124234674176</v>
+        <v>5094050889728</v>
       </c>
       <c r="G7" t="n">
-        <v>7.56</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>28.070107</v>
+        <v>26.67004</v>
       </c>
       <c r="J7" t="n">
-        <v>13.334297</v>
+        <v>13.255753</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>16.91334</v>
+        <v>16.813713</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03562508835587389</v>
+        <v>0.03749525976488434</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07499458083973422</v>
+        <v>0.07543894577171027</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02546458015308871</v>
+        <v>0.02555894661094367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -52923,10 +53445,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>507.93</v>
+        <v>516.79</v>
       </c>
       <c r="F8" t="n">
-        <v>829183033344</v>
+        <v>843646697472</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -52935,39 +53457,39 @@
         <v>15.76289</v>
       </c>
       <c r="I8" t="n">
-        <v>129.57397</v>
+        <v>131.83418</v>
       </c>
       <c r="J8" t="n">
-        <v>32.223152</v>
+        <v>32.78523</v>
       </c>
       <c r="K8" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="L8" t="n">
-        <v>20.07464</v>
+        <v>20.424807</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007717598881735672</v>
+        <v>0.007585286092997156</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03103358730533735</v>
+        <v>0.03050153834246019</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01849641338130816</v>
+        <v>-0.01937846081830641</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -52981,51 +53503,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>323.24</v>
+        <v>321.68</v>
       </c>
       <c r="F9" t="n">
-        <v>1543028080640</v>
+        <v>1535581224960</v>
       </c>
       <c r="G9" t="n">
-        <v>7.83</v>
+        <v>7.49</v>
       </c>
       <c r="H9" t="n">
-        <v>19.39695</v>
+        <v>19.4315</v>
       </c>
       <c r="I9" t="n">
-        <v>41.282246</v>
+        <v>42.94793</v>
       </c>
       <c r="J9" t="n">
-        <v>16.664474</v>
+        <v>16.554564</v>
       </c>
       <c r="K9" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="L9" t="n">
-        <v>17.317158</v>
+        <v>17.233583</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02422348719217918</v>
+        <v>0.02328400895299677</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06000788887513921</v>
+        <v>0.06040630440189008</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0104778881884937</v>
+        <v>0.01052630524112348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:15</t>
+          <t>2026-10-23 17:51:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -53039,40 +53561,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67.05</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>279192174592</v>
+        <v>274195415040</v>
       </c>
       <c r="G10" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="H10" t="n">
         <v>3.7692</v>
       </c>
       <c r="I10" t="n">
-        <v>18.781513</v>
+        <v>19.031792</v>
       </c>
       <c r="J10" t="n">
-        <v>17.788921</v>
+        <v>17.47055</v>
       </c>
       <c r="K10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="L10" t="n">
-        <v>5.613637</v>
+        <v>5.513169</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05324384787472036</v>
+        <v>0.05254365983295368</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05621476510067114</v>
+        <v>0.05723917995444192</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04953000068664551</v>
+        <v>0.0498799991607666</v>
       </c>
       <c r="P10" t="n">
-        <v>0.006684764414025636</v>
+        <v>0.00735918079367532</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P910"/>
+  <dimension ref="A1:P919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52977,6 +52977,528 @@
       </c>
       <c r="P910" t="n">
         <v>0.02555894661094367</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E911" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="F911" t="n">
+        <v>5019084521472</v>
+      </c>
+      <c r="G911" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H911" t="n">
+        <v>9.56195</v>
+      </c>
+      <c r="I911" t="n">
+        <v>39.43922</v>
+      </c>
+      <c r="J911" t="n">
+        <v>35.966515</v>
+      </c>
+      <c r="K911" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L911" t="n">
+        <v>10.751579</v>
+      </c>
+      <c r="M911" t="n">
+        <v>0.02535547090808642</v>
+      </c>
+      <c r="N911" t="n">
+        <v>0.0278036404873368</v>
+      </c>
+      <c r="O911" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P911" t="n">
+        <v>-0.02205636012301476</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E912" t="n">
+        <v>531.28</v>
+      </c>
+      <c r="F912" t="n">
+        <v>867301392384</v>
+      </c>
+      <c r="G912" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H912" t="n">
+        <v>15.76289</v>
+      </c>
+      <c r="I912" t="n">
+        <v>135.53062</v>
+      </c>
+      <c r="J912" t="n">
+        <v>33.704483</v>
+      </c>
+      <c r="K912" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L912" t="n">
+        <v>20.99749</v>
+      </c>
+      <c r="M912" t="n">
+        <v>0.007378406866435778</v>
+      </c>
+      <c r="N912" t="n">
+        <v>0.02966964689052854</v>
+      </c>
+      <c r="O912" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P912" t="n">
+        <v>-0.02019035371982303</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E913" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="F913" t="n">
+        <v>2686762614784</v>
+      </c>
+      <c r="G913" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H913" t="n">
+        <v>10.43008</v>
+      </c>
+      <c r="I913" t="n">
+        <v>20.03942</v>
+      </c>
+      <c r="J913" t="n">
+        <v>23.881886</v>
+      </c>
+      <c r="K913" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L913" t="n">
+        <v>3.463751</v>
+      </c>
+      <c r="M913" t="n">
+        <v>0.04990164197679554</v>
+      </c>
+      <c r="N913" t="n">
+        <v>0.041872736761813</v>
+      </c>
+      <c r="O913" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P913" t="n">
+        <v>-0.00798726384853856</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E914" t="n">
+        <v>329.17</v>
+      </c>
+      <c r="F914" t="n">
+        <v>1571335831552</v>
+      </c>
+      <c r="G914" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H914" t="n">
+        <v>19.4315</v>
+      </c>
+      <c r="I914" t="n">
+        <v>42.039593</v>
+      </c>
+      <c r="J914" t="n">
+        <v>16.940022</v>
+      </c>
+      <c r="K914" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L914" t="n">
+        <v>17.634851</v>
+      </c>
+      <c r="M914" t="n">
+        <v>0.02378710089011757</v>
+      </c>
+      <c r="N914" t="n">
+        <v>0.05903180727283774</v>
+      </c>
+      <c r="O914" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P914" t="n">
+        <v>0.009171806662486175</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E915" t="n">
+        <v>314.19</v>
+      </c>
+      <c r="F915" t="n">
+        <v>3842523267072</v>
+      </c>
+      <c r="G915" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H915" t="n">
+        <v>15.35864</v>
+      </c>
+      <c r="I915" t="n">
+        <v>15.764676</v>
+      </c>
+      <c r="J915" t="n">
+        <v>20.45689</v>
+      </c>
+      <c r="K915" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L915" t="n">
+        <v>8.618112999999999</v>
+      </c>
+      <c r="M915" t="n">
+        <v>0.06343295458162258</v>
+      </c>
+      <c r="N915" t="n">
+        <v>0.04888328718291479</v>
+      </c>
+      <c r="O915" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P915" t="n">
+        <v>-0.0009767134274367706</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E916" t="n">
+        <v>630.5599999999999</v>
+      </c>
+      <c r="F916" t="n">
+        <v>1606355517440</v>
+      </c>
+      <c r="G916" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H916" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="I916" t="n">
+        <v>21.513477</v>
+      </c>
+      <c r="J916" t="n">
+        <v>17.9903</v>
+      </c>
+      <c r="K916" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L916" t="n">
+        <v>6.648685</v>
+      </c>
+      <c r="M916" t="n">
+        <v>0.0464824917533621</v>
+      </c>
+      <c r="N916" t="n">
+        <v>0.05558551129155037</v>
+      </c>
+      <c r="O916" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P916" t="n">
+        <v>0.005725510681198809</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E917" t="n">
+        <v>532.6</v>
+      </c>
+      <c r="F917" t="n">
+        <v>3954845417472</v>
+      </c>
+      <c r="G917" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H917" t="n">
+        <v>23.68972</v>
+      </c>
+      <c r="I917" t="n">
+        <v>29.671307</v>
+      </c>
+      <c r="J917" t="n">
+        <v>22.482325</v>
+      </c>
+      <c r="K917" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L917" t="n">
+        <v>11.917964</v>
+      </c>
+      <c r="M917" t="n">
+        <v>0.03370259106271122</v>
+      </c>
+      <c r="N917" t="n">
+        <v>0.04447938415321066</v>
+      </c>
+      <c r="O917" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P917" t="n">
+        <v>-0.005380616457140899</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E918" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="F918" t="n">
+        <v>266075750400</v>
+      </c>
+      <c r="G918" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H918" t="n">
+        <v>3.76991</v>
+      </c>
+      <c r="I918" t="n">
+        <v>18.468208</v>
+      </c>
+      <c r="J918" t="n">
+        <v>16.950006</v>
+      </c>
+      <c r="K918" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L918" t="n">
+        <v>5.349909</v>
+      </c>
+      <c r="M918" t="n">
+        <v>0.0541471048513302</v>
+      </c>
+      <c r="N918" t="n">
+        <v>0.05899702660406886</v>
+      </c>
+      <c r="O918" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P918" t="n">
+        <v>0.009137025993717296</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:32:21</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E919" t="n">
+        <v>216</v>
+      </c>
+      <c r="F919" t="n">
+        <v>5215751766016</v>
+      </c>
+      <c r="G919" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H919" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I919" t="n">
+        <v>27.307207</v>
+      </c>
+      <c r="J919" t="n">
+        <v>13.572443</v>
+      </c>
+      <c r="K919" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L919" t="n">
+        <v>17.215406</v>
+      </c>
+      <c r="M919" t="n">
+        <v>0.03662037037037037</v>
+      </c>
+      <c r="N919" t="n">
+        <v>0.0736787037037037</v>
+      </c>
+      <c r="O919" t="n">
+        <v>0.04986000061035156</v>
+      </c>
+      <c r="P919" t="n">
+        <v>0.02381870309335214</v>
       </c>
     </row>
   </sheetData>
@@ -53078,12 +53600,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -53097,10 +53619,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>317.28</v>
+        <v>314.19</v>
       </c>
       <c r="F2" t="n">
-        <v>3880313683968</v>
+        <v>3842523267072</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -53109,39 +53631,39 @@
         <v>15.35864</v>
       </c>
       <c r="I2" t="n">
-        <v>15.919719</v>
+        <v>15.764676</v>
       </c>
       <c r="J2" t="n">
-        <v>20.65808</v>
+        <v>20.45689</v>
       </c>
       <c r="K2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="L2" t="n">
-        <v>8.702870000000001</v>
+        <v>8.618112999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06281517902168432</v>
+        <v>0.06343295458162258</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04840721129601614</v>
+        <v>0.04888328718291479</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.001472787864750462</v>
+        <v>-0.0009767134274367706</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -53155,51 +53677,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>524.51</v>
+        <v>532.6</v>
       </c>
       <c r="F3" t="n">
-        <v>3894773022720</v>
+        <v>3954845417472</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.70244</v>
+        <v>23.68972</v>
       </c>
       <c r="I3" t="n">
-        <v>29.220612</v>
+        <v>29.671307</v>
       </c>
       <c r="J3" t="n">
-        <v>22.128946</v>
+        <v>22.482325</v>
       </c>
       <c r="K3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="L3" t="n">
-        <v>11.736936</v>
+        <v>11.917964</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0342224171131151</v>
+        <v>0.03370259106271122</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0451896817982498</v>
+        <v>0.04447938415321066</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.004690317362516808</v>
+        <v>-0.005380616457140899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -53213,51 +53735,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>642.62</v>
+        <v>630.5599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1637078401024</v>
+        <v>1606355517440</v>
       </c>
       <c r="G4" t="n">
         <v>29.31</v>
       </c>
       <c r="H4" t="n">
-        <v>34.798</v>
+        <v>35.05</v>
       </c>
       <c r="I4" t="n">
-        <v>21.92494</v>
+        <v>21.513477</v>
       </c>
       <c r="J4" t="n">
-        <v>18.467154</v>
+        <v>17.9903</v>
       </c>
       <c r="K4" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7758465</v>
+        <v>6.648685</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04561015841399271</v>
+        <v>0.0464824917533621</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0541501976284585</v>
+        <v>0.05558551129155037</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004270198467691895</v>
+        <v>0.005725510681198809</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -53271,51 +53793,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248</v>
+        <v>249.09</v>
       </c>
       <c r="F5" t="n">
-        <v>2675005718528</v>
+        <v>2686762614784</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.43091</v>
+        <v>10.43008</v>
       </c>
       <c r="I5" t="n">
-        <v>19.951729</v>
+        <v>20.03942</v>
       </c>
       <c r="J5" t="n">
-        <v>23.77549</v>
+        <v>23.881886</v>
       </c>
       <c r="K5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4485943</v>
+        <v>3.463751</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05012096774193548</v>
+        <v>0.04990164197679554</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04206012096774194</v>
+        <v>0.041872736761813</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007819878193024661</v>
+        <v>-0.00798726384853856</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -53329,51 +53851,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>347.725</v>
+        <v>343.91</v>
       </c>
       <c r="F6" t="n">
-        <v>5074761285632</v>
+        <v>5019084521472</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5707</v>
+        <v>9.56195</v>
       </c>
       <c r="I6" t="n">
-        <v>39.87672</v>
+        <v>39.43922</v>
       </c>
       <c r="J6" t="n">
-        <v>36.332245</v>
+        <v>35.966515</v>
       </c>
       <c r="K6" t="n">
         <v>2.79</v>
       </c>
       <c r="L6" t="n">
-        <v>10.870847</v>
+        <v>10.751579</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02507728808685024</v>
+        <v>0.02535547090808642</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02752376159321303</v>
+        <v>0.0278036404873368</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02235623756755357</v>
+        <v>-0.02205636012301476</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -53387,10 +53909,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210.96</v>
+        <v>216</v>
       </c>
       <c r="F7" t="n">
-        <v>5094050889728</v>
+        <v>5215751766016</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -53399,39 +53921,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>26.67004</v>
+        <v>27.307207</v>
       </c>
       <c r="J7" t="n">
-        <v>13.255753</v>
+        <v>13.572443</v>
       </c>
       <c r="K7" t="n">
         <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>16.813713</v>
+        <v>17.215406</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03749525976488434</v>
+        <v>0.03662037037037037</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07543894577171027</v>
+        <v>0.0736787037037037</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02555894661094367</v>
+        <v>0.02381870309335214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -53445,10 +53967,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>516.79</v>
+        <v>531.28</v>
       </c>
       <c r="F8" t="n">
-        <v>843646697472</v>
+        <v>867301392384</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -53457,39 +53979,39 @@
         <v>15.76289</v>
       </c>
       <c r="I8" t="n">
-        <v>131.83418</v>
+        <v>135.53062</v>
       </c>
       <c r="J8" t="n">
-        <v>32.78523</v>
+        <v>33.704483</v>
       </c>
       <c r="K8" t="n">
         <v>0.51</v>
       </c>
       <c r="L8" t="n">
-        <v>20.424807</v>
+        <v>20.99749</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007585286092997156</v>
+        <v>0.007378406866435778</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03050153834246019</v>
+        <v>0.02966964689052854</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01937846081830641</v>
+        <v>-0.02019035371982303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -53503,51 +54025,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>321.68</v>
+        <v>329.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1535581224960</v>
+        <v>1571335831552</v>
       </c>
       <c r="G9" t="n">
-        <v>7.49</v>
+        <v>7.83</v>
       </c>
       <c r="H9" t="n">
         <v>19.4315</v>
       </c>
       <c r="I9" t="n">
-        <v>42.94793</v>
+        <v>42.039593</v>
       </c>
       <c r="J9" t="n">
-        <v>16.554564</v>
+        <v>16.940022</v>
       </c>
       <c r="K9" t="n">
         <v>0.32</v>
       </c>
       <c r="L9" t="n">
-        <v>17.233583</v>
+        <v>17.634851</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02328400895299677</v>
+        <v>0.02378710089011757</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06040630440189008</v>
+        <v>0.05903180727283774</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01052630524112348</v>
+        <v>0.009171806662486175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-23 17:51:08</t>
+          <t>2026-10-26 18:32:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -53561,40 +54083,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65.84999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="F10" t="n">
-        <v>274195415040</v>
+        <v>266075750400</v>
       </c>
       <c r="G10" t="n">
         <v>3.46</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7692</v>
+        <v>3.76991</v>
       </c>
       <c r="I10" t="n">
-        <v>19.031792</v>
+        <v>18.468208</v>
       </c>
       <c r="J10" t="n">
-        <v>17.47055</v>
+        <v>16.950006</v>
       </c>
       <c r="K10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="L10" t="n">
-        <v>5.513169</v>
+        <v>5.349909</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05254365983295368</v>
+        <v>0.0541471048513302</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05723917995444192</v>
+        <v>0.05899702660406886</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04986000061035156</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00735918079367532</v>
+        <v>0.009137025993717296</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P919"/>
+  <dimension ref="A1:P928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53499,6 +53499,528 @@
       </c>
       <c r="P919" t="n">
         <v>0.02381870309335214</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E920" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="F920" t="n">
+        <v>5065640247296</v>
+      </c>
+      <c r="G920" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H920" t="n">
+        <v>9.56245</v>
+      </c>
+      <c r="I920" t="n">
+        <v>39.805046</v>
+      </c>
+      <c r="J920" t="n">
+        <v>36.29823</v>
+      </c>
+      <c r="K920" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L920" t="n">
+        <v>10.851309</v>
+      </c>
+      <c r="M920" t="n">
+        <v>0.02512244309997119</v>
+      </c>
+      <c r="N920" t="n">
+        <v>0.02754955344281187</v>
+      </c>
+      <c r="O920" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P920" t="n">
+        <v>-0.02238044686236391</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E921" t="n">
+        <v>560.26</v>
+      </c>
+      <c r="F921" t="n">
+        <v>914610454528</v>
+      </c>
+      <c r="G921" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H921" t="n">
+        <v>15.75581</v>
+      </c>
+      <c r="I921" t="n">
+        <v>142.92346</v>
+      </c>
+      <c r="J921" t="n">
+        <v>35.55895</v>
+      </c>
+      <c r="K921" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L921" t="n">
+        <v>22.142849</v>
+      </c>
+      <c r="M921" t="n">
+        <v>0.006996751508228323</v>
+      </c>
+      <c r="N921" t="n">
+        <v>0.02812231820940278</v>
+      </c>
+      <c r="O921" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P921" t="n">
+        <v>-0.02180768209577301</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E922" t="n">
+        <v>253.1</v>
+      </c>
+      <c r="F922" t="n">
+        <v>2730015850496</v>
+      </c>
+      <c r="G922" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H922" t="n">
+        <v>10.43295</v>
+      </c>
+      <c r="I922" t="n">
+        <v>20.362028</v>
+      </c>
+      <c r="J922" t="n">
+        <v>24.259678</v>
+      </c>
+      <c r="K922" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L922" t="n">
+        <v>3.519513</v>
+      </c>
+      <c r="M922" t="n">
+        <v>0.04911102331094429</v>
+      </c>
+      <c r="N922" t="n">
+        <v>0.04122066376926116</v>
+      </c>
+      <c r="O922" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P922" t="n">
+        <v>-0.008709336535914623</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E923" t="n">
+        <v>342.33</v>
+      </c>
+      <c r="F923" t="n">
+        <v>1634156675072</v>
+      </c>
+      <c r="G923" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H923" t="n">
+        <v>19.4315</v>
+      </c>
+      <c r="I923" t="n">
+        <v>43.720306</v>
+      </c>
+      <c r="J923" t="n">
+        <v>17.617271</v>
+      </c>
+      <c r="K923" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L923" t="n">
+        <v>18.33988</v>
+      </c>
+      <c r="M923" t="n">
+        <v>0.02287266672508983</v>
+      </c>
+      <c r="N923" t="n">
+        <v>0.0567624806473286</v>
+      </c>
+      <c r="O923" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P923" t="n">
+        <v>0.006832480342152822</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E924" t="n">
+        <v>316.83</v>
+      </c>
+      <c r="F924" t="n">
+        <v>3874810232832</v>
+      </c>
+      <c r="G924" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H924" t="n">
+        <v>15.35864</v>
+      </c>
+      <c r="I924" t="n">
+        <v>15.89714</v>
+      </c>
+      <c r="J924" t="n">
+        <v>20.628778</v>
+      </c>
+      <c r="K924" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L924" t="n">
+        <v>8.690526999999999</v>
+      </c>
+      <c r="M924" t="n">
+        <v>0.06290439667960736</v>
+      </c>
+      <c r="N924" t="n">
+        <v>0.04847596502856422</v>
+      </c>
+      <c r="O924" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P924" t="n">
+        <v>-0.001454035276611566</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E925" t="n">
+        <v>620.1900000000001</v>
+      </c>
+      <c r="F925" t="n">
+        <v>1585722294272</v>
+      </c>
+      <c r="G925" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H925" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="I925" t="n">
+        <v>21.159674</v>
+      </c>
+      <c r="J925" t="n">
+        <v>17.624043</v>
+      </c>
+      <c r="K925" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L925" t="n">
+        <v>6.5632844</v>
+      </c>
+      <c r="M925" t="n">
+        <v>0.04725971073380737</v>
+      </c>
+      <c r="N925" t="n">
+        <v>0.05674067624437672</v>
+      </c>
+      <c r="O925" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P925" t="n">
+        <v>0.006810675939200934</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E926" t="n">
+        <v>531.33</v>
+      </c>
+      <c r="F926" t="n">
+        <v>3945415311360</v>
+      </c>
+      <c r="G926" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="H926" t="n">
+        <v>23.68972</v>
+      </c>
+      <c r="I926" t="n">
+        <v>29.145914</v>
+      </c>
+      <c r="J926" t="n">
+        <v>22.428717</v>
+      </c>
+      <c r="K926" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L926" t="n">
+        <v>11.889546</v>
+      </c>
+      <c r="M926" t="n">
+        <v>0.03431012741610675</v>
+      </c>
+      <c r="N926" t="n">
+        <v>0.04458570003575932</v>
+      </c>
+      <c r="O926" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P926" t="n">
+        <v>-0.005344300269416465</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E927" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="F927" t="n">
+        <v>260329504768</v>
+      </c>
+      <c r="G927" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H927" t="n">
+        <v>3.77134</v>
+      </c>
+      <c r="I927" t="n">
+        <v>18.069365</v>
+      </c>
+      <c r="J927" t="n">
+        <v>16.577663</v>
+      </c>
+      <c r="K927" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L927" t="n">
+        <v>5.2343707</v>
+      </c>
+      <c r="M927" t="n">
+        <v>0.05534229046705054</v>
+      </c>
+      <c r="N927" t="n">
+        <v>0.06032213691618682</v>
+      </c>
+      <c r="O927" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P927" t="n">
+        <v>0.01039213661101104</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:29:43</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E928" t="n">
+        <v>217.94</v>
+      </c>
+      <c r="F928" t="n">
+        <v>5262596898816</v>
+      </c>
+      <c r="G928" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H928" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I928" t="n">
+        <v>27.552465</v>
+      </c>
+      <c r="J928" t="n">
+        <v>13.694344</v>
+      </c>
+      <c r="K928" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L928" t="n">
+        <v>17.370026</v>
+      </c>
+      <c r="M928" t="n">
+        <v>0.03629439295218868</v>
+      </c>
+      <c r="N928" t="n">
+        <v>0.07302285032577774</v>
+      </c>
+      <c r="O928" t="n">
+        <v>0.04993000030517578</v>
+      </c>
+      <c r="P928" t="n">
+        <v>0.02309285002060196</v>
       </c>
     </row>
   </sheetData>
@@ -53600,12 +54122,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -53619,10 +54141,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314.19</v>
+        <v>316.83</v>
       </c>
       <c r="F2" t="n">
-        <v>3842523267072</v>
+        <v>3874810232832</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -53631,39 +54153,39 @@
         <v>15.35864</v>
       </c>
       <c r="I2" t="n">
-        <v>15.764676</v>
+        <v>15.89714</v>
       </c>
       <c r="J2" t="n">
-        <v>20.45689</v>
+        <v>20.628778</v>
       </c>
       <c r="K2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="L2" t="n">
-        <v>8.618112999999999</v>
+        <v>8.690526999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06343295458162258</v>
+        <v>0.06290439667960736</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04888328718291479</v>
+        <v>0.04847596502856422</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0009767134274367706</v>
+        <v>-0.001454035276611566</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -53677,51 +54199,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>532.6</v>
+        <v>531.33</v>
       </c>
       <c r="F3" t="n">
-        <v>3954845417472</v>
+        <v>3945415311360</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>18.23</v>
       </c>
       <c r="H3" t="n">
         <v>23.68972</v>
       </c>
       <c r="I3" t="n">
-        <v>29.671307</v>
+        <v>29.145914</v>
       </c>
       <c r="J3" t="n">
-        <v>22.482325</v>
+        <v>22.428717</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="L3" t="n">
-        <v>11.917964</v>
+        <v>11.889546</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03370259106271122</v>
+        <v>0.03431012741610675</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04447938415321066</v>
+        <v>0.04458570003575932</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.005380616457140899</v>
+        <v>-0.005344300269416465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -53735,51 +54257,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>630.5599999999999</v>
+        <v>620.1900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1606355517440</v>
+        <v>1585722294272</v>
       </c>
       <c r="G4" t="n">
         <v>29.31</v>
       </c>
       <c r="H4" t="n">
-        <v>35.05</v>
+        <v>35.19</v>
       </c>
       <c r="I4" t="n">
-        <v>21.513477</v>
+        <v>21.159674</v>
       </c>
       <c r="J4" t="n">
-        <v>17.9903</v>
+        <v>17.624043</v>
       </c>
       <c r="K4" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.648685</v>
+        <v>6.5632844</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0464824917533621</v>
+        <v>0.04725971073380737</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05558551129155037</v>
+        <v>0.05674067624437672</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005725510681198809</v>
+        <v>0.006810675939200934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -53793,51 +54315,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2686762614784</v>
+        <v>2730015850496</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.43008</v>
+        <v>10.43295</v>
       </c>
       <c r="I5" t="n">
-        <v>20.03942</v>
+        <v>20.362028</v>
       </c>
       <c r="J5" t="n">
-        <v>23.881886</v>
+        <v>24.259678</v>
       </c>
       <c r="K5" t="n">
         <v>1.44</v>
       </c>
       <c r="L5" t="n">
-        <v>3.463751</v>
+        <v>3.519513</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04990164197679554</v>
+        <v>0.04911102331094429</v>
       </c>
       <c r="N5" t="n">
-        <v>0.041872736761813</v>
+        <v>0.04122066376926116</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00798726384853856</v>
+        <v>-0.008709336535914623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -53851,51 +54373,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>343.91</v>
+        <v>347.1</v>
       </c>
       <c r="F6" t="n">
-        <v>5019084521472</v>
+        <v>5065640247296</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.56195</v>
+        <v>9.56245</v>
       </c>
       <c r="I6" t="n">
-        <v>39.43922</v>
+        <v>39.805046</v>
       </c>
       <c r="J6" t="n">
-        <v>35.966515</v>
+        <v>36.29823</v>
       </c>
       <c r="K6" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="L6" t="n">
-        <v>10.751579</v>
+        <v>10.851309</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02535547090808642</v>
+        <v>0.02512244309997119</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0278036404873368</v>
+        <v>0.02754955344281187</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02205636012301476</v>
+        <v>-0.02238044686236391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -53909,10 +54431,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>216</v>
+        <v>217.94</v>
       </c>
       <c r="F7" t="n">
-        <v>5215751766016</v>
+        <v>5262596898816</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -53921,39 +54443,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.307207</v>
+        <v>27.552465</v>
       </c>
       <c r="J7" t="n">
-        <v>13.572443</v>
+        <v>13.694344</v>
       </c>
       <c r="K7" t="n">
         <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>17.215406</v>
+        <v>17.370026</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03662037037037037</v>
+        <v>0.03629439295218868</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0736787037037037</v>
+        <v>0.07302285032577774</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02381870309335214</v>
+        <v>0.02309285002060196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -53967,51 +54489,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>531.28</v>
+        <v>560.26</v>
       </c>
       <c r="F8" t="n">
-        <v>867301392384</v>
+        <v>914610454528</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.76289</v>
+        <v>15.75581</v>
       </c>
       <c r="I8" t="n">
-        <v>135.53062</v>
+        <v>142.92346</v>
       </c>
       <c r="J8" t="n">
-        <v>33.704483</v>
+        <v>35.55895</v>
       </c>
       <c r="K8" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>20.99749</v>
+        <v>22.142849</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007378406866435778</v>
+        <v>0.006996751508228323</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02966964689052854</v>
+        <v>0.02812231820940278</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02019035371982303</v>
+        <v>-0.02180768209577301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -54025,10 +54547,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>329.17</v>
+        <v>342.33</v>
       </c>
       <c r="F9" t="n">
-        <v>1571335831552</v>
+        <v>1634156675072</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -54037,39 +54559,39 @@
         <v>19.4315</v>
       </c>
       <c r="I9" t="n">
-        <v>42.039593</v>
+        <v>43.720306</v>
       </c>
       <c r="J9" t="n">
-        <v>16.940022</v>
+        <v>17.617271</v>
       </c>
       <c r="K9" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="L9" t="n">
-        <v>17.634851</v>
+        <v>18.33988</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02378710089011757</v>
+        <v>0.02287266672508983</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05903180727283774</v>
+        <v>0.0567624806473286</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009171806662486175</v>
+        <v>0.006832480342152822</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-26 18:32:21</t>
+          <t>2026-10-27 18:29:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -54083,40 +54605,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.9</v>
+        <v>62.52</v>
       </c>
       <c r="F10" t="n">
-        <v>266075750400</v>
+        <v>260329504768</v>
       </c>
       <c r="G10" t="n">
         <v>3.46</v>
       </c>
       <c r="H10" t="n">
-        <v>3.76991</v>
+        <v>3.77134</v>
       </c>
       <c r="I10" t="n">
-        <v>18.468208</v>
+        <v>18.069365</v>
       </c>
       <c r="J10" t="n">
-        <v>16.950006</v>
+        <v>16.577663</v>
       </c>
       <c r="K10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="L10" t="n">
-        <v>5.349909</v>
+        <v>5.2343707</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0541471048513302</v>
+        <v>0.05534229046705054</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05899702660406886</v>
+        <v>0.06032213691618682</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04986000061035156</v>
+        <v>0.04993000030517578</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009137025993717296</v>
+        <v>0.01039213661101104</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P928"/>
+  <dimension ref="A1:P937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54021,6 +54021,528 @@
       </c>
       <c r="P928" t="n">
         <v>0.02309285002060196</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E929" t="n">
+        <v>343.83</v>
+      </c>
+      <c r="F929" t="n">
+        <v>5017916932096</v>
+      </c>
+      <c r="G929" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="H929" t="n">
+        <v>9.56245</v>
+      </c>
+      <c r="I929" t="n">
+        <v>39.795135</v>
+      </c>
+      <c r="J929" t="n">
+        <v>35.956264</v>
+      </c>
+      <c r="K929" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L929" t="n">
+        <v>10.749079</v>
+      </c>
+      <c r="M929" t="n">
+        <v>0.02512869732135067</v>
+      </c>
+      <c r="N929" t="n">
+        <v>0.02781156385423029</v>
+      </c>
+      <c r="O929" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P929" t="n">
+        <v>-0.02263843690870917</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E930" t="n">
+        <v>578.4400000000001</v>
+      </c>
+      <c r="F930" t="n">
+        <v>944288825344</v>
+      </c>
+      <c r="G930" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H930" t="n">
+        <v>15.84721</v>
+      </c>
+      <c r="I930" t="n">
+        <v>147.56122</v>
+      </c>
+      <c r="J930" t="n">
+        <v>36.501064</v>
+      </c>
+      <c r="K930" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L930" t="n">
+        <v>22.861368</v>
+      </c>
+      <c r="M930" t="n">
+        <v>0.006776848074130419</v>
+      </c>
+      <c r="N930" t="n">
+        <v>0.02739646290021437</v>
+      </c>
+      <c r="O930" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P930" t="n">
+        <v>-0.02305353786272509</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E931" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="F931" t="n">
+        <v>2746195378176</v>
+      </c>
+      <c r="G931" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H931" t="n">
+        <v>10.45009</v>
+      </c>
+      <c r="I931" t="n">
+        <v>20.482702</v>
+      </c>
+      <c r="J931" t="n">
+        <v>24.363426</v>
+      </c>
+      <c r="K931" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L931" t="n">
+        <v>3.5403714</v>
+      </c>
+      <c r="M931" t="n">
+        <v>0.0488216810683425</v>
+      </c>
+      <c r="N931" t="n">
+        <v>0.04104512961508248</v>
+      </c>
+      <c r="O931" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P931" t="n">
+        <v>-0.009404871147856979</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E932" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="F932" t="n">
+        <v>1679410724864</v>
+      </c>
+      <c r="G932" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H932" t="n">
+        <v>19.4315</v>
+      </c>
+      <c r="I932" t="n">
+        <v>44.931034</v>
+      </c>
+      <c r="J932" t="n">
+        <v>18.105139</v>
+      </c>
+      <c r="K932" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L932" t="n">
+        <v>18.84776</v>
+      </c>
+      <c r="M932" t="n">
+        <v>0.02225633154259402</v>
+      </c>
+      <c r="N932" t="n">
+        <v>0.05523293823370569</v>
+      </c>
+      <c r="O932" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P932" t="n">
+        <v>0.004782937470766233</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E933" t="n">
+        <v>321.89</v>
+      </c>
+      <c r="F933" t="n">
+        <v>3936694042624</v>
+      </c>
+      <c r="G933" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="H933" t="n">
+        <v>15.1882</v>
+      </c>
+      <c r="I933" t="n">
+        <v>15.895803</v>
+      </c>
+      <c r="J933" t="n">
+        <v>21.193428</v>
+      </c>
+      <c r="K933" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L933" t="n">
+        <v>8.829321</v>
+      </c>
+      <c r="M933" t="n">
+        <v>0.06290968964553108</v>
+      </c>
+      <c r="N933" t="n">
+        <v>0.04718444189008668</v>
+      </c>
+      <c r="O933" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P933" t="n">
+        <v>-0.003265558872852778</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E934" t="n">
+        <v>612.49</v>
+      </c>
+      <c r="F934" t="n">
+        <v>1594209206272</v>
+      </c>
+      <c r="G934" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H934" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="I934" t="n">
+        <v>20.896963</v>
+      </c>
+      <c r="J934" t="n">
+        <v>17.425035</v>
+      </c>
+      <c r="K934" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L934" t="n">
+        <v>6.5984116</v>
+      </c>
+      <c r="M934" t="n">
+        <v>0.04785384251171448</v>
+      </c>
+      <c r="N934" t="n">
+        <v>0.05738869206027853</v>
+      </c>
+      <c r="O934" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P934" t="n">
+        <v>0.006938691297339074</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E935" t="n">
+        <v>531.01</v>
+      </c>
+      <c r="F935" t="n">
+        <v>3943039238144</v>
+      </c>
+      <c r="G935" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H935" t="n">
+        <v>23.68972</v>
+      </c>
+      <c r="I935" t="n">
+        <v>29.58273</v>
+      </c>
+      <c r="J935" t="n">
+        <v>22.415209</v>
+      </c>
+      <c r="K935" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L935" t="n">
+        <v>11.882386</v>
+      </c>
+      <c r="M935" t="n">
+        <v>0.03380350652530084</v>
+      </c>
+      <c r="N935" t="n">
+        <v>0.04461256850153481</v>
+      </c>
+      <c r="O935" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P935" t="n">
+        <v>-0.005837432261404644</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E936" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="F936" t="n">
+        <v>258122629120</v>
+      </c>
+      <c r="G936" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H936" t="n">
+        <v>3.77134</v>
+      </c>
+      <c r="I936" t="n">
+        <v>18.072886</v>
+      </c>
+      <c r="J936" t="n">
+        <v>16.43713</v>
+      </c>
+      <c r="K936" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L936" t="n">
+        <v>5.1899977</v>
+      </c>
+      <c r="M936" t="n">
+        <v>0.05533150508146475</v>
+      </c>
+      <c r="N936" t="n">
+        <v>0.06083787707694789</v>
+      </c>
+      <c r="O936" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P936" t="n">
+        <v>0.01038787631400843</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:52:40</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E937" t="n">
+        <v>215.38</v>
+      </c>
+      <c r="F937" t="n">
+        <v>5200780722176</v>
+      </c>
+      <c r="G937" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="H937" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I937" t="n">
+        <v>27.5422</v>
+      </c>
+      <c r="J937" t="n">
+        <v>13.533485</v>
+      </c>
+      <c r="K937" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L937" t="n">
+        <v>17.16599</v>
+      </c>
+      <c r="M937" t="n">
+        <v>0.03630792088401895</v>
+      </c>
+      <c r="N937" t="n">
+        <v>0.07389079765994985</v>
+      </c>
+      <c r="O937" t="n">
+        <v>0.05045000076293946</v>
+      </c>
+      <c r="P937" t="n">
+        <v>0.0234407968970104</v>
       </c>
     </row>
   </sheetData>
@@ -54122,12 +54644,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -54141,51 +54663,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>316.83</v>
+        <v>321.89</v>
       </c>
       <c r="F2" t="n">
-        <v>3874810232832</v>
+        <v>3936694042624</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>20.25</v>
       </c>
       <c r="H2" t="n">
-        <v>15.35864</v>
+        <v>15.1882</v>
       </c>
       <c r="I2" t="n">
-        <v>15.89714</v>
+        <v>15.895803</v>
       </c>
       <c r="J2" t="n">
-        <v>20.628778</v>
+        <v>21.193428</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="L2" t="n">
-        <v>8.690526999999999</v>
+        <v>8.829321</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06290439667960736</v>
+        <v>0.06290968964553108</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04847596502856422</v>
+        <v>0.04718444189008668</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.001454035276611566</v>
+        <v>-0.003265558872852778</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -54199,51 +54721,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>531.33</v>
+        <v>531.01</v>
       </c>
       <c r="F3" t="n">
-        <v>3945415311360</v>
+        <v>3943039238144</v>
       </c>
       <c r="G3" t="n">
-        <v>18.23</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
         <v>23.68972</v>
       </c>
       <c r="I3" t="n">
-        <v>29.145914</v>
+        <v>29.58273</v>
       </c>
       <c r="J3" t="n">
-        <v>22.428717</v>
+        <v>22.415209</v>
       </c>
       <c r="K3" t="n">
         <v>1.73</v>
       </c>
       <c r="L3" t="n">
-        <v>11.889546</v>
+        <v>11.882386</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03431012741610675</v>
+        <v>0.03380350652530084</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04458570003575932</v>
+        <v>0.04461256850153481</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.005344300269416465</v>
+        <v>-0.005837432261404644</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -54257,51 +54779,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>620.1900000000001</v>
+        <v>612.49</v>
       </c>
       <c r="F4" t="n">
-        <v>1585722294272</v>
+        <v>1594209206272</v>
       </c>
       <c r="G4" t="n">
         <v>29.31</v>
       </c>
       <c r="H4" t="n">
-        <v>35.19</v>
+        <v>35.15</v>
       </c>
       <c r="I4" t="n">
-        <v>21.159674</v>
+        <v>20.896963</v>
       </c>
       <c r="J4" t="n">
-        <v>17.624043</v>
+        <v>17.425035</v>
       </c>
       <c r="K4" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5632844</v>
+        <v>6.5984116</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04725971073380737</v>
+        <v>0.04785384251171448</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05674067624437672</v>
+        <v>0.05738869206027853</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006810675939200934</v>
+        <v>0.006938691297339074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -54315,51 +54837,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>253.1</v>
+        <v>254.6</v>
       </c>
       <c r="F5" t="n">
-        <v>2730015850496</v>
+        <v>2746195378176</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.43295</v>
+        <v>10.45009</v>
       </c>
       <c r="I5" t="n">
-        <v>20.362028</v>
+        <v>20.482702</v>
       </c>
       <c r="J5" t="n">
-        <v>24.259678</v>
+        <v>24.363426</v>
       </c>
       <c r="K5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="L5" t="n">
-        <v>3.519513</v>
+        <v>3.5403714</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04911102331094429</v>
+        <v>0.0488216810683425</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04122066376926116</v>
+        <v>0.04104512961508248</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008709336535914623</v>
+        <v>-0.009404871147856979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -54373,51 +54895,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>347.1</v>
+        <v>343.83</v>
       </c>
       <c r="F6" t="n">
-        <v>5065640247296</v>
+        <v>5017916932096</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.56245</v>
       </c>
       <c r="I6" t="n">
-        <v>39.805046</v>
+        <v>39.795135</v>
       </c>
       <c r="J6" t="n">
-        <v>36.29823</v>
+        <v>35.956264</v>
       </c>
       <c r="K6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="L6" t="n">
-        <v>10.851309</v>
+        <v>10.749079</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02512244309997119</v>
+        <v>0.02512869732135067</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02754955344281187</v>
+        <v>0.02781156385423029</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02238044686236391</v>
+        <v>-0.02263843690870917</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -54431,51 +54953,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.94</v>
+        <v>215.38</v>
       </c>
       <c r="F7" t="n">
-        <v>5262596898816</v>
+        <v>5200780722176</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.82</v>
       </c>
       <c r="H7" t="n">
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.552465</v>
+        <v>27.5422</v>
       </c>
       <c r="J7" t="n">
-        <v>13.694344</v>
+        <v>13.533485</v>
       </c>
       <c r="K7" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="L7" t="n">
-        <v>17.370026</v>
+        <v>17.16599</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03629439295218868</v>
+        <v>0.03630792088401895</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07302285032577774</v>
+        <v>0.07389079765994985</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02309285002060196</v>
+        <v>0.0234407968970104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -54489,51 +55011,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>560.26</v>
+        <v>578.4400000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>914610454528</v>
+        <v>944288825344</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.75581</v>
+        <v>15.84721</v>
       </c>
       <c r="I8" t="n">
-        <v>142.92346</v>
+        <v>147.56122</v>
       </c>
       <c r="J8" t="n">
-        <v>35.55895</v>
+        <v>36.501064</v>
       </c>
       <c r="K8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>22.142849</v>
+        <v>22.861368</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006996751508228323</v>
+        <v>0.006776848074130419</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02812231820940278</v>
+        <v>0.02739646290021437</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02180768209577301</v>
+        <v>-0.02305353786272509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -54547,10 +55069,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>342.33</v>
+        <v>351.81</v>
       </c>
       <c r="F9" t="n">
-        <v>1634156675072</v>
+        <v>1679410724864</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -54559,39 +55081,39 @@
         <v>19.4315</v>
       </c>
       <c r="I9" t="n">
-        <v>43.720306</v>
+        <v>44.931034</v>
       </c>
       <c r="J9" t="n">
-        <v>17.617271</v>
+        <v>18.105139</v>
       </c>
       <c r="K9" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.33988</v>
+        <v>18.84776</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02287266672508983</v>
+        <v>0.02225633154259402</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0567624806473286</v>
+        <v>0.05523293823370569</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006832480342152822</v>
+        <v>0.004782937470766233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 18:29:43</t>
+          <t>2026-10-28 18:52:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -54605,40 +55127,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62.52</v>
+        <v>61.99</v>
       </c>
       <c r="F10" t="n">
-        <v>260329504768</v>
+        <v>258122629120</v>
       </c>
       <c r="G10" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="H10" t="n">
         <v>3.77134</v>
       </c>
       <c r="I10" t="n">
-        <v>18.069365</v>
+        <v>18.072886</v>
       </c>
       <c r="J10" t="n">
-        <v>16.577663</v>
+        <v>16.43713</v>
       </c>
       <c r="K10" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="L10" t="n">
-        <v>5.2343707</v>
+        <v>5.1899977</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05534229046705054</v>
+        <v>0.05533150508146475</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06032213691618682</v>
+        <v>0.06083787707694789</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05045000076293946</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01039213661101104</v>
+        <v>0.01038787631400843</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P937"/>
+  <dimension ref="A1:P946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54543,6 +54543,528 @@
       </c>
       <c r="P937" t="n">
         <v>0.0234407968970104</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E938" t="n">
+        <v>348.91</v>
+      </c>
+      <c r="F938" t="n">
+        <v>5092055449600</v>
+      </c>
+      <c r="G938" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H938" t="n">
+        <v>9.5562</v>
+      </c>
+      <c r="I938" t="n">
+        <v>40.012615</v>
+      </c>
+      <c r="J938" t="n">
+        <v>36.511375</v>
+      </c>
+      <c r="K938" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L938" t="n">
+        <v>10.907893</v>
+      </c>
+      <c r="M938" t="n">
+        <v>0.02499211831131237</v>
+      </c>
+      <c r="N938" t="n">
+        <v>0.02738872488607377</v>
+      </c>
+      <c r="O938" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P938" t="n">
+        <v>-0.02250127354990035</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E939" t="n">
+        <v>566.42</v>
+      </c>
+      <c r="F939" t="n">
+        <v>924666494976</v>
+      </c>
+      <c r="G939" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H939" t="n">
+        <v>15.90591</v>
+      </c>
+      <c r="I939" t="n">
+        <v>144.49489</v>
+      </c>
+      <c r="J939" t="n">
+        <v>35.610664</v>
+      </c>
+      <c r="K939" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L939" t="n">
+        <v>22.386309</v>
+      </c>
+      <c r="M939" t="n">
+        <v>0.006920659581229477</v>
+      </c>
+      <c r="N939" t="n">
+        <v>0.02808147664277392</v>
+      </c>
+      <c r="O939" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P939" t="n">
+        <v>-0.02180852179320021</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E940" t="n">
+        <v>243.79</v>
+      </c>
+      <c r="F940" t="n">
+        <v>2629595299840</v>
+      </c>
+      <c r="G940" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H940" t="n">
+        <v>10.45009</v>
+      </c>
+      <c r="I940" t="n">
+        <v>19.613031</v>
+      </c>
+      <c r="J940" t="n">
+        <v>23.328983</v>
+      </c>
+      <c r="K940" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L940" t="n">
+        <v>3.3900516</v>
+      </c>
+      <c r="M940" t="n">
+        <v>0.05098650477870299</v>
+      </c>
+      <c r="N940" t="n">
+        <v>0.04286512982484925</v>
+      </c>
+      <c r="O940" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P940" t="n">
+        <v>-0.00702486861112487</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E941" t="n">
+        <v>345</v>
+      </c>
+      <c r="F941" t="n">
+        <v>1646902378496</v>
+      </c>
+      <c r="G941" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H941" t="n">
+        <v>19.46507</v>
+      </c>
+      <c r="I941" t="n">
+        <v>44.061302</v>
+      </c>
+      <c r="J941" t="n">
+        <v>17.724056</v>
+      </c>
+      <c r="K941" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L941" t="n">
+        <v>18.482924</v>
+      </c>
+      <c r="M941" t="n">
+        <v>0.02269565217391304</v>
+      </c>
+      <c r="N941" t="n">
+        <v>0.05642049275362319</v>
+      </c>
+      <c r="O941" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P941" t="n">
+        <v>0.006530494317649065</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E942" t="n">
+        <v>282.32</v>
+      </c>
+      <c r="F942" t="n">
+        <v>3452755247104</v>
+      </c>
+      <c r="G942" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="H942" t="n">
+        <v>15.13866</v>
+      </c>
+      <c r="I942" t="n">
+        <v>14.742559</v>
+      </c>
+      <c r="J942" t="n">
+        <v>18.648943</v>
+      </c>
+      <c r="K942" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L942" t="n">
+        <v>7.743931</v>
+      </c>
+      <c r="M942" t="n">
+        <v>0.06783083026353075</v>
+      </c>
+      <c r="N942" t="n">
+        <v>0.05362234344006801</v>
+      </c>
+      <c r="O942" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P942" t="n">
+        <v>0.003732345004093883</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E943" t="n">
+        <v>624.52</v>
+      </c>
+      <c r="F943" t="n">
+        <v>1596793421824</v>
+      </c>
+      <c r="G943" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H943" t="n">
+        <v>35.58785</v>
+      </c>
+      <c r="I943" t="n">
+        <v>21.307405</v>
+      </c>
+      <c r="J943" t="n">
+        <v>17.548687</v>
+      </c>
+      <c r="K943" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L943" t="n">
+        <v>6.6091075</v>
+      </c>
+      <c r="M943" t="n">
+        <v>0.04693204380964581</v>
+      </c>
+      <c r="N943" t="n">
+        <v>0.0569843239608019</v>
+      </c>
+      <c r="O943" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P943" t="n">
+        <v>0.007094325524827777</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E944" t="n">
+        <v>530.14</v>
+      </c>
+      <c r="F944" t="n">
+        <v>3936578961408</v>
+      </c>
+      <c r="G944" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H944" t="n">
+        <v>23.68972</v>
+      </c>
+      <c r="I944" t="n">
+        <v>29.534262</v>
+      </c>
+      <c r="J944" t="n">
+        <v>22.378483</v>
+      </c>
+      <c r="K944" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L944" t="n">
+        <v>11.862918</v>
+      </c>
+      <c r="M944" t="n">
+        <v>0.03385898064662165</v>
+      </c>
+      <c r="N944" t="n">
+        <v>0.04468578111442261</v>
+      </c>
+      <c r="O944" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P944" t="n">
+        <v>-0.005204217321551512</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E945" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="F945" t="n">
+        <v>258372452352</v>
+      </c>
+      <c r="G945" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H945" t="n">
+        <v>3.77134</v>
+      </c>
+      <c r="I945" t="n">
+        <v>17.933525</v>
+      </c>
+      <c r="J945" t="n">
+        <v>16.453037</v>
+      </c>
+      <c r="K945" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L945" t="n">
+        <v>5.195021</v>
+      </c>
+      <c r="M945" t="n">
+        <v>0.05576148267526189</v>
+      </c>
+      <c r="N945" t="n">
+        <v>0.06077904915390814</v>
+      </c>
+      <c r="O945" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P945" t="n">
+        <v>0.01088905071793402</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:02:47</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E946" t="n">
+        <v>213.66</v>
+      </c>
+      <c r="F946" t="n">
+        <v>5159248199680</v>
+      </c>
+      <c r="G946" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H946" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I946" t="n">
+        <v>27.01138</v>
+      </c>
+      <c r="J946" t="n">
+        <v>13.425408</v>
+      </c>
+      <c r="K946" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L946" t="n">
+        <v>17.028908</v>
+      </c>
+      <c r="M946" t="n">
+        <v>0.03702143592623795</v>
+      </c>
+      <c r="N946" t="n">
+        <v>0.07448563137695403</v>
+      </c>
+      <c r="O946" t="n">
+        <v>0.04988999843597412</v>
+      </c>
+      <c r="P946" t="n">
+        <v>0.02459563294097991</v>
       </c>
     </row>
   </sheetData>
@@ -54644,12 +55166,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -54663,51 +55185,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>321.89</v>
+        <v>282.32</v>
       </c>
       <c r="F2" t="n">
-        <v>3936694042624</v>
+        <v>3452755247104</v>
       </c>
       <c r="G2" t="n">
-        <v>20.25</v>
+        <v>19.15</v>
       </c>
       <c r="H2" t="n">
-        <v>15.1882</v>
+        <v>15.13866</v>
       </c>
       <c r="I2" t="n">
-        <v>15.895803</v>
+        <v>14.742559</v>
       </c>
       <c r="J2" t="n">
-        <v>21.193428</v>
+        <v>18.648943</v>
       </c>
       <c r="K2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="L2" t="n">
-        <v>8.829321</v>
+        <v>7.743931</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06290968964553108</v>
+        <v>0.06783083026353075</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04718444189008668</v>
+        <v>0.05362234344006801</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003265558872852778</v>
+        <v>0.003732345004093883</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -54721,10 +55243,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>531.01</v>
+        <v>530.14</v>
       </c>
       <c r="F3" t="n">
-        <v>3943039238144</v>
+        <v>3936578961408</v>
       </c>
       <c r="G3" t="n">
         <v>17.95</v>
@@ -54733,39 +55255,39 @@
         <v>23.68972</v>
       </c>
       <c r="I3" t="n">
-        <v>29.58273</v>
+        <v>29.534262</v>
       </c>
       <c r="J3" t="n">
-        <v>22.415209</v>
+        <v>22.378483</v>
       </c>
       <c r="K3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L3" t="n">
-        <v>11.882386</v>
+        <v>11.862918</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03380350652530084</v>
+        <v>0.03385898064662165</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04461256850153481</v>
+        <v>0.04468578111442261</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.005837432261404644</v>
+        <v>-0.005204217321551512</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -54779,51 +55301,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>612.49</v>
+        <v>624.52</v>
       </c>
       <c r="F4" t="n">
-        <v>1594209206272</v>
+        <v>1596793421824</v>
       </c>
       <c r="G4" t="n">
         <v>29.31</v>
       </c>
       <c r="H4" t="n">
-        <v>35.15</v>
+        <v>35.58785</v>
       </c>
       <c r="I4" t="n">
-        <v>20.896963</v>
+        <v>21.307405</v>
       </c>
       <c r="J4" t="n">
-        <v>17.425035</v>
+        <v>17.548687</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5984116</v>
+        <v>6.6091075</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04785384251171448</v>
+        <v>0.04693204380964581</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05738869206027853</v>
+        <v>0.0569843239608019</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006938691297339074</v>
+        <v>0.007094325524827777</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -54837,10 +55359,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.6</v>
+        <v>243.79</v>
       </c>
       <c r="F5" t="n">
-        <v>2746195378176</v>
+        <v>2629595299840</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -54849,39 +55371,39 @@
         <v>10.45009</v>
       </c>
       <c r="I5" t="n">
-        <v>20.482702</v>
+        <v>19.613031</v>
       </c>
       <c r="J5" t="n">
-        <v>24.363426</v>
+        <v>23.328983</v>
       </c>
       <c r="K5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5403714</v>
+        <v>3.3900516</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0488216810683425</v>
+        <v>0.05098650477870299</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04104512961508248</v>
+        <v>0.04286512982484925</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009404871147856979</v>
+        <v>-0.00702486861112487</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -54895,51 +55417,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>343.83</v>
+        <v>348.91</v>
       </c>
       <c r="F6" t="n">
-        <v>5017916932096</v>
+        <v>5092055449600</v>
       </c>
       <c r="G6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.56245</v>
+        <v>9.5562</v>
       </c>
       <c r="I6" t="n">
-        <v>39.795135</v>
+        <v>40.012615</v>
       </c>
       <c r="J6" t="n">
-        <v>35.956264</v>
+        <v>36.511375</v>
       </c>
       <c r="K6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="L6" t="n">
-        <v>10.749079</v>
+        <v>10.907893</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02512869732135067</v>
+        <v>0.02499211831131237</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02781156385423029</v>
+        <v>0.02738872488607377</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02263843690870917</v>
+        <v>-0.02250127354990035</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -54953,51 +55475,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>215.38</v>
+        <v>213.66</v>
       </c>
       <c r="F7" t="n">
-        <v>5200780722176</v>
+        <v>5159248199680</v>
       </c>
       <c r="G7" t="n">
-        <v>7.82</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.5422</v>
+        <v>27.01138</v>
       </c>
       <c r="J7" t="n">
-        <v>13.533485</v>
+        <v>13.425408</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>17.16599</v>
+        <v>17.028908</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03630792088401895</v>
+        <v>0.03702143592623795</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07389079765994985</v>
+        <v>0.07448563137695403</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0234407968970104</v>
+        <v>0.02459563294097991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -55011,51 +55533,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>578.4400000000001</v>
+        <v>566.42</v>
       </c>
       <c r="F8" t="n">
-        <v>944288825344</v>
+        <v>924666494976</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.84721</v>
+        <v>15.90591</v>
       </c>
       <c r="I8" t="n">
-        <v>147.56122</v>
+        <v>144.49489</v>
       </c>
       <c r="J8" t="n">
-        <v>36.501064</v>
+        <v>35.610664</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L8" t="n">
-        <v>22.861368</v>
+        <v>22.386309</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006776848074130419</v>
+        <v>0.006920659581229477</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02739646290021437</v>
+        <v>0.02808147664277392</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02305353786272509</v>
+        <v>-0.02180852179320021</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -55069,51 +55591,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>351.81</v>
+        <v>345</v>
       </c>
       <c r="F9" t="n">
-        <v>1679410724864</v>
+        <v>1646902378496</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
       </c>
       <c r="H9" t="n">
-        <v>19.4315</v>
+        <v>19.46507</v>
       </c>
       <c r="I9" t="n">
-        <v>44.931034</v>
+        <v>44.061302</v>
       </c>
       <c r="J9" t="n">
-        <v>18.105139</v>
+        <v>17.724056</v>
       </c>
       <c r="K9" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>18.84776</v>
+        <v>18.482924</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02225633154259402</v>
+        <v>0.02269565217391304</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05523293823370569</v>
+        <v>0.05642049275362319</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004782937470766233</v>
+        <v>0.006530494317649065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52:40</t>
+          <t>2026-10-29 19:02:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -55127,40 +55649,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>61.99</v>
+        <v>62.05</v>
       </c>
       <c r="F10" t="n">
-        <v>258122629120</v>
+        <v>258372452352</v>
       </c>
       <c r="G10" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="H10" t="n">
         <v>3.77134</v>
       </c>
       <c r="I10" t="n">
-        <v>18.072886</v>
+        <v>17.933525</v>
       </c>
       <c r="J10" t="n">
-        <v>16.43713</v>
+        <v>16.453037</v>
       </c>
       <c r="K10" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="L10" t="n">
-        <v>5.1899977</v>
+        <v>5.195021</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05533150508146475</v>
+        <v>0.05576148267526189</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06083787707694789</v>
+        <v>0.06077904915390814</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05045000076293946</v>
+        <v>0.04988999843597412</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01038787631400843</v>
+        <v>0.01088905071793402</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P946"/>
+  <dimension ref="A1:P955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55065,6 +55065,528 @@
       </c>
       <c r="P946" t="n">
         <v>0.02459563294097991</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E947" t="n">
+        <v>344.63</v>
+      </c>
+      <c r="F947" t="n">
+        <v>5029592301568</v>
+      </c>
+      <c r="G947" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H947" t="n">
+        <v>9.554819999999999</v>
+      </c>
+      <c r="I947" t="n">
+        <v>39.52179</v>
+      </c>
+      <c r="J947" t="n">
+        <v>36.068707</v>
+      </c>
+      <c r="K947" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L947" t="n">
+        <v>10.774089</v>
+      </c>
+      <c r="M947" t="n">
+        <v>0.02530249833154398</v>
+      </c>
+      <c r="N947" t="n">
+        <v>0.02772486434727098</v>
+      </c>
+      <c r="O947" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P947" t="n">
+        <v>-0.02156513466090772</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E948" t="n">
+        <v>504.8</v>
+      </c>
+      <c r="F948" t="n">
+        <v>824073388032</v>
+      </c>
+      <c r="G948" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H948" t="n">
+        <v>15.90591</v>
+      </c>
+      <c r="I948" t="n">
+        <v>128.7755</v>
+      </c>
+      <c r="J948" t="n">
+        <v>31.736631</v>
+      </c>
+      <c r="K948" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L948" t="n">
+        <v>19.950935</v>
+      </c>
+      <c r="M948" t="n">
+        <v>0.007765451664025356</v>
+      </c>
+      <c r="N948" t="n">
+        <v>0.03150933042789224</v>
+      </c>
+      <c r="O948" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P948" t="n">
+        <v>-0.01778066858028647</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E949" t="n">
+        <v>240.35</v>
+      </c>
+      <c r="F949" t="n">
+        <v>2598423756800</v>
+      </c>
+      <c r="G949" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H949" t="n">
+        <v>10.55708</v>
+      </c>
+      <c r="I949" t="n">
+        <v>19.336283</v>
+      </c>
+      <c r="J949" t="n">
+        <v>22.766712</v>
+      </c>
+      <c r="K949" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L949" t="n">
+        <v>3.3498654</v>
+      </c>
+      <c r="M949" t="n">
+        <v>0.0517162471395881</v>
+      </c>
+      <c r="N949" t="n">
+        <v>0.04392377782400665</v>
+      </c>
+      <c r="O949" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P949" t="n">
+        <v>-0.005366221184172057</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E950" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="F950" t="n">
+        <v>1556585250816</v>
+      </c>
+      <c r="G950" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H950" t="n">
+        <v>19.46507</v>
+      </c>
+      <c r="I950" t="n">
+        <v>41.644955</v>
+      </c>
+      <c r="J950" t="n">
+        <v>16.752058</v>
+      </c>
+      <c r="K950" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L950" t="n">
+        <v>17.469309</v>
+      </c>
+      <c r="M950" t="n">
+        <v>0.02401251226692836</v>
+      </c>
+      <c r="N950" t="n">
+        <v>0.05969415480863592</v>
+      </c>
+      <c r="O950" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P950" t="n">
+        <v>0.01040415580045721</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E951" t="n">
+        <v>278.22</v>
+      </c>
+      <c r="F951" t="n">
+        <v>3420436561920</v>
+      </c>
+      <c r="G951" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="H951" t="n">
+        <v>15.13866</v>
+      </c>
+      <c r="I951" t="n">
+        <v>14.52846</v>
+      </c>
+      <c r="J951" t="n">
+        <v>18.378113</v>
+      </c>
+      <c r="K951" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L951" t="n">
+        <v>7.260563</v>
+      </c>
+      <c r="M951" t="n">
+        <v>0.06883042196822657</v>
+      </c>
+      <c r="N951" t="n">
+        <v>0.0544125512184602</v>
+      </c>
+      <c r="O951" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P951" t="n">
+        <v>0.005122552210281496</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E952" t="n">
+        <v>614.99</v>
+      </c>
+      <c r="F952" t="n">
+        <v>1572426743808</v>
+      </c>
+      <c r="G952" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H952" t="n">
+        <v>35.58785</v>
+      </c>
+      <c r="I952" t="n">
+        <v>20.982258</v>
+      </c>
+      <c r="J952" t="n">
+        <v>17.2809</v>
+      </c>
+      <c r="K952" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L952" t="n">
+        <v>6.508254</v>
+      </c>
+      <c r="M952" t="n">
+        <v>0.04765931153352087</v>
+      </c>
+      <c r="N952" t="n">
+        <v>0.05786736369697069</v>
+      </c>
+      <c r="O952" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P952" t="n">
+        <v>0.008577364688791979</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E953" t="n">
+        <v>521.91</v>
+      </c>
+      <c r="F953" t="n">
+        <v>3875804807168</v>
+      </c>
+      <c r="G953" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="H953" t="n">
+        <v>24.1416</v>
+      </c>
+      <c r="I953" t="n">
+        <v>27.239561</v>
+      </c>
+      <c r="J953" t="n">
+        <v>21.618698</v>
+      </c>
+      <c r="K953" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L953" t="n">
+        <v>11.18736</v>
+      </c>
+      <c r="M953" t="n">
+        <v>0.03671131037918415</v>
+      </c>
+      <c r="N953" t="n">
+        <v>0.04625625107777203</v>
+      </c>
+      <c r="O953" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P953" t="n">
+        <v>-0.003033747930406679</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E954" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="F954" t="n">
+        <v>258497380352</v>
+      </c>
+      <c r="G954" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H954" t="n">
+        <v>3.77134</v>
+      </c>
+      <c r="I954" t="n">
+        <v>17.942198</v>
+      </c>
+      <c r="J954" t="n">
+        <v>16.460993</v>
+      </c>
+      <c r="K954" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L954" t="n">
+        <v>5.1975327</v>
+      </c>
+      <c r="M954" t="n">
+        <v>0.05573453608247423</v>
+      </c>
+      <c r="N954" t="n">
+        <v>0.06074967783505154</v>
+      </c>
+      <c r="O954" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P954" t="n">
+        <v>0.01145967882687284</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:41:16</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E955" t="n">
+        <v>204.64</v>
+      </c>
+      <c r="F955" t="n">
+        <v>4941441662976</v>
+      </c>
+      <c r="G955" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H955" t="n">
+        <v>15.9146</v>
+      </c>
+      <c r="I955" t="n">
+        <v>25.87105</v>
+      </c>
+      <c r="J955" t="n">
+        <v>12.858633</v>
+      </c>
+      <c r="K955" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L955" t="n">
+        <v>16.310003</v>
+      </c>
+      <c r="M955" t="n">
+        <v>0.03865324472243941</v>
+      </c>
+      <c r="N955" t="n">
+        <v>0.07776876465989055</v>
+      </c>
+      <c r="O955" t="n">
+        <v>0.04928999900817871</v>
+      </c>
+      <c r="P955" t="n">
+        <v>0.02847876565171184</v>
       </c>
     </row>
   </sheetData>
@@ -55166,12 +55688,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -55185,10 +55707,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>282.32</v>
+        <v>278.22</v>
       </c>
       <c r="F2" t="n">
-        <v>3452755247104</v>
+        <v>3420436561920</v>
       </c>
       <c r="G2" t="n">
         <v>19.15</v>
@@ -55197,39 +55719,39 @@
         <v>15.13866</v>
       </c>
       <c r="I2" t="n">
-        <v>14.742559</v>
+        <v>14.52846</v>
       </c>
       <c r="J2" t="n">
-        <v>18.648943</v>
+        <v>18.378113</v>
       </c>
       <c r="K2" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="L2" t="n">
-        <v>7.743931</v>
+        <v>7.260563</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06783083026353075</v>
+        <v>0.06883042196822657</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05362234344006801</v>
+        <v>0.0544125512184602</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003732345004093883</v>
+        <v>0.005122552210281496</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -55243,51 +55765,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>530.14</v>
+        <v>521.91</v>
       </c>
       <c r="F3" t="n">
-        <v>3936578961408</v>
+        <v>3875804807168</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>19.16</v>
       </c>
       <c r="H3" t="n">
-        <v>23.68972</v>
+        <v>24.1416</v>
       </c>
       <c r="I3" t="n">
-        <v>29.534262</v>
+        <v>27.239561</v>
       </c>
       <c r="J3" t="n">
-        <v>22.378483</v>
+        <v>21.618698</v>
       </c>
       <c r="K3" t="n">
         <v>1.72</v>
       </c>
       <c r="L3" t="n">
-        <v>11.862918</v>
+        <v>11.18736</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03385898064662165</v>
+        <v>0.03671131037918415</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04468578111442261</v>
+        <v>0.04625625107777203</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.005204217321551512</v>
+        <v>-0.003033747930406679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -55301,10 +55823,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>624.52</v>
+        <v>614.99</v>
       </c>
       <c r="F4" t="n">
-        <v>1596793421824</v>
+        <v>1572426743808</v>
       </c>
       <c r="G4" t="n">
         <v>29.31</v>
@@ -55313,39 +55835,39 @@
         <v>35.58785</v>
       </c>
       <c r="I4" t="n">
-        <v>21.307405</v>
+        <v>20.982258</v>
       </c>
       <c r="J4" t="n">
-        <v>17.548687</v>
+        <v>17.2809</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6091075</v>
+        <v>6.508254</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04693204380964581</v>
+        <v>0.04765931153352087</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0569843239608019</v>
+        <v>0.05786736369697069</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007094325524827777</v>
+        <v>0.008577364688791979</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -55359,51 +55881,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>243.79</v>
+        <v>240.35</v>
       </c>
       <c r="F5" t="n">
-        <v>2629595299840</v>
+        <v>2598423756800</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.45009</v>
+        <v>10.55708</v>
       </c>
       <c r="I5" t="n">
-        <v>19.613031</v>
+        <v>19.336283</v>
       </c>
       <c r="J5" t="n">
-        <v>23.328983</v>
+        <v>22.766712</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3900516</v>
+        <v>3.3498654</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05098650477870299</v>
+        <v>0.0517162471395881</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04286512982484925</v>
+        <v>0.04392377782400665</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00702486861112487</v>
+        <v>-0.005366221184172057</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -55417,51 +55939,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>348.91</v>
+        <v>344.63</v>
       </c>
       <c r="F6" t="n">
-        <v>5092055449600</v>
+        <v>5029592301568</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5562</v>
+        <v>9.554819999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>40.012615</v>
+        <v>39.52179</v>
       </c>
       <c r="J6" t="n">
-        <v>36.511375</v>
+        <v>36.068707</v>
       </c>
       <c r="K6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="L6" t="n">
-        <v>10.907893</v>
+        <v>10.774089</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02499211831131237</v>
+        <v>0.02530249833154398</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02738872488607377</v>
+        <v>0.02772486434727098</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02250127354990035</v>
+        <v>-0.02156513466090772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -55475,10 +55997,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>213.66</v>
+        <v>204.64</v>
       </c>
       <c r="F7" t="n">
-        <v>5159248199680</v>
+        <v>4941441662976</v>
       </c>
       <c r="G7" t="n">
         <v>7.91</v>
@@ -55487,39 +56009,39 @@
         <v>15.9146</v>
       </c>
       <c r="I7" t="n">
-        <v>27.01138</v>
+        <v>25.87105</v>
       </c>
       <c r="J7" t="n">
-        <v>13.425408</v>
+        <v>12.858633</v>
       </c>
       <c r="K7" t="n">
         <v>0.26</v>
       </c>
       <c r="L7" t="n">
-        <v>17.028908</v>
+        <v>16.310003</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03702143592623795</v>
+        <v>0.03865324472243941</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07448563137695403</v>
+        <v>0.07776876465989055</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02459563294097991</v>
+        <v>0.02847876565171184</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -55533,10 +56055,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>566.42</v>
+        <v>504.8</v>
       </c>
       <c r="F8" t="n">
-        <v>924666494976</v>
+        <v>824073388032</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -55545,39 +56067,39 @@
         <v>15.90591</v>
       </c>
       <c r="I8" t="n">
-        <v>144.49489</v>
+        <v>128.7755</v>
       </c>
       <c r="J8" t="n">
-        <v>35.610664</v>
+        <v>31.736631</v>
       </c>
       <c r="K8" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>22.386309</v>
+        <v>19.950935</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006920659581229477</v>
+        <v>0.007765451664025356</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02808147664277392</v>
+        <v>0.03150933042789224</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02180852179320021</v>
+        <v>-0.01778066858028647</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -55591,10 +56113,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>345</v>
+        <v>326.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1646902378496</v>
+        <v>1556585250816</v>
       </c>
       <c r="G9" t="n">
         <v>7.83</v>
@@ -55603,39 +56125,39 @@
         <v>19.46507</v>
       </c>
       <c r="I9" t="n">
-        <v>44.061302</v>
+        <v>41.644955</v>
       </c>
       <c r="J9" t="n">
-        <v>17.724056</v>
+        <v>16.752058</v>
       </c>
       <c r="K9" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="L9" t="n">
-        <v>18.482924</v>
+        <v>17.469309</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02269565217391304</v>
+        <v>0.02401251226692836</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05642049275362319</v>
+        <v>0.05969415480863592</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006530494317649065</v>
+        <v>0.01040415580045721</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 19:02:47</t>
+          <t>2026-10-30 18:41:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -55649,10 +56171,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62.05</v>
+        <v>62.08</v>
       </c>
       <c r="F10" t="n">
-        <v>258372452352</v>
+        <v>258497380352</v>
       </c>
       <c r="G10" t="n">
         <v>3.46</v>
@@ -55661,28 +56183,28 @@
         <v>3.77134</v>
       </c>
       <c r="I10" t="n">
-        <v>17.933525</v>
+        <v>17.942198</v>
       </c>
       <c r="J10" t="n">
-        <v>16.453037</v>
+        <v>16.460993</v>
       </c>
       <c r="K10" t="n">
         <v>0.98</v>
       </c>
       <c r="L10" t="n">
-        <v>5.195021</v>
+        <v>5.1975327</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05576148267526189</v>
+        <v>0.05573453608247423</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06077904915390814</v>
+        <v>0.06074967783505154</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04988999843597412</v>
+        <v>0.04928999900817871</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01088905071793402</v>
+        <v>0.01145967882687284</v>
       </c>
     </row>
   </sheetData>
